--- a/development/MS/tools/listLogic/MS/MSListLogicDef.xlsx
+++ b/development/MS/tools/listLogic/MS/MSListLogicDef.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\tools\listLogic\MS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8999FA12-D090-49EA-AFAA-F6534867F0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05635D23-3F04-46C6-8155-1D34A9B6FE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" tabRatio="814" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5309,10 +5309,10 @@
     <t>sls_cond_typ</t>
   </si>
   <si>
-    <t>sls_cond_nm</t>
-  </si>
-  <si>
     <t>MSC_SLO_TYP</t>
+  </si>
+  <si>
+    <t>sls_cond_typ_nm</t>
   </si>
 </sst>
 </file>
@@ -7671,6 +7671,204 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="30" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="30" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="31" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="32" borderId="24" xfId="322" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="3" xfId="322" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="321" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="321" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="321" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="35" borderId="0" xfId="321" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="35" borderId="0" xfId="321" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="35" borderId="20" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="3" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="24" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="2" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="25" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="58" fillId="37" borderId="0" xfId="321" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="37" borderId="0" xfId="321" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="37" borderId="20" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="3" xfId="321" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="58" fillId="0" borderId="24" xfId="321" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="58" fillId="0" borderId="2" xfId="321" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="58" fillId="0" borderId="25" xfId="321" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="58" fillId="0" borderId="24" xfId="321" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="29" borderId="33" xfId="320" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="29" borderId="34" xfId="320" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="35" xfId="320" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="36" xfId="320" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="29" borderId="37" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="38" xfId="324" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="324" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="40" xfId="324" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="4" xfId="324" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="41" xfId="324" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="29" borderId="42" xfId="323" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="43" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="29" borderId="42" xfId="319" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="44" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="29" borderId="45" xfId="320" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="29" borderId="38" xfId="320" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="29" borderId="46" xfId="320" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="29" borderId="4" xfId="320" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="29" borderId="1" xfId="323" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="48" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="49" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="50" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="25" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -7680,21 +7878,45 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="47" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="25" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="2" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="25" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="48" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="49" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="51" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="49" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="51" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="52" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="53" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="54" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="47" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="52" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -7704,9 +7926,6 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="55" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="53" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="53" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -7725,230 +7944,11 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="25" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="52" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="54" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="47" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="48" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="49" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="50" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="48" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="49" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="51" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="49" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="51" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="29" borderId="33" xfId="320" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="29" borderId="34" xfId="320" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="35" xfId="320" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="36" xfId="320" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="29" borderId="37" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="38" xfId="324" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="324" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="40" xfId="324" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="4" xfId="324" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="41" xfId="324" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="29" borderId="42" xfId="323" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="43" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="29" borderId="42" xfId="319" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="44" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="29" borderId="45" xfId="320" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="29" borderId="38" xfId="320" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="29" borderId="46" xfId="320" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="29" borderId="4" xfId="320" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="29" borderId="1" xfId="323" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="321" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="321" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="321" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="35" borderId="0" xfId="321" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="35" borderId="0" xfId="321" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="35" borderId="20" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="36" borderId="3" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="36" borderId="24" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="36" borderId="2" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="36" borderId="25" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="58" fillId="37" borderId="0" xfId="321" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="37" borderId="0" xfId="321" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="37" borderId="20" xfId="321" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="3" xfId="321" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="58" fillId="0" borderId="24" xfId="321" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="58" fillId="0" borderId="2" xfId="321" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="58" fillId="0" borderId="25" xfId="321" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="58" fillId="0" borderId="24" xfId="321" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="32" borderId="3" xfId="322" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="44" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="31" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="30" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="30" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="31" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="32" borderId="24" xfId="322" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="335">
@@ -9450,130 +9450,130 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:47">
-      <c r="B3" s="103" t="s">
+      <c r="B3" s="68" t="s">
         <v>585</v>
       </c>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="AD3" s="104"/>
-      <c r="AE3" s="105"/>
-      <c r="AF3" s="105"/>
-      <c r="AG3" s="105"/>
-      <c r="AH3" s="105"/>
-      <c r="AI3" s="106"/>
-      <c r="AJ3" s="107" t="s">
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="AD3" s="69"/>
+      <c r="AE3" s="70"/>
+      <c r="AF3" s="70"/>
+      <c r="AG3" s="70"/>
+      <c r="AH3" s="70"/>
+      <c r="AI3" s="71"/>
+      <c r="AJ3" s="72" t="s">
         <v>586</v>
       </c>
-      <c r="AK3" s="107"/>
-      <c r="AL3" s="107"/>
-      <c r="AM3" s="107"/>
-      <c r="AN3" s="107"/>
-      <c r="AO3" s="107"/>
-      <c r="AP3" s="108" t="s">
+      <c r="AK3" s="72"/>
+      <c r="AL3" s="72"/>
+      <c r="AM3" s="72"/>
+      <c r="AN3" s="72"/>
+      <c r="AO3" s="72"/>
+      <c r="AP3" s="73" t="s">
         <v>587</v>
       </c>
-      <c r="AQ3" s="109"/>
-      <c r="AR3" s="109"/>
-      <c r="AS3" s="109"/>
-      <c r="AT3" s="109"/>
-      <c r="AU3" s="110"/>
+      <c r="AQ3" s="74"/>
+      <c r="AR3" s="74"/>
+      <c r="AS3" s="74"/>
+      <c r="AT3" s="74"/>
+      <c r="AU3" s="75"/>
     </row>
     <row r="4" spans="2:47">
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="103"/>
-      <c r="I4" s="103"/>
-      <c r="J4" s="103"/>
-      <c r="AD4" s="105"/>
-      <c r="AE4" s="105"/>
-      <c r="AF4" s="105"/>
-      <c r="AG4" s="105"/>
-      <c r="AH4" s="105"/>
-      <c r="AI4" s="106"/>
-      <c r="AJ4" s="107"/>
-      <c r="AK4" s="107"/>
-      <c r="AL4" s="107"/>
-      <c r="AM4" s="107"/>
-      <c r="AN4" s="107"/>
-      <c r="AO4" s="107"/>
-      <c r="AP4" s="108"/>
-      <c r="AQ4" s="109"/>
-      <c r="AR4" s="109"/>
-      <c r="AS4" s="109"/>
-      <c r="AT4" s="109"/>
-      <c r="AU4" s="110"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="AD4" s="70"/>
+      <c r="AE4" s="70"/>
+      <c r="AF4" s="70"/>
+      <c r="AG4" s="70"/>
+      <c r="AH4" s="70"/>
+      <c r="AI4" s="71"/>
+      <c r="AJ4" s="72"/>
+      <c r="AK4" s="72"/>
+      <c r="AL4" s="72"/>
+      <c r="AM4" s="72"/>
+      <c r="AN4" s="72"/>
+      <c r="AO4" s="72"/>
+      <c r="AP4" s="73"/>
+      <c r="AQ4" s="74"/>
+      <c r="AR4" s="74"/>
+      <c r="AS4" s="74"/>
+      <c r="AT4" s="74"/>
+      <c r="AU4" s="75"/>
     </row>
     <row r="5" spans="2:47">
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="AD5" s="111"/>
-      <c r="AE5" s="112"/>
-      <c r="AF5" s="112"/>
-      <c r="AG5" s="112"/>
-      <c r="AH5" s="112"/>
-      <c r="AI5" s="113"/>
-      <c r="AJ5" s="114" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="AD5" s="76"/>
+      <c r="AE5" s="77"/>
+      <c r="AF5" s="77"/>
+      <c r="AG5" s="77"/>
+      <c r="AH5" s="77"/>
+      <c r="AI5" s="78"/>
+      <c r="AJ5" s="79" t="s">
         <v>916</v>
       </c>
-      <c r="AK5" s="114"/>
-      <c r="AL5" s="114"/>
-      <c r="AM5" s="114"/>
-      <c r="AN5" s="114"/>
-      <c r="AO5" s="114"/>
-      <c r="AP5" s="115" t="s">
+      <c r="AK5" s="79"/>
+      <c r="AL5" s="79"/>
+      <c r="AM5" s="79"/>
+      <c r="AN5" s="79"/>
+      <c r="AO5" s="79"/>
+      <c r="AP5" s="80" t="s">
         <v>1137</v>
       </c>
-      <c r="AQ5" s="116"/>
-      <c r="AR5" s="116"/>
-      <c r="AS5" s="116"/>
-      <c r="AT5" s="116"/>
-      <c r="AU5" s="117"/>
+      <c r="AQ5" s="81"/>
+      <c r="AR5" s="81"/>
+      <c r="AS5" s="81"/>
+      <c r="AT5" s="81"/>
+      <c r="AU5" s="82"/>
     </row>
     <row r="6" spans="2:47">
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="103"/>
-      <c r="AD6" s="112"/>
-      <c r="AE6" s="112"/>
-      <c r="AF6" s="112"/>
-      <c r="AG6" s="112"/>
-      <c r="AH6" s="112"/>
-      <c r="AI6" s="113"/>
-      <c r="AJ6" s="114"/>
-      <c r="AK6" s="114"/>
-      <c r="AL6" s="114"/>
-      <c r="AM6" s="114"/>
-      <c r="AN6" s="114"/>
-      <c r="AO6" s="114"/>
-      <c r="AP6" s="118"/>
-      <c r="AQ6" s="116"/>
-      <c r="AR6" s="116"/>
-      <c r="AS6" s="116"/>
-      <c r="AT6" s="116"/>
-      <c r="AU6" s="117"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="AD6" s="77"/>
+      <c r="AE6" s="77"/>
+      <c r="AF6" s="77"/>
+      <c r="AG6" s="77"/>
+      <c r="AH6" s="77"/>
+      <c r="AI6" s="78"/>
+      <c r="AJ6" s="79"/>
+      <c r="AK6" s="79"/>
+      <c r="AL6" s="79"/>
+      <c r="AM6" s="79"/>
+      <c r="AN6" s="79"/>
+      <c r="AO6" s="79"/>
+      <c r="AP6" s="83"/>
+      <c r="AQ6" s="81"/>
+      <c r="AR6" s="81"/>
+      <c r="AS6" s="81"/>
+      <c r="AT6" s="81"/>
+      <c r="AU6" s="82"/>
     </row>
     <row r="7" spans="2:47" ht="24">
       <c r="B7" s="29" t="s">
@@ -9595,122 +9595,122 @@
       </c>
     </row>
     <row r="15" spans="2:47">
-      <c r="M15" s="101" t="s">
+      <c r="M15" s="66" t="s">
         <v>588</v>
       </c>
-      <c r="N15" s="102"/>
-      <c r="O15" s="102"/>
-      <c r="P15" s="102"/>
-      <c r="Q15" s="102"/>
-      <c r="R15" s="102"/>
-      <c r="S15" s="102"/>
-      <c r="T15" s="102"/>
-      <c r="U15" s="102"/>
-      <c r="V15" s="102"/>
-      <c r="W15" s="102"/>
-      <c r="X15" s="102"/>
-      <c r="Y15" s="102"/>
-      <c r="Z15" s="102"/>
-      <c r="AA15" s="102"/>
-      <c r="AB15" s="102"/>
-      <c r="AC15" s="102"/>
-      <c r="AD15" s="102"/>
-      <c r="AE15" s="102"/>
-      <c r="AF15" s="102"/>
-      <c r="AG15" s="102"/>
-      <c r="AH15" s="102"/>
-      <c r="AI15" s="102"/>
-      <c r="AJ15" s="102"/>
-      <c r="AK15" s="102"/>
-      <c r="AL15" s="102"/>
-      <c r="AM15" s="102"/>
+      <c r="N15" s="67"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
+      <c r="U15" s="67"/>
+      <c r="V15" s="67"/>
+      <c r="W15" s="67"/>
+      <c r="X15" s="67"/>
+      <c r="Y15" s="67"/>
+      <c r="Z15" s="67"/>
+      <c r="AA15" s="67"/>
+      <c r="AB15" s="67"/>
+      <c r="AC15" s="67"/>
+      <c r="AD15" s="67"/>
+      <c r="AE15" s="67"/>
+      <c r="AF15" s="67"/>
+      <c r="AG15" s="67"/>
+      <c r="AH15" s="67"/>
+      <c r="AI15" s="67"/>
+      <c r="AJ15" s="67"/>
+      <c r="AK15" s="67"/>
+      <c r="AL15" s="67"/>
+      <c r="AM15" s="67"/>
     </row>
     <row r="16" spans="2:47">
-      <c r="M16" s="102"/>
-      <c r="N16" s="102"/>
-      <c r="O16" s="102"/>
-      <c r="P16" s="102"/>
-      <c r="Q16" s="102"/>
-      <c r="R16" s="102"/>
-      <c r="S16" s="102"/>
-      <c r="T16" s="102"/>
-      <c r="U16" s="102"/>
-      <c r="V16" s="102"/>
-      <c r="W16" s="102"/>
-      <c r="X16" s="102"/>
-      <c r="Y16" s="102"/>
-      <c r="Z16" s="102"/>
-      <c r="AA16" s="102"/>
-      <c r="AB16" s="102"/>
-      <c r="AC16" s="102"/>
-      <c r="AD16" s="102"/>
-      <c r="AE16" s="102"/>
-      <c r="AF16" s="102"/>
-      <c r="AG16" s="102"/>
-      <c r="AH16" s="102"/>
-      <c r="AI16" s="102"/>
-      <c r="AJ16" s="102"/>
-      <c r="AK16" s="102"/>
-      <c r="AL16" s="102"/>
-      <c r="AM16" s="102"/>
+      <c r="M16" s="67"/>
+      <c r="N16" s="67"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="67"/>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="67"/>
+      <c r="S16" s="67"/>
+      <c r="T16" s="67"/>
+      <c r="U16" s="67"/>
+      <c r="V16" s="67"/>
+      <c r="W16" s="67"/>
+      <c r="X16" s="67"/>
+      <c r="Y16" s="67"/>
+      <c r="Z16" s="67"/>
+      <c r="AA16" s="67"/>
+      <c r="AB16" s="67"/>
+      <c r="AC16" s="67"/>
+      <c r="AD16" s="67"/>
+      <c r="AE16" s="67"/>
+      <c r="AF16" s="67"/>
+      <c r="AG16" s="67"/>
+      <c r="AH16" s="67"/>
+      <c r="AI16" s="67"/>
+      <c r="AJ16" s="67"/>
+      <c r="AK16" s="67"/>
+      <c r="AL16" s="67"/>
+      <c r="AM16" s="67"/>
     </row>
     <row r="17" spans="13:39">
-      <c r="M17" s="102"/>
-      <c r="N17" s="102"/>
-      <c r="O17" s="102"/>
-      <c r="P17" s="102"/>
-      <c r="Q17" s="102"/>
-      <c r="R17" s="102"/>
-      <c r="S17" s="102"/>
-      <c r="T17" s="102"/>
-      <c r="U17" s="102"/>
-      <c r="V17" s="102"/>
-      <c r="W17" s="102"/>
-      <c r="X17" s="102"/>
-      <c r="Y17" s="102"/>
-      <c r="Z17" s="102"/>
-      <c r="AA17" s="102"/>
-      <c r="AB17" s="102"/>
-      <c r="AC17" s="102"/>
-      <c r="AD17" s="102"/>
-      <c r="AE17" s="102"/>
-      <c r="AF17" s="102"/>
-      <c r="AG17" s="102"/>
-      <c r="AH17" s="102"/>
-      <c r="AI17" s="102"/>
-      <c r="AJ17" s="102"/>
-      <c r="AK17" s="102"/>
-      <c r="AL17" s="102"/>
-      <c r="AM17" s="102"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="67"/>
+      <c r="O17" s="67"/>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+      <c r="U17" s="67"/>
+      <c r="V17" s="67"/>
+      <c r="W17" s="67"/>
+      <c r="X17" s="67"/>
+      <c r="Y17" s="67"/>
+      <c r="Z17" s="67"/>
+      <c r="AA17" s="67"/>
+      <c r="AB17" s="67"/>
+      <c r="AC17" s="67"/>
+      <c r="AD17" s="67"/>
+      <c r="AE17" s="67"/>
+      <c r="AF17" s="67"/>
+      <c r="AG17" s="67"/>
+      <c r="AH17" s="67"/>
+      <c r="AI17" s="67"/>
+      <c r="AJ17" s="67"/>
+      <c r="AK17" s="67"/>
+      <c r="AL17" s="67"/>
+      <c r="AM17" s="67"/>
     </row>
     <row r="18" spans="13:39">
-      <c r="M18" s="102"/>
-      <c r="N18" s="102"/>
-      <c r="O18" s="102"/>
-      <c r="P18" s="102"/>
-      <c r="Q18" s="102"/>
-      <c r="R18" s="102"/>
-      <c r="S18" s="102"/>
-      <c r="T18" s="102"/>
-      <c r="U18" s="102"/>
-      <c r="V18" s="102"/>
-      <c r="W18" s="102"/>
-      <c r="X18" s="102"/>
-      <c r="Y18" s="102"/>
-      <c r="Z18" s="102"/>
-      <c r="AA18" s="102"/>
-      <c r="AB18" s="102"/>
-      <c r="AC18" s="102"/>
-      <c r="AD18" s="102"/>
-      <c r="AE18" s="102"/>
-      <c r="AF18" s="102"/>
-      <c r="AG18" s="102"/>
-      <c r="AH18" s="102"/>
-      <c r="AI18" s="102"/>
-      <c r="AJ18" s="102"/>
-      <c r="AK18" s="102"/>
-      <c r="AL18" s="102"/>
-      <c r="AM18" s="102"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="67"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
+      <c r="S18" s="67"/>
+      <c r="T18" s="67"/>
+      <c r="U18" s="67"/>
+      <c r="V18" s="67"/>
+      <c r="W18" s="67"/>
+      <c r="X18" s="67"/>
+      <c r="Y18" s="67"/>
+      <c r="Z18" s="67"/>
+      <c r="AA18" s="67"/>
+      <c r="AB18" s="67"/>
+      <c r="AC18" s="67"/>
+      <c r="AD18" s="67"/>
+      <c r="AE18" s="67"/>
+      <c r="AF18" s="67"/>
+      <c r="AG18" s="67"/>
+      <c r="AH18" s="67"/>
+      <c r="AI18" s="67"/>
+      <c r="AJ18" s="67"/>
+      <c r="AK18" s="67"/>
+      <c r="AL18" s="67"/>
+      <c r="AM18" s="67"/>
     </row>
     <row r="26" spans="13:39" ht="15.75" customHeight="1"/>
     <row r="27" spans="13:39" ht="15.75" customHeight="1"/>
@@ -9750,126 +9750,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" s="30" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="82" t="s">
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="83"/>
-      <c r="U1" s="83"/>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="X1" s="83"/>
-      <c r="Y1" s="83"/>
-      <c r="Z1" s="83"/>
-      <c r="AA1" s="83"/>
-      <c r="AB1" s="83"/>
-      <c r="AC1" s="83"/>
-      <c r="AD1" s="83"/>
-      <c r="AE1" s="83"/>
-      <c r="AF1" s="83"/>
-      <c r="AG1" s="83"/>
-      <c r="AH1" s="83"/>
-      <c r="AI1" s="83"/>
-      <c r="AJ1" s="83"/>
-      <c r="AK1" s="83"/>
-      <c r="AL1" s="83"/>
-      <c r="AM1" s="83"/>
-      <c r="AN1" s="83"/>
-      <c r="AO1" s="83"/>
-      <c r="AP1" s="83"/>
-      <c r="AQ1" s="83"/>
-      <c r="AR1" s="83"/>
-      <c r="AS1" s="83"/>
-      <c r="AT1" s="83"/>
-      <c r="AU1" s="83"/>
-      <c r="AV1" s="83"/>
-      <c r="AW1" s="83"/>
-      <c r="AX1" s="84"/>
-      <c r="AY1" s="78" t="s">
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
+      <c r="R1" s="89"/>
+      <c r="S1" s="89"/>
+      <c r="T1" s="89"/>
+      <c r="U1" s="89"/>
+      <c r="V1" s="89"/>
+      <c r="W1" s="89"/>
+      <c r="X1" s="89"/>
+      <c r="Y1" s="89"/>
+      <c r="Z1" s="89"/>
+      <c r="AA1" s="89"/>
+      <c r="AB1" s="89"/>
+      <c r="AC1" s="89"/>
+      <c r="AD1" s="89"/>
+      <c r="AE1" s="89"/>
+      <c r="AF1" s="89"/>
+      <c r="AG1" s="89"/>
+      <c r="AH1" s="89"/>
+      <c r="AI1" s="89"/>
+      <c r="AJ1" s="89"/>
+      <c r="AK1" s="89"/>
+      <c r="AL1" s="89"/>
+      <c r="AM1" s="89"/>
+      <c r="AN1" s="89"/>
+      <c r="AO1" s="89"/>
+      <c r="AP1" s="89"/>
+      <c r="AQ1" s="89"/>
+      <c r="AR1" s="89"/>
+      <c r="AS1" s="89"/>
+      <c r="AT1" s="89"/>
+      <c r="AU1" s="89"/>
+      <c r="AV1" s="89"/>
+      <c r="AW1" s="89"/>
+      <c r="AX1" s="90"/>
+      <c r="AY1" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="AZ1" s="78"/>
-      <c r="BA1" s="78"/>
-      <c r="BB1" s="78"/>
-      <c r="BC1" s="79"/>
+      <c r="AZ1" s="84"/>
+      <c r="BA1" s="84"/>
+      <c r="BB1" s="84"/>
+      <c r="BC1" s="85"/>
     </row>
     <row r="2" spans="1:55" s="30" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="96"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="86"/>
-      <c r="O2" s="86"/>
-      <c r="P2" s="86"/>
-      <c r="Q2" s="86"/>
-      <c r="R2" s="86"/>
-      <c r="S2" s="86"/>
-      <c r="T2" s="86"/>
-      <c r="U2" s="86"/>
-      <c r="V2" s="86"/>
-      <c r="W2" s="86"/>
-      <c r="X2" s="86"/>
-      <c r="Y2" s="86"/>
-      <c r="Z2" s="86"/>
-      <c r="AA2" s="86"/>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="86"/>
-      <c r="AD2" s="86"/>
-      <c r="AE2" s="86"/>
-      <c r="AF2" s="86"/>
-      <c r="AG2" s="86"/>
-      <c r="AH2" s="86"/>
-      <c r="AI2" s="86"/>
-      <c r="AJ2" s="86"/>
-      <c r="AK2" s="86"/>
-      <c r="AL2" s="86"/>
-      <c r="AM2" s="86"/>
-      <c r="AN2" s="86"/>
-      <c r="AO2" s="86"/>
-      <c r="AP2" s="86"/>
-      <c r="AQ2" s="86"/>
-      <c r="AR2" s="86"/>
-      <c r="AS2" s="86"/>
-      <c r="AT2" s="86"/>
-      <c r="AU2" s="86"/>
-      <c r="AV2" s="86"/>
-      <c r="AW2" s="86"/>
-      <c r="AX2" s="87"/>
-      <c r="AY2" s="80" t="s">
+      <c r="A2" s="102"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+      <c r="R2" s="92"/>
+      <c r="S2" s="92"/>
+      <c r="T2" s="92"/>
+      <c r="U2" s="92"/>
+      <c r="V2" s="92"/>
+      <c r="W2" s="92"/>
+      <c r="X2" s="92"/>
+      <c r="Y2" s="92"/>
+      <c r="Z2" s="92"/>
+      <c r="AA2" s="92"/>
+      <c r="AB2" s="92"/>
+      <c r="AC2" s="92"/>
+      <c r="AD2" s="92"/>
+      <c r="AE2" s="92"/>
+      <c r="AF2" s="92"/>
+      <c r="AG2" s="92"/>
+      <c r="AH2" s="92"/>
+      <c r="AI2" s="92"/>
+      <c r="AJ2" s="92"/>
+      <c r="AK2" s="92"/>
+      <c r="AL2" s="92"/>
+      <c r="AM2" s="92"/>
+      <c r="AN2" s="92"/>
+      <c r="AO2" s="92"/>
+      <c r="AP2" s="92"/>
+      <c r="AQ2" s="92"/>
+      <c r="AR2" s="92"/>
+      <c r="AS2" s="92"/>
+      <c r="AT2" s="92"/>
+      <c r="AU2" s="92"/>
+      <c r="AV2" s="92"/>
+      <c r="AW2" s="92"/>
+      <c r="AX2" s="93"/>
+      <c r="AY2" s="86" t="s">
         <v>916</v>
       </c>
-      <c r="AZ2" s="80"/>
-      <c r="BA2" s="80"/>
-      <c r="BB2" s="80"/>
-      <c r="BC2" s="81"/>
+      <c r="AZ2" s="86"/>
+      <c r="BA2" s="86"/>
+      <c r="BB2" s="86"/>
+      <c r="BC2" s="87"/>
     </row>
     <row r="3" spans="1:55" s="30" customFormat="1" ht="12" customHeight="1" thickBot="1">
       <c r="A3" s="31"/>
@@ -9921,1865 +9921,1923 @@
       <c r="A4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="88" t="s">
+      <c r="B4" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="88" t="s">
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="98"/>
-      <c r="P4" s="98"/>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="98"/>
-      <c r="W4" s="98"/>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="98"/>
-      <c r="AD4" s="98"/>
-      <c r="AE4" s="98"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="98"/>
-      <c r="AK4" s="99"/>
-      <c r="AL4" s="99"/>
-      <c r="AM4" s="99"/>
-      <c r="AN4" s="100"/>
-      <c r="AO4" s="91" t="s">
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="104"/>
+      <c r="N4" s="104"/>
+      <c r="O4" s="104"/>
+      <c r="P4" s="104"/>
+      <c r="Q4" s="104"/>
+      <c r="R4" s="104"/>
+      <c r="S4" s="104"/>
+      <c r="T4" s="104"/>
+      <c r="U4" s="104"/>
+      <c r="V4" s="104"/>
+      <c r="W4" s="104"/>
+      <c r="X4" s="104"/>
+      <c r="Y4" s="104"/>
+      <c r="Z4" s="104"/>
+      <c r="AA4" s="104"/>
+      <c r="AB4" s="104"/>
+      <c r="AC4" s="104"/>
+      <c r="AD4" s="104"/>
+      <c r="AE4" s="104"/>
+      <c r="AF4" s="104"/>
+      <c r="AG4" s="104"/>
+      <c r="AH4" s="104"/>
+      <c r="AI4" s="104"/>
+      <c r="AJ4" s="104"/>
+      <c r="AK4" s="105"/>
+      <c r="AL4" s="105"/>
+      <c r="AM4" s="105"/>
+      <c r="AN4" s="106"/>
+      <c r="AO4" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="AP4" s="92"/>
-      <c r="AQ4" s="92"/>
-      <c r="AR4" s="92"/>
-      <c r="AS4" s="92"/>
-      <c r="AT4" s="92"/>
-      <c r="AU4" s="92"/>
-      <c r="AV4" s="92"/>
-      <c r="AW4" s="92"/>
-      <c r="AX4" s="92"/>
-      <c r="AY4" s="92"/>
-      <c r="AZ4" s="92"/>
-      <c r="BA4" s="92"/>
-      <c r="BB4" s="92"/>
-      <c r="BC4" s="93"/>
+      <c r="AP4" s="98"/>
+      <c r="AQ4" s="98"/>
+      <c r="AR4" s="98"/>
+      <c r="AS4" s="98"/>
+      <c r="AT4" s="98"/>
+      <c r="AU4" s="98"/>
+      <c r="AV4" s="98"/>
+      <c r="AW4" s="98"/>
+      <c r="AX4" s="98"/>
+      <c r="AY4" s="98"/>
+      <c r="AZ4" s="98"/>
+      <c r="BA4" s="98"/>
+      <c r="BB4" s="98"/>
+      <c r="BC4" s="99"/>
     </row>
     <row r="5" spans="1:55" ht="15" customHeight="1">
       <c r="A5" s="35" t="s">
         <v>589</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="55" t="s">
+      <c r="B5" s="129"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="129" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="58"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="58"/>
-      <c r="T5" s="58"/>
-      <c r="U5" s="58"/>
-      <c r="V5" s="58"/>
-      <c r="W5" s="58"/>
-      <c r="X5" s="58"/>
-      <c r="Y5" s="58"/>
-      <c r="Z5" s="58"/>
-      <c r="AA5" s="58"/>
-      <c r="AB5" s="58"/>
-      <c r="AC5" s="58"/>
-      <c r="AD5" s="58"/>
-      <c r="AE5" s="58"/>
-      <c r="AF5" s="58"/>
-      <c r="AG5" s="58"/>
-      <c r="AH5" s="58"/>
-      <c r="AI5" s="58"/>
-      <c r="AJ5" s="58"/>
-      <c r="AK5" s="59"/>
-      <c r="AL5" s="59"/>
-      <c r="AM5" s="59"/>
-      <c r="AN5" s="60"/>
-      <c r="AO5" s="65"/>
-      <c r="AP5" s="58"/>
-      <c r="AQ5" s="58"/>
-      <c r="AR5" s="58"/>
-      <c r="AS5" s="58"/>
-      <c r="AT5" s="58"/>
-      <c r="AU5" s="58"/>
-      <c r="AV5" s="58"/>
-      <c r="AW5" s="58"/>
-      <c r="AX5" s="58"/>
-      <c r="AY5" s="58"/>
-      <c r="AZ5" s="58"/>
-      <c r="BA5" s="58"/>
-      <c r="BB5" s="58"/>
-      <c r="BC5" s="66"/>
+      <c r="J5" s="124"/>
+      <c r="K5" s="124"/>
+      <c r="L5" s="124"/>
+      <c r="M5" s="124"/>
+      <c r="N5" s="124"/>
+      <c r="O5" s="124"/>
+      <c r="P5" s="124"/>
+      <c r="Q5" s="124"/>
+      <c r="R5" s="124"/>
+      <c r="S5" s="124"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="124"/>
+      <c r="W5" s="124"/>
+      <c r="X5" s="124"/>
+      <c r="Y5" s="124"/>
+      <c r="Z5" s="124"/>
+      <c r="AA5" s="124"/>
+      <c r="AB5" s="124"/>
+      <c r="AC5" s="124"/>
+      <c r="AD5" s="124"/>
+      <c r="AE5" s="124"/>
+      <c r="AF5" s="124"/>
+      <c r="AG5" s="124"/>
+      <c r="AH5" s="124"/>
+      <c r="AI5" s="124"/>
+      <c r="AJ5" s="124"/>
+      <c r="AK5" s="132"/>
+      <c r="AL5" s="132"/>
+      <c r="AM5" s="132"/>
+      <c r="AN5" s="133"/>
+      <c r="AO5" s="123"/>
+      <c r="AP5" s="124"/>
+      <c r="AQ5" s="124"/>
+      <c r="AR5" s="124"/>
+      <c r="AS5" s="124"/>
+      <c r="AT5" s="124"/>
+      <c r="AU5" s="124"/>
+      <c r="AV5" s="124"/>
+      <c r="AW5" s="124"/>
+      <c r="AX5" s="124"/>
+      <c r="AY5" s="124"/>
+      <c r="AZ5" s="124"/>
+      <c r="BA5" s="124"/>
+      <c r="BB5" s="124"/>
+      <c r="BC5" s="125"/>
     </row>
     <row r="6" spans="1:55" ht="15" customHeight="1">
       <c r="A6" s="36" t="s">
         <v>957</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="50" t="s">
+      <c r="B6" s="110"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="110" t="s">
         <v>958</v>
       </c>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="48"/>
-      <c r="U6" s="48"/>
-      <c r="V6" s="48"/>
-      <c r="W6" s="48"/>
-      <c r="X6" s="48"/>
-      <c r="Y6" s="48"/>
-      <c r="Z6" s="48"/>
-      <c r="AA6" s="48"/>
-      <c r="AB6" s="48"/>
-      <c r="AC6" s="48"/>
-      <c r="AD6" s="48"/>
-      <c r="AE6" s="48"/>
-      <c r="AF6" s="48"/>
-      <c r="AG6" s="48"/>
-      <c r="AH6" s="48"/>
-      <c r="AI6" s="48"/>
-      <c r="AJ6" s="48"/>
-      <c r="AK6" s="53"/>
-      <c r="AL6" s="53"/>
-      <c r="AM6" s="53"/>
-      <c r="AN6" s="54"/>
-      <c r="AO6" s="47" t="s">
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="114"/>
+      <c r="M6" s="114"/>
+      <c r="N6" s="114"/>
+      <c r="O6" s="114"/>
+      <c r="P6" s="114"/>
+      <c r="Q6" s="114"/>
+      <c r="R6" s="114"/>
+      <c r="S6" s="114"/>
+      <c r="T6" s="114"/>
+      <c r="U6" s="114"/>
+      <c r="V6" s="114"/>
+      <c r="W6" s="114"/>
+      <c r="X6" s="114"/>
+      <c r="Y6" s="114"/>
+      <c r="Z6" s="114"/>
+      <c r="AA6" s="114"/>
+      <c r="AB6" s="114"/>
+      <c r="AC6" s="114"/>
+      <c r="AD6" s="114"/>
+      <c r="AE6" s="114"/>
+      <c r="AF6" s="114"/>
+      <c r="AG6" s="114"/>
+      <c r="AH6" s="114"/>
+      <c r="AI6" s="114"/>
+      <c r="AJ6" s="114"/>
+      <c r="AK6" s="116"/>
+      <c r="AL6" s="116"/>
+      <c r="AM6" s="116"/>
+      <c r="AN6" s="117"/>
+      <c r="AO6" s="113" t="s">
         <v>956</v>
       </c>
-      <c r="AP6" s="48"/>
-      <c r="AQ6" s="48"/>
-      <c r="AR6" s="48"/>
-      <c r="AS6" s="48"/>
-      <c r="AT6" s="48"/>
-      <c r="AU6" s="48"/>
-      <c r="AV6" s="48"/>
-      <c r="AW6" s="48"/>
-      <c r="AX6" s="48"/>
-      <c r="AY6" s="48"/>
-      <c r="AZ6" s="48"/>
-      <c r="BA6" s="48"/>
-      <c r="BB6" s="48"/>
-      <c r="BC6" s="49"/>
+      <c r="AP6" s="114"/>
+      <c r="AQ6" s="114"/>
+      <c r="AR6" s="114"/>
+      <c r="AS6" s="114"/>
+      <c r="AT6" s="114"/>
+      <c r="AU6" s="114"/>
+      <c r="AV6" s="114"/>
+      <c r="AW6" s="114"/>
+      <c r="AX6" s="114"/>
+      <c r="AY6" s="114"/>
+      <c r="AZ6" s="114"/>
+      <c r="BA6" s="114"/>
+      <c r="BB6" s="114"/>
+      <c r="BC6" s="115"/>
     </row>
     <row r="7" spans="1:55" ht="15" customHeight="1">
       <c r="A7" s="36" t="s">
         <v>1134</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="61" t="s">
+      <c r="B7" s="110"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="E7" s="111"/>
+      <c r="F7" s="111"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="134" t="s">
         <v>1135</v>
       </c>
-      <c r="J7" s="62"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
-      <c r="M7" s="62"/>
-      <c r="N7" s="62"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="62"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="62"/>
-      <c r="T7" s="62"/>
-      <c r="U7" s="62"/>
-      <c r="V7" s="62"/>
-      <c r="W7" s="62"/>
-      <c r="X7" s="62"/>
-      <c r="Y7" s="62"/>
-      <c r="Z7" s="62"/>
-      <c r="AA7" s="62"/>
-      <c r="AB7" s="62"/>
-      <c r="AC7" s="62"/>
-      <c r="AD7" s="62"/>
-      <c r="AE7" s="62"/>
-      <c r="AF7" s="62"/>
-      <c r="AG7" s="62"/>
-      <c r="AH7" s="62"/>
-      <c r="AI7" s="62"/>
-      <c r="AJ7" s="62"/>
-      <c r="AK7" s="63"/>
-      <c r="AL7" s="63"/>
-      <c r="AM7" s="63"/>
-      <c r="AN7" s="64"/>
-      <c r="AO7" s="67" t="s">
+      <c r="J7" s="135"/>
+      <c r="K7" s="135"/>
+      <c r="L7" s="135"/>
+      <c r="M7" s="135"/>
+      <c r="N7" s="135"/>
+      <c r="O7" s="135"/>
+      <c r="P7" s="135"/>
+      <c r="Q7" s="135"/>
+      <c r="R7" s="135"/>
+      <c r="S7" s="135"/>
+      <c r="T7" s="135"/>
+      <c r="U7" s="135"/>
+      <c r="V7" s="135"/>
+      <c r="W7" s="135"/>
+      <c r="X7" s="135"/>
+      <c r="Y7" s="135"/>
+      <c r="Z7" s="135"/>
+      <c r="AA7" s="135"/>
+      <c r="AB7" s="135"/>
+      <c r="AC7" s="135"/>
+      <c r="AD7" s="135"/>
+      <c r="AE7" s="135"/>
+      <c r="AF7" s="135"/>
+      <c r="AG7" s="135"/>
+      <c r="AH7" s="135"/>
+      <c r="AI7" s="135"/>
+      <c r="AJ7" s="135"/>
+      <c r="AK7" s="136"/>
+      <c r="AL7" s="136"/>
+      <c r="AM7" s="136"/>
+      <c r="AN7" s="137"/>
+      <c r="AO7" s="126" t="s">
         <v>1136</v>
       </c>
-      <c r="AP7" s="68"/>
-      <c r="AQ7" s="68"/>
-      <c r="AR7" s="68"/>
-      <c r="AS7" s="68"/>
-      <c r="AT7" s="68"/>
-      <c r="AU7" s="68"/>
-      <c r="AV7" s="68"/>
-      <c r="AW7" s="68"/>
-      <c r="AX7" s="68"/>
-      <c r="AY7" s="68"/>
-      <c r="AZ7" s="68"/>
-      <c r="BA7" s="68"/>
-      <c r="BB7" s="68"/>
-      <c r="BC7" s="69"/>
+      <c r="AP7" s="127"/>
+      <c r="AQ7" s="127"/>
+      <c r="AR7" s="127"/>
+      <c r="AS7" s="127"/>
+      <c r="AT7" s="127"/>
+      <c r="AU7" s="127"/>
+      <c r="AV7" s="127"/>
+      <c r="AW7" s="127"/>
+      <c r="AX7" s="127"/>
+      <c r="AY7" s="127"/>
+      <c r="AZ7" s="127"/>
+      <c r="BA7" s="127"/>
+      <c r="BB7" s="127"/>
+      <c r="BC7" s="128"/>
     </row>
     <row r="8" spans="1:55" ht="15" customHeight="1">
       <c r="A8" s="36"/>
-      <c r="B8" s="50"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
-      <c r="N8" s="48"/>
-      <c r="O8" s="48"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="48"/>
-      <c r="R8" s="48"/>
-      <c r="S8" s="48"/>
-      <c r="T8" s="48"/>
-      <c r="U8" s="48"/>
-      <c r="V8" s="48"/>
-      <c r="W8" s="48"/>
-      <c r="X8" s="48"/>
-      <c r="Y8" s="48"/>
-      <c r="Z8" s="48"/>
-      <c r="AA8" s="48"/>
-      <c r="AB8" s="48"/>
-      <c r="AC8" s="48"/>
-      <c r="AD8" s="48"/>
-      <c r="AE8" s="48"/>
-      <c r="AF8" s="48"/>
-      <c r="AG8" s="48"/>
-      <c r="AH8" s="48"/>
-      <c r="AI8" s="48"/>
-      <c r="AJ8" s="48"/>
-      <c r="AK8" s="53"/>
-      <c r="AL8" s="53"/>
-      <c r="AM8" s="53"/>
-      <c r="AN8" s="54"/>
-      <c r="AO8" s="47"/>
-      <c r="AP8" s="48"/>
-      <c r="AQ8" s="48"/>
-      <c r="AR8" s="48"/>
-      <c r="AS8" s="48"/>
-      <c r="AT8" s="48"/>
-      <c r="AU8" s="48"/>
-      <c r="AV8" s="48"/>
-      <c r="AW8" s="48"/>
-      <c r="AX8" s="48"/>
-      <c r="AY8" s="48"/>
-      <c r="AZ8" s="48"/>
-      <c r="BA8" s="48"/>
-      <c r="BB8" s="48"/>
-      <c r="BC8" s="49"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="111"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="114"/>
+      <c r="K8" s="114"/>
+      <c r="L8" s="114"/>
+      <c r="M8" s="114"/>
+      <c r="N8" s="114"/>
+      <c r="O8" s="114"/>
+      <c r="P8" s="114"/>
+      <c r="Q8" s="114"/>
+      <c r="R8" s="114"/>
+      <c r="S8" s="114"/>
+      <c r="T8" s="114"/>
+      <c r="U8" s="114"/>
+      <c r="V8" s="114"/>
+      <c r="W8" s="114"/>
+      <c r="X8" s="114"/>
+      <c r="Y8" s="114"/>
+      <c r="Z8" s="114"/>
+      <c r="AA8" s="114"/>
+      <c r="AB8" s="114"/>
+      <c r="AC8" s="114"/>
+      <c r="AD8" s="114"/>
+      <c r="AE8" s="114"/>
+      <c r="AF8" s="114"/>
+      <c r="AG8" s="114"/>
+      <c r="AH8" s="114"/>
+      <c r="AI8" s="114"/>
+      <c r="AJ8" s="114"/>
+      <c r="AK8" s="116"/>
+      <c r="AL8" s="116"/>
+      <c r="AM8" s="116"/>
+      <c r="AN8" s="117"/>
+      <c r="AO8" s="113"/>
+      <c r="AP8" s="114"/>
+      <c r="AQ8" s="114"/>
+      <c r="AR8" s="114"/>
+      <c r="AS8" s="114"/>
+      <c r="AT8" s="114"/>
+      <c r="AU8" s="114"/>
+      <c r="AV8" s="114"/>
+      <c r="AW8" s="114"/>
+      <c r="AX8" s="114"/>
+      <c r="AY8" s="114"/>
+      <c r="AZ8" s="114"/>
+      <c r="BA8" s="114"/>
+      <c r="BB8" s="114"/>
+      <c r="BC8" s="115"/>
     </row>
     <row r="9" spans="1:55" ht="15" customHeight="1">
       <c r="A9" s="36"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="48"/>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="48"/>
-      <c r="V9" s="48"/>
-      <c r="W9" s="48"/>
-      <c r="X9" s="48"/>
-      <c r="Y9" s="48"/>
-      <c r="Z9" s="48"/>
-      <c r="AA9" s="48"/>
-      <c r="AB9" s="48"/>
-      <c r="AC9" s="48"/>
-      <c r="AD9" s="48"/>
-      <c r="AE9" s="48"/>
-      <c r="AF9" s="48"/>
-      <c r="AG9" s="48"/>
-      <c r="AH9" s="48"/>
-      <c r="AI9" s="48"/>
-      <c r="AJ9" s="48"/>
-      <c r="AK9" s="53"/>
-      <c r="AL9" s="53"/>
-      <c r="AM9" s="53"/>
-      <c r="AN9" s="54"/>
-      <c r="AO9" s="47"/>
-      <c r="AP9" s="48"/>
-      <c r="AQ9" s="48"/>
-      <c r="AR9" s="48"/>
-      <c r="AS9" s="48"/>
-      <c r="AT9" s="48"/>
-      <c r="AU9" s="48"/>
-      <c r="AV9" s="48"/>
-      <c r="AW9" s="48"/>
-      <c r="AX9" s="48"/>
-      <c r="AY9" s="48"/>
-      <c r="AZ9" s="48"/>
-      <c r="BA9" s="48"/>
-      <c r="BB9" s="48"/>
-      <c r="BC9" s="49"/>
+      <c r="B9" s="110"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+      <c r="F9" s="111"/>
+      <c r="G9" s="111"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="114"/>
+      <c r="K9" s="114"/>
+      <c r="L9" s="114"/>
+      <c r="M9" s="114"/>
+      <c r="N9" s="114"/>
+      <c r="O9" s="114"/>
+      <c r="P9" s="114"/>
+      <c r="Q9" s="114"/>
+      <c r="R9" s="114"/>
+      <c r="S9" s="114"/>
+      <c r="T9" s="114"/>
+      <c r="U9" s="114"/>
+      <c r="V9" s="114"/>
+      <c r="W9" s="114"/>
+      <c r="X9" s="114"/>
+      <c r="Y9" s="114"/>
+      <c r="Z9" s="114"/>
+      <c r="AA9" s="114"/>
+      <c r="AB9" s="114"/>
+      <c r="AC9" s="114"/>
+      <c r="AD9" s="114"/>
+      <c r="AE9" s="114"/>
+      <c r="AF9" s="114"/>
+      <c r="AG9" s="114"/>
+      <c r="AH9" s="114"/>
+      <c r="AI9" s="114"/>
+      <c r="AJ9" s="114"/>
+      <c r="AK9" s="116"/>
+      <c r="AL9" s="116"/>
+      <c r="AM9" s="116"/>
+      <c r="AN9" s="117"/>
+      <c r="AO9" s="113"/>
+      <c r="AP9" s="114"/>
+      <c r="AQ9" s="114"/>
+      <c r="AR9" s="114"/>
+      <c r="AS9" s="114"/>
+      <c r="AT9" s="114"/>
+      <c r="AU9" s="114"/>
+      <c r="AV9" s="114"/>
+      <c r="AW9" s="114"/>
+      <c r="AX9" s="114"/>
+      <c r="AY9" s="114"/>
+      <c r="AZ9" s="114"/>
+      <c r="BA9" s="114"/>
+      <c r="BB9" s="114"/>
+      <c r="BC9" s="115"/>
     </row>
     <row r="10" spans="1:55" ht="15" customHeight="1">
       <c r="A10" s="36"/>
-      <c r="B10" s="50"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="48"/>
-      <c r="P10" s="48"/>
-      <c r="Q10" s="48"/>
-      <c r="R10" s="48"/>
-      <c r="S10" s="48"/>
-      <c r="T10" s="48"/>
-      <c r="U10" s="48"/>
-      <c r="V10" s="48"/>
-      <c r="W10" s="48"/>
-      <c r="X10" s="48"/>
-      <c r="Y10" s="48"/>
-      <c r="Z10" s="48"/>
-      <c r="AA10" s="48"/>
-      <c r="AB10" s="48"/>
-      <c r="AC10" s="48"/>
-      <c r="AD10" s="48"/>
-      <c r="AE10" s="48"/>
-      <c r="AF10" s="48"/>
-      <c r="AG10" s="48"/>
-      <c r="AH10" s="48"/>
-      <c r="AI10" s="48"/>
-      <c r="AJ10" s="48"/>
-      <c r="AK10" s="53"/>
-      <c r="AL10" s="53"/>
-      <c r="AM10" s="53"/>
-      <c r="AN10" s="54"/>
-      <c r="AO10" s="47"/>
-      <c r="AP10" s="48"/>
-      <c r="AQ10" s="48"/>
-      <c r="AR10" s="48"/>
-      <c r="AS10" s="48"/>
-      <c r="AT10" s="48"/>
-      <c r="AU10" s="48"/>
-      <c r="AV10" s="48"/>
-      <c r="AW10" s="48"/>
-      <c r="AX10" s="48"/>
-      <c r="AY10" s="48"/>
-      <c r="AZ10" s="48"/>
-      <c r="BA10" s="48"/>
-      <c r="BB10" s="48"/>
-      <c r="BC10" s="49"/>
+      <c r="B10" s="110"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="111"/>
+      <c r="G10" s="111"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="114"/>
+      <c r="L10" s="114"/>
+      <c r="M10" s="114"/>
+      <c r="N10" s="114"/>
+      <c r="O10" s="114"/>
+      <c r="P10" s="114"/>
+      <c r="Q10" s="114"/>
+      <c r="R10" s="114"/>
+      <c r="S10" s="114"/>
+      <c r="T10" s="114"/>
+      <c r="U10" s="114"/>
+      <c r="V10" s="114"/>
+      <c r="W10" s="114"/>
+      <c r="X10" s="114"/>
+      <c r="Y10" s="114"/>
+      <c r="Z10" s="114"/>
+      <c r="AA10" s="114"/>
+      <c r="AB10" s="114"/>
+      <c r="AC10" s="114"/>
+      <c r="AD10" s="114"/>
+      <c r="AE10" s="114"/>
+      <c r="AF10" s="114"/>
+      <c r="AG10" s="114"/>
+      <c r="AH10" s="114"/>
+      <c r="AI10" s="114"/>
+      <c r="AJ10" s="114"/>
+      <c r="AK10" s="116"/>
+      <c r="AL10" s="116"/>
+      <c r="AM10" s="116"/>
+      <c r="AN10" s="117"/>
+      <c r="AO10" s="113"/>
+      <c r="AP10" s="114"/>
+      <c r="AQ10" s="114"/>
+      <c r="AR10" s="114"/>
+      <c r="AS10" s="114"/>
+      <c r="AT10" s="114"/>
+      <c r="AU10" s="114"/>
+      <c r="AV10" s="114"/>
+      <c r="AW10" s="114"/>
+      <c r="AX10" s="114"/>
+      <c r="AY10" s="114"/>
+      <c r="AZ10" s="114"/>
+      <c r="BA10" s="114"/>
+      <c r="BB10" s="114"/>
+      <c r="BC10" s="115"/>
     </row>
     <row r="11" spans="1:55" ht="15" customHeight="1">
       <c r="A11" s="36"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="48"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="48"/>
-      <c r="P11" s="48"/>
-      <c r="Q11" s="48"/>
-      <c r="R11" s="48"/>
-      <c r="S11" s="48"/>
-      <c r="T11" s="48"/>
-      <c r="U11" s="48"/>
-      <c r="V11" s="48"/>
-      <c r="W11" s="48"/>
-      <c r="X11" s="48"/>
-      <c r="Y11" s="48"/>
-      <c r="Z11" s="48"/>
-      <c r="AA11" s="48"/>
-      <c r="AB11" s="48"/>
-      <c r="AC11" s="48"/>
-      <c r="AD11" s="48"/>
-      <c r="AE11" s="48"/>
-      <c r="AF11" s="48"/>
-      <c r="AG11" s="48"/>
-      <c r="AH11" s="48"/>
-      <c r="AI11" s="48"/>
-      <c r="AJ11" s="48"/>
-      <c r="AK11" s="53"/>
-      <c r="AL11" s="53"/>
-      <c r="AM11" s="53"/>
-      <c r="AN11" s="54"/>
-      <c r="AO11" s="47"/>
-      <c r="AP11" s="48"/>
-      <c r="AQ11" s="48"/>
-      <c r="AR11" s="48"/>
-      <c r="AS11" s="48"/>
-      <c r="AT11" s="48"/>
-      <c r="AU11" s="48"/>
-      <c r="AV11" s="48"/>
-      <c r="AW11" s="48"/>
-      <c r="AX11" s="48"/>
-      <c r="AY11" s="48"/>
-      <c r="AZ11" s="48"/>
-      <c r="BA11" s="48"/>
-      <c r="BB11" s="48"/>
-      <c r="BC11" s="49"/>
+      <c r="B11" s="110"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="111"/>
+      <c r="F11" s="111"/>
+      <c r="G11" s="111"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="114"/>
+      <c r="K11" s="114"/>
+      <c r="L11" s="114"/>
+      <c r="M11" s="114"/>
+      <c r="N11" s="114"/>
+      <c r="O11" s="114"/>
+      <c r="P11" s="114"/>
+      <c r="Q11" s="114"/>
+      <c r="R11" s="114"/>
+      <c r="S11" s="114"/>
+      <c r="T11" s="114"/>
+      <c r="U11" s="114"/>
+      <c r="V11" s="114"/>
+      <c r="W11" s="114"/>
+      <c r="X11" s="114"/>
+      <c r="Y11" s="114"/>
+      <c r="Z11" s="114"/>
+      <c r="AA11" s="114"/>
+      <c r="AB11" s="114"/>
+      <c r="AC11" s="114"/>
+      <c r="AD11" s="114"/>
+      <c r="AE11" s="114"/>
+      <c r="AF11" s="114"/>
+      <c r="AG11" s="114"/>
+      <c r="AH11" s="114"/>
+      <c r="AI11" s="114"/>
+      <c r="AJ11" s="114"/>
+      <c r="AK11" s="116"/>
+      <c r="AL11" s="116"/>
+      <c r="AM11" s="116"/>
+      <c r="AN11" s="117"/>
+      <c r="AO11" s="113"/>
+      <c r="AP11" s="114"/>
+      <c r="AQ11" s="114"/>
+      <c r="AR11" s="114"/>
+      <c r="AS11" s="114"/>
+      <c r="AT11" s="114"/>
+      <c r="AU11" s="114"/>
+      <c r="AV11" s="114"/>
+      <c r="AW11" s="114"/>
+      <c r="AX11" s="114"/>
+      <c r="AY11" s="114"/>
+      <c r="AZ11" s="114"/>
+      <c r="BA11" s="114"/>
+      <c r="BB11" s="114"/>
+      <c r="BC11" s="115"/>
     </row>
     <row r="12" spans="1:55" ht="15" customHeight="1">
       <c r="A12" s="36"/>
-      <c r="B12" s="50"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="48"/>
-      <c r="P12" s="48"/>
-      <c r="Q12" s="48"/>
-      <c r="R12" s="48"/>
-      <c r="S12" s="48"/>
-      <c r="T12" s="48"/>
-      <c r="U12" s="48"/>
-      <c r="V12" s="48"/>
-      <c r="W12" s="48"/>
-      <c r="X12" s="48"/>
-      <c r="Y12" s="48"/>
-      <c r="Z12" s="48"/>
-      <c r="AA12" s="48"/>
-      <c r="AB12" s="48"/>
-      <c r="AC12" s="48"/>
-      <c r="AD12" s="48"/>
-      <c r="AE12" s="48"/>
-      <c r="AF12" s="48"/>
-      <c r="AG12" s="48"/>
-      <c r="AH12" s="48"/>
-      <c r="AI12" s="48"/>
-      <c r="AJ12" s="48"/>
-      <c r="AK12" s="53"/>
-      <c r="AL12" s="53"/>
-      <c r="AM12" s="53"/>
-      <c r="AN12" s="54"/>
-      <c r="AO12" s="47"/>
-      <c r="AP12" s="48"/>
-      <c r="AQ12" s="48"/>
-      <c r="AR12" s="48"/>
-      <c r="AS12" s="48"/>
-      <c r="AT12" s="48"/>
-      <c r="AU12" s="48"/>
-      <c r="AV12" s="48"/>
-      <c r="AW12" s="48"/>
-      <c r="AX12" s="48"/>
-      <c r="AY12" s="48"/>
-      <c r="AZ12" s="48"/>
-      <c r="BA12" s="48"/>
-      <c r="BB12" s="48"/>
-      <c r="BC12" s="49"/>
+      <c r="B12" s="110"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="114"/>
+      <c r="K12" s="114"/>
+      <c r="L12" s="114"/>
+      <c r="M12" s="114"/>
+      <c r="N12" s="114"/>
+      <c r="O12" s="114"/>
+      <c r="P12" s="114"/>
+      <c r="Q12" s="114"/>
+      <c r="R12" s="114"/>
+      <c r="S12" s="114"/>
+      <c r="T12" s="114"/>
+      <c r="U12" s="114"/>
+      <c r="V12" s="114"/>
+      <c r="W12" s="114"/>
+      <c r="X12" s="114"/>
+      <c r="Y12" s="114"/>
+      <c r="Z12" s="114"/>
+      <c r="AA12" s="114"/>
+      <c r="AB12" s="114"/>
+      <c r="AC12" s="114"/>
+      <c r="AD12" s="114"/>
+      <c r="AE12" s="114"/>
+      <c r="AF12" s="114"/>
+      <c r="AG12" s="114"/>
+      <c r="AH12" s="114"/>
+      <c r="AI12" s="114"/>
+      <c r="AJ12" s="114"/>
+      <c r="AK12" s="116"/>
+      <c r="AL12" s="116"/>
+      <c r="AM12" s="116"/>
+      <c r="AN12" s="117"/>
+      <c r="AO12" s="113"/>
+      <c r="AP12" s="114"/>
+      <c r="AQ12" s="114"/>
+      <c r="AR12" s="114"/>
+      <c r="AS12" s="114"/>
+      <c r="AT12" s="114"/>
+      <c r="AU12" s="114"/>
+      <c r="AV12" s="114"/>
+      <c r="AW12" s="114"/>
+      <c r="AX12" s="114"/>
+      <c r="AY12" s="114"/>
+      <c r="AZ12" s="114"/>
+      <c r="BA12" s="114"/>
+      <c r="BB12" s="114"/>
+      <c r="BC12" s="115"/>
     </row>
     <row r="13" spans="1:55" ht="15" customHeight="1">
       <c r="A13" s="36"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="48"/>
-      <c r="O13" s="48"/>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="48"/>
-      <c r="R13" s="48"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="48"/>
-      <c r="U13" s="48"/>
-      <c r="V13" s="48"/>
-      <c r="W13" s="48"/>
-      <c r="X13" s="48"/>
-      <c r="Y13" s="48"/>
-      <c r="Z13" s="48"/>
-      <c r="AA13" s="48"/>
-      <c r="AB13" s="48"/>
-      <c r="AC13" s="48"/>
-      <c r="AD13" s="48"/>
-      <c r="AE13" s="48"/>
-      <c r="AF13" s="48"/>
-      <c r="AG13" s="48"/>
-      <c r="AH13" s="48"/>
-      <c r="AI13" s="48"/>
-      <c r="AJ13" s="48"/>
-      <c r="AK13" s="53"/>
-      <c r="AL13" s="53"/>
-      <c r="AM13" s="53"/>
-      <c r="AN13" s="54"/>
-      <c r="AO13" s="47"/>
-      <c r="AP13" s="48"/>
-      <c r="AQ13" s="48"/>
-      <c r="AR13" s="48"/>
-      <c r="AS13" s="48"/>
-      <c r="AT13" s="48"/>
-      <c r="AU13" s="48"/>
-      <c r="AV13" s="48"/>
-      <c r="AW13" s="48"/>
-      <c r="AX13" s="48"/>
-      <c r="AY13" s="48"/>
-      <c r="AZ13" s="48"/>
-      <c r="BA13" s="48"/>
-      <c r="BB13" s="48"/>
-      <c r="BC13" s="49"/>
+      <c r="B13" s="110"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="114"/>
+      <c r="K13" s="114"/>
+      <c r="L13" s="114"/>
+      <c r="M13" s="114"/>
+      <c r="N13" s="114"/>
+      <c r="O13" s="114"/>
+      <c r="P13" s="114"/>
+      <c r="Q13" s="114"/>
+      <c r="R13" s="114"/>
+      <c r="S13" s="114"/>
+      <c r="T13" s="114"/>
+      <c r="U13" s="114"/>
+      <c r="V13" s="114"/>
+      <c r="W13" s="114"/>
+      <c r="X13" s="114"/>
+      <c r="Y13" s="114"/>
+      <c r="Z13" s="114"/>
+      <c r="AA13" s="114"/>
+      <c r="AB13" s="114"/>
+      <c r="AC13" s="114"/>
+      <c r="AD13" s="114"/>
+      <c r="AE13" s="114"/>
+      <c r="AF13" s="114"/>
+      <c r="AG13" s="114"/>
+      <c r="AH13" s="114"/>
+      <c r="AI13" s="114"/>
+      <c r="AJ13" s="114"/>
+      <c r="AK13" s="116"/>
+      <c r="AL13" s="116"/>
+      <c r="AM13" s="116"/>
+      <c r="AN13" s="117"/>
+      <c r="AO13" s="113"/>
+      <c r="AP13" s="114"/>
+      <c r="AQ13" s="114"/>
+      <c r="AR13" s="114"/>
+      <c r="AS13" s="114"/>
+      <c r="AT13" s="114"/>
+      <c r="AU13" s="114"/>
+      <c r="AV13" s="114"/>
+      <c r="AW13" s="114"/>
+      <c r="AX13" s="114"/>
+      <c r="AY13" s="114"/>
+      <c r="AZ13" s="114"/>
+      <c r="BA13" s="114"/>
+      <c r="BB13" s="114"/>
+      <c r="BC13" s="115"/>
     </row>
     <row r="14" spans="1:55" ht="15" customHeight="1">
       <c r="A14" s="36"/>
-      <c r="B14" s="50"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="48"/>
-      <c r="N14" s="48"/>
-      <c r="O14" s="48"/>
-      <c r="P14" s="48"/>
-      <c r="Q14" s="48"/>
-      <c r="R14" s="48"/>
-      <c r="S14" s="48"/>
-      <c r="T14" s="48"/>
-      <c r="U14" s="48"/>
-      <c r="V14" s="48"/>
-      <c r="W14" s="48"/>
-      <c r="X14" s="48"/>
-      <c r="Y14" s="48"/>
-      <c r="Z14" s="48"/>
-      <c r="AA14" s="48"/>
-      <c r="AB14" s="48"/>
-      <c r="AC14" s="48"/>
-      <c r="AD14" s="48"/>
-      <c r="AE14" s="48"/>
-      <c r="AF14" s="48"/>
-      <c r="AG14" s="48"/>
-      <c r="AH14" s="48"/>
-      <c r="AI14" s="48"/>
-      <c r="AJ14" s="48"/>
-      <c r="AK14" s="53"/>
-      <c r="AL14" s="53"/>
-      <c r="AM14" s="53"/>
-      <c r="AN14" s="54"/>
-      <c r="AO14" s="47"/>
-      <c r="AP14" s="48"/>
-      <c r="AQ14" s="48"/>
-      <c r="AR14" s="48"/>
-      <c r="AS14" s="48"/>
-      <c r="AT14" s="48"/>
-      <c r="AU14" s="48"/>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
-      <c r="BB14" s="48"/>
-      <c r="BC14" s="49"/>
+      <c r="B14" s="110"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="114"/>
+      <c r="L14" s="114"/>
+      <c r="M14" s="114"/>
+      <c r="N14" s="114"/>
+      <c r="O14" s="114"/>
+      <c r="P14" s="114"/>
+      <c r="Q14" s="114"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="114"/>
+      <c r="T14" s="114"/>
+      <c r="U14" s="114"/>
+      <c r="V14" s="114"/>
+      <c r="W14" s="114"/>
+      <c r="X14" s="114"/>
+      <c r="Y14" s="114"/>
+      <c r="Z14" s="114"/>
+      <c r="AA14" s="114"/>
+      <c r="AB14" s="114"/>
+      <c r="AC14" s="114"/>
+      <c r="AD14" s="114"/>
+      <c r="AE14" s="114"/>
+      <c r="AF14" s="114"/>
+      <c r="AG14" s="114"/>
+      <c r="AH14" s="114"/>
+      <c r="AI14" s="114"/>
+      <c r="AJ14" s="114"/>
+      <c r="AK14" s="116"/>
+      <c r="AL14" s="116"/>
+      <c r="AM14" s="116"/>
+      <c r="AN14" s="117"/>
+      <c r="AO14" s="113"/>
+      <c r="AP14" s="114"/>
+      <c r="AQ14" s="114"/>
+      <c r="AR14" s="114"/>
+      <c r="AS14" s="114"/>
+      <c r="AT14" s="114"/>
+      <c r="AU14" s="114"/>
+      <c r="AV14" s="114"/>
+      <c r="AW14" s="114"/>
+      <c r="AX14" s="114"/>
+      <c r="AY14" s="114"/>
+      <c r="AZ14" s="114"/>
+      <c r="BA14" s="114"/>
+      <c r="BB14" s="114"/>
+      <c r="BC14" s="115"/>
     </row>
     <row r="15" spans="1:55" ht="15" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="48"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="48"/>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="48"/>
-      <c r="R15" s="48"/>
-      <c r="S15" s="48"/>
-      <c r="T15" s="48"/>
-      <c r="U15" s="48"/>
-      <c r="V15" s="48"/>
-      <c r="W15" s="48"/>
-      <c r="X15" s="48"/>
-      <c r="Y15" s="48"/>
-      <c r="Z15" s="48"/>
-      <c r="AA15" s="48"/>
-      <c r="AB15" s="48"/>
-      <c r="AC15" s="48"/>
-      <c r="AD15" s="48"/>
-      <c r="AE15" s="48"/>
-      <c r="AF15" s="48"/>
-      <c r="AG15" s="48"/>
-      <c r="AH15" s="48"/>
-      <c r="AI15" s="48"/>
-      <c r="AJ15" s="48"/>
-      <c r="AK15" s="53"/>
-      <c r="AL15" s="53"/>
-      <c r="AM15" s="53"/>
-      <c r="AN15" s="54"/>
-      <c r="AO15" s="47"/>
-      <c r="AP15" s="48"/>
-      <c r="AQ15" s="48"/>
-      <c r="AR15" s="48"/>
-      <c r="AS15" s="48"/>
-      <c r="AT15" s="48"/>
-      <c r="AU15" s="48"/>
-      <c r="AV15" s="48"/>
-      <c r="AW15" s="48"/>
-      <c r="AX15" s="48"/>
-      <c r="AY15" s="48"/>
-      <c r="AZ15" s="48"/>
-      <c r="BA15" s="48"/>
-      <c r="BB15" s="48"/>
-      <c r="BC15" s="49"/>
+      <c r="B15" s="110"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="114"/>
+      <c r="K15" s="114"/>
+      <c r="L15" s="114"/>
+      <c r="M15" s="114"/>
+      <c r="N15" s="114"/>
+      <c r="O15" s="114"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="114"/>
+      <c r="R15" s="114"/>
+      <c r="S15" s="114"/>
+      <c r="T15" s="114"/>
+      <c r="U15" s="114"/>
+      <c r="V15" s="114"/>
+      <c r="W15" s="114"/>
+      <c r="X15" s="114"/>
+      <c r="Y15" s="114"/>
+      <c r="Z15" s="114"/>
+      <c r="AA15" s="114"/>
+      <c r="AB15" s="114"/>
+      <c r="AC15" s="114"/>
+      <c r="AD15" s="114"/>
+      <c r="AE15" s="114"/>
+      <c r="AF15" s="114"/>
+      <c r="AG15" s="114"/>
+      <c r="AH15" s="114"/>
+      <c r="AI15" s="114"/>
+      <c r="AJ15" s="114"/>
+      <c r="AK15" s="116"/>
+      <c r="AL15" s="116"/>
+      <c r="AM15" s="116"/>
+      <c r="AN15" s="117"/>
+      <c r="AO15" s="113"/>
+      <c r="AP15" s="114"/>
+      <c r="AQ15" s="114"/>
+      <c r="AR15" s="114"/>
+      <c r="AS15" s="114"/>
+      <c r="AT15" s="114"/>
+      <c r="AU15" s="114"/>
+      <c r="AV15" s="114"/>
+      <c r="AW15" s="114"/>
+      <c r="AX15" s="114"/>
+      <c r="AY15" s="114"/>
+      <c r="AZ15" s="114"/>
+      <c r="BA15" s="114"/>
+      <c r="BB15" s="114"/>
+      <c r="BC15" s="115"/>
     </row>
     <row r="16" spans="1:55" ht="15" customHeight="1">
       <c r="A16" s="37"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="48"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="48"/>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="48"/>
-      <c r="R16" s="48"/>
-      <c r="S16" s="48"/>
-      <c r="T16" s="48"/>
-      <c r="U16" s="48"/>
-      <c r="V16" s="48"/>
-      <c r="W16" s="48"/>
-      <c r="X16" s="48"/>
-      <c r="Y16" s="48"/>
-      <c r="Z16" s="48"/>
-      <c r="AA16" s="48"/>
-      <c r="AB16" s="48"/>
-      <c r="AC16" s="48"/>
-      <c r="AD16" s="48"/>
-      <c r="AE16" s="48"/>
-      <c r="AF16" s="48"/>
-      <c r="AG16" s="48"/>
-      <c r="AH16" s="48"/>
-      <c r="AI16" s="48"/>
-      <c r="AJ16" s="48"/>
-      <c r="AK16" s="53"/>
-      <c r="AL16" s="53"/>
-      <c r="AM16" s="53"/>
-      <c r="AN16" s="54"/>
-      <c r="AO16" s="47"/>
-      <c r="AP16" s="48"/>
-      <c r="AQ16" s="48"/>
-      <c r="AR16" s="48"/>
-      <c r="AS16" s="48"/>
-      <c r="AT16" s="48"/>
-      <c r="AU16" s="48"/>
-      <c r="AV16" s="48"/>
-      <c r="AW16" s="48"/>
-      <c r="AX16" s="48"/>
-      <c r="AY16" s="48"/>
-      <c r="AZ16" s="48"/>
-      <c r="BA16" s="48"/>
-      <c r="BB16" s="48"/>
-      <c r="BC16" s="49"/>
+      <c r="B16" s="110"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="114"/>
+      <c r="L16" s="114"/>
+      <c r="M16" s="114"/>
+      <c r="N16" s="114"/>
+      <c r="O16" s="114"/>
+      <c r="P16" s="114"/>
+      <c r="Q16" s="114"/>
+      <c r="R16" s="114"/>
+      <c r="S16" s="114"/>
+      <c r="T16" s="114"/>
+      <c r="U16" s="114"/>
+      <c r="V16" s="114"/>
+      <c r="W16" s="114"/>
+      <c r="X16" s="114"/>
+      <c r="Y16" s="114"/>
+      <c r="Z16" s="114"/>
+      <c r="AA16" s="114"/>
+      <c r="AB16" s="114"/>
+      <c r="AC16" s="114"/>
+      <c r="AD16" s="114"/>
+      <c r="AE16" s="114"/>
+      <c r="AF16" s="114"/>
+      <c r="AG16" s="114"/>
+      <c r="AH16" s="114"/>
+      <c r="AI16" s="114"/>
+      <c r="AJ16" s="114"/>
+      <c r="AK16" s="116"/>
+      <c r="AL16" s="116"/>
+      <c r="AM16" s="116"/>
+      <c r="AN16" s="117"/>
+      <c r="AO16" s="113"/>
+      <c r="AP16" s="114"/>
+      <c r="AQ16" s="114"/>
+      <c r="AR16" s="114"/>
+      <c r="AS16" s="114"/>
+      <c r="AT16" s="114"/>
+      <c r="AU16" s="114"/>
+      <c r="AV16" s="114"/>
+      <c r="AW16" s="114"/>
+      <c r="AX16" s="114"/>
+      <c r="AY16" s="114"/>
+      <c r="AZ16" s="114"/>
+      <c r="BA16" s="114"/>
+      <c r="BB16" s="114"/>
+      <c r="BC16" s="115"/>
     </row>
     <row r="17" spans="1:55" ht="15" customHeight="1">
       <c r="A17" s="37"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="48"/>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="48"/>
-      <c r="R17" s="48"/>
-      <c r="S17" s="48"/>
-      <c r="T17" s="48"/>
-      <c r="U17" s="48"/>
-      <c r="V17" s="48"/>
-      <c r="W17" s="48"/>
-      <c r="X17" s="48"/>
-      <c r="Y17" s="48"/>
-      <c r="Z17" s="48"/>
-      <c r="AA17" s="48"/>
-      <c r="AB17" s="48"/>
-      <c r="AC17" s="48"/>
-      <c r="AD17" s="48"/>
-      <c r="AE17" s="48"/>
-      <c r="AF17" s="48"/>
-      <c r="AG17" s="48"/>
-      <c r="AH17" s="48"/>
-      <c r="AI17" s="48"/>
-      <c r="AJ17" s="48"/>
-      <c r="AK17" s="53"/>
-      <c r="AL17" s="53"/>
-      <c r="AM17" s="53"/>
-      <c r="AN17" s="54"/>
-      <c r="AO17" s="47"/>
-      <c r="AP17" s="48"/>
-      <c r="AQ17" s="48"/>
-      <c r="AR17" s="48"/>
-      <c r="AS17" s="48"/>
-      <c r="AT17" s="48"/>
-      <c r="AU17" s="48"/>
-      <c r="AV17" s="48"/>
-      <c r="AW17" s="48"/>
-      <c r="AX17" s="48"/>
-      <c r="AY17" s="48"/>
-      <c r="AZ17" s="48"/>
-      <c r="BA17" s="48"/>
-      <c r="BB17" s="48"/>
-      <c r="BC17" s="49"/>
+      <c r="B17" s="110"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="111"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="114"/>
+      <c r="L17" s="114"/>
+      <c r="M17" s="114"/>
+      <c r="N17" s="114"/>
+      <c r="O17" s="114"/>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="114"/>
+      <c r="T17" s="114"/>
+      <c r="U17" s="114"/>
+      <c r="V17" s="114"/>
+      <c r="W17" s="114"/>
+      <c r="X17" s="114"/>
+      <c r="Y17" s="114"/>
+      <c r="Z17" s="114"/>
+      <c r="AA17" s="114"/>
+      <c r="AB17" s="114"/>
+      <c r="AC17" s="114"/>
+      <c r="AD17" s="114"/>
+      <c r="AE17" s="114"/>
+      <c r="AF17" s="114"/>
+      <c r="AG17" s="114"/>
+      <c r="AH17" s="114"/>
+      <c r="AI17" s="114"/>
+      <c r="AJ17" s="114"/>
+      <c r="AK17" s="116"/>
+      <c r="AL17" s="116"/>
+      <c r="AM17" s="116"/>
+      <c r="AN17" s="117"/>
+      <c r="AO17" s="113"/>
+      <c r="AP17" s="114"/>
+      <c r="AQ17" s="114"/>
+      <c r="AR17" s="114"/>
+      <c r="AS17" s="114"/>
+      <c r="AT17" s="114"/>
+      <c r="AU17" s="114"/>
+      <c r="AV17" s="114"/>
+      <c r="AW17" s="114"/>
+      <c r="AX17" s="114"/>
+      <c r="AY17" s="114"/>
+      <c r="AZ17" s="114"/>
+      <c r="BA17" s="114"/>
+      <c r="BB17" s="114"/>
+      <c r="BC17" s="115"/>
     </row>
     <row r="18" spans="1:55" ht="15" customHeight="1">
       <c r="A18" s="36"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="48"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="48"/>
-      <c r="O18" s="48"/>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="48"/>
-      <c r="R18" s="48"/>
-      <c r="S18" s="48"/>
-      <c r="T18" s="48"/>
-      <c r="U18" s="48"/>
-      <c r="V18" s="48"/>
-      <c r="W18" s="48"/>
-      <c r="X18" s="48"/>
-      <c r="Y18" s="48"/>
-      <c r="Z18" s="48"/>
-      <c r="AA18" s="48"/>
-      <c r="AB18" s="48"/>
-      <c r="AC18" s="48"/>
-      <c r="AD18" s="48"/>
-      <c r="AE18" s="48"/>
-      <c r="AF18" s="48"/>
-      <c r="AG18" s="48"/>
-      <c r="AH18" s="48"/>
-      <c r="AI18" s="48"/>
-      <c r="AJ18" s="48"/>
-      <c r="AK18" s="53"/>
-      <c r="AL18" s="53"/>
-      <c r="AM18" s="53"/>
-      <c r="AN18" s="54"/>
-      <c r="AO18" s="47"/>
-      <c r="AP18" s="48"/>
-      <c r="AQ18" s="48"/>
-      <c r="AR18" s="48"/>
-      <c r="AS18" s="48"/>
-      <c r="AT18" s="48"/>
-      <c r="AU18" s="48"/>
-      <c r="AV18" s="48"/>
-      <c r="AW18" s="48"/>
-      <c r="AX18" s="48"/>
-      <c r="AY18" s="48"/>
-      <c r="AZ18" s="48"/>
-      <c r="BA18" s="48"/>
-      <c r="BB18" s="48"/>
-      <c r="BC18" s="49"/>
+      <c r="B18" s="110"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="110"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="114"/>
+      <c r="L18" s="114"/>
+      <c r="M18" s="114"/>
+      <c r="N18" s="114"/>
+      <c r="O18" s="114"/>
+      <c r="P18" s="114"/>
+      <c r="Q18" s="114"/>
+      <c r="R18" s="114"/>
+      <c r="S18" s="114"/>
+      <c r="T18" s="114"/>
+      <c r="U18" s="114"/>
+      <c r="V18" s="114"/>
+      <c r="W18" s="114"/>
+      <c r="X18" s="114"/>
+      <c r="Y18" s="114"/>
+      <c r="Z18" s="114"/>
+      <c r="AA18" s="114"/>
+      <c r="AB18" s="114"/>
+      <c r="AC18" s="114"/>
+      <c r="AD18" s="114"/>
+      <c r="AE18" s="114"/>
+      <c r="AF18" s="114"/>
+      <c r="AG18" s="114"/>
+      <c r="AH18" s="114"/>
+      <c r="AI18" s="114"/>
+      <c r="AJ18" s="114"/>
+      <c r="AK18" s="116"/>
+      <c r="AL18" s="116"/>
+      <c r="AM18" s="116"/>
+      <c r="AN18" s="117"/>
+      <c r="AO18" s="113"/>
+      <c r="AP18" s="114"/>
+      <c r="AQ18" s="114"/>
+      <c r="AR18" s="114"/>
+      <c r="AS18" s="114"/>
+      <c r="AT18" s="114"/>
+      <c r="AU18" s="114"/>
+      <c r="AV18" s="114"/>
+      <c r="AW18" s="114"/>
+      <c r="AX18" s="114"/>
+      <c r="AY18" s="114"/>
+      <c r="AZ18" s="114"/>
+      <c r="BA18" s="114"/>
+      <c r="BB18" s="114"/>
+      <c r="BC18" s="115"/>
     </row>
     <row r="19" spans="1:55" ht="15" customHeight="1">
       <c r="A19" s="36"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="53"/>
-      <c r="AL19" s="53"/>
-      <c r="AM19" s="53"/>
-      <c r="AN19" s="54"/>
-      <c r="AO19" s="47"/>
-      <c r="AP19" s="48"/>
-      <c r="AQ19" s="48"/>
-      <c r="AR19" s="48"/>
-      <c r="AS19" s="48"/>
-      <c r="AT19" s="48"/>
-      <c r="AU19" s="48"/>
-      <c r="AV19" s="48"/>
-      <c r="AW19" s="48"/>
-      <c r="AX19" s="48"/>
-      <c r="AY19" s="48"/>
-      <c r="AZ19" s="48"/>
-      <c r="BA19" s="48"/>
-      <c r="BB19" s="48"/>
-      <c r="BC19" s="49"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="114"/>
+      <c r="L19" s="114"/>
+      <c r="M19" s="114"/>
+      <c r="N19" s="114"/>
+      <c r="O19" s="114"/>
+      <c r="P19" s="114"/>
+      <c r="Q19" s="114"/>
+      <c r="R19" s="114"/>
+      <c r="S19" s="114"/>
+      <c r="T19" s="114"/>
+      <c r="U19" s="114"/>
+      <c r="V19" s="114"/>
+      <c r="W19" s="114"/>
+      <c r="X19" s="114"/>
+      <c r="Y19" s="114"/>
+      <c r="Z19" s="114"/>
+      <c r="AA19" s="114"/>
+      <c r="AB19" s="114"/>
+      <c r="AC19" s="114"/>
+      <c r="AD19" s="114"/>
+      <c r="AE19" s="114"/>
+      <c r="AF19" s="114"/>
+      <c r="AG19" s="114"/>
+      <c r="AH19" s="114"/>
+      <c r="AI19" s="114"/>
+      <c r="AJ19" s="114"/>
+      <c r="AK19" s="116"/>
+      <c r="AL19" s="116"/>
+      <c r="AM19" s="116"/>
+      <c r="AN19" s="117"/>
+      <c r="AO19" s="113"/>
+      <c r="AP19" s="114"/>
+      <c r="AQ19" s="114"/>
+      <c r="AR19" s="114"/>
+      <c r="AS19" s="114"/>
+      <c r="AT19" s="114"/>
+      <c r="AU19" s="114"/>
+      <c r="AV19" s="114"/>
+      <c r="AW19" s="114"/>
+      <c r="AX19" s="114"/>
+      <c r="AY19" s="114"/>
+      <c r="AZ19" s="114"/>
+      <c r="BA19" s="114"/>
+      <c r="BB19" s="114"/>
+      <c r="BC19" s="115"/>
     </row>
     <row r="20" spans="1:55" ht="15" customHeight="1">
       <c r="A20" s="36"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="48"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="48"/>
-      <c r="P20" s="48"/>
-      <c r="Q20" s="48"/>
-      <c r="R20" s="48"/>
-      <c r="S20" s="48"/>
-      <c r="T20" s="48"/>
-      <c r="U20" s="48"/>
-      <c r="V20" s="48"/>
-      <c r="W20" s="48"/>
-      <c r="X20" s="48"/>
-      <c r="Y20" s="48"/>
-      <c r="Z20" s="48"/>
-      <c r="AA20" s="48"/>
-      <c r="AB20" s="48"/>
-      <c r="AC20" s="48"/>
-      <c r="AD20" s="48"/>
-      <c r="AE20" s="48"/>
-      <c r="AF20" s="48"/>
-      <c r="AG20" s="48"/>
-      <c r="AH20" s="48"/>
-      <c r="AI20" s="48"/>
-      <c r="AJ20" s="48"/>
-      <c r="AK20" s="53"/>
-      <c r="AL20" s="53"/>
-      <c r="AM20" s="53"/>
-      <c r="AN20" s="54"/>
-      <c r="AO20" s="47"/>
-      <c r="AP20" s="48"/>
-      <c r="AQ20" s="48"/>
-      <c r="AR20" s="48"/>
-      <c r="AS20" s="48"/>
-      <c r="AT20" s="48"/>
-      <c r="AU20" s="48"/>
-      <c r="AV20" s="48"/>
-      <c r="AW20" s="48"/>
-      <c r="AX20" s="48"/>
-      <c r="AY20" s="48"/>
-      <c r="AZ20" s="48"/>
-      <c r="BA20" s="48"/>
-      <c r="BB20" s="48"/>
-      <c r="BC20" s="49"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="114"/>
+      <c r="L20" s="114"/>
+      <c r="M20" s="114"/>
+      <c r="N20" s="114"/>
+      <c r="O20" s="114"/>
+      <c r="P20" s="114"/>
+      <c r="Q20" s="114"/>
+      <c r="R20" s="114"/>
+      <c r="S20" s="114"/>
+      <c r="T20" s="114"/>
+      <c r="U20" s="114"/>
+      <c r="V20" s="114"/>
+      <c r="W20" s="114"/>
+      <c r="X20" s="114"/>
+      <c r="Y20" s="114"/>
+      <c r="Z20" s="114"/>
+      <c r="AA20" s="114"/>
+      <c r="AB20" s="114"/>
+      <c r="AC20" s="114"/>
+      <c r="AD20" s="114"/>
+      <c r="AE20" s="114"/>
+      <c r="AF20" s="114"/>
+      <c r="AG20" s="114"/>
+      <c r="AH20" s="114"/>
+      <c r="AI20" s="114"/>
+      <c r="AJ20" s="114"/>
+      <c r="AK20" s="116"/>
+      <c r="AL20" s="116"/>
+      <c r="AM20" s="116"/>
+      <c r="AN20" s="117"/>
+      <c r="AO20" s="113"/>
+      <c r="AP20" s="114"/>
+      <c r="AQ20" s="114"/>
+      <c r="AR20" s="114"/>
+      <c r="AS20" s="114"/>
+      <c r="AT20" s="114"/>
+      <c r="AU20" s="114"/>
+      <c r="AV20" s="114"/>
+      <c r="AW20" s="114"/>
+      <c r="AX20" s="114"/>
+      <c r="AY20" s="114"/>
+      <c r="AZ20" s="114"/>
+      <c r="BA20" s="114"/>
+      <c r="BB20" s="114"/>
+      <c r="BC20" s="115"/>
     </row>
     <row r="21" spans="1:55" ht="15" customHeight="1">
       <c r="A21" s="36"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="48"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="48"/>
-      <c r="M21" s="48"/>
-      <c r="N21" s="48"/>
-      <c r="O21" s="48"/>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="48"/>
-      <c r="R21" s="48"/>
-      <c r="S21" s="48"/>
-      <c r="T21" s="48"/>
-      <c r="U21" s="48"/>
-      <c r="V21" s="48"/>
-      <c r="W21" s="48"/>
-      <c r="X21" s="48"/>
-      <c r="Y21" s="48"/>
-      <c r="Z21" s="48"/>
-      <c r="AA21" s="48"/>
-      <c r="AB21" s="48"/>
-      <c r="AC21" s="48"/>
-      <c r="AD21" s="48"/>
-      <c r="AE21" s="48"/>
-      <c r="AF21" s="48"/>
-      <c r="AG21" s="48"/>
-      <c r="AH21" s="48"/>
-      <c r="AI21" s="48"/>
-      <c r="AJ21" s="48"/>
-      <c r="AK21" s="53"/>
-      <c r="AL21" s="53"/>
-      <c r="AM21" s="53"/>
-      <c r="AN21" s="54"/>
-      <c r="AO21" s="47"/>
-      <c r="AP21" s="48"/>
-      <c r="AQ21" s="48"/>
-      <c r="AR21" s="48"/>
-      <c r="AS21" s="48"/>
-      <c r="AT21" s="48"/>
-      <c r="AU21" s="48"/>
-      <c r="AV21" s="48"/>
-      <c r="AW21" s="48"/>
-      <c r="AX21" s="48"/>
-      <c r="AY21" s="48"/>
-      <c r="AZ21" s="48"/>
-      <c r="BA21" s="48"/>
-      <c r="BB21" s="48"/>
-      <c r="BC21" s="49"/>
+      <c r="B21" s="110"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="114"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="114"/>
+      <c r="N21" s="114"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="114"/>
+      <c r="Q21" s="114"/>
+      <c r="R21" s="114"/>
+      <c r="S21" s="114"/>
+      <c r="T21" s="114"/>
+      <c r="U21" s="114"/>
+      <c r="V21" s="114"/>
+      <c r="W21" s="114"/>
+      <c r="X21" s="114"/>
+      <c r="Y21" s="114"/>
+      <c r="Z21" s="114"/>
+      <c r="AA21" s="114"/>
+      <c r="AB21" s="114"/>
+      <c r="AC21" s="114"/>
+      <c r="AD21" s="114"/>
+      <c r="AE21" s="114"/>
+      <c r="AF21" s="114"/>
+      <c r="AG21" s="114"/>
+      <c r="AH21" s="114"/>
+      <c r="AI21" s="114"/>
+      <c r="AJ21" s="114"/>
+      <c r="AK21" s="116"/>
+      <c r="AL21" s="116"/>
+      <c r="AM21" s="116"/>
+      <c r="AN21" s="117"/>
+      <c r="AO21" s="113"/>
+      <c r="AP21" s="114"/>
+      <c r="AQ21" s="114"/>
+      <c r="AR21" s="114"/>
+      <c r="AS21" s="114"/>
+      <c r="AT21" s="114"/>
+      <c r="AU21" s="114"/>
+      <c r="AV21" s="114"/>
+      <c r="AW21" s="114"/>
+      <c r="AX21" s="114"/>
+      <c r="AY21" s="114"/>
+      <c r="AZ21" s="114"/>
+      <c r="BA21" s="114"/>
+      <c r="BB21" s="114"/>
+      <c r="BC21" s="115"/>
     </row>
     <row r="22" spans="1:55" ht="15" customHeight="1">
       <c r="A22" s="36"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="48"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="48"/>
-      <c r="O22" s="48"/>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="48"/>
-      <c r="R22" s="48"/>
-      <c r="S22" s="48"/>
-      <c r="T22" s="48"/>
-      <c r="U22" s="48"/>
-      <c r="V22" s="48"/>
-      <c r="W22" s="48"/>
-      <c r="X22" s="48"/>
-      <c r="Y22" s="48"/>
-      <c r="Z22" s="48"/>
-      <c r="AA22" s="48"/>
-      <c r="AB22" s="48"/>
-      <c r="AC22" s="48"/>
-      <c r="AD22" s="48"/>
-      <c r="AE22" s="48"/>
-      <c r="AF22" s="48"/>
-      <c r="AG22" s="48"/>
-      <c r="AH22" s="48"/>
-      <c r="AI22" s="48"/>
-      <c r="AJ22" s="48"/>
-      <c r="AK22" s="53"/>
-      <c r="AL22" s="53"/>
-      <c r="AM22" s="53"/>
-      <c r="AN22" s="54"/>
-      <c r="AO22" s="47"/>
-      <c r="AP22" s="48"/>
-      <c r="AQ22" s="48"/>
-      <c r="AR22" s="48"/>
-      <c r="AS22" s="48"/>
-      <c r="AT22" s="48"/>
-      <c r="AU22" s="48"/>
-      <c r="AV22" s="48"/>
-      <c r="AW22" s="48"/>
-      <c r="AX22" s="48"/>
-      <c r="AY22" s="48"/>
-      <c r="AZ22" s="48"/>
-      <c r="BA22" s="48"/>
-      <c r="BB22" s="48"/>
-      <c r="BC22" s="49"/>
+      <c r="B22" s="110"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="111"/>
+      <c r="H22" s="112"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="114"/>
+      <c r="L22" s="114"/>
+      <c r="M22" s="114"/>
+      <c r="N22" s="114"/>
+      <c r="O22" s="114"/>
+      <c r="P22" s="114"/>
+      <c r="Q22" s="114"/>
+      <c r="R22" s="114"/>
+      <c r="S22" s="114"/>
+      <c r="T22" s="114"/>
+      <c r="U22" s="114"/>
+      <c r="V22" s="114"/>
+      <c r="W22" s="114"/>
+      <c r="X22" s="114"/>
+      <c r="Y22" s="114"/>
+      <c r="Z22" s="114"/>
+      <c r="AA22" s="114"/>
+      <c r="AB22" s="114"/>
+      <c r="AC22" s="114"/>
+      <c r="AD22" s="114"/>
+      <c r="AE22" s="114"/>
+      <c r="AF22" s="114"/>
+      <c r="AG22" s="114"/>
+      <c r="AH22" s="114"/>
+      <c r="AI22" s="114"/>
+      <c r="AJ22" s="114"/>
+      <c r="AK22" s="116"/>
+      <c r="AL22" s="116"/>
+      <c r="AM22" s="116"/>
+      <c r="AN22" s="117"/>
+      <c r="AO22" s="113"/>
+      <c r="AP22" s="114"/>
+      <c r="AQ22" s="114"/>
+      <c r="AR22" s="114"/>
+      <c r="AS22" s="114"/>
+      <c r="AT22" s="114"/>
+      <c r="AU22" s="114"/>
+      <c r="AV22" s="114"/>
+      <c r="AW22" s="114"/>
+      <c r="AX22" s="114"/>
+      <c r="AY22" s="114"/>
+      <c r="AZ22" s="114"/>
+      <c r="BA22" s="114"/>
+      <c r="BB22" s="114"/>
+      <c r="BC22" s="115"/>
     </row>
     <row r="23" spans="1:55" ht="15" customHeight="1">
       <c r="A23" s="36"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="48"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="48"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="48"/>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="48"/>
-      <c r="R23" s="48"/>
-      <c r="S23" s="48"/>
-      <c r="T23" s="48"/>
-      <c r="U23" s="48"/>
-      <c r="V23" s="48"/>
-      <c r="W23" s="48"/>
-      <c r="X23" s="48"/>
-      <c r="Y23" s="48"/>
-      <c r="Z23" s="48"/>
-      <c r="AA23" s="48"/>
-      <c r="AB23" s="48"/>
-      <c r="AC23" s="48"/>
-      <c r="AD23" s="48"/>
-      <c r="AE23" s="48"/>
-      <c r="AF23" s="48"/>
-      <c r="AG23" s="48"/>
-      <c r="AH23" s="48"/>
-      <c r="AI23" s="48"/>
-      <c r="AJ23" s="48"/>
-      <c r="AK23" s="53"/>
-      <c r="AL23" s="53"/>
-      <c r="AM23" s="53"/>
-      <c r="AN23" s="54"/>
-      <c r="AO23" s="47"/>
-      <c r="AP23" s="48"/>
-      <c r="AQ23" s="48"/>
-      <c r="AR23" s="48"/>
-      <c r="AS23" s="48"/>
-      <c r="AT23" s="48"/>
-      <c r="AU23" s="48"/>
-      <c r="AV23" s="48"/>
-      <c r="AW23" s="48"/>
-      <c r="AX23" s="48"/>
-      <c r="AY23" s="48"/>
-      <c r="AZ23" s="48"/>
-      <c r="BA23" s="48"/>
-      <c r="BB23" s="48"/>
-      <c r="BC23" s="49"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="111"/>
+      <c r="F23" s="111"/>
+      <c r="G23" s="111"/>
+      <c r="H23" s="112"/>
+      <c r="I23" s="110"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="114"/>
+      <c r="L23" s="114"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="114"/>
+      <c r="O23" s="114"/>
+      <c r="P23" s="114"/>
+      <c r="Q23" s="114"/>
+      <c r="R23" s="114"/>
+      <c r="S23" s="114"/>
+      <c r="T23" s="114"/>
+      <c r="U23" s="114"/>
+      <c r="V23" s="114"/>
+      <c r="W23" s="114"/>
+      <c r="X23" s="114"/>
+      <c r="Y23" s="114"/>
+      <c r="Z23" s="114"/>
+      <c r="AA23" s="114"/>
+      <c r="AB23" s="114"/>
+      <c r="AC23" s="114"/>
+      <c r="AD23" s="114"/>
+      <c r="AE23" s="114"/>
+      <c r="AF23" s="114"/>
+      <c r="AG23" s="114"/>
+      <c r="AH23" s="114"/>
+      <c r="AI23" s="114"/>
+      <c r="AJ23" s="114"/>
+      <c r="AK23" s="116"/>
+      <c r="AL23" s="116"/>
+      <c r="AM23" s="116"/>
+      <c r="AN23" s="117"/>
+      <c r="AO23" s="113"/>
+      <c r="AP23" s="114"/>
+      <c r="AQ23" s="114"/>
+      <c r="AR23" s="114"/>
+      <c r="AS23" s="114"/>
+      <c r="AT23" s="114"/>
+      <c r="AU23" s="114"/>
+      <c r="AV23" s="114"/>
+      <c r="AW23" s="114"/>
+      <c r="AX23" s="114"/>
+      <c r="AY23" s="114"/>
+      <c r="AZ23" s="114"/>
+      <c r="BA23" s="114"/>
+      <c r="BB23" s="114"/>
+      <c r="BC23" s="115"/>
     </row>
     <row r="24" spans="1:55" ht="15" customHeight="1">
       <c r="A24" s="36"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="48"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="48"/>
-      <c r="R24" s="48"/>
-      <c r="S24" s="48"/>
-      <c r="T24" s="48"/>
-      <c r="U24" s="48"/>
-      <c r="V24" s="48"/>
-      <c r="W24" s="48"/>
-      <c r="X24" s="48"/>
-      <c r="Y24" s="48"/>
-      <c r="Z24" s="48"/>
-      <c r="AA24" s="48"/>
-      <c r="AB24" s="48"/>
-      <c r="AC24" s="48"/>
-      <c r="AD24" s="48"/>
-      <c r="AE24" s="48"/>
-      <c r="AF24" s="48"/>
-      <c r="AG24" s="48"/>
-      <c r="AH24" s="48"/>
-      <c r="AI24" s="48"/>
-      <c r="AJ24" s="48"/>
-      <c r="AK24" s="53"/>
-      <c r="AL24" s="53"/>
-      <c r="AM24" s="53"/>
-      <c r="AN24" s="54"/>
-      <c r="AO24" s="47"/>
-      <c r="AP24" s="48"/>
-      <c r="AQ24" s="48"/>
-      <c r="AR24" s="48"/>
-      <c r="AS24" s="48"/>
-      <c r="AT24" s="48"/>
-      <c r="AU24" s="48"/>
-      <c r="AV24" s="48"/>
-      <c r="AW24" s="48"/>
-      <c r="AX24" s="48"/>
-      <c r="AY24" s="48"/>
-      <c r="AZ24" s="48"/>
-      <c r="BA24" s="48"/>
-      <c r="BB24" s="48"/>
-      <c r="BC24" s="49"/>
+      <c r="B24" s="110"/>
+      <c r="C24" s="111"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="111"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="112"/>
+      <c r="I24" s="110"/>
+      <c r="J24" s="114"/>
+      <c r="K24" s="114"/>
+      <c r="L24" s="114"/>
+      <c r="M24" s="114"/>
+      <c r="N24" s="114"/>
+      <c r="O24" s="114"/>
+      <c r="P24" s="114"/>
+      <c r="Q24" s="114"/>
+      <c r="R24" s="114"/>
+      <c r="S24" s="114"/>
+      <c r="T24" s="114"/>
+      <c r="U24" s="114"/>
+      <c r="V24" s="114"/>
+      <c r="W24" s="114"/>
+      <c r="X24" s="114"/>
+      <c r="Y24" s="114"/>
+      <c r="Z24" s="114"/>
+      <c r="AA24" s="114"/>
+      <c r="AB24" s="114"/>
+      <c r="AC24" s="114"/>
+      <c r="AD24" s="114"/>
+      <c r="AE24" s="114"/>
+      <c r="AF24" s="114"/>
+      <c r="AG24" s="114"/>
+      <c r="AH24" s="114"/>
+      <c r="AI24" s="114"/>
+      <c r="AJ24" s="114"/>
+      <c r="AK24" s="116"/>
+      <c r="AL24" s="116"/>
+      <c r="AM24" s="116"/>
+      <c r="AN24" s="117"/>
+      <c r="AO24" s="113"/>
+      <c r="AP24" s="114"/>
+      <c r="AQ24" s="114"/>
+      <c r="AR24" s="114"/>
+      <c r="AS24" s="114"/>
+      <c r="AT24" s="114"/>
+      <c r="AU24" s="114"/>
+      <c r="AV24" s="114"/>
+      <c r="AW24" s="114"/>
+      <c r="AX24" s="114"/>
+      <c r="AY24" s="114"/>
+      <c r="AZ24" s="114"/>
+      <c r="BA24" s="114"/>
+      <c r="BB24" s="114"/>
+      <c r="BC24" s="115"/>
     </row>
     <row r="25" spans="1:55" ht="15" customHeight="1">
       <c r="A25" s="36"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="48"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="48"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="48"/>
-      <c r="R25" s="48"/>
-      <c r="S25" s="48"/>
-      <c r="T25" s="48"/>
-      <c r="U25" s="48"/>
-      <c r="V25" s="48"/>
-      <c r="W25" s="48"/>
-      <c r="X25" s="48"/>
-      <c r="Y25" s="48"/>
-      <c r="Z25" s="48"/>
-      <c r="AA25" s="48"/>
-      <c r="AB25" s="48"/>
-      <c r="AC25" s="48"/>
-      <c r="AD25" s="48"/>
-      <c r="AE25" s="48"/>
-      <c r="AF25" s="48"/>
-      <c r="AG25" s="48"/>
-      <c r="AH25" s="48"/>
-      <c r="AI25" s="48"/>
-      <c r="AJ25" s="48"/>
-      <c r="AK25" s="53"/>
-      <c r="AL25" s="53"/>
-      <c r="AM25" s="53"/>
-      <c r="AN25" s="54"/>
-      <c r="AO25" s="47"/>
-      <c r="AP25" s="48"/>
-      <c r="AQ25" s="48"/>
-      <c r="AR25" s="48"/>
-      <c r="AS25" s="48"/>
-      <c r="AT25" s="48"/>
-      <c r="AU25" s="48"/>
-      <c r="AV25" s="48"/>
-      <c r="AW25" s="48"/>
-      <c r="AX25" s="48"/>
-      <c r="AY25" s="48"/>
-      <c r="AZ25" s="48"/>
-      <c r="BA25" s="48"/>
-      <c r="BB25" s="48"/>
-      <c r="BC25" s="49"/>
+      <c r="B25" s="110"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="110"/>
+      <c r="J25" s="114"/>
+      <c r="K25" s="114"/>
+      <c r="L25" s="114"/>
+      <c r="M25" s="114"/>
+      <c r="N25" s="114"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="114"/>
+      <c r="Q25" s="114"/>
+      <c r="R25" s="114"/>
+      <c r="S25" s="114"/>
+      <c r="T25" s="114"/>
+      <c r="U25" s="114"/>
+      <c r="V25" s="114"/>
+      <c r="W25" s="114"/>
+      <c r="X25" s="114"/>
+      <c r="Y25" s="114"/>
+      <c r="Z25" s="114"/>
+      <c r="AA25" s="114"/>
+      <c r="AB25" s="114"/>
+      <c r="AC25" s="114"/>
+      <c r="AD25" s="114"/>
+      <c r="AE25" s="114"/>
+      <c r="AF25" s="114"/>
+      <c r="AG25" s="114"/>
+      <c r="AH25" s="114"/>
+      <c r="AI25" s="114"/>
+      <c r="AJ25" s="114"/>
+      <c r="AK25" s="116"/>
+      <c r="AL25" s="116"/>
+      <c r="AM25" s="116"/>
+      <c r="AN25" s="117"/>
+      <c r="AO25" s="113"/>
+      <c r="AP25" s="114"/>
+      <c r="AQ25" s="114"/>
+      <c r="AR25" s="114"/>
+      <c r="AS25" s="114"/>
+      <c r="AT25" s="114"/>
+      <c r="AU25" s="114"/>
+      <c r="AV25" s="114"/>
+      <c r="AW25" s="114"/>
+      <c r="AX25" s="114"/>
+      <c r="AY25" s="114"/>
+      <c r="AZ25" s="114"/>
+      <c r="BA25" s="114"/>
+      <c r="BB25" s="114"/>
+      <c r="BC25" s="115"/>
     </row>
     <row r="26" spans="1:55" ht="15" customHeight="1">
       <c r="A26" s="36"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="48"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="48"/>
-      <c r="R26" s="48"/>
-      <c r="S26" s="48"/>
-      <c r="T26" s="48"/>
-      <c r="U26" s="48"/>
-      <c r="V26" s="48"/>
-      <c r="W26" s="48"/>
-      <c r="X26" s="48"/>
-      <c r="Y26" s="48"/>
-      <c r="Z26" s="48"/>
-      <c r="AA26" s="48"/>
-      <c r="AB26" s="48"/>
-      <c r="AC26" s="48"/>
-      <c r="AD26" s="48"/>
-      <c r="AE26" s="48"/>
-      <c r="AF26" s="48"/>
-      <c r="AG26" s="48"/>
-      <c r="AH26" s="48"/>
-      <c r="AI26" s="48"/>
-      <c r="AJ26" s="48"/>
-      <c r="AK26" s="53"/>
-      <c r="AL26" s="53"/>
-      <c r="AM26" s="53"/>
-      <c r="AN26" s="54"/>
-      <c r="AO26" s="47"/>
-      <c r="AP26" s="48"/>
-      <c r="AQ26" s="48"/>
-      <c r="AR26" s="48"/>
-      <c r="AS26" s="48"/>
-      <c r="AT26" s="48"/>
-      <c r="AU26" s="48"/>
-      <c r="AV26" s="48"/>
-      <c r="AW26" s="48"/>
-      <c r="AX26" s="48"/>
-      <c r="AY26" s="48"/>
-      <c r="AZ26" s="48"/>
-      <c r="BA26" s="48"/>
-      <c r="BB26" s="48"/>
-      <c r="BC26" s="49"/>
+      <c r="B26" s="110"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="110"/>
+      <c r="J26" s="114"/>
+      <c r="K26" s="114"/>
+      <c r="L26" s="114"/>
+      <c r="M26" s="114"/>
+      <c r="N26" s="114"/>
+      <c r="O26" s="114"/>
+      <c r="P26" s="114"/>
+      <c r="Q26" s="114"/>
+      <c r="R26" s="114"/>
+      <c r="S26" s="114"/>
+      <c r="T26" s="114"/>
+      <c r="U26" s="114"/>
+      <c r="V26" s="114"/>
+      <c r="W26" s="114"/>
+      <c r="X26" s="114"/>
+      <c r="Y26" s="114"/>
+      <c r="Z26" s="114"/>
+      <c r="AA26" s="114"/>
+      <c r="AB26" s="114"/>
+      <c r="AC26" s="114"/>
+      <c r="AD26" s="114"/>
+      <c r="AE26" s="114"/>
+      <c r="AF26" s="114"/>
+      <c r="AG26" s="114"/>
+      <c r="AH26" s="114"/>
+      <c r="AI26" s="114"/>
+      <c r="AJ26" s="114"/>
+      <c r="AK26" s="116"/>
+      <c r="AL26" s="116"/>
+      <c r="AM26" s="116"/>
+      <c r="AN26" s="117"/>
+      <c r="AO26" s="113"/>
+      <c r="AP26" s="114"/>
+      <c r="AQ26" s="114"/>
+      <c r="AR26" s="114"/>
+      <c r="AS26" s="114"/>
+      <c r="AT26" s="114"/>
+      <c r="AU26" s="114"/>
+      <c r="AV26" s="114"/>
+      <c r="AW26" s="114"/>
+      <c r="AX26" s="114"/>
+      <c r="AY26" s="114"/>
+      <c r="AZ26" s="114"/>
+      <c r="BA26" s="114"/>
+      <c r="BB26" s="114"/>
+      <c r="BC26" s="115"/>
     </row>
     <row r="27" spans="1:55" ht="15" customHeight="1">
       <c r="A27" s="36"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="48"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="48"/>
-      <c r="R27" s="48"/>
-      <c r="S27" s="48"/>
-      <c r="T27" s="48"/>
-      <c r="U27" s="48"/>
-      <c r="V27" s="48"/>
-      <c r="W27" s="48"/>
-      <c r="X27" s="48"/>
-      <c r="Y27" s="48"/>
-      <c r="Z27" s="48"/>
-      <c r="AA27" s="48"/>
-      <c r="AB27" s="48"/>
-      <c r="AC27" s="48"/>
-      <c r="AD27" s="48"/>
-      <c r="AE27" s="48"/>
-      <c r="AF27" s="48"/>
-      <c r="AG27" s="48"/>
-      <c r="AH27" s="48"/>
-      <c r="AI27" s="48"/>
-      <c r="AJ27" s="48"/>
-      <c r="AK27" s="53"/>
-      <c r="AL27" s="53"/>
-      <c r="AM27" s="53"/>
-      <c r="AN27" s="54"/>
-      <c r="AO27" s="47"/>
-      <c r="AP27" s="48"/>
-      <c r="AQ27" s="48"/>
-      <c r="AR27" s="48"/>
-      <c r="AS27" s="48"/>
-      <c r="AT27" s="48"/>
-      <c r="AU27" s="48"/>
-      <c r="AV27" s="48"/>
-      <c r="AW27" s="48"/>
-      <c r="AX27" s="48"/>
-      <c r="AY27" s="48"/>
-      <c r="AZ27" s="48"/>
-      <c r="BA27" s="48"/>
-      <c r="BB27" s="48"/>
-      <c r="BC27" s="49"/>
+      <c r="B27" s="110"/>
+      <c r="C27" s="111"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="111"/>
+      <c r="F27" s="111"/>
+      <c r="G27" s="111"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="110"/>
+      <c r="J27" s="114"/>
+      <c r="K27" s="114"/>
+      <c r="L27" s="114"/>
+      <c r="M27" s="114"/>
+      <c r="N27" s="114"/>
+      <c r="O27" s="114"/>
+      <c r="P27" s="114"/>
+      <c r="Q27" s="114"/>
+      <c r="R27" s="114"/>
+      <c r="S27" s="114"/>
+      <c r="T27" s="114"/>
+      <c r="U27" s="114"/>
+      <c r="V27" s="114"/>
+      <c r="W27" s="114"/>
+      <c r="X27" s="114"/>
+      <c r="Y27" s="114"/>
+      <c r="Z27" s="114"/>
+      <c r="AA27" s="114"/>
+      <c r="AB27" s="114"/>
+      <c r="AC27" s="114"/>
+      <c r="AD27" s="114"/>
+      <c r="AE27" s="114"/>
+      <c r="AF27" s="114"/>
+      <c r="AG27" s="114"/>
+      <c r="AH27" s="114"/>
+      <c r="AI27" s="114"/>
+      <c r="AJ27" s="114"/>
+      <c r="AK27" s="116"/>
+      <c r="AL27" s="116"/>
+      <c r="AM27" s="116"/>
+      <c r="AN27" s="117"/>
+      <c r="AO27" s="113"/>
+      <c r="AP27" s="114"/>
+      <c r="AQ27" s="114"/>
+      <c r="AR27" s="114"/>
+      <c r="AS27" s="114"/>
+      <c r="AT27" s="114"/>
+      <c r="AU27" s="114"/>
+      <c r="AV27" s="114"/>
+      <c r="AW27" s="114"/>
+      <c r="AX27" s="114"/>
+      <c r="AY27" s="114"/>
+      <c r="AZ27" s="114"/>
+      <c r="BA27" s="114"/>
+      <c r="BB27" s="114"/>
+      <c r="BC27" s="115"/>
     </row>
     <row r="28" spans="1:55" ht="15" customHeight="1">
       <c r="A28" s="36"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="48"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="48"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="48"/>
-      <c r="R28" s="48"/>
-      <c r="S28" s="48"/>
-      <c r="T28" s="48"/>
-      <c r="U28" s="48"/>
-      <c r="V28" s="48"/>
-      <c r="W28" s="48"/>
-      <c r="X28" s="48"/>
-      <c r="Y28" s="48"/>
-      <c r="Z28" s="48"/>
-      <c r="AA28" s="48"/>
-      <c r="AB28" s="48"/>
-      <c r="AC28" s="48"/>
-      <c r="AD28" s="48"/>
-      <c r="AE28" s="48"/>
-      <c r="AF28" s="48"/>
-      <c r="AG28" s="48"/>
-      <c r="AH28" s="48"/>
-      <c r="AI28" s="48"/>
-      <c r="AJ28" s="48"/>
-      <c r="AK28" s="53"/>
-      <c r="AL28" s="53"/>
-      <c r="AM28" s="53"/>
-      <c r="AN28" s="54"/>
-      <c r="AO28" s="47"/>
-      <c r="AP28" s="48"/>
-      <c r="AQ28" s="48"/>
-      <c r="AR28" s="48"/>
-      <c r="AS28" s="48"/>
-      <c r="AT28" s="48"/>
-      <c r="AU28" s="48"/>
-      <c r="AV28" s="48"/>
-      <c r="AW28" s="48"/>
-      <c r="AX28" s="48"/>
-      <c r="AY28" s="48"/>
-      <c r="AZ28" s="48"/>
-      <c r="BA28" s="48"/>
-      <c r="BB28" s="48"/>
-      <c r="BC28" s="49"/>
+      <c r="B28" s="110"/>
+      <c r="C28" s="111"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="111"/>
+      <c r="H28" s="112"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="114"/>
+      <c r="L28" s="114"/>
+      <c r="M28" s="114"/>
+      <c r="N28" s="114"/>
+      <c r="O28" s="114"/>
+      <c r="P28" s="114"/>
+      <c r="Q28" s="114"/>
+      <c r="R28" s="114"/>
+      <c r="S28" s="114"/>
+      <c r="T28" s="114"/>
+      <c r="U28" s="114"/>
+      <c r="V28" s="114"/>
+      <c r="W28" s="114"/>
+      <c r="X28" s="114"/>
+      <c r="Y28" s="114"/>
+      <c r="Z28" s="114"/>
+      <c r="AA28" s="114"/>
+      <c r="AB28" s="114"/>
+      <c r="AC28" s="114"/>
+      <c r="AD28" s="114"/>
+      <c r="AE28" s="114"/>
+      <c r="AF28" s="114"/>
+      <c r="AG28" s="114"/>
+      <c r="AH28" s="114"/>
+      <c r="AI28" s="114"/>
+      <c r="AJ28" s="114"/>
+      <c r="AK28" s="116"/>
+      <c r="AL28" s="116"/>
+      <c r="AM28" s="116"/>
+      <c r="AN28" s="117"/>
+      <c r="AO28" s="113"/>
+      <c r="AP28" s="114"/>
+      <c r="AQ28" s="114"/>
+      <c r="AR28" s="114"/>
+      <c r="AS28" s="114"/>
+      <c r="AT28" s="114"/>
+      <c r="AU28" s="114"/>
+      <c r="AV28" s="114"/>
+      <c r="AW28" s="114"/>
+      <c r="AX28" s="114"/>
+      <c r="AY28" s="114"/>
+      <c r="AZ28" s="114"/>
+      <c r="BA28" s="114"/>
+      <c r="BB28" s="114"/>
+      <c r="BC28" s="115"/>
     </row>
     <row r="29" spans="1:55" ht="15" customHeight="1">
       <c r="A29" s="36"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="48"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="48"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="48"/>
-      <c r="U29" s="48"/>
-      <c r="V29" s="48"/>
-      <c r="W29" s="48"/>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="48"/>
-      <c r="Z29" s="48"/>
-      <c r="AA29" s="48"/>
-      <c r="AB29" s="48"/>
-      <c r="AC29" s="48"/>
-      <c r="AD29" s="48"/>
-      <c r="AE29" s="48"/>
-      <c r="AF29" s="48"/>
-      <c r="AG29" s="48"/>
-      <c r="AH29" s="48"/>
-      <c r="AI29" s="48"/>
-      <c r="AJ29" s="48"/>
-      <c r="AK29" s="53"/>
-      <c r="AL29" s="53"/>
-      <c r="AM29" s="53"/>
-      <c r="AN29" s="54"/>
-      <c r="AO29" s="47"/>
-      <c r="AP29" s="48"/>
-      <c r="AQ29" s="48"/>
-      <c r="AR29" s="48"/>
-      <c r="AS29" s="48"/>
-      <c r="AT29" s="48"/>
-      <c r="AU29" s="48"/>
-      <c r="AV29" s="48"/>
-      <c r="AW29" s="48"/>
-      <c r="AX29" s="48"/>
-      <c r="AY29" s="48"/>
-      <c r="AZ29" s="48"/>
-      <c r="BA29" s="48"/>
-      <c r="BB29" s="48"/>
-      <c r="BC29" s="49"/>
+      <c r="B29" s="110"/>
+      <c r="C29" s="111"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="111"/>
+      <c r="F29" s="111"/>
+      <c r="G29" s="111"/>
+      <c r="H29" s="112"/>
+      <c r="I29" s="110"/>
+      <c r="J29" s="114"/>
+      <c r="K29" s="114"/>
+      <c r="L29" s="114"/>
+      <c r="M29" s="114"/>
+      <c r="N29" s="114"/>
+      <c r="O29" s="114"/>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="114"/>
+      <c r="R29" s="114"/>
+      <c r="S29" s="114"/>
+      <c r="T29" s="114"/>
+      <c r="U29" s="114"/>
+      <c r="V29" s="114"/>
+      <c r="W29" s="114"/>
+      <c r="X29" s="114"/>
+      <c r="Y29" s="114"/>
+      <c r="Z29" s="114"/>
+      <c r="AA29" s="114"/>
+      <c r="AB29" s="114"/>
+      <c r="AC29" s="114"/>
+      <c r="AD29" s="114"/>
+      <c r="AE29" s="114"/>
+      <c r="AF29" s="114"/>
+      <c r="AG29" s="114"/>
+      <c r="AH29" s="114"/>
+      <c r="AI29" s="114"/>
+      <c r="AJ29" s="114"/>
+      <c r="AK29" s="116"/>
+      <c r="AL29" s="116"/>
+      <c r="AM29" s="116"/>
+      <c r="AN29" s="117"/>
+      <c r="AO29" s="113"/>
+      <c r="AP29" s="114"/>
+      <c r="AQ29" s="114"/>
+      <c r="AR29" s="114"/>
+      <c r="AS29" s="114"/>
+      <c r="AT29" s="114"/>
+      <c r="AU29" s="114"/>
+      <c r="AV29" s="114"/>
+      <c r="AW29" s="114"/>
+      <c r="AX29" s="114"/>
+      <c r="AY29" s="114"/>
+      <c r="AZ29" s="114"/>
+      <c r="BA29" s="114"/>
+      <c r="BB29" s="114"/>
+      <c r="BC29" s="115"/>
     </row>
     <row r="30" spans="1:55" ht="15" customHeight="1">
       <c r="A30" s="36"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="48"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="48"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="48"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="48"/>
-      <c r="R30" s="48"/>
-      <c r="S30" s="48"/>
-      <c r="T30" s="48"/>
-      <c r="U30" s="48"/>
-      <c r="V30" s="48"/>
-      <c r="W30" s="48"/>
-      <c r="X30" s="48"/>
-      <c r="Y30" s="48"/>
-      <c r="Z30" s="48"/>
-      <c r="AA30" s="48"/>
-      <c r="AB30" s="48"/>
-      <c r="AC30" s="48"/>
-      <c r="AD30" s="48"/>
-      <c r="AE30" s="48"/>
-      <c r="AF30" s="48"/>
-      <c r="AG30" s="48"/>
-      <c r="AH30" s="48"/>
-      <c r="AI30" s="48"/>
-      <c r="AJ30" s="48"/>
-      <c r="AK30" s="53"/>
-      <c r="AL30" s="53"/>
-      <c r="AM30" s="53"/>
-      <c r="AN30" s="54"/>
-      <c r="AO30" s="47"/>
-      <c r="AP30" s="48"/>
-      <c r="AQ30" s="48"/>
-      <c r="AR30" s="48"/>
-      <c r="AS30" s="48"/>
-      <c r="AT30" s="48"/>
-      <c r="AU30" s="48"/>
-      <c r="AV30" s="48"/>
-      <c r="AW30" s="48"/>
-      <c r="AX30" s="48"/>
-      <c r="AY30" s="48"/>
-      <c r="AZ30" s="48"/>
-      <c r="BA30" s="48"/>
-      <c r="BB30" s="48"/>
-      <c r="BC30" s="49"/>
+      <c r="B30" s="110"/>
+      <c r="C30" s="111"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="111"/>
+      <c r="F30" s="111"/>
+      <c r="G30" s="111"/>
+      <c r="H30" s="112"/>
+      <c r="I30" s="110"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="114"/>
+      <c r="L30" s="114"/>
+      <c r="M30" s="114"/>
+      <c r="N30" s="114"/>
+      <c r="O30" s="114"/>
+      <c r="P30" s="114"/>
+      <c r="Q30" s="114"/>
+      <c r="R30" s="114"/>
+      <c r="S30" s="114"/>
+      <c r="T30" s="114"/>
+      <c r="U30" s="114"/>
+      <c r="V30" s="114"/>
+      <c r="W30" s="114"/>
+      <c r="X30" s="114"/>
+      <c r="Y30" s="114"/>
+      <c r="Z30" s="114"/>
+      <c r="AA30" s="114"/>
+      <c r="AB30" s="114"/>
+      <c r="AC30" s="114"/>
+      <c r="AD30" s="114"/>
+      <c r="AE30" s="114"/>
+      <c r="AF30" s="114"/>
+      <c r="AG30" s="114"/>
+      <c r="AH30" s="114"/>
+      <c r="AI30" s="114"/>
+      <c r="AJ30" s="114"/>
+      <c r="AK30" s="116"/>
+      <c r="AL30" s="116"/>
+      <c r="AM30" s="116"/>
+      <c r="AN30" s="117"/>
+      <c r="AO30" s="113"/>
+      <c r="AP30" s="114"/>
+      <c r="AQ30" s="114"/>
+      <c r="AR30" s="114"/>
+      <c r="AS30" s="114"/>
+      <c r="AT30" s="114"/>
+      <c r="AU30" s="114"/>
+      <c r="AV30" s="114"/>
+      <c r="AW30" s="114"/>
+      <c r="AX30" s="114"/>
+      <c r="AY30" s="114"/>
+      <c r="AZ30" s="114"/>
+      <c r="BA30" s="114"/>
+      <c r="BB30" s="114"/>
+      <c r="BC30" s="115"/>
     </row>
     <row r="31" spans="1:55" ht="15" customHeight="1">
       <c r="A31" s="36"/>
-      <c r="B31" s="50"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="48"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="48"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="48"/>
-      <c r="O31" s="48"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="48"/>
-      <c r="R31" s="48"/>
-      <c r="S31" s="48"/>
-      <c r="T31" s="48"/>
-      <c r="U31" s="48"/>
-      <c r="V31" s="48"/>
-      <c r="W31" s="48"/>
-      <c r="X31" s="48"/>
-      <c r="Y31" s="48"/>
-      <c r="Z31" s="48"/>
-      <c r="AA31" s="48"/>
-      <c r="AB31" s="48"/>
-      <c r="AC31" s="48"/>
-      <c r="AD31" s="48"/>
-      <c r="AE31" s="48"/>
-      <c r="AF31" s="48"/>
-      <c r="AG31" s="48"/>
-      <c r="AH31" s="48"/>
-      <c r="AI31" s="48"/>
-      <c r="AJ31" s="48"/>
-      <c r="AK31" s="53"/>
-      <c r="AL31" s="53"/>
-      <c r="AM31" s="53"/>
-      <c r="AN31" s="54"/>
-      <c r="AO31" s="47"/>
-      <c r="AP31" s="48"/>
-      <c r="AQ31" s="48"/>
-      <c r="AR31" s="48"/>
-      <c r="AS31" s="48"/>
-      <c r="AT31" s="48"/>
-      <c r="AU31" s="48"/>
-      <c r="AV31" s="48"/>
-      <c r="AW31" s="48"/>
-      <c r="AX31" s="48"/>
-      <c r="AY31" s="48"/>
-      <c r="AZ31" s="48"/>
-      <c r="BA31" s="48"/>
-      <c r="BB31" s="48"/>
-      <c r="BC31" s="49"/>
+      <c r="B31" s="110"/>
+      <c r="C31" s="111"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="111"/>
+      <c r="F31" s="111"/>
+      <c r="G31" s="111"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="110"/>
+      <c r="J31" s="114"/>
+      <c r="K31" s="114"/>
+      <c r="L31" s="114"/>
+      <c r="M31" s="114"/>
+      <c r="N31" s="114"/>
+      <c r="O31" s="114"/>
+      <c r="P31" s="114"/>
+      <c r="Q31" s="114"/>
+      <c r="R31" s="114"/>
+      <c r="S31" s="114"/>
+      <c r="T31" s="114"/>
+      <c r="U31" s="114"/>
+      <c r="V31" s="114"/>
+      <c r="W31" s="114"/>
+      <c r="X31" s="114"/>
+      <c r="Y31" s="114"/>
+      <c r="Z31" s="114"/>
+      <c r="AA31" s="114"/>
+      <c r="AB31" s="114"/>
+      <c r="AC31" s="114"/>
+      <c r="AD31" s="114"/>
+      <c r="AE31" s="114"/>
+      <c r="AF31" s="114"/>
+      <c r="AG31" s="114"/>
+      <c r="AH31" s="114"/>
+      <c r="AI31" s="114"/>
+      <c r="AJ31" s="114"/>
+      <c r="AK31" s="116"/>
+      <c r="AL31" s="116"/>
+      <c r="AM31" s="116"/>
+      <c r="AN31" s="117"/>
+      <c r="AO31" s="113"/>
+      <c r="AP31" s="114"/>
+      <c r="AQ31" s="114"/>
+      <c r="AR31" s="114"/>
+      <c r="AS31" s="114"/>
+      <c r="AT31" s="114"/>
+      <c r="AU31" s="114"/>
+      <c r="AV31" s="114"/>
+      <c r="AW31" s="114"/>
+      <c r="AX31" s="114"/>
+      <c r="AY31" s="114"/>
+      <c r="AZ31" s="114"/>
+      <c r="BA31" s="114"/>
+      <c r="BB31" s="114"/>
+      <c r="BC31" s="115"/>
     </row>
     <row r="32" spans="1:55" ht="15" customHeight="1">
       <c r="A32" s="36"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="48"/>
-      <c r="M32" s="48"/>
-      <c r="N32" s="48"/>
-      <c r="O32" s="48"/>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="48"/>
-      <c r="R32" s="48"/>
-      <c r="S32" s="48"/>
-      <c r="T32" s="48"/>
-      <c r="U32" s="48"/>
-      <c r="V32" s="48"/>
-      <c r="W32" s="48"/>
-      <c r="X32" s="48"/>
-      <c r="Y32" s="48"/>
-      <c r="Z32" s="48"/>
-      <c r="AA32" s="48"/>
-      <c r="AB32" s="48"/>
-      <c r="AC32" s="48"/>
-      <c r="AD32" s="48"/>
-      <c r="AE32" s="48"/>
-      <c r="AF32" s="48"/>
-      <c r="AG32" s="48"/>
-      <c r="AH32" s="48"/>
-      <c r="AI32" s="48"/>
-      <c r="AJ32" s="48"/>
-      <c r="AK32" s="53"/>
-      <c r="AL32" s="53"/>
-      <c r="AM32" s="53"/>
-      <c r="AN32" s="54"/>
-      <c r="AO32" s="47"/>
-      <c r="AP32" s="48"/>
-      <c r="AQ32" s="48"/>
-      <c r="AR32" s="48"/>
-      <c r="AS32" s="48"/>
-      <c r="AT32" s="48"/>
-      <c r="AU32" s="48"/>
-      <c r="AV32" s="48"/>
-      <c r="AW32" s="48"/>
-      <c r="AX32" s="48"/>
-      <c r="AY32" s="48"/>
-      <c r="AZ32" s="48"/>
-      <c r="BA32" s="48"/>
-      <c r="BB32" s="48"/>
-      <c r="BC32" s="49"/>
+      <c r="B32" s="110"/>
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="111"/>
+      <c r="F32" s="111"/>
+      <c r="G32" s="111"/>
+      <c r="H32" s="112"/>
+      <c r="I32" s="110"/>
+      <c r="J32" s="114"/>
+      <c r="K32" s="114"/>
+      <c r="L32" s="114"/>
+      <c r="M32" s="114"/>
+      <c r="N32" s="114"/>
+      <c r="O32" s="114"/>
+      <c r="P32" s="114"/>
+      <c r="Q32" s="114"/>
+      <c r="R32" s="114"/>
+      <c r="S32" s="114"/>
+      <c r="T32" s="114"/>
+      <c r="U32" s="114"/>
+      <c r="V32" s="114"/>
+      <c r="W32" s="114"/>
+      <c r="X32" s="114"/>
+      <c r="Y32" s="114"/>
+      <c r="Z32" s="114"/>
+      <c r="AA32" s="114"/>
+      <c r="AB32" s="114"/>
+      <c r="AC32" s="114"/>
+      <c r="AD32" s="114"/>
+      <c r="AE32" s="114"/>
+      <c r="AF32" s="114"/>
+      <c r="AG32" s="114"/>
+      <c r="AH32" s="114"/>
+      <c r="AI32" s="114"/>
+      <c r="AJ32" s="114"/>
+      <c r="AK32" s="116"/>
+      <c r="AL32" s="116"/>
+      <c r="AM32" s="116"/>
+      <c r="AN32" s="117"/>
+      <c r="AO32" s="113"/>
+      <c r="AP32" s="114"/>
+      <c r="AQ32" s="114"/>
+      <c r="AR32" s="114"/>
+      <c r="AS32" s="114"/>
+      <c r="AT32" s="114"/>
+      <c r="AU32" s="114"/>
+      <c r="AV32" s="114"/>
+      <c r="AW32" s="114"/>
+      <c r="AX32" s="114"/>
+      <c r="AY32" s="114"/>
+      <c r="AZ32" s="114"/>
+      <c r="BA32" s="114"/>
+      <c r="BB32" s="114"/>
+      <c r="BC32" s="115"/>
     </row>
     <row r="33" spans="1:55" ht="15" customHeight="1">
       <c r="A33" s="36"/>
-      <c r="B33" s="50"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="50"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="48"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="48"/>
-      <c r="O33" s="48"/>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="48"/>
-      <c r="R33" s="48"/>
-      <c r="S33" s="48"/>
-      <c r="T33" s="48"/>
-      <c r="U33" s="48"/>
-      <c r="V33" s="48"/>
-      <c r="W33" s="48"/>
-      <c r="X33" s="48"/>
-      <c r="Y33" s="48"/>
-      <c r="Z33" s="48"/>
-      <c r="AA33" s="48"/>
-      <c r="AB33" s="48"/>
-      <c r="AC33" s="48"/>
-      <c r="AD33" s="48"/>
-      <c r="AE33" s="48"/>
-      <c r="AF33" s="48"/>
-      <c r="AG33" s="48"/>
-      <c r="AH33" s="48"/>
-      <c r="AI33" s="48"/>
-      <c r="AJ33" s="48"/>
-      <c r="AK33" s="53"/>
-      <c r="AL33" s="53"/>
-      <c r="AM33" s="53"/>
-      <c r="AN33" s="54"/>
-      <c r="AO33" s="47"/>
-      <c r="AP33" s="48"/>
-      <c r="AQ33" s="48"/>
-      <c r="AR33" s="48"/>
-      <c r="AS33" s="48"/>
-      <c r="AT33" s="48"/>
-      <c r="AU33" s="48"/>
-      <c r="AV33" s="48"/>
-      <c r="AW33" s="48"/>
-      <c r="AX33" s="48"/>
-      <c r="AY33" s="48"/>
-      <c r="AZ33" s="48"/>
-      <c r="BA33" s="48"/>
-      <c r="BB33" s="48"/>
-      <c r="BC33" s="49"/>
+      <c r="B33" s="110"/>
+      <c r="C33" s="111"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="111"/>
+      <c r="F33" s="111"/>
+      <c r="G33" s="111"/>
+      <c r="H33" s="112"/>
+      <c r="I33" s="110"/>
+      <c r="J33" s="114"/>
+      <c r="K33" s="114"/>
+      <c r="L33" s="114"/>
+      <c r="M33" s="114"/>
+      <c r="N33" s="114"/>
+      <c r="O33" s="114"/>
+      <c r="P33" s="114"/>
+      <c r="Q33" s="114"/>
+      <c r="R33" s="114"/>
+      <c r="S33" s="114"/>
+      <c r="T33" s="114"/>
+      <c r="U33" s="114"/>
+      <c r="V33" s="114"/>
+      <c r="W33" s="114"/>
+      <c r="X33" s="114"/>
+      <c r="Y33" s="114"/>
+      <c r="Z33" s="114"/>
+      <c r="AA33" s="114"/>
+      <c r="AB33" s="114"/>
+      <c r="AC33" s="114"/>
+      <c r="AD33" s="114"/>
+      <c r="AE33" s="114"/>
+      <c r="AF33" s="114"/>
+      <c r="AG33" s="114"/>
+      <c r="AH33" s="114"/>
+      <c r="AI33" s="114"/>
+      <c r="AJ33" s="114"/>
+      <c r="AK33" s="116"/>
+      <c r="AL33" s="116"/>
+      <c r="AM33" s="116"/>
+      <c r="AN33" s="117"/>
+      <c r="AO33" s="113"/>
+      <c r="AP33" s="114"/>
+      <c r="AQ33" s="114"/>
+      <c r="AR33" s="114"/>
+      <c r="AS33" s="114"/>
+      <c r="AT33" s="114"/>
+      <c r="AU33" s="114"/>
+      <c r="AV33" s="114"/>
+      <c r="AW33" s="114"/>
+      <c r="AX33" s="114"/>
+      <c r="AY33" s="114"/>
+      <c r="AZ33" s="114"/>
+      <c r="BA33" s="114"/>
+      <c r="BB33" s="114"/>
+      <c r="BC33" s="115"/>
     </row>
     <row r="34" spans="1:55" ht="15" customHeight="1">
       <c r="A34" s="36"/>
-      <c r="B34" s="50"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="50"/>
-      <c r="J34" s="48"/>
-      <c r="K34" s="48"/>
-      <c r="L34" s="48"/>
-      <c r="M34" s="48"/>
-      <c r="N34" s="48"/>
-      <c r="O34" s="48"/>
-      <c r="P34" s="48"/>
-      <c r="Q34" s="48"/>
-      <c r="R34" s="48"/>
-      <c r="S34" s="48"/>
-      <c r="T34" s="48"/>
-      <c r="U34" s="48"/>
-      <c r="V34" s="48"/>
-      <c r="W34" s="48"/>
-      <c r="X34" s="48"/>
-      <c r="Y34" s="48"/>
-      <c r="Z34" s="48"/>
-      <c r="AA34" s="48"/>
-      <c r="AB34" s="48"/>
-      <c r="AC34" s="48"/>
-      <c r="AD34" s="48"/>
-      <c r="AE34" s="48"/>
-      <c r="AF34" s="48"/>
-      <c r="AG34" s="48"/>
-      <c r="AH34" s="48"/>
-      <c r="AI34" s="48"/>
-      <c r="AJ34" s="48"/>
-      <c r="AK34" s="53"/>
-      <c r="AL34" s="53"/>
-      <c r="AM34" s="53"/>
-      <c r="AN34" s="54"/>
-      <c r="AO34" s="47"/>
-      <c r="AP34" s="48"/>
-      <c r="AQ34" s="48"/>
-      <c r="AR34" s="48"/>
-      <c r="AS34" s="48"/>
-      <c r="AT34" s="48"/>
-      <c r="AU34" s="48"/>
-      <c r="AV34" s="48"/>
-      <c r="AW34" s="48"/>
-      <c r="AX34" s="48"/>
-      <c r="AY34" s="48"/>
-      <c r="AZ34" s="48"/>
-      <c r="BA34" s="48"/>
-      <c r="BB34" s="48"/>
-      <c r="BC34" s="49"/>
+      <c r="B34" s="110"/>
+      <c r="C34" s="111"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="111"/>
+      <c r="F34" s="111"/>
+      <c r="G34" s="111"/>
+      <c r="H34" s="112"/>
+      <c r="I34" s="110"/>
+      <c r="J34" s="114"/>
+      <c r="K34" s="114"/>
+      <c r="L34" s="114"/>
+      <c r="M34" s="114"/>
+      <c r="N34" s="114"/>
+      <c r="O34" s="114"/>
+      <c r="P34" s="114"/>
+      <c r="Q34" s="114"/>
+      <c r="R34" s="114"/>
+      <c r="S34" s="114"/>
+      <c r="T34" s="114"/>
+      <c r="U34" s="114"/>
+      <c r="V34" s="114"/>
+      <c r="W34" s="114"/>
+      <c r="X34" s="114"/>
+      <c r="Y34" s="114"/>
+      <c r="Z34" s="114"/>
+      <c r="AA34" s="114"/>
+      <c r="AB34" s="114"/>
+      <c r="AC34" s="114"/>
+      <c r="AD34" s="114"/>
+      <c r="AE34" s="114"/>
+      <c r="AF34" s="114"/>
+      <c r="AG34" s="114"/>
+      <c r="AH34" s="114"/>
+      <c r="AI34" s="114"/>
+      <c r="AJ34" s="114"/>
+      <c r="AK34" s="116"/>
+      <c r="AL34" s="116"/>
+      <c r="AM34" s="116"/>
+      <c r="AN34" s="117"/>
+      <c r="AO34" s="113"/>
+      <c r="AP34" s="114"/>
+      <c r="AQ34" s="114"/>
+      <c r="AR34" s="114"/>
+      <c r="AS34" s="114"/>
+      <c r="AT34" s="114"/>
+      <c r="AU34" s="114"/>
+      <c r="AV34" s="114"/>
+      <c r="AW34" s="114"/>
+      <c r="AX34" s="114"/>
+      <c r="AY34" s="114"/>
+      <c r="AZ34" s="114"/>
+      <c r="BA34" s="114"/>
+      <c r="BB34" s="114"/>
+      <c r="BC34" s="115"/>
     </row>
     <row r="35" spans="1:55" ht="15" customHeight="1" thickBot="1">
       <c r="A35" s="38"/>
-      <c r="B35" s="73"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="77"/>
-      <c r="I35" s="73"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="71"/>
-      <c r="L35" s="71"/>
-      <c r="M35" s="71"/>
-      <c r="N35" s="71"/>
-      <c r="O35" s="71"/>
-      <c r="P35" s="71"/>
-      <c r="Q35" s="71"/>
-      <c r="R35" s="71"/>
-      <c r="S35" s="71"/>
-      <c r="T35" s="71"/>
-      <c r="U35" s="71"/>
-      <c r="V35" s="71"/>
-      <c r="W35" s="71"/>
-      <c r="X35" s="71"/>
-      <c r="Y35" s="71"/>
-      <c r="Z35" s="71"/>
-      <c r="AA35" s="71"/>
-      <c r="AB35" s="71"/>
-      <c r="AC35" s="71"/>
-      <c r="AD35" s="71"/>
-      <c r="AE35" s="71"/>
-      <c r="AF35" s="71"/>
-      <c r="AG35" s="71"/>
-      <c r="AH35" s="71"/>
-      <c r="AI35" s="71"/>
-      <c r="AJ35" s="71"/>
-      <c r="AK35" s="74"/>
-      <c r="AL35" s="74"/>
-      <c r="AM35" s="74"/>
-      <c r="AN35" s="75"/>
-      <c r="AO35" s="70"/>
-      <c r="AP35" s="71"/>
-      <c r="AQ35" s="71"/>
-      <c r="AR35" s="71"/>
-      <c r="AS35" s="71"/>
-      <c r="AT35" s="71"/>
-      <c r="AU35" s="71"/>
-      <c r="AV35" s="71"/>
-      <c r="AW35" s="71"/>
-      <c r="AX35" s="71"/>
-      <c r="AY35" s="71"/>
-      <c r="AZ35" s="71"/>
-      <c r="BA35" s="71"/>
-      <c r="BB35" s="71"/>
-      <c r="BC35" s="72"/>
+      <c r="B35" s="118"/>
+      <c r="C35" s="121"/>
+      <c r="D35" s="121"/>
+      <c r="E35" s="121"/>
+      <c r="F35" s="121"/>
+      <c r="G35" s="121"/>
+      <c r="H35" s="122"/>
+      <c r="I35" s="118"/>
+      <c r="J35" s="108"/>
+      <c r="K35" s="108"/>
+      <c r="L35" s="108"/>
+      <c r="M35" s="108"/>
+      <c r="N35" s="108"/>
+      <c r="O35" s="108"/>
+      <c r="P35" s="108"/>
+      <c r="Q35" s="108"/>
+      <c r="R35" s="108"/>
+      <c r="S35" s="108"/>
+      <c r="T35" s="108"/>
+      <c r="U35" s="108"/>
+      <c r="V35" s="108"/>
+      <c r="W35" s="108"/>
+      <c r="X35" s="108"/>
+      <c r="Y35" s="108"/>
+      <c r="Z35" s="108"/>
+      <c r="AA35" s="108"/>
+      <c r="AB35" s="108"/>
+      <c r="AC35" s="108"/>
+      <c r="AD35" s="108"/>
+      <c r="AE35" s="108"/>
+      <c r="AF35" s="108"/>
+      <c r="AG35" s="108"/>
+      <c r="AH35" s="108"/>
+      <c r="AI35" s="108"/>
+      <c r="AJ35" s="108"/>
+      <c r="AK35" s="119"/>
+      <c r="AL35" s="119"/>
+      <c r="AM35" s="119"/>
+      <c r="AN35" s="120"/>
+      <c r="AO35" s="107"/>
+      <c r="AP35" s="108"/>
+      <c r="AQ35" s="108"/>
+      <c r="AR35" s="108"/>
+      <c r="AS35" s="108"/>
+      <c r="AT35" s="108"/>
+      <c r="AU35" s="108"/>
+      <c r="AV35" s="108"/>
+      <c r="AW35" s="108"/>
+      <c r="AX35" s="108"/>
+      <c r="AY35" s="108"/>
+      <c r="AZ35" s="108"/>
+      <c r="BA35" s="108"/>
+      <c r="BB35" s="108"/>
+      <c r="BC35" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="AY1:BC1"/>
-    <mergeCell ref="AY2:BC2"/>
-    <mergeCell ref="I1:AX2"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="AO4:BC4"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="I4:AN4"/>
-    <mergeCell ref="AO35:BC35"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="AO34:BC34"/>
-    <mergeCell ref="I34:AN34"/>
-    <mergeCell ref="I35:AN35"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="AO10:BC10"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I25:AN25"/>
+    <mergeCell ref="AO25:BC25"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="I26:AN26"/>
+    <mergeCell ref="AO26:BC26"/>
+    <mergeCell ref="I23:AN23"/>
+    <mergeCell ref="AO23:BC23"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="I24:AN24"/>
+    <mergeCell ref="AO24:BC24"/>
+    <mergeCell ref="AO13:BC13"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="AO12:BC12"/>
+    <mergeCell ref="I12:AN12"/>
+    <mergeCell ref="I11:AN11"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="I13:AN13"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="I9:AN9"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="I5:AN5"/>
+    <mergeCell ref="I7:AN7"/>
+    <mergeCell ref="I8:AN8"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="I6:AN6"/>
+    <mergeCell ref="AO5:BC5"/>
+    <mergeCell ref="AO33:BC33"/>
+    <mergeCell ref="I21:AN21"/>
+    <mergeCell ref="AO7:BC7"/>
+    <mergeCell ref="AO32:BC32"/>
+    <mergeCell ref="AO20:BC20"/>
+    <mergeCell ref="I16:AN16"/>
+    <mergeCell ref="AO28:BC28"/>
+    <mergeCell ref="AO17:BC17"/>
+    <mergeCell ref="I15:AN15"/>
+    <mergeCell ref="I30:AN30"/>
+    <mergeCell ref="I31:AN31"/>
+    <mergeCell ref="I28:AN28"/>
+    <mergeCell ref="AO21:BC21"/>
+    <mergeCell ref="AO30:BC30"/>
+    <mergeCell ref="AO16:BC16"/>
+    <mergeCell ref="AO31:BC31"/>
+    <mergeCell ref="I33:AN33"/>
+    <mergeCell ref="I17:AN17"/>
+    <mergeCell ref="I18:AN18"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="I20:AN20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="I29:AN29"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="I22:AN22"/>
+    <mergeCell ref="AO22:BC22"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:AN14"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="I32:AN32"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="I27:AN27"/>
+    <mergeCell ref="I19:AN19"/>
     <mergeCell ref="AO6:BC6"/>
     <mergeCell ref="B29:H29"/>
     <mergeCell ref="AO29:BC29"/>
@@ -11796,77 +11854,19 @@
     <mergeCell ref="AO19:BC19"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I14:AN14"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="I32:AN32"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="I27:AN27"/>
-    <mergeCell ref="I19:AN19"/>
-    <mergeCell ref="AO31:BC31"/>
-    <mergeCell ref="I33:AN33"/>
-    <mergeCell ref="I17:AN17"/>
-    <mergeCell ref="I18:AN18"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="I20:AN20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="I29:AN29"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="I22:AN22"/>
-    <mergeCell ref="AO22:BC22"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="AO5:BC5"/>
-    <mergeCell ref="AO33:BC33"/>
-    <mergeCell ref="I21:AN21"/>
-    <mergeCell ref="AO7:BC7"/>
-    <mergeCell ref="AO32:BC32"/>
-    <mergeCell ref="AO20:BC20"/>
-    <mergeCell ref="I16:AN16"/>
-    <mergeCell ref="AO28:BC28"/>
-    <mergeCell ref="AO17:BC17"/>
-    <mergeCell ref="I15:AN15"/>
-    <mergeCell ref="I30:AN30"/>
-    <mergeCell ref="I31:AN31"/>
-    <mergeCell ref="I28:AN28"/>
-    <mergeCell ref="AO21:BC21"/>
-    <mergeCell ref="AO30:BC30"/>
-    <mergeCell ref="AO16:BC16"/>
-    <mergeCell ref="I11:AN11"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="I13:AN13"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="I9:AN9"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="I5:AN5"/>
-    <mergeCell ref="I7:AN7"/>
-    <mergeCell ref="I8:AN8"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="I6:AN6"/>
-    <mergeCell ref="AO10:BC10"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I25:AN25"/>
-    <mergeCell ref="AO25:BC25"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="I26:AN26"/>
-    <mergeCell ref="AO26:BC26"/>
-    <mergeCell ref="I23:AN23"/>
-    <mergeCell ref="AO23:BC23"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="I24:AN24"/>
-    <mergeCell ref="AO24:BC24"/>
-    <mergeCell ref="AO13:BC13"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="AO12:BC12"/>
-    <mergeCell ref="I12:AN12"/>
+    <mergeCell ref="AO35:BC35"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="AO34:BC34"/>
+    <mergeCell ref="I34:AN34"/>
+    <mergeCell ref="I35:AN35"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="AY1:BC1"/>
+    <mergeCell ref="AY2:BC2"/>
+    <mergeCell ref="I1:AX2"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="AO4:BC4"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I4:AN4"/>
   </mergeCells>
   <phoneticPr fontId="37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -11924,17 +11924,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9"/>
-      <c r="B3" s="119" t="s">
+      <c r="B3" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
       <c r="K3" s="42"/>
     </row>
     <row r="4" spans="1:11">
@@ -12000,17 +12000,17 @@
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="120" t="s">
+      <c r="B7" s="62" t="s">
         <v>609</v>
       </c>
-      <c r="C7" s="121"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="122"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="64"/>
       <c r="K7" s="44"/>
     </row>
     <row r="8" spans="1:11" ht="36">
@@ -12239,17 +12239,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9"/>
-      <c r="B3" s="119" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
+      <c r="B3" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
       <c r="K3" s="42"/>
     </row>
     <row r="4" spans="1:11">
@@ -12315,17 +12315,17 @@
     </row>
     <row r="7" spans="1:11" ht="24" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="120" t="s">
+      <c r="B7" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="C7" s="121"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="122"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="64"/>
       <c r="K7" s="44"/>
     </row>
     <row r="8" spans="1:11">
@@ -12410,17 +12410,17 @@
     </row>
     <row r="12" spans="1:11" ht="24" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="120" t="s">
+      <c r="B12" s="62" t="s">
         <v>611</v>
       </c>
-      <c r="C12" s="121"/>
-      <c r="D12" s="121"/>
-      <c r="E12" s="121"/>
-      <c r="F12" s="121"/>
-      <c r="G12" s="121"/>
-      <c r="H12" s="121"/>
-      <c r="I12" s="121"/>
-      <c r="J12" s="122"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="64"/>
       <c r="K12" s="44"/>
     </row>
     <row r="13" spans="1:11">
@@ -12502,17 +12502,17 @@
     </row>
     <row r="17" spans="1:11" ht="24" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="120" t="s">
+      <c r="B17" s="62" t="s">
         <v>612</v>
       </c>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="122"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="64"/>
       <c r="K17" s="44"/>
     </row>
     <row r="18" spans="1:11">
@@ -12594,17 +12594,17 @@
     </row>
     <row r="22" spans="1:11" ht="24" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="120" t="s">
+      <c r="B22" s="62" t="s">
         <v>613</v>
       </c>
-      <c r="C22" s="121"/>
-      <c r="D22" s="121"/>
-      <c r="E22" s="121"/>
-      <c r="F22" s="121"/>
-      <c r="G22" s="121"/>
-      <c r="H22" s="121"/>
-      <c r="I22" s="121"/>
-      <c r="J22" s="122"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="64"/>
       <c r="K22" s="44"/>
     </row>
     <row r="23" spans="1:11">
@@ -12686,17 +12686,17 @@
     </row>
     <row r="27" spans="1:11" ht="24" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="120" t="s">
+      <c r="B27" s="62" t="s">
         <v>615</v>
       </c>
-      <c r="C27" s="121"/>
-      <c r="D27" s="121"/>
-      <c r="E27" s="121"/>
-      <c r="F27" s="121"/>
-      <c r="G27" s="121"/>
-      <c r="H27" s="121"/>
-      <c r="I27" s="121"/>
-      <c r="J27" s="122"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="64"/>
       <c r="K27" s="44"/>
     </row>
     <row r="28" spans="1:11">
@@ -12778,17 +12778,17 @@
     </row>
     <row r="32" spans="1:11" ht="24" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="120" t="s">
+      <c r="B32" s="62" t="s">
         <v>617</v>
       </c>
-      <c r="C32" s="121"/>
-      <c r="D32" s="121"/>
-      <c r="E32" s="121"/>
-      <c r="F32" s="121"/>
-      <c r="G32" s="121"/>
-      <c r="H32" s="121"/>
-      <c r="I32" s="121"/>
-      <c r="J32" s="122"/>
+      <c r="C32" s="63"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="64"/>
       <c r="K32" s="44"/>
     </row>
     <row r="33" spans="1:11">
@@ -12870,17 +12870,17 @@
     </row>
     <row r="37" spans="1:11" ht="24" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="120" t="s">
+      <c r="B37" s="62" t="s">
         <v>619</v>
       </c>
-      <c r="C37" s="121"/>
-      <c r="D37" s="121"/>
-      <c r="E37" s="121"/>
-      <c r="F37" s="121"/>
-      <c r="G37" s="121"/>
-      <c r="H37" s="121"/>
-      <c r="I37" s="121"/>
-      <c r="J37" s="122"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="63"/>
+      <c r="J37" s="64"/>
       <c r="K37" s="44"/>
     </row>
     <row r="38" spans="1:11">
@@ -12962,17 +12962,17 @@
     </row>
     <row r="42" spans="1:11" ht="24" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="120" t="s">
+      <c r="B42" s="62" t="s">
         <v>621</v>
       </c>
-      <c r="C42" s="121"/>
-      <c r="D42" s="121"/>
-      <c r="E42" s="121"/>
-      <c r="F42" s="121"/>
-      <c r="G42" s="121"/>
-      <c r="H42" s="121"/>
-      <c r="I42" s="121"/>
-      <c r="J42" s="122"/>
+      <c r="C42" s="63"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="63"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="64"/>
       <c r="K42" s="44"/>
     </row>
     <row r="43" spans="1:11">
@@ -13054,17 +13054,17 @@
     </row>
     <row r="47" spans="1:11" ht="24" customHeight="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="120" t="s">
+      <c r="B47" s="62" t="s">
         <v>623</v>
       </c>
-      <c r="C47" s="121"/>
-      <c r="D47" s="121"/>
-      <c r="E47" s="121"/>
-      <c r="F47" s="121"/>
-      <c r="G47" s="121"/>
-      <c r="H47" s="121"/>
-      <c r="I47" s="121"/>
-      <c r="J47" s="122"/>
+      <c r="C47" s="63"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="63"/>
+      <c r="I47" s="63"/>
+      <c r="J47" s="64"/>
       <c r="K47" s="44"/>
     </row>
     <row r="48" spans="1:11">
@@ -13146,17 +13146,17 @@
     </row>
     <row r="52" spans="1:11" ht="36" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="120" t="s">
+      <c r="B52" s="62" t="s">
         <v>849</v>
       </c>
-      <c r="C52" s="121"/>
-      <c r="D52" s="121"/>
-      <c r="E52" s="121"/>
-      <c r="F52" s="121"/>
-      <c r="G52" s="121"/>
-      <c r="H52" s="121"/>
-      <c r="I52" s="121"/>
-      <c r="J52" s="122"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="63"/>
+      <c r="I52" s="63"/>
+      <c r="J52" s="64"/>
       <c r="K52" s="44"/>
     </row>
     <row r="53" spans="1:11">
@@ -13238,17 +13238,17 @@
     </row>
     <row r="57" spans="1:11" ht="24" customHeight="1">
       <c r="A57" s="1"/>
-      <c r="B57" s="120" t="s">
+      <c r="B57" s="62" t="s">
         <v>626</v>
       </c>
-      <c r="C57" s="121"/>
-      <c r="D57" s="121"/>
-      <c r="E57" s="121"/>
-      <c r="F57" s="121"/>
-      <c r="G57" s="121"/>
-      <c r="H57" s="121"/>
-      <c r="I57" s="121"/>
-      <c r="J57" s="122"/>
+      <c r="C57" s="63"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="63"/>
+      <c r="F57" s="63"/>
+      <c r="G57" s="63"/>
+      <c r="H57" s="63"/>
+      <c r="I57" s="63"/>
+      <c r="J57" s="64"/>
       <c r="K57" s="44"/>
     </row>
     <row r="58" spans="1:11">
@@ -13330,17 +13330,17 @@
     </row>
     <row r="62" spans="1:11" ht="24" customHeight="1">
       <c r="A62" s="1"/>
-      <c r="B62" s="120" t="s">
+      <c r="B62" s="62" t="s">
         <v>628</v>
       </c>
-      <c r="C62" s="121"/>
-      <c r="D62" s="121"/>
-      <c r="E62" s="121"/>
-      <c r="F62" s="121"/>
-      <c r="G62" s="121"/>
-      <c r="H62" s="121"/>
-      <c r="I62" s="121"/>
-      <c r="J62" s="122"/>
+      <c r="C62" s="63"/>
+      <c r="D62" s="63"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="63"/>
+      <c r="H62" s="63"/>
+      <c r="I62" s="63"/>
+      <c r="J62" s="64"/>
       <c r="K62" s="44"/>
     </row>
     <row r="63" spans="1:11">
@@ -13422,17 +13422,17 @@
     </row>
     <row r="67" spans="1:11" ht="24" customHeight="1">
       <c r="A67" s="1"/>
-      <c r="B67" s="120" t="s">
+      <c r="B67" s="62" t="s">
         <v>630</v>
       </c>
-      <c r="C67" s="121"/>
-      <c r="D67" s="121"/>
-      <c r="E67" s="121"/>
-      <c r="F67" s="121"/>
-      <c r="G67" s="121"/>
-      <c r="H67" s="121"/>
-      <c r="I67" s="121"/>
-      <c r="J67" s="122"/>
+      <c r="C67" s="63"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="63"/>
+      <c r="F67" s="63"/>
+      <c r="G67" s="63"/>
+      <c r="H67" s="63"/>
+      <c r="I67" s="63"/>
+      <c r="J67" s="64"/>
       <c r="K67" s="44"/>
     </row>
     <row r="68" spans="1:11">
@@ -13514,17 +13514,17 @@
     </row>
     <row r="72" spans="1:11" ht="24" customHeight="1">
       <c r="A72" s="1"/>
-      <c r="B72" s="120" t="s">
+      <c r="B72" s="62" t="s">
         <v>632</v>
       </c>
-      <c r="C72" s="121"/>
-      <c r="D72" s="121"/>
-      <c r="E72" s="121"/>
-      <c r="F72" s="121"/>
-      <c r="G72" s="121"/>
-      <c r="H72" s="121"/>
-      <c r="I72" s="121"/>
-      <c r="J72" s="122"/>
+      <c r="C72" s="63"/>
+      <c r="D72" s="63"/>
+      <c r="E72" s="63"/>
+      <c r="F72" s="63"/>
+      <c r="G72" s="63"/>
+      <c r="H72" s="63"/>
+      <c r="I72" s="63"/>
+      <c r="J72" s="64"/>
       <c r="K72" s="44"/>
     </row>
     <row r="73" spans="1:11">
@@ -13606,17 +13606,17 @@
     </row>
     <row r="77" spans="1:11" ht="24" customHeight="1">
       <c r="A77" s="1"/>
-      <c r="B77" s="120" t="s">
+      <c r="B77" s="62" t="s">
         <v>633</v>
       </c>
-      <c r="C77" s="121"/>
-      <c r="D77" s="121"/>
-      <c r="E77" s="121"/>
-      <c r="F77" s="121"/>
-      <c r="G77" s="121"/>
-      <c r="H77" s="121"/>
-      <c r="I77" s="121"/>
-      <c r="J77" s="122"/>
+      <c r="C77" s="63"/>
+      <c r="D77" s="63"/>
+      <c r="E77" s="63"/>
+      <c r="F77" s="63"/>
+      <c r="G77" s="63"/>
+      <c r="H77" s="63"/>
+      <c r="I77" s="63"/>
+      <c r="J77" s="64"/>
       <c r="K77" s="44"/>
     </row>
     <row r="78" spans="1:11">
@@ -13698,17 +13698,17 @@
     </row>
     <row r="82" spans="1:11" ht="24" customHeight="1">
       <c r="A82" s="1"/>
-      <c r="B82" s="120" t="s">
+      <c r="B82" s="62" t="s">
         <v>635</v>
       </c>
-      <c r="C82" s="121"/>
-      <c r="D82" s="121"/>
-      <c r="E82" s="121"/>
-      <c r="F82" s="121"/>
-      <c r="G82" s="121"/>
-      <c r="H82" s="121"/>
-      <c r="I82" s="121"/>
-      <c r="J82" s="122"/>
+      <c r="C82" s="63"/>
+      <c r="D82" s="63"/>
+      <c r="E82" s="63"/>
+      <c r="F82" s="63"/>
+      <c r="G82" s="63"/>
+      <c r="H82" s="63"/>
+      <c r="I82" s="63"/>
+      <c r="J82" s="64"/>
       <c r="K82" s="44"/>
     </row>
     <row r="83" spans="1:11">
@@ -13790,17 +13790,17 @@
     </row>
     <row r="87" spans="1:11" ht="24" customHeight="1">
       <c r="A87" s="1"/>
-      <c r="B87" s="120" t="s">
+      <c r="B87" s="62" t="s">
         <v>637</v>
       </c>
-      <c r="C87" s="121"/>
-      <c r="D87" s="121"/>
-      <c r="E87" s="121"/>
-      <c r="F87" s="121"/>
-      <c r="G87" s="121"/>
-      <c r="H87" s="121"/>
-      <c r="I87" s="121"/>
-      <c r="J87" s="122"/>
+      <c r="C87" s="63"/>
+      <c r="D87" s="63"/>
+      <c r="E87" s="63"/>
+      <c r="F87" s="63"/>
+      <c r="G87" s="63"/>
+      <c r="H87" s="63"/>
+      <c r="I87" s="63"/>
+      <c r="J87" s="64"/>
       <c r="K87" s="44"/>
     </row>
     <row r="88" spans="1:11">
@@ -13882,17 +13882,17 @@
     </row>
     <row r="92" spans="1:11" ht="24" customHeight="1">
       <c r="A92" s="1"/>
-      <c r="B92" s="120" t="s">
+      <c r="B92" s="62" t="s">
         <v>639</v>
       </c>
-      <c r="C92" s="121"/>
-      <c r="D92" s="121"/>
-      <c r="E92" s="121"/>
-      <c r="F92" s="121"/>
-      <c r="G92" s="121"/>
-      <c r="H92" s="121"/>
-      <c r="I92" s="121"/>
-      <c r="J92" s="122"/>
+      <c r="C92" s="63"/>
+      <c r="D92" s="63"/>
+      <c r="E92" s="63"/>
+      <c r="F92" s="63"/>
+      <c r="G92" s="63"/>
+      <c r="H92" s="63"/>
+      <c r="I92" s="63"/>
+      <c r="J92" s="64"/>
       <c r="K92" s="44"/>
     </row>
     <row r="93" spans="1:11">
@@ -13974,17 +13974,17 @@
     </row>
     <row r="97" spans="1:11" ht="24" customHeight="1">
       <c r="A97" s="1"/>
-      <c r="B97" s="120" t="s">
+      <c r="B97" s="62" t="s">
         <v>641</v>
       </c>
-      <c r="C97" s="121"/>
-      <c r="D97" s="121"/>
-      <c r="E97" s="121"/>
-      <c r="F97" s="121"/>
-      <c r="G97" s="121"/>
-      <c r="H97" s="121"/>
-      <c r="I97" s="121"/>
-      <c r="J97" s="122"/>
+      <c r="C97" s="63"/>
+      <c r="D97" s="63"/>
+      <c r="E97" s="63"/>
+      <c r="F97" s="63"/>
+      <c r="G97" s="63"/>
+      <c r="H97" s="63"/>
+      <c r="I97" s="63"/>
+      <c r="J97" s="64"/>
       <c r="K97" s="44"/>
     </row>
     <row r="98" spans="1:11">
@@ -14066,17 +14066,17 @@
     </row>
     <row r="102" spans="1:11" ht="24" customHeight="1">
       <c r="A102" s="1"/>
-      <c r="B102" s="120" t="s">
+      <c r="B102" s="62" t="s">
         <v>643</v>
       </c>
-      <c r="C102" s="121"/>
-      <c r="D102" s="121"/>
-      <c r="E102" s="121"/>
-      <c r="F102" s="121"/>
-      <c r="G102" s="121"/>
-      <c r="H102" s="121"/>
-      <c r="I102" s="121"/>
-      <c r="J102" s="122"/>
+      <c r="C102" s="63"/>
+      <c r="D102" s="63"/>
+      <c r="E102" s="63"/>
+      <c r="F102" s="63"/>
+      <c r="G102" s="63"/>
+      <c r="H102" s="63"/>
+      <c r="I102" s="63"/>
+      <c r="J102" s="64"/>
       <c r="K102" s="44"/>
     </row>
     <row r="103" spans="1:11">
@@ -14158,17 +14158,17 @@
     </row>
     <row r="107" spans="1:11" ht="24" customHeight="1">
       <c r="A107" s="1"/>
-      <c r="B107" s="120" t="s">
+      <c r="B107" s="62" t="s">
         <v>645</v>
       </c>
-      <c r="C107" s="121"/>
-      <c r="D107" s="121"/>
-      <c r="E107" s="121"/>
-      <c r="F107" s="121"/>
-      <c r="G107" s="121"/>
-      <c r="H107" s="121"/>
-      <c r="I107" s="121"/>
-      <c r="J107" s="122"/>
+      <c r="C107" s="63"/>
+      <c r="D107" s="63"/>
+      <c r="E107" s="63"/>
+      <c r="F107" s="63"/>
+      <c r="G107" s="63"/>
+      <c r="H107" s="63"/>
+      <c r="I107" s="63"/>
+      <c r="J107" s="64"/>
       <c r="K107" s="44"/>
     </row>
     <row r="108" spans="1:11">
@@ -14250,17 +14250,17 @@
     </row>
     <row r="112" spans="1:11" ht="24" customHeight="1">
       <c r="A112" s="1"/>
-      <c r="B112" s="120" t="s">
+      <c r="B112" s="62" t="s">
         <v>647</v>
       </c>
-      <c r="C112" s="121"/>
-      <c r="D112" s="121"/>
-      <c r="E112" s="121"/>
-      <c r="F112" s="121"/>
-      <c r="G112" s="121"/>
-      <c r="H112" s="121"/>
-      <c r="I112" s="121"/>
-      <c r="J112" s="122"/>
+      <c r="C112" s="63"/>
+      <c r="D112" s="63"/>
+      <c r="E112" s="63"/>
+      <c r="F112" s="63"/>
+      <c r="G112" s="63"/>
+      <c r="H112" s="63"/>
+      <c r="I112" s="63"/>
+      <c r="J112" s="64"/>
       <c r="K112" s="44"/>
     </row>
     <row r="113" spans="1:11">
@@ -14342,17 +14342,17 @@
     </row>
     <row r="117" spans="1:11" ht="24" customHeight="1">
       <c r="A117" s="1"/>
-      <c r="B117" s="120" t="s">
+      <c r="B117" s="62" t="s">
         <v>649</v>
       </c>
-      <c r="C117" s="121"/>
-      <c r="D117" s="121"/>
-      <c r="E117" s="121"/>
-      <c r="F117" s="121"/>
-      <c r="G117" s="121"/>
-      <c r="H117" s="121"/>
-      <c r="I117" s="121"/>
-      <c r="J117" s="122"/>
+      <c r="C117" s="63"/>
+      <c r="D117" s="63"/>
+      <c r="E117" s="63"/>
+      <c r="F117" s="63"/>
+      <c r="G117" s="63"/>
+      <c r="H117" s="63"/>
+      <c r="I117" s="63"/>
+      <c r="J117" s="64"/>
       <c r="K117" s="44"/>
     </row>
     <row r="118" spans="1:11">
@@ -14434,17 +14434,17 @@
     </row>
     <row r="122" spans="1:11" ht="24" customHeight="1">
       <c r="A122" s="1"/>
-      <c r="B122" s="120" t="s">
+      <c r="B122" s="62" t="s">
         <v>651</v>
       </c>
-      <c r="C122" s="121"/>
-      <c r="D122" s="121"/>
-      <c r="E122" s="121"/>
-      <c r="F122" s="121"/>
-      <c r="G122" s="121"/>
-      <c r="H122" s="121"/>
-      <c r="I122" s="121"/>
-      <c r="J122" s="122"/>
+      <c r="C122" s="63"/>
+      <c r="D122" s="63"/>
+      <c r="E122" s="63"/>
+      <c r="F122" s="63"/>
+      <c r="G122" s="63"/>
+      <c r="H122" s="63"/>
+      <c r="I122" s="63"/>
+      <c r="J122" s="64"/>
       <c r="K122" s="44"/>
     </row>
     <row r="123" spans="1:11">
@@ -14526,17 +14526,17 @@
     </row>
     <row r="127" spans="1:11" ht="24" customHeight="1">
       <c r="A127" s="1"/>
-      <c r="B127" s="120" t="s">
+      <c r="B127" s="62" t="s">
         <v>653</v>
       </c>
-      <c r="C127" s="121"/>
-      <c r="D127" s="121"/>
-      <c r="E127" s="121"/>
-      <c r="F127" s="121"/>
-      <c r="G127" s="121"/>
-      <c r="H127" s="121"/>
-      <c r="I127" s="121"/>
-      <c r="J127" s="122"/>
+      <c r="C127" s="63"/>
+      <c r="D127" s="63"/>
+      <c r="E127" s="63"/>
+      <c r="F127" s="63"/>
+      <c r="G127" s="63"/>
+      <c r="H127" s="63"/>
+      <c r="I127" s="63"/>
+      <c r="J127" s="64"/>
       <c r="K127" s="44"/>
     </row>
     <row r="128" spans="1:11">
@@ -14616,17 +14616,17 @@
     </row>
     <row r="132" spans="1:11" ht="24" customHeight="1">
       <c r="A132" s="1"/>
-      <c r="B132" s="120" t="s">
+      <c r="B132" s="62" t="s">
         <v>655</v>
       </c>
-      <c r="C132" s="121"/>
-      <c r="D132" s="121"/>
-      <c r="E132" s="121"/>
-      <c r="F132" s="121"/>
-      <c r="G132" s="121"/>
-      <c r="H132" s="121"/>
-      <c r="I132" s="121"/>
-      <c r="J132" s="122"/>
+      <c r="C132" s="63"/>
+      <c r="D132" s="63"/>
+      <c r="E132" s="63"/>
+      <c r="F132" s="63"/>
+      <c r="G132" s="63"/>
+      <c r="H132" s="63"/>
+      <c r="I132" s="63"/>
+      <c r="J132" s="64"/>
       <c r="K132" s="44"/>
     </row>
     <row r="133" spans="1:11">
@@ -14679,7 +14679,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="24">
+    <row r="136" spans="1:11">
       <c r="A136" s="1" t="s">
         <v>37</v>
       </c>
@@ -14706,17 +14706,17 @@
     </row>
     <row r="137" spans="1:11" ht="24" customHeight="1">
       <c r="A137" s="1"/>
-      <c r="B137" s="120" t="s">
+      <c r="B137" s="62" t="s">
         <v>657</v>
       </c>
-      <c r="C137" s="121"/>
-      <c r="D137" s="121"/>
-      <c r="E137" s="121"/>
-      <c r="F137" s="121"/>
-      <c r="G137" s="121"/>
-      <c r="H137" s="121"/>
-      <c r="I137" s="121"/>
-      <c r="J137" s="122"/>
+      <c r="C137" s="63"/>
+      <c r="D137" s="63"/>
+      <c r="E137" s="63"/>
+      <c r="F137" s="63"/>
+      <c r="G137" s="63"/>
+      <c r="H137" s="63"/>
+      <c r="I137" s="63"/>
+      <c r="J137" s="64"/>
       <c r="K137" s="44"/>
     </row>
     <row r="138" spans="1:11">
@@ -14796,17 +14796,17 @@
     </row>
     <row r="142" spans="1:11" ht="24" customHeight="1">
       <c r="A142" s="1"/>
-      <c r="B142" s="120" t="s">
+      <c r="B142" s="62" t="s">
         <v>659</v>
       </c>
-      <c r="C142" s="121"/>
-      <c r="D142" s="121"/>
-      <c r="E142" s="121"/>
-      <c r="F142" s="121"/>
-      <c r="G142" s="121"/>
-      <c r="H142" s="121"/>
-      <c r="I142" s="121"/>
-      <c r="J142" s="122"/>
+      <c r="C142" s="63"/>
+      <c r="D142" s="63"/>
+      <c r="E142" s="63"/>
+      <c r="F142" s="63"/>
+      <c r="G142" s="63"/>
+      <c r="H142" s="63"/>
+      <c r="I142" s="63"/>
+      <c r="J142" s="64"/>
       <c r="K142" s="44"/>
     </row>
     <row r="143" spans="1:11">
@@ -14886,17 +14886,17 @@
     </row>
     <row r="147" spans="1:11" ht="24" customHeight="1">
       <c r="A147" s="1"/>
-      <c r="B147" s="120" t="s">
+      <c r="B147" s="62" t="s">
         <v>661</v>
       </c>
-      <c r="C147" s="121"/>
-      <c r="D147" s="121"/>
-      <c r="E147" s="121"/>
-      <c r="F147" s="121"/>
-      <c r="G147" s="121"/>
-      <c r="H147" s="121"/>
-      <c r="I147" s="121"/>
-      <c r="J147" s="122"/>
+      <c r="C147" s="63"/>
+      <c r="D147" s="63"/>
+      <c r="E147" s="63"/>
+      <c r="F147" s="63"/>
+      <c r="G147" s="63"/>
+      <c r="H147" s="63"/>
+      <c r="I147" s="63"/>
+      <c r="J147" s="64"/>
       <c r="K147" s="44"/>
     </row>
     <row r="148" spans="1:11">
@@ -14978,17 +14978,17 @@
     </row>
     <row r="152" spans="1:11" ht="24" customHeight="1">
       <c r="A152" s="1"/>
-      <c r="B152" s="120" t="s">
+      <c r="B152" s="62" t="s">
         <v>663</v>
       </c>
-      <c r="C152" s="121"/>
-      <c r="D152" s="121"/>
-      <c r="E152" s="121"/>
-      <c r="F152" s="121"/>
-      <c r="G152" s="121"/>
-      <c r="H152" s="121"/>
-      <c r="I152" s="121"/>
-      <c r="J152" s="122"/>
+      <c r="C152" s="63"/>
+      <c r="D152" s="63"/>
+      <c r="E152" s="63"/>
+      <c r="F152" s="63"/>
+      <c r="G152" s="63"/>
+      <c r="H152" s="63"/>
+      <c r="I152" s="63"/>
+      <c r="J152" s="64"/>
       <c r="K152" s="44"/>
     </row>
     <row r="153" spans="1:11">
@@ -15070,17 +15070,17 @@
     </row>
     <row r="157" spans="1:11" ht="24" customHeight="1">
       <c r="A157" s="1"/>
-      <c r="B157" s="120" t="s">
+      <c r="B157" s="62" t="s">
         <v>665</v>
       </c>
-      <c r="C157" s="121"/>
-      <c r="D157" s="121"/>
-      <c r="E157" s="121"/>
-      <c r="F157" s="121"/>
-      <c r="G157" s="121"/>
-      <c r="H157" s="121"/>
-      <c r="I157" s="121"/>
-      <c r="J157" s="122"/>
+      <c r="C157" s="63"/>
+      <c r="D157" s="63"/>
+      <c r="E157" s="63"/>
+      <c r="F157" s="63"/>
+      <c r="G157" s="63"/>
+      <c r="H157" s="63"/>
+      <c r="I157" s="63"/>
+      <c r="J157" s="64"/>
       <c r="K157" s="44"/>
     </row>
     <row r="158" spans="1:11">
@@ -15162,17 +15162,17 @@
     </row>
     <row r="162" spans="1:11" ht="24" customHeight="1">
       <c r="A162" s="1"/>
-      <c r="B162" s="120" t="s">
+      <c r="B162" s="62" t="s">
         <v>667</v>
       </c>
-      <c r="C162" s="121"/>
-      <c r="D162" s="121"/>
-      <c r="E162" s="121"/>
-      <c r="F162" s="121"/>
-      <c r="G162" s="121"/>
-      <c r="H162" s="121"/>
-      <c r="I162" s="121"/>
-      <c r="J162" s="122"/>
+      <c r="C162" s="63"/>
+      <c r="D162" s="63"/>
+      <c r="E162" s="63"/>
+      <c r="F162" s="63"/>
+      <c r="G162" s="63"/>
+      <c r="H162" s="63"/>
+      <c r="I162" s="63"/>
+      <c r="J162" s="64"/>
       <c r="K162" s="44"/>
     </row>
     <row r="163" spans="1:11">
@@ -15254,17 +15254,17 @@
     </row>
     <row r="167" spans="1:11" ht="24" customHeight="1">
       <c r="A167" s="1"/>
-      <c r="B167" s="120" t="s">
+      <c r="B167" s="62" t="s">
         <v>669</v>
       </c>
-      <c r="C167" s="121"/>
-      <c r="D167" s="121"/>
-      <c r="E167" s="121"/>
-      <c r="F167" s="121"/>
-      <c r="G167" s="121"/>
-      <c r="H167" s="121"/>
-      <c r="I167" s="121"/>
-      <c r="J167" s="122"/>
+      <c r="C167" s="63"/>
+      <c r="D167" s="63"/>
+      <c r="E167" s="63"/>
+      <c r="F167" s="63"/>
+      <c r="G167" s="63"/>
+      <c r="H167" s="63"/>
+      <c r="I167" s="63"/>
+      <c r="J167" s="64"/>
       <c r="K167" s="44"/>
     </row>
     <row r="168" spans="1:11">
@@ -15342,17 +15342,17 @@
     </row>
     <row r="172" spans="1:11" ht="24" customHeight="1">
       <c r="A172" s="1"/>
-      <c r="B172" s="120" t="s">
+      <c r="B172" s="62" t="s">
         <v>670</v>
       </c>
-      <c r="C172" s="121"/>
-      <c r="D172" s="121"/>
-      <c r="E172" s="121"/>
-      <c r="F172" s="121"/>
-      <c r="G172" s="121"/>
-      <c r="H172" s="121"/>
-      <c r="I172" s="121"/>
-      <c r="J172" s="122"/>
+      <c r="C172" s="63"/>
+      <c r="D172" s="63"/>
+      <c r="E172" s="63"/>
+      <c r="F172" s="63"/>
+      <c r="G172" s="63"/>
+      <c r="H172" s="63"/>
+      <c r="I172" s="63"/>
+      <c r="J172" s="64"/>
       <c r="K172" s="44"/>
     </row>
     <row r="173" spans="1:11">
@@ -15434,17 +15434,17 @@
     </row>
     <row r="177" spans="1:11" ht="24" customHeight="1">
       <c r="A177" s="1"/>
-      <c r="B177" s="120" t="s">
+      <c r="B177" s="62" t="s">
         <v>672</v>
       </c>
-      <c r="C177" s="121"/>
-      <c r="D177" s="121"/>
-      <c r="E177" s="121"/>
-      <c r="F177" s="121"/>
-      <c r="G177" s="121"/>
-      <c r="H177" s="121"/>
-      <c r="I177" s="121"/>
-      <c r="J177" s="122"/>
+      <c r="C177" s="63"/>
+      <c r="D177" s="63"/>
+      <c r="E177" s="63"/>
+      <c r="F177" s="63"/>
+      <c r="G177" s="63"/>
+      <c r="H177" s="63"/>
+      <c r="I177" s="63"/>
+      <c r="J177" s="64"/>
       <c r="K177" s="44"/>
     </row>
     <row r="178" spans="1:11">
@@ -15526,17 +15526,17 @@
     </row>
     <row r="182" spans="1:11" ht="24" customHeight="1">
       <c r="A182" s="1"/>
-      <c r="B182" s="120" t="s">
+      <c r="B182" s="62" t="s">
         <v>674</v>
       </c>
-      <c r="C182" s="121"/>
-      <c r="D182" s="121"/>
-      <c r="E182" s="121"/>
-      <c r="F182" s="121"/>
-      <c r="G182" s="121"/>
-      <c r="H182" s="121"/>
-      <c r="I182" s="121"/>
-      <c r="J182" s="122"/>
+      <c r="C182" s="63"/>
+      <c r="D182" s="63"/>
+      <c r="E182" s="63"/>
+      <c r="F182" s="63"/>
+      <c r="G182" s="63"/>
+      <c r="H182" s="63"/>
+      <c r="I182" s="63"/>
+      <c r="J182" s="64"/>
       <c r="K182" s="44"/>
     </row>
     <row r="183" spans="1:11">
@@ -15618,17 +15618,17 @@
     </row>
     <row r="187" spans="1:11" ht="24" customHeight="1">
       <c r="A187" s="1"/>
-      <c r="B187" s="120" t="s">
+      <c r="B187" s="62" t="s">
         <v>676</v>
       </c>
-      <c r="C187" s="121"/>
-      <c r="D187" s="121"/>
-      <c r="E187" s="121"/>
-      <c r="F187" s="121"/>
-      <c r="G187" s="121"/>
-      <c r="H187" s="121"/>
-      <c r="I187" s="121"/>
-      <c r="J187" s="122"/>
+      <c r="C187" s="63"/>
+      <c r="D187" s="63"/>
+      <c r="E187" s="63"/>
+      <c r="F187" s="63"/>
+      <c r="G187" s="63"/>
+      <c r="H187" s="63"/>
+      <c r="I187" s="63"/>
+      <c r="J187" s="64"/>
       <c r="K187" s="44"/>
     </row>
     <row r="188" spans="1:11">
@@ -15710,17 +15710,17 @@
     </row>
     <row r="192" spans="1:11" ht="24" customHeight="1">
       <c r="A192" s="1"/>
-      <c r="B192" s="120" t="s">
+      <c r="B192" s="62" t="s">
         <v>678</v>
       </c>
-      <c r="C192" s="121"/>
-      <c r="D192" s="121"/>
-      <c r="E192" s="121"/>
-      <c r="F192" s="121"/>
-      <c r="G192" s="121"/>
-      <c r="H192" s="121"/>
-      <c r="I192" s="121"/>
-      <c r="J192" s="122"/>
+      <c r="C192" s="63"/>
+      <c r="D192" s="63"/>
+      <c r="E192" s="63"/>
+      <c r="F192" s="63"/>
+      <c r="G192" s="63"/>
+      <c r="H192" s="63"/>
+      <c r="I192" s="63"/>
+      <c r="J192" s="64"/>
       <c r="K192" s="44"/>
     </row>
     <row r="193" spans="1:11">
@@ -15802,17 +15802,17 @@
     </row>
     <row r="197" spans="1:11" ht="24" customHeight="1">
       <c r="A197" s="1"/>
-      <c r="B197" s="120" t="s">
+      <c r="B197" s="62" t="s">
         <v>680</v>
       </c>
-      <c r="C197" s="121"/>
-      <c r="D197" s="121"/>
-      <c r="E197" s="121"/>
-      <c r="F197" s="121"/>
-      <c r="G197" s="121"/>
-      <c r="H197" s="121"/>
-      <c r="I197" s="121"/>
-      <c r="J197" s="122"/>
+      <c r="C197" s="63"/>
+      <c r="D197" s="63"/>
+      <c r="E197" s="63"/>
+      <c r="F197" s="63"/>
+      <c r="G197" s="63"/>
+      <c r="H197" s="63"/>
+      <c r="I197" s="63"/>
+      <c r="J197" s="64"/>
       <c r="K197" s="44"/>
     </row>
     <row r="198" spans="1:11">
@@ -15894,17 +15894,17 @@
     </row>
     <row r="202" spans="1:11" ht="24" customHeight="1">
       <c r="A202" s="1"/>
-      <c r="B202" s="120" t="s">
+      <c r="B202" s="62" t="s">
         <v>682</v>
       </c>
-      <c r="C202" s="121"/>
-      <c r="D202" s="121"/>
-      <c r="E202" s="121"/>
-      <c r="F202" s="121"/>
-      <c r="G202" s="121"/>
-      <c r="H202" s="121"/>
-      <c r="I202" s="121"/>
-      <c r="J202" s="122"/>
+      <c r="C202" s="63"/>
+      <c r="D202" s="63"/>
+      <c r="E202" s="63"/>
+      <c r="F202" s="63"/>
+      <c r="G202" s="63"/>
+      <c r="H202" s="63"/>
+      <c r="I202" s="63"/>
+      <c r="J202" s="64"/>
       <c r="K202" s="44"/>
     </row>
     <row r="203" spans="1:11">
@@ -15986,17 +15986,17 @@
     </row>
     <row r="207" spans="1:11" ht="24" customHeight="1">
       <c r="A207" s="1"/>
-      <c r="B207" s="120" t="s">
+      <c r="B207" s="62" t="s">
         <v>684</v>
       </c>
-      <c r="C207" s="121"/>
-      <c r="D207" s="121"/>
-      <c r="E207" s="121"/>
-      <c r="F207" s="121"/>
-      <c r="G207" s="121"/>
-      <c r="H207" s="121"/>
-      <c r="I207" s="121"/>
-      <c r="J207" s="122"/>
+      <c r="C207" s="63"/>
+      <c r="D207" s="63"/>
+      <c r="E207" s="63"/>
+      <c r="F207" s="63"/>
+      <c r="G207" s="63"/>
+      <c r="H207" s="63"/>
+      <c r="I207" s="63"/>
+      <c r="J207" s="64"/>
       <c r="K207" s="44"/>
     </row>
     <row r="208" spans="1:11">
@@ -16078,17 +16078,17 @@
     </row>
     <row r="212" spans="1:11" ht="24" customHeight="1">
       <c r="A212" s="1"/>
-      <c r="B212" s="120" t="s">
+      <c r="B212" s="62" t="s">
         <v>686</v>
       </c>
-      <c r="C212" s="121"/>
-      <c r="D212" s="121"/>
-      <c r="E212" s="121"/>
-      <c r="F212" s="121"/>
-      <c r="G212" s="121"/>
-      <c r="H212" s="121"/>
-      <c r="I212" s="121"/>
-      <c r="J212" s="122"/>
+      <c r="C212" s="63"/>
+      <c r="D212" s="63"/>
+      <c r="E212" s="63"/>
+      <c r="F212" s="63"/>
+      <c r="G212" s="63"/>
+      <c r="H212" s="63"/>
+      <c r="I212" s="63"/>
+      <c r="J212" s="64"/>
       <c r="K212" s="44"/>
     </row>
     <row r="213" spans="1:11">
@@ -16170,17 +16170,17 @@
     </row>
     <row r="217" spans="1:11" ht="24" customHeight="1">
       <c r="A217" s="1"/>
-      <c r="B217" s="120" t="s">
+      <c r="B217" s="62" t="s">
         <v>688</v>
       </c>
-      <c r="C217" s="121"/>
-      <c r="D217" s="121"/>
-      <c r="E217" s="121"/>
-      <c r="F217" s="121"/>
-      <c r="G217" s="121"/>
-      <c r="H217" s="121"/>
-      <c r="I217" s="121"/>
-      <c r="J217" s="122"/>
+      <c r="C217" s="63"/>
+      <c r="D217" s="63"/>
+      <c r="E217" s="63"/>
+      <c r="F217" s="63"/>
+      <c r="G217" s="63"/>
+      <c r="H217" s="63"/>
+      <c r="I217" s="63"/>
+      <c r="J217" s="64"/>
       <c r="K217" s="44"/>
     </row>
     <row r="218" spans="1:11">
@@ -16262,17 +16262,17 @@
     </row>
     <row r="222" spans="1:11" ht="24" customHeight="1">
       <c r="A222" s="1"/>
-      <c r="B222" s="120" t="s">
+      <c r="B222" s="62" t="s">
         <v>689</v>
       </c>
-      <c r="C222" s="121"/>
-      <c r="D222" s="121"/>
-      <c r="E222" s="121"/>
-      <c r="F222" s="121"/>
-      <c r="G222" s="121"/>
-      <c r="H222" s="121"/>
-      <c r="I222" s="121"/>
-      <c r="J222" s="122"/>
+      <c r="C222" s="63"/>
+      <c r="D222" s="63"/>
+      <c r="E222" s="63"/>
+      <c r="F222" s="63"/>
+      <c r="G222" s="63"/>
+      <c r="H222" s="63"/>
+      <c r="I222" s="63"/>
+      <c r="J222" s="64"/>
       <c r="K222" s="44"/>
     </row>
     <row r="223" spans="1:11">
@@ -16354,17 +16354,17 @@
     </row>
     <row r="227" spans="1:11" ht="24" customHeight="1">
       <c r="A227" s="1"/>
-      <c r="B227" s="120" t="s">
+      <c r="B227" s="62" t="s">
         <v>691</v>
       </c>
-      <c r="C227" s="121"/>
-      <c r="D227" s="121"/>
-      <c r="E227" s="121"/>
-      <c r="F227" s="121"/>
-      <c r="G227" s="121"/>
-      <c r="H227" s="121"/>
-      <c r="I227" s="121"/>
-      <c r="J227" s="122"/>
+      <c r="C227" s="63"/>
+      <c r="D227" s="63"/>
+      <c r="E227" s="63"/>
+      <c r="F227" s="63"/>
+      <c r="G227" s="63"/>
+      <c r="H227" s="63"/>
+      <c r="I227" s="63"/>
+      <c r="J227" s="64"/>
       <c r="K227" s="44"/>
     </row>
     <row r="228" spans="1:11">
@@ -16446,17 +16446,17 @@
     </row>
     <row r="232" spans="1:11" ht="24" customHeight="1">
       <c r="A232" s="1"/>
-      <c r="B232" s="120" t="s">
+      <c r="B232" s="62" t="s">
         <v>693</v>
       </c>
-      <c r="C232" s="121"/>
-      <c r="D232" s="121"/>
-      <c r="E232" s="121"/>
-      <c r="F232" s="121"/>
-      <c r="G232" s="121"/>
-      <c r="H232" s="121"/>
-      <c r="I232" s="121"/>
-      <c r="J232" s="122"/>
+      <c r="C232" s="63"/>
+      <c r="D232" s="63"/>
+      <c r="E232" s="63"/>
+      <c r="F232" s="63"/>
+      <c r="G232" s="63"/>
+      <c r="H232" s="63"/>
+      <c r="I232" s="63"/>
+      <c r="J232" s="64"/>
       <c r="K232" s="44"/>
     </row>
     <row r="233" spans="1:11">
@@ -16538,17 +16538,17 @@
     </row>
     <row r="237" spans="1:11" ht="24" customHeight="1">
       <c r="A237" s="1"/>
-      <c r="B237" s="120" t="s">
+      <c r="B237" s="62" t="s">
         <v>695</v>
       </c>
-      <c r="C237" s="121"/>
-      <c r="D237" s="121"/>
-      <c r="E237" s="121"/>
-      <c r="F237" s="121"/>
-      <c r="G237" s="121"/>
-      <c r="H237" s="121"/>
-      <c r="I237" s="121"/>
-      <c r="J237" s="122"/>
+      <c r="C237" s="63"/>
+      <c r="D237" s="63"/>
+      <c r="E237" s="63"/>
+      <c r="F237" s="63"/>
+      <c r="G237" s="63"/>
+      <c r="H237" s="63"/>
+      <c r="I237" s="63"/>
+      <c r="J237" s="64"/>
       <c r="K237" s="44"/>
     </row>
     <row r="238" spans="1:11">
@@ -16630,17 +16630,17 @@
     </row>
     <row r="242" spans="1:11" ht="24" customHeight="1">
       <c r="A242" s="1"/>
-      <c r="B242" s="120" t="s">
+      <c r="B242" s="62" t="s">
         <v>697</v>
       </c>
-      <c r="C242" s="121"/>
-      <c r="D242" s="121"/>
-      <c r="E242" s="121"/>
-      <c r="F242" s="121"/>
-      <c r="G242" s="121"/>
-      <c r="H242" s="121"/>
-      <c r="I242" s="121"/>
-      <c r="J242" s="122"/>
+      <c r="C242" s="63"/>
+      <c r="D242" s="63"/>
+      <c r="E242" s="63"/>
+      <c r="F242" s="63"/>
+      <c r="G242" s="63"/>
+      <c r="H242" s="63"/>
+      <c r="I242" s="63"/>
+      <c r="J242" s="64"/>
       <c r="K242" s="44"/>
     </row>
     <row r="243" spans="1:11">
@@ -16722,17 +16722,17 @@
     </row>
     <row r="247" spans="1:11" ht="24" customHeight="1">
       <c r="A247" s="1"/>
-      <c r="B247" s="120" t="s">
+      <c r="B247" s="62" t="s">
         <v>699</v>
       </c>
-      <c r="C247" s="121"/>
-      <c r="D247" s="121"/>
-      <c r="E247" s="121"/>
-      <c r="F247" s="121"/>
-      <c r="G247" s="121"/>
-      <c r="H247" s="121"/>
-      <c r="I247" s="121"/>
-      <c r="J247" s="122"/>
+      <c r="C247" s="63"/>
+      <c r="D247" s="63"/>
+      <c r="E247" s="63"/>
+      <c r="F247" s="63"/>
+      <c r="G247" s="63"/>
+      <c r="H247" s="63"/>
+      <c r="I247" s="63"/>
+      <c r="J247" s="64"/>
       <c r="K247" s="44"/>
     </row>
     <row r="248" spans="1:11">
@@ -16814,17 +16814,17 @@
     </row>
     <row r="252" spans="1:11" ht="24" customHeight="1">
       <c r="A252" s="1"/>
-      <c r="B252" s="120" t="s">
+      <c r="B252" s="62" t="s">
         <v>701</v>
       </c>
-      <c r="C252" s="121"/>
-      <c r="D252" s="121"/>
-      <c r="E252" s="121"/>
-      <c r="F252" s="121"/>
-      <c r="G252" s="121"/>
-      <c r="H252" s="121"/>
-      <c r="I252" s="121"/>
-      <c r="J252" s="122"/>
+      <c r="C252" s="63"/>
+      <c r="D252" s="63"/>
+      <c r="E252" s="63"/>
+      <c r="F252" s="63"/>
+      <c r="G252" s="63"/>
+      <c r="H252" s="63"/>
+      <c r="I252" s="63"/>
+      <c r="J252" s="64"/>
       <c r="K252" s="44"/>
     </row>
     <row r="253" spans="1:11">
@@ -16906,17 +16906,17 @@
     </row>
     <row r="257" spans="1:11" ht="24" customHeight="1">
       <c r="A257" s="1"/>
-      <c r="B257" s="120" t="s">
+      <c r="B257" s="62" t="s">
         <v>703</v>
       </c>
-      <c r="C257" s="121"/>
-      <c r="D257" s="121"/>
-      <c r="E257" s="121"/>
-      <c r="F257" s="121"/>
-      <c r="G257" s="121"/>
-      <c r="H257" s="121"/>
-      <c r="I257" s="121"/>
-      <c r="J257" s="122"/>
+      <c r="C257" s="63"/>
+      <c r="D257" s="63"/>
+      <c r="E257" s="63"/>
+      <c r="F257" s="63"/>
+      <c r="G257" s="63"/>
+      <c r="H257" s="63"/>
+      <c r="I257" s="63"/>
+      <c r="J257" s="64"/>
       <c r="K257" s="44"/>
     </row>
     <row r="258" spans="1:11">
@@ -16998,17 +16998,17 @@
     </row>
     <row r="262" spans="1:11" ht="24" customHeight="1">
       <c r="A262" s="1"/>
-      <c r="B262" s="120" t="s">
+      <c r="B262" s="62" t="s">
         <v>705</v>
       </c>
-      <c r="C262" s="121"/>
-      <c r="D262" s="121"/>
-      <c r="E262" s="121"/>
-      <c r="F262" s="121"/>
-      <c r="G262" s="121"/>
-      <c r="H262" s="121"/>
-      <c r="I262" s="121"/>
-      <c r="J262" s="122"/>
+      <c r="C262" s="63"/>
+      <c r="D262" s="63"/>
+      <c r="E262" s="63"/>
+      <c r="F262" s="63"/>
+      <c r="G262" s="63"/>
+      <c r="H262" s="63"/>
+      <c r="I262" s="63"/>
+      <c r="J262" s="64"/>
       <c r="K262" s="44"/>
     </row>
     <row r="263" spans="1:11">
@@ -17090,17 +17090,17 @@
     </row>
     <row r="267" spans="1:11" ht="24" customHeight="1">
       <c r="A267" s="1"/>
-      <c r="B267" s="120" t="s">
+      <c r="B267" s="62" t="s">
         <v>707</v>
       </c>
-      <c r="C267" s="121"/>
-      <c r="D267" s="121"/>
-      <c r="E267" s="121"/>
-      <c r="F267" s="121"/>
-      <c r="G267" s="121"/>
-      <c r="H267" s="121"/>
-      <c r="I267" s="121"/>
-      <c r="J267" s="122"/>
+      <c r="C267" s="63"/>
+      <c r="D267" s="63"/>
+      <c r="E267" s="63"/>
+      <c r="F267" s="63"/>
+      <c r="G267" s="63"/>
+      <c r="H267" s="63"/>
+      <c r="I267" s="63"/>
+      <c r="J267" s="64"/>
       <c r="K267" s="44"/>
     </row>
     <row r="268" spans="1:11">
@@ -17182,17 +17182,17 @@
     </row>
     <row r="272" spans="1:11" ht="24" customHeight="1">
       <c r="A272" s="1"/>
-      <c r="B272" s="120" t="s">
+      <c r="B272" s="62" t="s">
         <v>709</v>
       </c>
-      <c r="C272" s="121"/>
-      <c r="D272" s="121"/>
-      <c r="E272" s="121"/>
-      <c r="F272" s="121"/>
-      <c r="G272" s="121"/>
-      <c r="H272" s="121"/>
-      <c r="I272" s="121"/>
-      <c r="J272" s="122"/>
+      <c r="C272" s="63"/>
+      <c r="D272" s="63"/>
+      <c r="E272" s="63"/>
+      <c r="F272" s="63"/>
+      <c r="G272" s="63"/>
+      <c r="H272" s="63"/>
+      <c r="I272" s="63"/>
+      <c r="J272" s="64"/>
       <c r="K272" s="44"/>
     </row>
     <row r="273" spans="1:11">
@@ -17274,17 +17274,17 @@
     </row>
     <row r="277" spans="1:11" ht="24" customHeight="1">
       <c r="A277" s="1"/>
-      <c r="B277" s="120" t="s">
+      <c r="B277" s="62" t="s">
         <v>711</v>
       </c>
-      <c r="C277" s="121"/>
-      <c r="D277" s="121"/>
-      <c r="E277" s="121"/>
-      <c r="F277" s="121"/>
-      <c r="G277" s="121"/>
-      <c r="H277" s="121"/>
-      <c r="I277" s="121"/>
-      <c r="J277" s="122"/>
+      <c r="C277" s="63"/>
+      <c r="D277" s="63"/>
+      <c r="E277" s="63"/>
+      <c r="F277" s="63"/>
+      <c r="G277" s="63"/>
+      <c r="H277" s="63"/>
+      <c r="I277" s="63"/>
+      <c r="J277" s="64"/>
       <c r="K277" s="44"/>
     </row>
     <row r="278" spans="1:11">
@@ -17366,17 +17366,17 @@
     </row>
     <row r="282" spans="1:11" ht="24" customHeight="1">
       <c r="A282" s="1"/>
-      <c r="B282" s="120" t="s">
+      <c r="B282" s="62" t="s">
         <v>713</v>
       </c>
-      <c r="C282" s="121"/>
-      <c r="D282" s="121"/>
-      <c r="E282" s="121"/>
-      <c r="F282" s="121"/>
-      <c r="G282" s="121"/>
-      <c r="H282" s="121"/>
-      <c r="I282" s="121"/>
-      <c r="J282" s="122"/>
+      <c r="C282" s="63"/>
+      <c r="D282" s="63"/>
+      <c r="E282" s="63"/>
+      <c r="F282" s="63"/>
+      <c r="G282" s="63"/>
+      <c r="H282" s="63"/>
+      <c r="I282" s="63"/>
+      <c r="J282" s="64"/>
       <c r="K282" s="44"/>
     </row>
     <row r="283" spans="1:11">
@@ -17458,17 +17458,17 @@
     </row>
     <row r="287" spans="1:11" ht="24" customHeight="1">
       <c r="A287" s="1"/>
-      <c r="B287" s="120" t="s">
+      <c r="B287" s="62" t="s">
         <v>715</v>
       </c>
-      <c r="C287" s="121"/>
-      <c r="D287" s="121"/>
-      <c r="E287" s="121"/>
-      <c r="F287" s="121"/>
-      <c r="G287" s="121"/>
-      <c r="H287" s="121"/>
-      <c r="I287" s="121"/>
-      <c r="J287" s="122"/>
+      <c r="C287" s="63"/>
+      <c r="D287" s="63"/>
+      <c r="E287" s="63"/>
+      <c r="F287" s="63"/>
+      <c r="G287" s="63"/>
+      <c r="H287" s="63"/>
+      <c r="I287" s="63"/>
+      <c r="J287" s="64"/>
       <c r="K287" s="44"/>
     </row>
     <row r="288" spans="1:11">
@@ -17550,17 +17550,17 @@
     </row>
     <row r="292" spans="1:11" ht="24" customHeight="1">
       <c r="A292" s="1"/>
-      <c r="B292" s="120" t="s">
+      <c r="B292" s="62" t="s">
         <v>717</v>
       </c>
-      <c r="C292" s="121"/>
-      <c r="D292" s="121"/>
-      <c r="E292" s="121"/>
-      <c r="F292" s="121"/>
-      <c r="G292" s="121"/>
-      <c r="H292" s="121"/>
-      <c r="I292" s="121"/>
-      <c r="J292" s="122"/>
+      <c r="C292" s="63"/>
+      <c r="D292" s="63"/>
+      <c r="E292" s="63"/>
+      <c r="F292" s="63"/>
+      <c r="G292" s="63"/>
+      <c r="H292" s="63"/>
+      <c r="I292" s="63"/>
+      <c r="J292" s="64"/>
       <c r="K292" s="44"/>
     </row>
     <row r="293" spans="1:11">
@@ -17642,17 +17642,17 @@
     </row>
     <row r="297" spans="1:11" ht="24" customHeight="1">
       <c r="A297" s="1"/>
-      <c r="B297" s="120" t="s">
+      <c r="B297" s="62" t="s">
         <v>719</v>
       </c>
-      <c r="C297" s="121"/>
-      <c r="D297" s="121"/>
-      <c r="E297" s="121"/>
-      <c r="F297" s="121"/>
-      <c r="G297" s="121"/>
-      <c r="H297" s="121"/>
-      <c r="I297" s="121"/>
-      <c r="J297" s="122"/>
+      <c r="C297" s="63"/>
+      <c r="D297" s="63"/>
+      <c r="E297" s="63"/>
+      <c r="F297" s="63"/>
+      <c r="G297" s="63"/>
+      <c r="H297" s="63"/>
+      <c r="I297" s="63"/>
+      <c r="J297" s="64"/>
       <c r="K297" s="44"/>
     </row>
     <row r="298" spans="1:11">
@@ -17734,17 +17734,17 @@
     </row>
     <row r="302" spans="1:11" ht="24" customHeight="1">
       <c r="A302" s="1"/>
-      <c r="B302" s="120" t="s">
+      <c r="B302" s="62" t="s">
         <v>721</v>
       </c>
-      <c r="C302" s="121"/>
-      <c r="D302" s="121"/>
-      <c r="E302" s="121"/>
-      <c r="F302" s="121"/>
-      <c r="G302" s="121"/>
-      <c r="H302" s="121"/>
-      <c r="I302" s="121"/>
-      <c r="J302" s="122"/>
+      <c r="C302" s="63"/>
+      <c r="D302" s="63"/>
+      <c r="E302" s="63"/>
+      <c r="F302" s="63"/>
+      <c r="G302" s="63"/>
+      <c r="H302" s="63"/>
+      <c r="I302" s="63"/>
+      <c r="J302" s="64"/>
       <c r="K302" s="44"/>
     </row>
     <row r="303" spans="1:11">
@@ -17826,17 +17826,17 @@
     </row>
     <row r="307" spans="1:11" ht="24" customHeight="1">
       <c r="A307" s="1"/>
-      <c r="B307" s="120" t="s">
+      <c r="B307" s="62" t="s">
         <v>723</v>
       </c>
-      <c r="C307" s="121"/>
-      <c r="D307" s="121"/>
-      <c r="E307" s="121"/>
-      <c r="F307" s="121"/>
-      <c r="G307" s="121"/>
-      <c r="H307" s="121"/>
-      <c r="I307" s="121"/>
-      <c r="J307" s="122"/>
+      <c r="C307" s="63"/>
+      <c r="D307" s="63"/>
+      <c r="E307" s="63"/>
+      <c r="F307" s="63"/>
+      <c r="G307" s="63"/>
+      <c r="H307" s="63"/>
+      <c r="I307" s="63"/>
+      <c r="J307" s="64"/>
       <c r="K307" s="44"/>
     </row>
     <row r="308" spans="1:11">
@@ -17918,17 +17918,17 @@
     </row>
     <row r="312" spans="1:11" ht="24" customHeight="1">
       <c r="A312" s="1"/>
-      <c r="B312" s="120" t="s">
+      <c r="B312" s="62" t="s">
         <v>725</v>
       </c>
-      <c r="C312" s="121"/>
-      <c r="D312" s="121"/>
-      <c r="E312" s="121"/>
-      <c r="F312" s="121"/>
-      <c r="G312" s="121"/>
-      <c r="H312" s="121"/>
-      <c r="I312" s="121"/>
-      <c r="J312" s="122"/>
+      <c r="C312" s="63"/>
+      <c r="D312" s="63"/>
+      <c r="E312" s="63"/>
+      <c r="F312" s="63"/>
+      <c r="G312" s="63"/>
+      <c r="H312" s="63"/>
+      <c r="I312" s="63"/>
+      <c r="J312" s="64"/>
       <c r="K312" s="44"/>
     </row>
     <row r="313" spans="1:11">
@@ -18010,17 +18010,17 @@
     </row>
     <row r="317" spans="1:11" ht="24" customHeight="1">
       <c r="A317" s="1"/>
-      <c r="B317" s="120" t="s">
+      <c r="B317" s="62" t="s">
         <v>727</v>
       </c>
-      <c r="C317" s="121"/>
-      <c r="D317" s="121"/>
-      <c r="E317" s="121"/>
-      <c r="F317" s="121"/>
-      <c r="G317" s="121"/>
-      <c r="H317" s="121"/>
-      <c r="I317" s="121"/>
-      <c r="J317" s="122"/>
+      <c r="C317" s="63"/>
+      <c r="D317" s="63"/>
+      <c r="E317" s="63"/>
+      <c r="F317" s="63"/>
+      <c r="G317" s="63"/>
+      <c r="H317" s="63"/>
+      <c r="I317" s="63"/>
+      <c r="J317" s="64"/>
       <c r="K317" s="44"/>
     </row>
     <row r="318" spans="1:11">
@@ -18102,17 +18102,17 @@
     </row>
     <row r="322" spans="1:11" ht="24" customHeight="1">
       <c r="A322" s="1"/>
-      <c r="B322" s="120" t="s">
+      <c r="B322" s="62" t="s">
         <v>729</v>
       </c>
-      <c r="C322" s="121"/>
-      <c r="D322" s="121"/>
-      <c r="E322" s="121"/>
-      <c r="F322" s="121"/>
-      <c r="G322" s="121"/>
-      <c r="H322" s="121"/>
-      <c r="I322" s="121"/>
-      <c r="J322" s="122"/>
+      <c r="C322" s="63"/>
+      <c r="D322" s="63"/>
+      <c r="E322" s="63"/>
+      <c r="F322" s="63"/>
+      <c r="G322" s="63"/>
+      <c r="H322" s="63"/>
+      <c r="I322" s="63"/>
+      <c r="J322" s="64"/>
       <c r="K322" s="44"/>
     </row>
     <row r="323" spans="1:11">
@@ -18194,17 +18194,17 @@
     </row>
     <row r="327" spans="1:11" ht="24" customHeight="1">
       <c r="A327" s="1"/>
-      <c r="B327" s="120" t="s">
+      <c r="B327" s="62" t="s">
         <v>731</v>
       </c>
-      <c r="C327" s="121"/>
-      <c r="D327" s="121"/>
-      <c r="E327" s="121"/>
-      <c r="F327" s="121"/>
-      <c r="G327" s="121"/>
-      <c r="H327" s="121"/>
-      <c r="I327" s="121"/>
-      <c r="J327" s="122"/>
+      <c r="C327" s="63"/>
+      <c r="D327" s="63"/>
+      <c r="E327" s="63"/>
+      <c r="F327" s="63"/>
+      <c r="G327" s="63"/>
+      <c r="H327" s="63"/>
+      <c r="I327" s="63"/>
+      <c r="J327" s="64"/>
       <c r="K327" s="44"/>
     </row>
     <row r="328" spans="1:11">
@@ -18286,17 +18286,17 @@
     </row>
     <row r="332" spans="1:11" ht="24" customHeight="1">
       <c r="A332" s="1"/>
-      <c r="B332" s="120" t="s">
+      <c r="B332" s="62" t="s">
         <v>733</v>
       </c>
-      <c r="C332" s="121"/>
-      <c r="D332" s="121"/>
-      <c r="E332" s="121"/>
-      <c r="F332" s="121"/>
-      <c r="G332" s="121"/>
-      <c r="H332" s="121"/>
-      <c r="I332" s="121"/>
-      <c r="J332" s="122"/>
+      <c r="C332" s="63"/>
+      <c r="D332" s="63"/>
+      <c r="E332" s="63"/>
+      <c r="F332" s="63"/>
+      <c r="G332" s="63"/>
+      <c r="H332" s="63"/>
+      <c r="I332" s="63"/>
+      <c r="J332" s="64"/>
       <c r="K332" s="44"/>
     </row>
     <row r="333" spans="1:11">
@@ -18378,17 +18378,17 @@
     </row>
     <row r="337" spans="1:11" ht="24" customHeight="1">
       <c r="A337" s="1"/>
-      <c r="B337" s="120" t="s">
+      <c r="B337" s="62" t="s">
         <v>734</v>
       </c>
-      <c r="C337" s="121"/>
-      <c r="D337" s="121"/>
-      <c r="E337" s="121"/>
-      <c r="F337" s="121"/>
-      <c r="G337" s="121"/>
-      <c r="H337" s="121"/>
-      <c r="I337" s="121"/>
-      <c r="J337" s="122"/>
+      <c r="C337" s="63"/>
+      <c r="D337" s="63"/>
+      <c r="E337" s="63"/>
+      <c r="F337" s="63"/>
+      <c r="G337" s="63"/>
+      <c r="H337" s="63"/>
+      <c r="I337" s="63"/>
+      <c r="J337" s="64"/>
       <c r="K337" s="44"/>
     </row>
     <row r="338" spans="1:11">
@@ -18470,17 +18470,17 @@
     </row>
     <row r="342" spans="1:11" ht="24" customHeight="1">
       <c r="A342" s="1"/>
-      <c r="B342" s="120" t="s">
+      <c r="B342" s="62" t="s">
         <v>736</v>
       </c>
-      <c r="C342" s="121"/>
-      <c r="D342" s="121"/>
-      <c r="E342" s="121"/>
-      <c r="F342" s="121"/>
-      <c r="G342" s="121"/>
-      <c r="H342" s="121"/>
-      <c r="I342" s="121"/>
-      <c r="J342" s="122"/>
+      <c r="C342" s="63"/>
+      <c r="D342" s="63"/>
+      <c r="E342" s="63"/>
+      <c r="F342" s="63"/>
+      <c r="G342" s="63"/>
+      <c r="H342" s="63"/>
+      <c r="I342" s="63"/>
+      <c r="J342" s="64"/>
       <c r="K342" s="44"/>
     </row>
     <row r="343" spans="1:11">
@@ -18562,17 +18562,17 @@
     </row>
     <row r="347" spans="1:11" ht="24" customHeight="1">
       <c r="A347" s="1"/>
-      <c r="B347" s="120" t="s">
+      <c r="B347" s="62" t="s">
         <v>738</v>
       </c>
-      <c r="C347" s="121"/>
-      <c r="D347" s="121"/>
-      <c r="E347" s="121"/>
-      <c r="F347" s="121"/>
-      <c r="G347" s="121"/>
-      <c r="H347" s="121"/>
-      <c r="I347" s="121"/>
-      <c r="J347" s="122"/>
+      <c r="C347" s="63"/>
+      <c r="D347" s="63"/>
+      <c r="E347" s="63"/>
+      <c r="F347" s="63"/>
+      <c r="G347" s="63"/>
+      <c r="H347" s="63"/>
+      <c r="I347" s="63"/>
+      <c r="J347" s="64"/>
       <c r="K347" s="44"/>
     </row>
     <row r="348" spans="1:11">
@@ -18643,7 +18643,7 @@
         <v>2</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H351" s="3"/>
       <c r="I351" s="2"/>
@@ -18654,17 +18654,17 @@
     </row>
     <row r="352" spans="1:11" ht="24" customHeight="1">
       <c r="A352" s="1"/>
-      <c r="B352" s="120" t="s">
+      <c r="B352" s="62" t="s">
         <v>740</v>
       </c>
-      <c r="C352" s="121"/>
-      <c r="D352" s="121"/>
-      <c r="E352" s="121"/>
-      <c r="F352" s="121"/>
-      <c r="G352" s="121"/>
-      <c r="H352" s="121"/>
-      <c r="I352" s="121"/>
-      <c r="J352" s="122"/>
+      <c r="C352" s="63"/>
+      <c r="D352" s="63"/>
+      <c r="E352" s="63"/>
+      <c r="F352" s="63"/>
+      <c r="G352" s="63"/>
+      <c r="H352" s="63"/>
+      <c r="I352" s="63"/>
+      <c r="J352" s="64"/>
       <c r="K352" s="44"/>
     </row>
     <row r="353" spans="1:11">
@@ -18746,17 +18746,17 @@
     </row>
     <row r="357" spans="1:11" ht="24" customHeight="1">
       <c r="A357" s="1"/>
-      <c r="B357" s="120" t="s">
+      <c r="B357" s="62" t="s">
         <v>742</v>
       </c>
-      <c r="C357" s="121"/>
-      <c r="D357" s="121"/>
-      <c r="E357" s="121"/>
-      <c r="F357" s="121"/>
-      <c r="G357" s="121"/>
-      <c r="H357" s="121"/>
-      <c r="I357" s="121"/>
-      <c r="J357" s="122"/>
+      <c r="C357" s="63"/>
+      <c r="D357" s="63"/>
+      <c r="E357" s="63"/>
+      <c r="F357" s="63"/>
+      <c r="G357" s="63"/>
+      <c r="H357" s="63"/>
+      <c r="I357" s="63"/>
+      <c r="J357" s="64"/>
       <c r="K357" s="44"/>
     </row>
     <row r="358" spans="1:11">
@@ -18838,17 +18838,17 @@
     </row>
     <row r="362" spans="1:11" ht="24" customHeight="1">
       <c r="A362" s="1"/>
-      <c r="B362" s="120" t="s">
+      <c r="B362" s="62" t="s">
         <v>744</v>
       </c>
-      <c r="C362" s="121"/>
-      <c r="D362" s="121"/>
-      <c r="E362" s="121"/>
-      <c r="F362" s="121"/>
-      <c r="G362" s="121"/>
-      <c r="H362" s="121"/>
-      <c r="I362" s="121"/>
-      <c r="J362" s="122"/>
+      <c r="C362" s="63"/>
+      <c r="D362" s="63"/>
+      <c r="E362" s="63"/>
+      <c r="F362" s="63"/>
+      <c r="G362" s="63"/>
+      <c r="H362" s="63"/>
+      <c r="I362" s="63"/>
+      <c r="J362" s="64"/>
       <c r="K362" s="44"/>
     </row>
     <row r="363" spans="1:11">
@@ -18930,17 +18930,17 @@
     </row>
     <row r="367" spans="1:11" ht="24" customHeight="1">
       <c r="A367" s="1"/>
-      <c r="B367" s="120" t="s">
+      <c r="B367" s="62" t="s">
         <v>745</v>
       </c>
-      <c r="C367" s="121"/>
-      <c r="D367" s="121"/>
-      <c r="E367" s="121"/>
-      <c r="F367" s="121"/>
-      <c r="G367" s="121"/>
-      <c r="H367" s="121"/>
-      <c r="I367" s="121"/>
-      <c r="J367" s="122"/>
+      <c r="C367" s="63"/>
+      <c r="D367" s="63"/>
+      <c r="E367" s="63"/>
+      <c r="F367" s="63"/>
+      <c r="G367" s="63"/>
+      <c r="H367" s="63"/>
+      <c r="I367" s="63"/>
+      <c r="J367" s="64"/>
       <c r="K367" s="44"/>
     </row>
     <row r="368" spans="1:11">
@@ -19022,17 +19022,17 @@
     </row>
     <row r="372" spans="1:11" ht="24" customHeight="1">
       <c r="A372" s="1"/>
-      <c r="B372" s="120" t="s">
+      <c r="B372" s="62" t="s">
         <v>747</v>
       </c>
-      <c r="C372" s="121"/>
-      <c r="D372" s="121"/>
-      <c r="E372" s="121"/>
-      <c r="F372" s="121"/>
-      <c r="G372" s="121"/>
-      <c r="H372" s="121"/>
-      <c r="I372" s="121"/>
-      <c r="J372" s="122"/>
+      <c r="C372" s="63"/>
+      <c r="D372" s="63"/>
+      <c r="E372" s="63"/>
+      <c r="F372" s="63"/>
+      <c r="G372" s="63"/>
+      <c r="H372" s="63"/>
+      <c r="I372" s="63"/>
+      <c r="J372" s="64"/>
       <c r="K372" s="44"/>
     </row>
     <row r="373" spans="1:11">
@@ -19114,17 +19114,17 @@
     </row>
     <row r="377" spans="1:11" ht="24" customHeight="1">
       <c r="A377" s="1"/>
-      <c r="B377" s="120" t="s">
+      <c r="B377" s="62" t="s">
         <v>749</v>
       </c>
-      <c r="C377" s="121"/>
-      <c r="D377" s="121"/>
-      <c r="E377" s="121"/>
-      <c r="F377" s="121"/>
-      <c r="G377" s="121"/>
-      <c r="H377" s="121"/>
-      <c r="I377" s="121"/>
-      <c r="J377" s="122"/>
+      <c r="C377" s="63"/>
+      <c r="D377" s="63"/>
+      <c r="E377" s="63"/>
+      <c r="F377" s="63"/>
+      <c r="G377" s="63"/>
+      <c r="H377" s="63"/>
+      <c r="I377" s="63"/>
+      <c r="J377" s="64"/>
       <c r="K377" s="44"/>
     </row>
     <row r="378" spans="1:11">
@@ -19206,17 +19206,17 @@
     </row>
     <row r="382" spans="1:11" ht="24" customHeight="1">
       <c r="A382" s="1"/>
-      <c r="B382" s="120" t="s">
+      <c r="B382" s="62" t="s">
         <v>751</v>
       </c>
-      <c r="C382" s="121"/>
-      <c r="D382" s="121"/>
-      <c r="E382" s="121"/>
-      <c r="F382" s="121"/>
-      <c r="G382" s="121"/>
-      <c r="H382" s="121"/>
-      <c r="I382" s="121"/>
-      <c r="J382" s="122"/>
+      <c r="C382" s="63"/>
+      <c r="D382" s="63"/>
+      <c r="E382" s="63"/>
+      <c r="F382" s="63"/>
+      <c r="G382" s="63"/>
+      <c r="H382" s="63"/>
+      <c r="I382" s="63"/>
+      <c r="J382" s="64"/>
       <c r="K382" s="44"/>
     </row>
     <row r="383" spans="1:11">
@@ -19298,17 +19298,17 @@
     </row>
     <row r="387" spans="1:11" ht="24" customHeight="1">
       <c r="A387" s="1"/>
-      <c r="B387" s="120" t="s">
+      <c r="B387" s="62" t="s">
         <v>753</v>
       </c>
-      <c r="C387" s="121"/>
-      <c r="D387" s="121"/>
-      <c r="E387" s="121"/>
-      <c r="F387" s="121"/>
-      <c r="G387" s="121"/>
-      <c r="H387" s="121"/>
-      <c r="I387" s="121"/>
-      <c r="J387" s="122"/>
+      <c r="C387" s="63"/>
+      <c r="D387" s="63"/>
+      <c r="E387" s="63"/>
+      <c r="F387" s="63"/>
+      <c r="G387" s="63"/>
+      <c r="H387" s="63"/>
+      <c r="I387" s="63"/>
+      <c r="J387" s="64"/>
       <c r="K387" s="44"/>
     </row>
     <row r="388" spans="1:11">
@@ -19390,17 +19390,17 @@
     </row>
     <row r="392" spans="1:11" ht="24" customHeight="1">
       <c r="A392" s="1"/>
-      <c r="B392" s="120" t="s">
+      <c r="B392" s="62" t="s">
         <v>755</v>
       </c>
-      <c r="C392" s="121"/>
-      <c r="D392" s="121"/>
-      <c r="E392" s="121"/>
-      <c r="F392" s="121"/>
-      <c r="G392" s="121"/>
-      <c r="H392" s="121"/>
-      <c r="I392" s="121"/>
-      <c r="J392" s="122"/>
+      <c r="C392" s="63"/>
+      <c r="D392" s="63"/>
+      <c r="E392" s="63"/>
+      <c r="F392" s="63"/>
+      <c r="G392" s="63"/>
+      <c r="H392" s="63"/>
+      <c r="I392" s="63"/>
+      <c r="J392" s="64"/>
       <c r="K392" s="44"/>
     </row>
     <row r="393" spans="1:11">
@@ -19482,17 +19482,17 @@
     </row>
     <row r="397" spans="1:11" ht="24" customHeight="1">
       <c r="A397" s="1"/>
-      <c r="B397" s="120" t="s">
+      <c r="B397" s="62" t="s">
         <v>757</v>
       </c>
-      <c r="C397" s="121"/>
-      <c r="D397" s="121"/>
-      <c r="E397" s="121"/>
-      <c r="F397" s="121"/>
-      <c r="G397" s="121"/>
-      <c r="H397" s="121"/>
-      <c r="I397" s="121"/>
-      <c r="J397" s="122"/>
+      <c r="C397" s="63"/>
+      <c r="D397" s="63"/>
+      <c r="E397" s="63"/>
+      <c r="F397" s="63"/>
+      <c r="G397" s="63"/>
+      <c r="H397" s="63"/>
+      <c r="I397" s="63"/>
+      <c r="J397" s="64"/>
       <c r="K397" s="44"/>
     </row>
     <row r="398" spans="1:11">
@@ -19574,17 +19574,17 @@
     </row>
     <row r="402" spans="1:11" ht="24" customHeight="1">
       <c r="A402" s="1"/>
-      <c r="B402" s="120" t="s">
+      <c r="B402" s="62" t="s">
         <v>759</v>
       </c>
-      <c r="C402" s="121"/>
-      <c r="D402" s="121"/>
-      <c r="E402" s="121"/>
-      <c r="F402" s="121"/>
-      <c r="G402" s="121"/>
-      <c r="H402" s="121"/>
-      <c r="I402" s="121"/>
-      <c r="J402" s="122"/>
+      <c r="C402" s="63"/>
+      <c r="D402" s="63"/>
+      <c r="E402" s="63"/>
+      <c r="F402" s="63"/>
+      <c r="G402" s="63"/>
+      <c r="H402" s="63"/>
+      <c r="I402" s="63"/>
+      <c r="J402" s="64"/>
       <c r="K402" s="44"/>
     </row>
     <row r="403" spans="1:11">
@@ -19666,17 +19666,17 @@
     </row>
     <row r="407" spans="1:11" ht="24" customHeight="1">
       <c r="A407" s="1"/>
-      <c r="B407" s="120" t="s">
+      <c r="B407" s="62" t="s">
         <v>848</v>
       </c>
-      <c r="C407" s="121"/>
-      <c r="D407" s="121"/>
-      <c r="E407" s="121"/>
-      <c r="F407" s="121"/>
-      <c r="G407" s="121"/>
-      <c r="H407" s="121"/>
-      <c r="I407" s="121"/>
-      <c r="J407" s="122"/>
+      <c r="C407" s="63"/>
+      <c r="D407" s="63"/>
+      <c r="E407" s="63"/>
+      <c r="F407" s="63"/>
+      <c r="G407" s="63"/>
+      <c r="H407" s="63"/>
+      <c r="I407" s="63"/>
+      <c r="J407" s="64"/>
       <c r="K407" s="44"/>
     </row>
     <row r="408" spans="1:11">
@@ -19758,17 +19758,17 @@
     </row>
     <row r="412" spans="1:11" ht="24" customHeight="1">
       <c r="A412" s="1"/>
-      <c r="B412" s="120" t="s">
+      <c r="B412" s="62" t="s">
         <v>761</v>
       </c>
-      <c r="C412" s="121"/>
-      <c r="D412" s="121"/>
-      <c r="E412" s="121"/>
-      <c r="F412" s="121"/>
-      <c r="G412" s="121"/>
-      <c r="H412" s="121"/>
-      <c r="I412" s="121"/>
-      <c r="J412" s="122"/>
+      <c r="C412" s="63"/>
+      <c r="D412" s="63"/>
+      <c r="E412" s="63"/>
+      <c r="F412" s="63"/>
+      <c r="G412" s="63"/>
+      <c r="H412" s="63"/>
+      <c r="I412" s="63"/>
+      <c r="J412" s="64"/>
       <c r="K412" s="44"/>
     </row>
     <row r="413" spans="1:11">
@@ -19823,7 +19823,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="416" spans="1:11" ht="36">
+    <row r="416" spans="1:11" ht="24">
       <c r="A416" s="1" t="s">
         <v>37</v>
       </c>
@@ -19850,17 +19850,17 @@
     </row>
     <row r="417" spans="1:11" ht="24" customHeight="1">
       <c r="A417" s="1"/>
-      <c r="B417" s="120" t="s">
+      <c r="B417" s="62" t="s">
         <v>763</v>
       </c>
-      <c r="C417" s="121"/>
-      <c r="D417" s="121"/>
-      <c r="E417" s="121"/>
-      <c r="F417" s="121"/>
-      <c r="G417" s="121"/>
-      <c r="H417" s="121"/>
-      <c r="I417" s="121"/>
-      <c r="J417" s="122"/>
+      <c r="C417" s="63"/>
+      <c r="D417" s="63"/>
+      <c r="E417" s="63"/>
+      <c r="F417" s="63"/>
+      <c r="G417" s="63"/>
+      <c r="H417" s="63"/>
+      <c r="I417" s="63"/>
+      <c r="J417" s="64"/>
       <c r="K417" s="44"/>
     </row>
     <row r="418" spans="1:11">
@@ -19915,7 +19915,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="421" spans="1:11" ht="36">
+    <row r="421" spans="1:11" ht="24">
       <c r="A421" s="1" t="s">
         <v>37</v>
       </c>
@@ -19942,17 +19942,17 @@
     </row>
     <row r="422" spans="1:11" ht="24" customHeight="1">
       <c r="A422" s="1"/>
-      <c r="B422" s="120" t="s">
+      <c r="B422" s="62" t="s">
         <v>765</v>
       </c>
-      <c r="C422" s="121"/>
-      <c r="D422" s="121"/>
-      <c r="E422" s="121"/>
-      <c r="F422" s="121"/>
-      <c r="G422" s="121"/>
-      <c r="H422" s="121"/>
-      <c r="I422" s="121"/>
-      <c r="J422" s="122"/>
+      <c r="C422" s="63"/>
+      <c r="D422" s="63"/>
+      <c r="E422" s="63"/>
+      <c r="F422" s="63"/>
+      <c r="G422" s="63"/>
+      <c r="H422" s="63"/>
+      <c r="I422" s="63"/>
+      <c r="J422" s="64"/>
       <c r="K422" s="44"/>
     </row>
     <row r="423" spans="1:11">
@@ -20034,17 +20034,17 @@
     </row>
     <row r="427" spans="1:11" ht="24" customHeight="1">
       <c r="A427" s="1"/>
-      <c r="B427" s="120" t="s">
+      <c r="B427" s="62" t="s">
         <v>767</v>
       </c>
-      <c r="C427" s="121"/>
-      <c r="D427" s="121"/>
-      <c r="E427" s="121"/>
-      <c r="F427" s="121"/>
-      <c r="G427" s="121"/>
-      <c r="H427" s="121"/>
-      <c r="I427" s="121"/>
-      <c r="J427" s="122"/>
+      <c r="C427" s="63"/>
+      <c r="D427" s="63"/>
+      <c r="E427" s="63"/>
+      <c r="F427" s="63"/>
+      <c r="G427" s="63"/>
+      <c r="H427" s="63"/>
+      <c r="I427" s="63"/>
+      <c r="J427" s="64"/>
       <c r="K427" s="44"/>
     </row>
     <row r="428" spans="1:11">
@@ -20126,17 +20126,17 @@
     </row>
     <row r="432" spans="1:11" ht="24" customHeight="1">
       <c r="A432" s="1"/>
-      <c r="B432" s="120" t="s">
+      <c r="B432" s="62" t="s">
         <v>769</v>
       </c>
-      <c r="C432" s="121"/>
-      <c r="D432" s="121"/>
-      <c r="E432" s="121"/>
-      <c r="F432" s="121"/>
-      <c r="G432" s="121"/>
-      <c r="H432" s="121"/>
-      <c r="I432" s="121"/>
-      <c r="J432" s="122"/>
+      <c r="C432" s="63"/>
+      <c r="D432" s="63"/>
+      <c r="E432" s="63"/>
+      <c r="F432" s="63"/>
+      <c r="G432" s="63"/>
+      <c r="H432" s="63"/>
+      <c r="I432" s="63"/>
+      <c r="J432" s="64"/>
       <c r="K432" s="44"/>
     </row>
     <row r="433" spans="1:11">
@@ -20218,17 +20218,17 @@
     </row>
     <row r="437" spans="1:11" ht="24" customHeight="1">
       <c r="A437" s="1"/>
-      <c r="B437" s="120" t="s">
+      <c r="B437" s="62" t="s">
         <v>771</v>
       </c>
-      <c r="C437" s="121"/>
-      <c r="D437" s="121"/>
-      <c r="E437" s="121"/>
-      <c r="F437" s="121"/>
-      <c r="G437" s="121"/>
-      <c r="H437" s="121"/>
-      <c r="I437" s="121"/>
-      <c r="J437" s="122"/>
+      <c r="C437" s="63"/>
+      <c r="D437" s="63"/>
+      <c r="E437" s="63"/>
+      <c r="F437" s="63"/>
+      <c r="G437" s="63"/>
+      <c r="H437" s="63"/>
+      <c r="I437" s="63"/>
+      <c r="J437" s="64"/>
       <c r="K437" s="44"/>
     </row>
     <row r="438" spans="1:11">
@@ -20310,17 +20310,17 @@
     </row>
     <row r="442" spans="1:11" ht="24" customHeight="1">
       <c r="A442" s="1"/>
-      <c r="B442" s="120" t="s">
+      <c r="B442" s="62" t="s">
         <v>773</v>
       </c>
-      <c r="C442" s="121"/>
-      <c r="D442" s="121"/>
-      <c r="E442" s="121"/>
-      <c r="F442" s="121"/>
-      <c r="G442" s="121"/>
-      <c r="H442" s="121"/>
-      <c r="I442" s="121"/>
-      <c r="J442" s="122"/>
+      <c r="C442" s="63"/>
+      <c r="D442" s="63"/>
+      <c r="E442" s="63"/>
+      <c r="F442" s="63"/>
+      <c r="G442" s="63"/>
+      <c r="H442" s="63"/>
+      <c r="I442" s="63"/>
+      <c r="J442" s="64"/>
       <c r="K442" s="44"/>
     </row>
     <row r="443" spans="1:11">
@@ -20402,17 +20402,17 @@
     </row>
     <row r="447" spans="1:11" ht="24" customHeight="1">
       <c r="A447" s="1"/>
-      <c r="B447" s="120" t="s">
+      <c r="B447" s="62" t="s">
         <v>775</v>
       </c>
-      <c r="C447" s="121"/>
-      <c r="D447" s="121"/>
-      <c r="E447" s="121"/>
-      <c r="F447" s="121"/>
-      <c r="G447" s="121"/>
-      <c r="H447" s="121"/>
-      <c r="I447" s="121"/>
-      <c r="J447" s="122"/>
+      <c r="C447" s="63"/>
+      <c r="D447" s="63"/>
+      <c r="E447" s="63"/>
+      <c r="F447" s="63"/>
+      <c r="G447" s="63"/>
+      <c r="H447" s="63"/>
+      <c r="I447" s="63"/>
+      <c r="J447" s="64"/>
       <c r="K447" s="44"/>
     </row>
     <row r="448" spans="1:11">
@@ -20494,17 +20494,17 @@
     </row>
     <row r="452" spans="1:11" ht="24" customHeight="1">
       <c r="A452" s="1"/>
-      <c r="B452" s="120" t="s">
+      <c r="B452" s="62" t="s">
         <v>777</v>
       </c>
-      <c r="C452" s="121"/>
-      <c r="D452" s="121"/>
-      <c r="E452" s="121"/>
-      <c r="F452" s="121"/>
-      <c r="G452" s="121"/>
-      <c r="H452" s="121"/>
-      <c r="I452" s="121"/>
-      <c r="J452" s="122"/>
+      <c r="C452" s="63"/>
+      <c r="D452" s="63"/>
+      <c r="E452" s="63"/>
+      <c r="F452" s="63"/>
+      <c r="G452" s="63"/>
+      <c r="H452" s="63"/>
+      <c r="I452" s="63"/>
+      <c r="J452" s="64"/>
       <c r="K452" s="44"/>
     </row>
     <row r="453" spans="1:11">
@@ -20586,17 +20586,17 @@
     </row>
     <row r="457" spans="1:11" ht="24" customHeight="1">
       <c r="A457" s="1"/>
-      <c r="B457" s="120" t="s">
+      <c r="B457" s="62" t="s">
         <v>779</v>
       </c>
-      <c r="C457" s="121"/>
-      <c r="D457" s="121"/>
-      <c r="E457" s="121"/>
-      <c r="F457" s="121"/>
-      <c r="G457" s="121"/>
-      <c r="H457" s="121"/>
-      <c r="I457" s="121"/>
-      <c r="J457" s="122"/>
+      <c r="C457" s="63"/>
+      <c r="D457" s="63"/>
+      <c r="E457" s="63"/>
+      <c r="F457" s="63"/>
+      <c r="G457" s="63"/>
+      <c r="H457" s="63"/>
+      <c r="I457" s="63"/>
+      <c r="J457" s="64"/>
       <c r="K457" s="44"/>
     </row>
     <row r="458" spans="1:11">
@@ -20678,17 +20678,17 @@
     </row>
     <row r="462" spans="1:11" ht="24" customHeight="1">
       <c r="A462" s="1"/>
-      <c r="B462" s="120" t="s">
+      <c r="B462" s="62" t="s">
         <v>781</v>
       </c>
-      <c r="C462" s="121"/>
-      <c r="D462" s="121"/>
-      <c r="E462" s="121"/>
-      <c r="F462" s="121"/>
-      <c r="G462" s="121"/>
-      <c r="H462" s="121"/>
-      <c r="I462" s="121"/>
-      <c r="J462" s="122"/>
+      <c r="C462" s="63"/>
+      <c r="D462" s="63"/>
+      <c r="E462" s="63"/>
+      <c r="F462" s="63"/>
+      <c r="G462" s="63"/>
+      <c r="H462" s="63"/>
+      <c r="I462" s="63"/>
+      <c r="J462" s="64"/>
       <c r="K462" s="44"/>
     </row>
     <row r="463" spans="1:11">
@@ -20770,17 +20770,17 @@
     </row>
     <row r="467" spans="1:11" ht="24" customHeight="1">
       <c r="A467" s="1"/>
-      <c r="B467" s="120" t="s">
+      <c r="B467" s="62" t="s">
         <v>783</v>
       </c>
-      <c r="C467" s="121"/>
-      <c r="D467" s="121"/>
-      <c r="E467" s="121"/>
-      <c r="F467" s="121"/>
-      <c r="G467" s="121"/>
-      <c r="H467" s="121"/>
-      <c r="I467" s="121"/>
-      <c r="J467" s="122"/>
+      <c r="C467" s="63"/>
+      <c r="D467" s="63"/>
+      <c r="E467" s="63"/>
+      <c r="F467" s="63"/>
+      <c r="G467" s="63"/>
+      <c r="H467" s="63"/>
+      <c r="I467" s="63"/>
+      <c r="J467" s="64"/>
       <c r="K467" s="44"/>
     </row>
     <row r="468" spans="1:11">
@@ -20862,17 +20862,17 @@
     </row>
     <row r="472" spans="1:11" ht="24" customHeight="1">
       <c r="A472" s="1"/>
-      <c r="B472" s="120" t="s">
+      <c r="B472" s="62" t="s">
         <v>785</v>
       </c>
-      <c r="C472" s="121"/>
-      <c r="D472" s="121"/>
-      <c r="E472" s="121"/>
-      <c r="F472" s="121"/>
-      <c r="G472" s="121"/>
-      <c r="H472" s="121"/>
-      <c r="I472" s="121"/>
-      <c r="J472" s="122"/>
+      <c r="C472" s="63"/>
+      <c r="D472" s="63"/>
+      <c r="E472" s="63"/>
+      <c r="F472" s="63"/>
+      <c r="G472" s="63"/>
+      <c r="H472" s="63"/>
+      <c r="I472" s="63"/>
+      <c r="J472" s="64"/>
       <c r="K472" s="44"/>
     </row>
     <row r="473" spans="1:11">
@@ -20927,7 +20927,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="476" spans="1:11" ht="24">
+    <row r="476" spans="1:11">
       <c r="A476" s="1" t="s">
         <v>37</v>
       </c>
@@ -20954,17 +20954,17 @@
     </row>
     <row r="477" spans="1:11" ht="24" customHeight="1">
       <c r="A477" s="1"/>
-      <c r="B477" s="120" t="s">
+      <c r="B477" s="62" t="s">
         <v>786</v>
       </c>
-      <c r="C477" s="121"/>
-      <c r="D477" s="121"/>
-      <c r="E477" s="121"/>
-      <c r="F477" s="121"/>
-      <c r="G477" s="121"/>
-      <c r="H477" s="121"/>
-      <c r="I477" s="121"/>
-      <c r="J477" s="122"/>
+      <c r="C477" s="63"/>
+      <c r="D477" s="63"/>
+      <c r="E477" s="63"/>
+      <c r="F477" s="63"/>
+      <c r="G477" s="63"/>
+      <c r="H477" s="63"/>
+      <c r="I477" s="63"/>
+      <c r="J477" s="64"/>
       <c r="K477" s="44"/>
     </row>
     <row r="478" spans="1:11">
@@ -21046,17 +21046,17 @@
     </row>
     <row r="482" spans="1:11" ht="24" customHeight="1">
       <c r="A482" s="1"/>
-      <c r="B482" s="120" t="s">
+      <c r="B482" s="62" t="s">
         <v>788</v>
       </c>
-      <c r="C482" s="121"/>
-      <c r="D482" s="121"/>
-      <c r="E482" s="121"/>
-      <c r="F482" s="121"/>
-      <c r="G482" s="121"/>
-      <c r="H482" s="121"/>
-      <c r="I482" s="121"/>
-      <c r="J482" s="122"/>
+      <c r="C482" s="63"/>
+      <c r="D482" s="63"/>
+      <c r="E482" s="63"/>
+      <c r="F482" s="63"/>
+      <c r="G482" s="63"/>
+      <c r="H482" s="63"/>
+      <c r="I482" s="63"/>
+      <c r="J482" s="64"/>
       <c r="K482" s="44"/>
     </row>
     <row r="483" spans="1:11">
@@ -21138,17 +21138,17 @@
     </row>
     <row r="487" spans="1:11" ht="24" customHeight="1">
       <c r="A487" s="1"/>
-      <c r="B487" s="120" t="s">
+      <c r="B487" s="62" t="s">
         <v>790</v>
       </c>
-      <c r="C487" s="121"/>
-      <c r="D487" s="121"/>
-      <c r="E487" s="121"/>
-      <c r="F487" s="121"/>
-      <c r="G487" s="121"/>
-      <c r="H487" s="121"/>
-      <c r="I487" s="121"/>
-      <c r="J487" s="122"/>
+      <c r="C487" s="63"/>
+      <c r="D487" s="63"/>
+      <c r="E487" s="63"/>
+      <c r="F487" s="63"/>
+      <c r="G487" s="63"/>
+      <c r="H487" s="63"/>
+      <c r="I487" s="63"/>
+      <c r="J487" s="64"/>
       <c r="K487" s="44"/>
     </row>
     <row r="488" spans="1:11">
@@ -21230,17 +21230,17 @@
     </row>
     <row r="492" spans="1:11" ht="24" customHeight="1">
       <c r="A492" s="1"/>
-      <c r="B492" s="120" t="s">
+      <c r="B492" s="62" t="s">
         <v>792</v>
       </c>
-      <c r="C492" s="121"/>
-      <c r="D492" s="121"/>
-      <c r="E492" s="121"/>
-      <c r="F492" s="121"/>
-      <c r="G492" s="121"/>
-      <c r="H492" s="121"/>
-      <c r="I492" s="121"/>
-      <c r="J492" s="122"/>
+      <c r="C492" s="63"/>
+      <c r="D492" s="63"/>
+      <c r="E492" s="63"/>
+      <c r="F492" s="63"/>
+      <c r="G492" s="63"/>
+      <c r="H492" s="63"/>
+      <c r="I492" s="63"/>
+      <c r="J492" s="64"/>
       <c r="K492" s="44"/>
     </row>
     <row r="493" spans="1:11">
@@ -21322,17 +21322,17 @@
     </row>
     <row r="497" spans="1:11" ht="24" customHeight="1">
       <c r="A497" s="1"/>
-      <c r="B497" s="120" t="s">
+      <c r="B497" s="62" t="s">
         <v>794</v>
       </c>
-      <c r="C497" s="121"/>
-      <c r="D497" s="121"/>
-      <c r="E497" s="121"/>
-      <c r="F497" s="121"/>
-      <c r="G497" s="121"/>
-      <c r="H497" s="121"/>
-      <c r="I497" s="121"/>
-      <c r="J497" s="122"/>
+      <c r="C497" s="63"/>
+      <c r="D497" s="63"/>
+      <c r="E497" s="63"/>
+      <c r="F497" s="63"/>
+      <c r="G497" s="63"/>
+      <c r="H497" s="63"/>
+      <c r="I497" s="63"/>
+      <c r="J497" s="64"/>
       <c r="K497" s="44"/>
     </row>
     <row r="498" spans="1:11">
@@ -21414,17 +21414,17 @@
     </row>
     <row r="502" spans="1:11" ht="24" customHeight="1">
       <c r="A502" s="1"/>
-      <c r="B502" s="120" t="s">
+      <c r="B502" s="62" t="s">
         <v>796</v>
       </c>
-      <c r="C502" s="121"/>
-      <c r="D502" s="121"/>
-      <c r="E502" s="121"/>
-      <c r="F502" s="121"/>
-      <c r="G502" s="121"/>
-      <c r="H502" s="121"/>
-      <c r="I502" s="121"/>
-      <c r="J502" s="122"/>
+      <c r="C502" s="63"/>
+      <c r="D502" s="63"/>
+      <c r="E502" s="63"/>
+      <c r="F502" s="63"/>
+      <c r="G502" s="63"/>
+      <c r="H502" s="63"/>
+      <c r="I502" s="63"/>
+      <c r="J502" s="64"/>
       <c r="K502" s="44"/>
     </row>
     <row r="503" spans="1:11">
@@ -21506,17 +21506,17 @@
     </row>
     <row r="507" spans="1:11" ht="24" customHeight="1">
       <c r="A507" s="1"/>
-      <c r="B507" s="120" t="s">
+      <c r="B507" s="62" t="s">
         <v>798</v>
       </c>
-      <c r="C507" s="121"/>
-      <c r="D507" s="121"/>
-      <c r="E507" s="121"/>
-      <c r="F507" s="121"/>
-      <c r="G507" s="121"/>
-      <c r="H507" s="121"/>
-      <c r="I507" s="121"/>
-      <c r="J507" s="122"/>
+      <c r="C507" s="63"/>
+      <c r="D507" s="63"/>
+      <c r="E507" s="63"/>
+      <c r="F507" s="63"/>
+      <c r="G507" s="63"/>
+      <c r="H507" s="63"/>
+      <c r="I507" s="63"/>
+      <c r="J507" s="64"/>
       <c r="K507" s="44"/>
     </row>
     <row r="508" spans="1:11">
@@ -21598,17 +21598,17 @@
     </row>
     <row r="512" spans="1:11" ht="24" customHeight="1">
       <c r="A512" s="1"/>
-      <c r="B512" s="120" t="s">
+      <c r="B512" s="62" t="s">
         <v>800</v>
       </c>
-      <c r="C512" s="121"/>
-      <c r="D512" s="121"/>
-      <c r="E512" s="121"/>
-      <c r="F512" s="121"/>
-      <c r="G512" s="121"/>
-      <c r="H512" s="121"/>
-      <c r="I512" s="121"/>
-      <c r="J512" s="122"/>
+      <c r="C512" s="63"/>
+      <c r="D512" s="63"/>
+      <c r="E512" s="63"/>
+      <c r="F512" s="63"/>
+      <c r="G512" s="63"/>
+      <c r="H512" s="63"/>
+      <c r="I512" s="63"/>
+      <c r="J512" s="64"/>
       <c r="K512" s="44"/>
     </row>
     <row r="513" spans="1:11">
@@ -21690,17 +21690,17 @@
     </row>
     <row r="517" spans="1:11" ht="24" customHeight="1">
       <c r="A517" s="1"/>
-      <c r="B517" s="120" t="s">
+      <c r="B517" s="62" t="s">
         <v>802</v>
       </c>
-      <c r="C517" s="121"/>
-      <c r="D517" s="121"/>
-      <c r="E517" s="121"/>
-      <c r="F517" s="121"/>
-      <c r="G517" s="121"/>
-      <c r="H517" s="121"/>
-      <c r="I517" s="121"/>
-      <c r="J517" s="122"/>
+      <c r="C517" s="63"/>
+      <c r="D517" s="63"/>
+      <c r="E517" s="63"/>
+      <c r="F517" s="63"/>
+      <c r="G517" s="63"/>
+      <c r="H517" s="63"/>
+      <c r="I517" s="63"/>
+      <c r="J517" s="64"/>
       <c r="K517" s="44"/>
     </row>
     <row r="518" spans="1:11" ht="24">
@@ -21782,17 +21782,17 @@
     </row>
     <row r="522" spans="1:11" ht="24" customHeight="1">
       <c r="A522" s="1"/>
-      <c r="B522" s="120" t="s">
+      <c r="B522" s="62" t="s">
         <v>804</v>
       </c>
-      <c r="C522" s="121"/>
-      <c r="D522" s="121"/>
-      <c r="E522" s="121"/>
-      <c r="F522" s="121"/>
-      <c r="G522" s="121"/>
-      <c r="H522" s="121"/>
-      <c r="I522" s="121"/>
-      <c r="J522" s="122"/>
+      <c r="C522" s="63"/>
+      <c r="D522" s="63"/>
+      <c r="E522" s="63"/>
+      <c r="F522" s="63"/>
+      <c r="G522" s="63"/>
+      <c r="H522" s="63"/>
+      <c r="I522" s="63"/>
+      <c r="J522" s="64"/>
       <c r="K522" s="44"/>
     </row>
     <row r="523" spans="1:11">
@@ -21874,17 +21874,17 @@
     </row>
     <row r="527" spans="1:11" ht="24" customHeight="1">
       <c r="A527" s="1"/>
-      <c r="B527" s="120" t="s">
+      <c r="B527" s="62" t="s">
         <v>806</v>
       </c>
-      <c r="C527" s="121"/>
-      <c r="D527" s="121"/>
-      <c r="E527" s="121"/>
-      <c r="F527" s="121"/>
-      <c r="G527" s="121"/>
-      <c r="H527" s="121"/>
-      <c r="I527" s="121"/>
-      <c r="J527" s="122"/>
+      <c r="C527" s="63"/>
+      <c r="D527" s="63"/>
+      <c r="E527" s="63"/>
+      <c r="F527" s="63"/>
+      <c r="G527" s="63"/>
+      <c r="H527" s="63"/>
+      <c r="I527" s="63"/>
+      <c r="J527" s="64"/>
       <c r="K527" s="44"/>
     </row>
     <row r="528" spans="1:11">
@@ -21966,17 +21966,17 @@
     </row>
     <row r="532" spans="1:11" ht="24" customHeight="1">
       <c r="A532" s="1"/>
-      <c r="B532" s="120" t="s">
+      <c r="B532" s="62" t="s">
         <v>807</v>
       </c>
-      <c r="C532" s="121"/>
-      <c r="D532" s="121"/>
-      <c r="E532" s="121"/>
-      <c r="F532" s="121"/>
-      <c r="G532" s="121"/>
-      <c r="H532" s="121"/>
-      <c r="I532" s="121"/>
-      <c r="J532" s="122"/>
+      <c r="C532" s="63"/>
+      <c r="D532" s="63"/>
+      <c r="E532" s="63"/>
+      <c r="F532" s="63"/>
+      <c r="G532" s="63"/>
+      <c r="H532" s="63"/>
+      <c r="I532" s="63"/>
+      <c r="J532" s="64"/>
       <c r="K532" s="44"/>
     </row>
     <row r="533" spans="1:11">
@@ -22058,17 +22058,17 @@
     </row>
     <row r="537" spans="1:11" ht="24" customHeight="1">
       <c r="A537" s="1"/>
-      <c r="B537" s="120" t="s">
+      <c r="B537" s="62" t="s">
         <v>809</v>
       </c>
-      <c r="C537" s="121"/>
-      <c r="D537" s="121"/>
-      <c r="E537" s="121"/>
-      <c r="F537" s="121"/>
-      <c r="G537" s="121"/>
-      <c r="H537" s="121"/>
-      <c r="I537" s="121"/>
-      <c r="J537" s="122"/>
+      <c r="C537" s="63"/>
+      <c r="D537" s="63"/>
+      <c r="E537" s="63"/>
+      <c r="F537" s="63"/>
+      <c r="G537" s="63"/>
+      <c r="H537" s="63"/>
+      <c r="I537" s="63"/>
+      <c r="J537" s="64"/>
       <c r="K537" s="44"/>
     </row>
     <row r="538" spans="1:11">
@@ -22150,17 +22150,17 @@
     </row>
     <row r="542" spans="1:11" ht="24" customHeight="1">
       <c r="A542" s="1"/>
-      <c r="B542" s="120" t="s">
+      <c r="B542" s="62" t="s">
         <v>811</v>
       </c>
-      <c r="C542" s="121"/>
-      <c r="D542" s="121"/>
-      <c r="E542" s="121"/>
-      <c r="F542" s="121"/>
-      <c r="G542" s="121"/>
-      <c r="H542" s="121"/>
-      <c r="I542" s="121"/>
-      <c r="J542" s="122"/>
+      <c r="C542" s="63"/>
+      <c r="D542" s="63"/>
+      <c r="E542" s="63"/>
+      <c r="F542" s="63"/>
+      <c r="G542" s="63"/>
+      <c r="H542" s="63"/>
+      <c r="I542" s="63"/>
+      <c r="J542" s="64"/>
       <c r="K542" s="44"/>
     </row>
     <row r="543" spans="1:11">
@@ -22242,17 +22242,17 @@
     </row>
     <row r="547" spans="1:11" ht="24" customHeight="1">
       <c r="A547" s="1"/>
-      <c r="B547" s="120" t="s">
+      <c r="B547" s="62" t="s">
         <v>813</v>
       </c>
-      <c r="C547" s="121"/>
-      <c r="D547" s="121"/>
-      <c r="E547" s="121"/>
-      <c r="F547" s="121"/>
-      <c r="G547" s="121"/>
-      <c r="H547" s="121"/>
-      <c r="I547" s="121"/>
-      <c r="J547" s="122"/>
+      <c r="C547" s="63"/>
+      <c r="D547" s="63"/>
+      <c r="E547" s="63"/>
+      <c r="F547" s="63"/>
+      <c r="G547" s="63"/>
+      <c r="H547" s="63"/>
+      <c r="I547" s="63"/>
+      <c r="J547" s="64"/>
       <c r="K547" s="44"/>
     </row>
     <row r="548" spans="1:11">
@@ -22334,17 +22334,17 @@
     </row>
     <row r="552" spans="1:11" ht="24" customHeight="1">
       <c r="A552" s="1"/>
-      <c r="B552" s="120" t="s">
+      <c r="B552" s="62" t="s">
         <v>814</v>
       </c>
-      <c r="C552" s="121"/>
-      <c r="D552" s="121"/>
-      <c r="E552" s="121"/>
-      <c r="F552" s="121"/>
-      <c r="G552" s="121"/>
-      <c r="H552" s="121"/>
-      <c r="I552" s="121"/>
-      <c r="J552" s="122"/>
+      <c r="C552" s="63"/>
+      <c r="D552" s="63"/>
+      <c r="E552" s="63"/>
+      <c r="F552" s="63"/>
+      <c r="G552" s="63"/>
+      <c r="H552" s="63"/>
+      <c r="I552" s="63"/>
+      <c r="J552" s="64"/>
       <c r="K552" s="44"/>
     </row>
     <row r="553" spans="1:11">
@@ -22426,17 +22426,17 @@
     </row>
     <row r="557" spans="1:11" ht="24" customHeight="1">
       <c r="A557" s="1"/>
-      <c r="B557" s="120" t="s">
+      <c r="B557" s="62" t="s">
         <v>816</v>
       </c>
-      <c r="C557" s="121"/>
-      <c r="D557" s="121"/>
-      <c r="E557" s="121"/>
-      <c r="F557" s="121"/>
-      <c r="G557" s="121"/>
-      <c r="H557" s="121"/>
-      <c r="I557" s="121"/>
-      <c r="J557" s="122"/>
+      <c r="C557" s="63"/>
+      <c r="D557" s="63"/>
+      <c r="E557" s="63"/>
+      <c r="F557" s="63"/>
+      <c r="G557" s="63"/>
+      <c r="H557" s="63"/>
+      <c r="I557" s="63"/>
+      <c r="J557" s="64"/>
       <c r="K557" s="44"/>
     </row>
     <row r="558" spans="1:11">
@@ -22518,17 +22518,17 @@
     </row>
     <row r="562" spans="1:11" ht="24" customHeight="1">
       <c r="A562" s="1"/>
-      <c r="B562" s="120" t="s">
+      <c r="B562" s="62" t="s">
         <v>818</v>
       </c>
-      <c r="C562" s="121"/>
-      <c r="D562" s="121"/>
-      <c r="E562" s="121"/>
-      <c r="F562" s="121"/>
-      <c r="G562" s="121"/>
-      <c r="H562" s="121"/>
-      <c r="I562" s="121"/>
-      <c r="J562" s="122"/>
+      <c r="C562" s="63"/>
+      <c r="D562" s="63"/>
+      <c r="E562" s="63"/>
+      <c r="F562" s="63"/>
+      <c r="G562" s="63"/>
+      <c r="H562" s="63"/>
+      <c r="I562" s="63"/>
+      <c r="J562" s="64"/>
       <c r="K562" s="44"/>
     </row>
     <row r="563" spans="1:11">
@@ -22610,17 +22610,17 @@
     </row>
     <row r="567" spans="1:11" ht="24" customHeight="1">
       <c r="A567" s="1"/>
-      <c r="B567" s="120" t="s">
+      <c r="B567" s="62" t="s">
         <v>820</v>
       </c>
-      <c r="C567" s="121"/>
-      <c r="D567" s="121"/>
-      <c r="E567" s="121"/>
-      <c r="F567" s="121"/>
-      <c r="G567" s="121"/>
-      <c r="H567" s="121"/>
-      <c r="I567" s="121"/>
-      <c r="J567" s="122"/>
+      <c r="C567" s="63"/>
+      <c r="D567" s="63"/>
+      <c r="E567" s="63"/>
+      <c r="F567" s="63"/>
+      <c r="G567" s="63"/>
+      <c r="H567" s="63"/>
+      <c r="I567" s="63"/>
+      <c r="J567" s="64"/>
       <c r="K567" s="44"/>
     </row>
     <row r="568" spans="1:11">
@@ -22702,17 +22702,17 @@
     </row>
     <row r="572" spans="1:11" ht="24" customHeight="1">
       <c r="A572" s="1"/>
-      <c r="B572" s="120" t="s">
+      <c r="B572" s="62" t="s">
         <v>822</v>
       </c>
-      <c r="C572" s="121"/>
-      <c r="D572" s="121"/>
-      <c r="E572" s="121"/>
-      <c r="F572" s="121"/>
-      <c r="G572" s="121"/>
-      <c r="H572" s="121"/>
-      <c r="I572" s="121"/>
-      <c r="J572" s="122"/>
+      <c r="C572" s="63"/>
+      <c r="D572" s="63"/>
+      <c r="E572" s="63"/>
+      <c r="F572" s="63"/>
+      <c r="G572" s="63"/>
+      <c r="H572" s="63"/>
+      <c r="I572" s="63"/>
+      <c r="J572" s="64"/>
       <c r="K572" s="44"/>
     </row>
     <row r="573" spans="1:11">
@@ -22794,17 +22794,17 @@
     </row>
     <row r="577" spans="1:11" ht="24" customHeight="1">
       <c r="A577" s="1"/>
-      <c r="B577" s="120" t="s">
+      <c r="B577" s="62" t="s">
         <v>823</v>
       </c>
-      <c r="C577" s="121"/>
-      <c r="D577" s="121"/>
-      <c r="E577" s="121"/>
-      <c r="F577" s="121"/>
-      <c r="G577" s="121"/>
-      <c r="H577" s="121"/>
-      <c r="I577" s="121"/>
-      <c r="J577" s="122"/>
+      <c r="C577" s="63"/>
+      <c r="D577" s="63"/>
+      <c r="E577" s="63"/>
+      <c r="F577" s="63"/>
+      <c r="G577" s="63"/>
+      <c r="H577" s="63"/>
+      <c r="I577" s="63"/>
+      <c r="J577" s="64"/>
       <c r="K577" s="44"/>
     </row>
     <row r="578" spans="1:11">
@@ -22886,17 +22886,17 @@
     </row>
     <row r="582" spans="1:11" ht="24" customHeight="1">
       <c r="A582" s="1"/>
-      <c r="B582" s="120" t="s">
+      <c r="B582" s="62" t="s">
         <v>824</v>
       </c>
-      <c r="C582" s="121"/>
-      <c r="D582" s="121"/>
-      <c r="E582" s="121"/>
-      <c r="F582" s="121"/>
-      <c r="G582" s="121"/>
-      <c r="H582" s="121"/>
-      <c r="I582" s="121"/>
-      <c r="J582" s="122"/>
+      <c r="C582" s="63"/>
+      <c r="D582" s="63"/>
+      <c r="E582" s="63"/>
+      <c r="F582" s="63"/>
+      <c r="G582" s="63"/>
+      <c r="H582" s="63"/>
+      <c r="I582" s="63"/>
+      <c r="J582" s="64"/>
       <c r="K582" s="44"/>
     </row>
     <row r="583" spans="1:11">
@@ -22978,17 +22978,17 @@
     </row>
     <row r="587" spans="1:11" ht="24" customHeight="1">
       <c r="A587" s="1"/>
-      <c r="B587" s="120" t="s">
+      <c r="B587" s="62" t="s">
         <v>825</v>
       </c>
-      <c r="C587" s="121"/>
-      <c r="D587" s="121"/>
-      <c r="E587" s="121"/>
-      <c r="F587" s="121"/>
-      <c r="G587" s="121"/>
-      <c r="H587" s="121"/>
-      <c r="I587" s="121"/>
-      <c r="J587" s="122"/>
+      <c r="C587" s="63"/>
+      <c r="D587" s="63"/>
+      <c r="E587" s="63"/>
+      <c r="F587" s="63"/>
+      <c r="G587" s="63"/>
+      <c r="H587" s="63"/>
+      <c r="I587" s="63"/>
+      <c r="J587" s="64"/>
       <c r="K587" s="44"/>
     </row>
     <row r="588" spans="1:11">
@@ -23070,17 +23070,17 @@
     </row>
     <row r="592" spans="1:11" ht="24" customHeight="1">
       <c r="A592" s="1"/>
-      <c r="B592" s="120" t="s">
+      <c r="B592" s="62" t="s">
         <v>826</v>
       </c>
-      <c r="C592" s="121"/>
-      <c r="D592" s="121"/>
-      <c r="E592" s="121"/>
-      <c r="F592" s="121"/>
-      <c r="G592" s="121"/>
-      <c r="H592" s="121"/>
-      <c r="I592" s="121"/>
-      <c r="J592" s="122"/>
+      <c r="C592" s="63"/>
+      <c r="D592" s="63"/>
+      <c r="E592" s="63"/>
+      <c r="F592" s="63"/>
+      <c r="G592" s="63"/>
+      <c r="H592" s="63"/>
+      <c r="I592" s="63"/>
+      <c r="J592" s="64"/>
       <c r="K592" s="44"/>
     </row>
     <row r="593" spans="1:11">
@@ -23162,17 +23162,17 @@
     </row>
     <row r="597" spans="1:11" ht="24" customHeight="1">
       <c r="A597" s="1"/>
-      <c r="B597" s="120" t="s">
+      <c r="B597" s="62" t="s">
         <v>828</v>
       </c>
-      <c r="C597" s="121"/>
-      <c r="D597" s="121"/>
-      <c r="E597" s="121"/>
-      <c r="F597" s="121"/>
-      <c r="G597" s="121"/>
-      <c r="H597" s="121"/>
-      <c r="I597" s="121"/>
-      <c r="J597" s="122"/>
+      <c r="C597" s="63"/>
+      <c r="D597" s="63"/>
+      <c r="E597" s="63"/>
+      <c r="F597" s="63"/>
+      <c r="G597" s="63"/>
+      <c r="H597" s="63"/>
+      <c r="I597" s="63"/>
+      <c r="J597" s="64"/>
       <c r="K597" s="44"/>
     </row>
     <row r="598" spans="1:11">
@@ -23254,17 +23254,17 @@
     </row>
     <row r="602" spans="1:11" ht="24" customHeight="1">
       <c r="A602" s="1"/>
-      <c r="B602" s="120" t="s">
+      <c r="B602" s="62" t="s">
         <v>830</v>
       </c>
-      <c r="C602" s="121"/>
-      <c r="D602" s="121"/>
-      <c r="E602" s="121"/>
-      <c r="F602" s="121"/>
-      <c r="G602" s="121"/>
-      <c r="H602" s="121"/>
-      <c r="I602" s="121"/>
-      <c r="J602" s="122"/>
+      <c r="C602" s="63"/>
+      <c r="D602" s="63"/>
+      <c r="E602" s="63"/>
+      <c r="F602" s="63"/>
+      <c r="G602" s="63"/>
+      <c r="H602" s="63"/>
+      <c r="I602" s="63"/>
+      <c r="J602" s="64"/>
       <c r="K602" s="44"/>
     </row>
     <row r="603" spans="1:11">
@@ -23346,17 +23346,17 @@
     </row>
     <row r="607" spans="1:11" ht="24" customHeight="1">
       <c r="A607" s="1"/>
-      <c r="B607" s="120" t="s">
+      <c r="B607" s="62" t="s">
         <v>832</v>
       </c>
-      <c r="C607" s="121"/>
-      <c r="D607" s="121"/>
-      <c r="E607" s="121"/>
-      <c r="F607" s="121"/>
-      <c r="G607" s="121"/>
-      <c r="H607" s="121"/>
-      <c r="I607" s="121"/>
-      <c r="J607" s="122"/>
+      <c r="C607" s="63"/>
+      <c r="D607" s="63"/>
+      <c r="E607" s="63"/>
+      <c r="F607" s="63"/>
+      <c r="G607" s="63"/>
+      <c r="H607" s="63"/>
+      <c r="I607" s="63"/>
+      <c r="J607" s="64"/>
       <c r="K607" s="44"/>
     </row>
     <row r="608" spans="1:11">
@@ -23438,17 +23438,17 @@
     </row>
     <row r="612" spans="1:11" ht="24" customHeight="1">
       <c r="A612" s="1"/>
-      <c r="B612" s="120" t="s">
+      <c r="B612" s="62" t="s">
         <v>834</v>
       </c>
-      <c r="C612" s="121"/>
-      <c r="D612" s="121"/>
-      <c r="E612" s="121"/>
-      <c r="F612" s="121"/>
-      <c r="G612" s="121"/>
-      <c r="H612" s="121"/>
-      <c r="I612" s="121"/>
-      <c r="J612" s="122"/>
+      <c r="C612" s="63"/>
+      <c r="D612" s="63"/>
+      <c r="E612" s="63"/>
+      <c r="F612" s="63"/>
+      <c r="G612" s="63"/>
+      <c r="H612" s="63"/>
+      <c r="I612" s="63"/>
+      <c r="J612" s="64"/>
       <c r="K612" s="44"/>
     </row>
     <row r="613" spans="1:11">
@@ -23530,17 +23530,17 @@
     </row>
     <row r="617" spans="1:11" ht="24" customHeight="1">
       <c r="A617" s="1"/>
-      <c r="B617" s="120" t="s">
+      <c r="B617" s="62" t="s">
         <v>836</v>
       </c>
-      <c r="C617" s="121"/>
-      <c r="D617" s="121"/>
-      <c r="E617" s="121"/>
-      <c r="F617" s="121"/>
-      <c r="G617" s="121"/>
-      <c r="H617" s="121"/>
-      <c r="I617" s="121"/>
-      <c r="J617" s="122"/>
+      <c r="C617" s="63"/>
+      <c r="D617" s="63"/>
+      <c r="E617" s="63"/>
+      <c r="F617" s="63"/>
+      <c r="G617" s="63"/>
+      <c r="H617" s="63"/>
+      <c r="I617" s="63"/>
+      <c r="J617" s="64"/>
       <c r="K617" s="44"/>
     </row>
     <row r="618" spans="1:11">
@@ -23622,17 +23622,17 @@
     </row>
     <row r="622" spans="1:11" ht="24" customHeight="1">
       <c r="A622" s="1"/>
-      <c r="B622" s="120" t="s">
+      <c r="B622" s="62" t="s">
         <v>838</v>
       </c>
-      <c r="C622" s="121"/>
-      <c r="D622" s="121"/>
-      <c r="E622" s="121"/>
-      <c r="F622" s="121"/>
-      <c r="G622" s="121"/>
-      <c r="H622" s="121"/>
-      <c r="I622" s="121"/>
-      <c r="J622" s="122"/>
+      <c r="C622" s="63"/>
+      <c r="D622" s="63"/>
+      <c r="E622" s="63"/>
+      <c r="F622" s="63"/>
+      <c r="G622" s="63"/>
+      <c r="H622" s="63"/>
+      <c r="I622" s="63"/>
+      <c r="J622" s="64"/>
       <c r="K622" s="44"/>
     </row>
     <row r="623" spans="1:11">
@@ -23714,17 +23714,17 @@
     </row>
     <row r="627" spans="1:11" ht="24" customHeight="1">
       <c r="A627" s="1"/>
-      <c r="B627" s="120" t="s">
+      <c r="B627" s="62" t="s">
         <v>840</v>
       </c>
-      <c r="C627" s="121"/>
-      <c r="D627" s="121"/>
-      <c r="E627" s="121"/>
-      <c r="F627" s="121"/>
-      <c r="G627" s="121"/>
-      <c r="H627" s="121"/>
-      <c r="I627" s="121"/>
-      <c r="J627" s="122"/>
+      <c r="C627" s="63"/>
+      <c r="D627" s="63"/>
+      <c r="E627" s="63"/>
+      <c r="F627" s="63"/>
+      <c r="G627" s="63"/>
+      <c r="H627" s="63"/>
+      <c r="I627" s="63"/>
+      <c r="J627" s="64"/>
       <c r="K627" s="44"/>
     </row>
     <row r="628" spans="1:11">
@@ -23806,17 +23806,17 @@
     </row>
     <row r="632" spans="1:11" ht="24" customHeight="1">
       <c r="A632" s="1"/>
-      <c r="B632" s="120" t="s">
+      <c r="B632" s="62" t="s">
         <v>841</v>
       </c>
-      <c r="C632" s="121"/>
-      <c r="D632" s="121"/>
-      <c r="E632" s="121"/>
-      <c r="F632" s="121"/>
-      <c r="G632" s="121"/>
-      <c r="H632" s="121"/>
-      <c r="I632" s="121"/>
-      <c r="J632" s="122"/>
+      <c r="C632" s="63"/>
+      <c r="D632" s="63"/>
+      <c r="E632" s="63"/>
+      <c r="F632" s="63"/>
+      <c r="G632" s="63"/>
+      <c r="H632" s="63"/>
+      <c r="I632" s="63"/>
+      <c r="J632" s="64"/>
       <c r="K632" s="44"/>
     </row>
     <row r="633" spans="1:11">
@@ -23898,17 +23898,17 @@
     </row>
     <row r="637" spans="1:11" ht="24" customHeight="1">
       <c r="A637" s="1"/>
-      <c r="B637" s="120" t="s">
+      <c r="B637" s="62" t="s">
         <v>842</v>
       </c>
-      <c r="C637" s="121"/>
-      <c r="D637" s="121"/>
-      <c r="E637" s="121"/>
-      <c r="F637" s="121"/>
-      <c r="G637" s="121"/>
-      <c r="H637" s="121"/>
-      <c r="I637" s="121"/>
-      <c r="J637" s="122"/>
+      <c r="C637" s="63"/>
+      <c r="D637" s="63"/>
+      <c r="E637" s="63"/>
+      <c r="F637" s="63"/>
+      <c r="G637" s="63"/>
+      <c r="H637" s="63"/>
+      <c r="I637" s="63"/>
+      <c r="J637" s="64"/>
       <c r="K637" s="44"/>
     </row>
     <row r="638" spans="1:11">
@@ -23990,17 +23990,17 @@
     </row>
     <row r="642" spans="1:11" ht="24" customHeight="1">
       <c r="A642" s="1"/>
-      <c r="B642" s="120" t="s">
+      <c r="B642" s="62" t="s">
         <v>844</v>
       </c>
-      <c r="C642" s="121"/>
-      <c r="D642" s="121"/>
-      <c r="E642" s="121"/>
-      <c r="F642" s="121"/>
-      <c r="G642" s="121"/>
-      <c r="H642" s="121"/>
-      <c r="I642" s="121"/>
-      <c r="J642" s="122"/>
+      <c r="C642" s="63"/>
+      <c r="D642" s="63"/>
+      <c r="E642" s="63"/>
+      <c r="F642" s="63"/>
+      <c r="G642" s="63"/>
+      <c r="H642" s="63"/>
+      <c r="I642" s="63"/>
+      <c r="J642" s="64"/>
       <c r="K642" s="44"/>
     </row>
     <row r="643" spans="1:11">
@@ -24082,17 +24082,17 @@
     </row>
     <row r="647" spans="1:11" ht="24" customHeight="1">
       <c r="A647" s="1"/>
-      <c r="B647" s="120" t="s">
+      <c r="B647" s="62" t="s">
         <v>846</v>
       </c>
-      <c r="C647" s="121"/>
-      <c r="D647" s="121"/>
-      <c r="E647" s="121"/>
-      <c r="F647" s="121"/>
-      <c r="G647" s="121"/>
-      <c r="H647" s="121"/>
-      <c r="I647" s="121"/>
-      <c r="J647" s="122"/>
+      <c r="C647" s="63"/>
+      <c r="D647" s="63"/>
+      <c r="E647" s="63"/>
+      <c r="F647" s="63"/>
+      <c r="G647" s="63"/>
+      <c r="H647" s="63"/>
+      <c r="I647" s="63"/>
+      <c r="J647" s="64"/>
       <c r="K647" s="44"/>
     </row>
     <row r="648" spans="1:11">
@@ -24174,17 +24174,17 @@
     </row>
     <row r="652" spans="1:11" ht="24" customHeight="1">
       <c r="A652" s="1"/>
-      <c r="B652" s="120" t="s">
+      <c r="B652" s="62" t="s">
         <v>919</v>
       </c>
-      <c r="C652" s="121"/>
-      <c r="D652" s="121"/>
-      <c r="E652" s="121"/>
-      <c r="F652" s="121"/>
-      <c r="G652" s="121"/>
-      <c r="H652" s="121"/>
-      <c r="I652" s="121"/>
-      <c r="J652" s="122"/>
+      <c r="C652" s="63"/>
+      <c r="D652" s="63"/>
+      <c r="E652" s="63"/>
+      <c r="F652" s="63"/>
+      <c r="G652" s="63"/>
+      <c r="H652" s="63"/>
+      <c r="I652" s="63"/>
+      <c r="J652" s="64"/>
       <c r="K652" s="44"/>
     </row>
     <row r="653" spans="1:11">
@@ -24266,17 +24266,17 @@
     </row>
     <row r="657" spans="1:11" ht="24" customHeight="1">
       <c r="A657" s="1"/>
-      <c r="B657" s="120" t="s">
+      <c r="B657" s="62" t="s">
         <v>923</v>
       </c>
-      <c r="C657" s="121"/>
-      <c r="D657" s="121"/>
-      <c r="E657" s="121"/>
-      <c r="F657" s="121"/>
-      <c r="G657" s="121"/>
-      <c r="H657" s="121"/>
-      <c r="I657" s="121"/>
-      <c r="J657" s="122"/>
+      <c r="C657" s="63"/>
+      <c r="D657" s="63"/>
+      <c r="E657" s="63"/>
+      <c r="F657" s="63"/>
+      <c r="G657" s="63"/>
+      <c r="H657" s="63"/>
+      <c r="I657" s="63"/>
+      <c r="J657" s="64"/>
       <c r="K657" s="44"/>
     </row>
     <row r="658" spans="1:11">
@@ -24331,103 +24331,212 @@
         <v>970</v>
       </c>
     </row>
-    <row r="661" spans="1:11" s="132" customFormat="1">
-      <c r="A661" s="125" t="s">
+    <row r="661" spans="1:11" s="54" customFormat="1">
+      <c r="A661" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B661" s="126" t="s">
+      <c r="B661" s="48" t="s">
         <v>1138</v>
       </c>
-      <c r="C661" s="127"/>
-      <c r="D661" s="128" t="s">
+      <c r="C661" s="49"/>
+      <c r="D661" s="50" t="s">
         <v>1139</v>
       </c>
-      <c r="E661" s="129"/>
-      <c r="F661" s="130">
+      <c r="E661" s="51"/>
+      <c r="F661" s="52">
         <v>2</v>
       </c>
-      <c r="G661" s="126" t="s">
+      <c r="G661" s="48" t="s">
         <v>1140</v>
       </c>
-      <c r="H661" s="127"/>
-      <c r="I661" s="126"/>
-      <c r="J661" s="127"/>
-      <c r="K661" s="131" t="s">
+      <c r="H661" s="49"/>
+      <c r="I661" s="48"/>
+      <c r="J661" s="49"/>
+      <c r="K661" s="53" t="s">
         <v>1141</v>
       </c>
     </row>
-    <row r="662" spans="1:11" s="132" customFormat="1" ht="24" customHeight="1">
-      <c r="A662" s="125"/>
-      <c r="B662" s="133" t="s">
+    <row r="662" spans="1:11" s="54" customFormat="1" ht="24" customHeight="1">
+      <c r="A662" s="47"/>
+      <c r="B662" s="59" t="s">
         <v>1142</v>
       </c>
-      <c r="C662" s="134"/>
-      <c r="D662" s="134"/>
-      <c r="E662" s="134"/>
-      <c r="F662" s="134"/>
-      <c r="G662" s="134"/>
-      <c r="H662" s="134"/>
-      <c r="I662" s="134"/>
-      <c r="J662" s="135"/>
-      <c r="K662" s="131"/>
-    </row>
-    <row r="663" spans="1:11" s="132" customFormat="1">
-      <c r="A663" s="125"/>
-      <c r="B663" s="130" t="s">
-        <v>44</v>
-      </c>
-      <c r="C663" s="136" t="s">
+      <c r="C662" s="60"/>
+      <c r="D662" s="60"/>
+      <c r="E662" s="60"/>
+      <c r="F662" s="60"/>
+      <c r="G662" s="60"/>
+      <c r="H662" s="60"/>
+      <c r="I662" s="60"/>
+      <c r="J662" s="61"/>
+      <c r="K662" s="53"/>
+    </row>
+    <row r="663" spans="1:11" s="54" customFormat="1">
+      <c r="A663" s="47"/>
+      <c r="B663" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C663" s="55" t="s">
         <v>1143</v>
       </c>
-      <c r="D663" s="130" t="s">
-        <v>42</v>
-      </c>
-      <c r="E663" s="130">
-        <v>10</v>
-      </c>
-      <c r="F663" s="130">
-        <v>10</v>
-      </c>
-      <c r="G663" s="137" t="s">
+      <c r="D663" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="E663" s="52">
+        <v>10</v>
+      </c>
+      <c r="F663" s="52">
+        <v>10</v>
+      </c>
+      <c r="G663" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H663" s="138"/>
-      <c r="I663" s="138"/>
-      <c r="J663" s="129"/>
-      <c r="K663" s="131" t="s">
+      <c r="H663" s="57"/>
+      <c r="I663" s="57"/>
+      <c r="J663" s="51"/>
+      <c r="K663" s="53" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="664" spans="1:11" s="132" customFormat="1">
-      <c r="A664" s="125"/>
-      <c r="B664" s="130" t="s">
-        <v>44</v>
-      </c>
-      <c r="C664" s="136" t="s">
-        <v>1144</v>
-      </c>
-      <c r="D664" s="130" t="s">
-        <v>42</v>
-      </c>
-      <c r="E664" s="130">
+    <row r="664" spans="1:11" s="54" customFormat="1">
+      <c r="A664" s="47"/>
+      <c r="B664" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C664" s="55" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D664" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="E664" s="52">
         <v>20</v>
       </c>
-      <c r="F664" s="130"/>
-      <c r="G664" s="137" t="s">
+      <c r="F664" s="52"/>
+      <c r="G664" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="H664" s="138"/>
-      <c r="I664" s="138"/>
-      <c r="J664" s="129"/>
-      <c r="K664" s="131" t="s">
+      <c r="H664" s="57"/>
+      <c r="I664" s="57"/>
+      <c r="J664" s="51"/>
+      <c r="K664" s="53" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="665" spans="1:11" s="132" customFormat="1">
-      <c r="K665" s="139"/>
+    <row r="665" spans="1:11" s="54" customFormat="1">
+      <c r="K665" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="B522:J522"/>
+    <mergeCell ref="B497:J497"/>
+    <mergeCell ref="B462:J462"/>
+    <mergeCell ref="B467:J467"/>
+    <mergeCell ref="B647:J647"/>
+    <mergeCell ref="B642:J642"/>
+    <mergeCell ref="B112:J112"/>
+    <mergeCell ref="B602:J602"/>
+    <mergeCell ref="B607:J607"/>
+    <mergeCell ref="B612:J612"/>
+    <mergeCell ref="B617:J617"/>
+    <mergeCell ref="B472:J472"/>
+    <mergeCell ref="B477:J477"/>
+    <mergeCell ref="B482:J482"/>
+    <mergeCell ref="B487:J487"/>
+    <mergeCell ref="B492:J492"/>
+    <mergeCell ref="B592:J592"/>
+    <mergeCell ref="B597:J597"/>
+    <mergeCell ref="B457:J457"/>
+    <mergeCell ref="B587:J587"/>
+    <mergeCell ref="B577:J577"/>
+    <mergeCell ref="B552:J552"/>
+    <mergeCell ref="B557:J557"/>
+    <mergeCell ref="B537:J537"/>
+    <mergeCell ref="B532:J532"/>
+    <mergeCell ref="B527:J527"/>
+    <mergeCell ref="B422:J422"/>
+    <mergeCell ref="B427:J427"/>
+    <mergeCell ref="B432:J432"/>
+    <mergeCell ref="B437:J437"/>
+    <mergeCell ref="B382:J382"/>
+    <mergeCell ref="B582:J582"/>
+    <mergeCell ref="B562:J562"/>
+    <mergeCell ref="B567:J567"/>
+    <mergeCell ref="B442:J442"/>
+    <mergeCell ref="B392:J392"/>
+    <mergeCell ref="B397:J397"/>
+    <mergeCell ref="B402:J402"/>
+    <mergeCell ref="B407:J407"/>
+    <mergeCell ref="B412:J412"/>
+    <mergeCell ref="B417:J417"/>
+    <mergeCell ref="B447:J447"/>
+    <mergeCell ref="B452:J452"/>
+    <mergeCell ref="B502:J502"/>
+    <mergeCell ref="B507:J507"/>
+    <mergeCell ref="B512:J512"/>
+    <mergeCell ref="B517:J517"/>
+    <mergeCell ref="B547:J547"/>
+    <mergeCell ref="B542:J542"/>
+    <mergeCell ref="B572:J572"/>
+    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="B92:J92"/>
+    <mergeCell ref="B97:J97"/>
+    <mergeCell ref="B102:J102"/>
+    <mergeCell ref="B107:J107"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B72:J72"/>
+    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="B47:J47"/>
+    <mergeCell ref="B52:J52"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="B62:J62"/>
+    <mergeCell ref="B67:J67"/>
+    <mergeCell ref="B387:J387"/>
+    <mergeCell ref="B222:J222"/>
+    <mergeCell ref="B192:J192"/>
+    <mergeCell ref="B197:J197"/>
+    <mergeCell ref="B202:J202"/>
+    <mergeCell ref="B207:J207"/>
+    <mergeCell ref="B212:J212"/>
+    <mergeCell ref="B272:J272"/>
+    <mergeCell ref="B227:J227"/>
+    <mergeCell ref="B232:J232"/>
+    <mergeCell ref="B242:J242"/>
+    <mergeCell ref="B347:J347"/>
+    <mergeCell ref="B352:J352"/>
+    <mergeCell ref="B357:J357"/>
+    <mergeCell ref="B367:J367"/>
+    <mergeCell ref="B237:J237"/>
+    <mergeCell ref="B632:J632"/>
+    <mergeCell ref="B277:J277"/>
+    <mergeCell ref="B282:J282"/>
+    <mergeCell ref="B287:J287"/>
+    <mergeCell ref="B292:J292"/>
+    <mergeCell ref="B247:J247"/>
+    <mergeCell ref="B252:J252"/>
+    <mergeCell ref="B257:J257"/>
+    <mergeCell ref="B262:J262"/>
+    <mergeCell ref="B267:J267"/>
+    <mergeCell ref="B337:J337"/>
+    <mergeCell ref="B342:J342"/>
+    <mergeCell ref="B297:J297"/>
+    <mergeCell ref="B302:J302"/>
+    <mergeCell ref="B307:J307"/>
+    <mergeCell ref="B312:J312"/>
+    <mergeCell ref="B317:J317"/>
+    <mergeCell ref="B372:J372"/>
+    <mergeCell ref="B377:J377"/>
+    <mergeCell ref="B322:J322"/>
+    <mergeCell ref="B327:J327"/>
+    <mergeCell ref="B332:J332"/>
+    <mergeCell ref="B362:J362"/>
     <mergeCell ref="B662:J662"/>
     <mergeCell ref="B657:J657"/>
     <mergeCell ref="B652:J652"/>
@@ -24452,115 +24561,6 @@
     <mergeCell ref="B162:J162"/>
     <mergeCell ref="B217:J217"/>
     <mergeCell ref="B182:J182"/>
-    <mergeCell ref="B237:J237"/>
-    <mergeCell ref="B632:J632"/>
-    <mergeCell ref="B277:J277"/>
-    <mergeCell ref="B282:J282"/>
-    <mergeCell ref="B287:J287"/>
-    <mergeCell ref="B292:J292"/>
-    <mergeCell ref="B247:J247"/>
-    <mergeCell ref="B252:J252"/>
-    <mergeCell ref="B257:J257"/>
-    <mergeCell ref="B262:J262"/>
-    <mergeCell ref="B267:J267"/>
-    <mergeCell ref="B337:J337"/>
-    <mergeCell ref="B342:J342"/>
-    <mergeCell ref="B297:J297"/>
-    <mergeCell ref="B302:J302"/>
-    <mergeCell ref="B307:J307"/>
-    <mergeCell ref="B312:J312"/>
-    <mergeCell ref="B317:J317"/>
-    <mergeCell ref="B372:J372"/>
-    <mergeCell ref="B377:J377"/>
-    <mergeCell ref="B322:J322"/>
-    <mergeCell ref="B327:J327"/>
-    <mergeCell ref="B332:J332"/>
-    <mergeCell ref="B362:J362"/>
-    <mergeCell ref="B387:J387"/>
-    <mergeCell ref="B222:J222"/>
-    <mergeCell ref="B192:J192"/>
-    <mergeCell ref="B197:J197"/>
-    <mergeCell ref="B202:J202"/>
-    <mergeCell ref="B207:J207"/>
-    <mergeCell ref="B212:J212"/>
-    <mergeCell ref="B272:J272"/>
-    <mergeCell ref="B227:J227"/>
-    <mergeCell ref="B232:J232"/>
-    <mergeCell ref="B242:J242"/>
-    <mergeCell ref="B87:J87"/>
-    <mergeCell ref="B92:J92"/>
-    <mergeCell ref="B97:J97"/>
-    <mergeCell ref="B102:J102"/>
-    <mergeCell ref="B107:J107"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B72:J72"/>
-    <mergeCell ref="B42:J42"/>
-    <mergeCell ref="B47:J47"/>
-    <mergeCell ref="B52:J52"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B37:J37"/>
-    <mergeCell ref="B57:J57"/>
-    <mergeCell ref="B62:J62"/>
-    <mergeCell ref="B67:J67"/>
-    <mergeCell ref="B347:J347"/>
-    <mergeCell ref="B352:J352"/>
-    <mergeCell ref="B357:J357"/>
-    <mergeCell ref="B367:J367"/>
-    <mergeCell ref="B422:J422"/>
-    <mergeCell ref="B427:J427"/>
-    <mergeCell ref="B432:J432"/>
-    <mergeCell ref="B437:J437"/>
-    <mergeCell ref="B382:J382"/>
-    <mergeCell ref="B582:J582"/>
-    <mergeCell ref="B562:J562"/>
-    <mergeCell ref="B567:J567"/>
-    <mergeCell ref="B442:J442"/>
-    <mergeCell ref="B392:J392"/>
-    <mergeCell ref="B397:J397"/>
-    <mergeCell ref="B402:J402"/>
-    <mergeCell ref="B407:J407"/>
-    <mergeCell ref="B412:J412"/>
-    <mergeCell ref="B417:J417"/>
-    <mergeCell ref="B447:J447"/>
-    <mergeCell ref="B452:J452"/>
-    <mergeCell ref="B502:J502"/>
-    <mergeCell ref="B507:J507"/>
-    <mergeCell ref="B512:J512"/>
-    <mergeCell ref="B517:J517"/>
-    <mergeCell ref="B547:J547"/>
-    <mergeCell ref="B542:J542"/>
-    <mergeCell ref="B572:J572"/>
-    <mergeCell ref="B462:J462"/>
-    <mergeCell ref="B467:J467"/>
-    <mergeCell ref="B647:J647"/>
-    <mergeCell ref="B642:J642"/>
-    <mergeCell ref="B112:J112"/>
-    <mergeCell ref="B602:J602"/>
-    <mergeCell ref="B607:J607"/>
-    <mergeCell ref="B612:J612"/>
-    <mergeCell ref="B617:J617"/>
-    <mergeCell ref="B472:J472"/>
-    <mergeCell ref="B477:J477"/>
-    <mergeCell ref="B482:J482"/>
-    <mergeCell ref="B487:J487"/>
-    <mergeCell ref="B492:J492"/>
-    <mergeCell ref="B592:J592"/>
-    <mergeCell ref="B597:J597"/>
-    <mergeCell ref="B457:J457"/>
-    <mergeCell ref="B587:J587"/>
-    <mergeCell ref="B577:J577"/>
-    <mergeCell ref="B552:J552"/>
-    <mergeCell ref="B557:J557"/>
-    <mergeCell ref="B537:J537"/>
-    <mergeCell ref="B532:J532"/>
-    <mergeCell ref="B527:J527"/>
-    <mergeCell ref="B522:J522"/>
-    <mergeCell ref="B497:J497"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -24618,17 +24618,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9"/>
-      <c r="B3" s="119" t="s">
+      <c r="B3" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
       <c r="K3" s="42"/>
     </row>
     <row r="4" spans="1:11">
@@ -24684,17 +24684,17 @@
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="120" t="s">
+      <c r="B7" s="62" t="s">
         <v>853</v>
       </c>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="123"/>
-      <c r="H7" s="123"/>
-      <c r="I7" s="123"/>
-      <c r="J7" s="124"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
       <c r="K7" s="44"/>
     </row>
     <row r="8" spans="1:11" ht="24">

--- a/development/MS/tools/listLogic/MS/MSListLogicDef.xlsx
+++ b/development/MS/tools/listLogic/MS/MSListLogicDef.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\tools\listLogic\MS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05635D23-3F04-46C6-8155-1D34A9B6FE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F78B058-F3A3-4863-97C1-2332B0B08659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" tabRatio="814" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -647,7 +647,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="1146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="1153">
   <si>
     <t>変更来歴</t>
     <rPh sb="0" eb="2">
@@ -5313,6 +5313,28 @@
   </si>
   <si>
     <t>sls_cond_typ_nm</t>
+  </si>
+  <si>
+    <t>FreeRsnTyp</t>
+  </si>
+  <si>
+    <t>MSC_FREE_RSN_TYP</t>
+  </si>
+  <si>
+    <t>無償理由区分</t>
+  </si>
+  <si>
+    <t>Free of Charge Reason Type</t>
+  </si>
+  <si>
+    <t>free_rsn_typ</t>
+  </si>
+  <si>
+    <t>無償理由区分を表す定数を取得する&lt;br&gt;
+無償理由区分：無償理由を表す</t>
+  </si>
+  <si>
+    <t>free_rsn_typ_nm</t>
   </si>
 </sst>
 </file>
@@ -7707,6 +7729,18 @@
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="3" xfId="322" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="66" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7716,18 +7750,6 @@
     <xf numFmtId="0" fontId="66" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="32" borderId="3" xfId="322" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="321" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -7782,6 +7804,99 @@
     <xf numFmtId="168" fontId="58" fillId="0" borderId="24" xfId="321" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="47" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="25" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="2" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="25" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="52" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="53" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="55" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="53" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="53" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="55" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="2" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="25" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="52" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="54" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="47" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="48" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="49" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="50" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="48" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="49" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="51" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="49" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="51" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="64" fillId="29" borderId="33" xfId="320" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7850,99 +7965,6 @@
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="48" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="49" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="50" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="25" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="47" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="2" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="25" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="48" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="49" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="51" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="49" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="51" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="52" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="53" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="54" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="47" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="52" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="53" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="55" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="53" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="55" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="323" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="319" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="2" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="25" xfId="324" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9750,126 +9772,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" s="30" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="88" t="s">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="89"/>
-      <c r="K1" s="89"/>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="89"/>
-      <c r="P1" s="89"/>
-      <c r="Q1" s="89"/>
-      <c r="R1" s="89"/>
-      <c r="S1" s="89"/>
-      <c r="T1" s="89"/>
-      <c r="U1" s="89"/>
-      <c r="V1" s="89"/>
-      <c r="W1" s="89"/>
-      <c r="X1" s="89"/>
-      <c r="Y1" s="89"/>
-      <c r="Z1" s="89"/>
-      <c r="AA1" s="89"/>
-      <c r="AB1" s="89"/>
-      <c r="AC1" s="89"/>
-      <c r="AD1" s="89"/>
-      <c r="AE1" s="89"/>
-      <c r="AF1" s="89"/>
-      <c r="AG1" s="89"/>
-      <c r="AH1" s="89"/>
-      <c r="AI1" s="89"/>
-      <c r="AJ1" s="89"/>
-      <c r="AK1" s="89"/>
-      <c r="AL1" s="89"/>
-      <c r="AM1" s="89"/>
-      <c r="AN1" s="89"/>
-      <c r="AO1" s="89"/>
-      <c r="AP1" s="89"/>
-      <c r="AQ1" s="89"/>
-      <c r="AR1" s="89"/>
-      <c r="AS1" s="89"/>
-      <c r="AT1" s="89"/>
-      <c r="AU1" s="89"/>
-      <c r="AV1" s="89"/>
-      <c r="AW1" s="89"/>
-      <c r="AX1" s="90"/>
-      <c r="AY1" s="84" t="s">
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
+      <c r="V1" s="120"/>
+      <c r="W1" s="120"/>
+      <c r="X1" s="120"/>
+      <c r="Y1" s="120"/>
+      <c r="Z1" s="120"/>
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="120"/>
+      <c r="AC1" s="120"/>
+      <c r="AD1" s="120"/>
+      <c r="AE1" s="120"/>
+      <c r="AF1" s="120"/>
+      <c r="AG1" s="120"/>
+      <c r="AH1" s="120"/>
+      <c r="AI1" s="120"/>
+      <c r="AJ1" s="120"/>
+      <c r="AK1" s="120"/>
+      <c r="AL1" s="120"/>
+      <c r="AM1" s="120"/>
+      <c r="AN1" s="120"/>
+      <c r="AO1" s="120"/>
+      <c r="AP1" s="120"/>
+      <c r="AQ1" s="120"/>
+      <c r="AR1" s="120"/>
+      <c r="AS1" s="120"/>
+      <c r="AT1" s="120"/>
+      <c r="AU1" s="120"/>
+      <c r="AV1" s="120"/>
+      <c r="AW1" s="120"/>
+      <c r="AX1" s="121"/>
+      <c r="AY1" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="AZ1" s="84"/>
-      <c r="BA1" s="84"/>
-      <c r="BB1" s="84"/>
-      <c r="BC1" s="85"/>
+      <c r="AZ1" s="115"/>
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="115"/>
+      <c r="BC1" s="116"/>
     </row>
     <row r="2" spans="1:55" s="30" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A2" s="102"/>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92"/>
-      <c r="R2" s="92"/>
-      <c r="S2" s="92"/>
-      <c r="T2" s="92"/>
-      <c r="U2" s="92"/>
-      <c r="V2" s="92"/>
-      <c r="W2" s="92"/>
-      <c r="X2" s="92"/>
-      <c r="Y2" s="92"/>
-      <c r="Z2" s="92"/>
-      <c r="AA2" s="92"/>
-      <c r="AB2" s="92"/>
-      <c r="AC2" s="92"/>
-      <c r="AD2" s="92"/>
-      <c r="AE2" s="92"/>
-      <c r="AF2" s="92"/>
-      <c r="AG2" s="92"/>
-      <c r="AH2" s="92"/>
-      <c r="AI2" s="92"/>
-      <c r="AJ2" s="92"/>
-      <c r="AK2" s="92"/>
-      <c r="AL2" s="92"/>
-      <c r="AM2" s="92"/>
-      <c r="AN2" s="92"/>
-      <c r="AO2" s="92"/>
-      <c r="AP2" s="92"/>
-      <c r="AQ2" s="92"/>
-      <c r="AR2" s="92"/>
-      <c r="AS2" s="92"/>
-      <c r="AT2" s="92"/>
-      <c r="AU2" s="92"/>
-      <c r="AV2" s="92"/>
-      <c r="AW2" s="92"/>
-      <c r="AX2" s="93"/>
-      <c r="AY2" s="86" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
+      <c r="P2" s="123"/>
+      <c r="Q2" s="123"/>
+      <c r="R2" s="123"/>
+      <c r="S2" s="123"/>
+      <c r="T2" s="123"/>
+      <c r="U2" s="123"/>
+      <c r="V2" s="123"/>
+      <c r="W2" s="123"/>
+      <c r="X2" s="123"/>
+      <c r="Y2" s="123"/>
+      <c r="Z2" s="123"/>
+      <c r="AA2" s="123"/>
+      <c r="AB2" s="123"/>
+      <c r="AC2" s="123"/>
+      <c r="AD2" s="123"/>
+      <c r="AE2" s="123"/>
+      <c r="AF2" s="123"/>
+      <c r="AG2" s="123"/>
+      <c r="AH2" s="123"/>
+      <c r="AI2" s="123"/>
+      <c r="AJ2" s="123"/>
+      <c r="AK2" s="123"/>
+      <c r="AL2" s="123"/>
+      <c r="AM2" s="123"/>
+      <c r="AN2" s="123"/>
+      <c r="AO2" s="123"/>
+      <c r="AP2" s="123"/>
+      <c r="AQ2" s="123"/>
+      <c r="AR2" s="123"/>
+      <c r="AS2" s="123"/>
+      <c r="AT2" s="123"/>
+      <c r="AU2" s="123"/>
+      <c r="AV2" s="123"/>
+      <c r="AW2" s="123"/>
+      <c r="AX2" s="124"/>
+      <c r="AY2" s="117" t="s">
         <v>916</v>
       </c>
-      <c r="AZ2" s="86"/>
-      <c r="BA2" s="86"/>
-      <c r="BB2" s="86"/>
-      <c r="BC2" s="87"/>
+      <c r="AZ2" s="117"/>
+      <c r="BA2" s="117"/>
+      <c r="BB2" s="117"/>
+      <c r="BC2" s="118"/>
     </row>
     <row r="3" spans="1:55" s="30" customFormat="1" ht="12" customHeight="1" thickBot="1">
       <c r="A3" s="31"/>
@@ -9921,1803 +9943,1803 @@
       <c r="A4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="94" t="s">
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="104"/>
-      <c r="K4" s="104"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="104"/>
-      <c r="N4" s="104"/>
-      <c r="O4" s="104"/>
-      <c r="P4" s="104"/>
-      <c r="Q4" s="104"/>
-      <c r="R4" s="104"/>
-      <c r="S4" s="104"/>
-      <c r="T4" s="104"/>
-      <c r="U4" s="104"/>
-      <c r="V4" s="104"/>
-      <c r="W4" s="104"/>
-      <c r="X4" s="104"/>
-      <c r="Y4" s="104"/>
-      <c r="Z4" s="104"/>
-      <c r="AA4" s="104"/>
-      <c r="AB4" s="104"/>
-      <c r="AC4" s="104"/>
-      <c r="AD4" s="104"/>
-      <c r="AE4" s="104"/>
-      <c r="AF4" s="104"/>
-      <c r="AG4" s="104"/>
-      <c r="AH4" s="104"/>
-      <c r="AI4" s="104"/>
-      <c r="AJ4" s="104"/>
-      <c r="AK4" s="105"/>
-      <c r="AL4" s="105"/>
-      <c r="AM4" s="105"/>
-      <c r="AN4" s="106"/>
-      <c r="AO4" s="97" t="s">
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="M4" s="135"/>
+      <c r="N4" s="135"/>
+      <c r="O4" s="135"/>
+      <c r="P4" s="135"/>
+      <c r="Q4" s="135"/>
+      <c r="R4" s="135"/>
+      <c r="S4" s="135"/>
+      <c r="T4" s="135"/>
+      <c r="U4" s="135"/>
+      <c r="V4" s="135"/>
+      <c r="W4" s="135"/>
+      <c r="X4" s="135"/>
+      <c r="Y4" s="135"/>
+      <c r="Z4" s="135"/>
+      <c r="AA4" s="135"/>
+      <c r="AB4" s="135"/>
+      <c r="AC4" s="135"/>
+      <c r="AD4" s="135"/>
+      <c r="AE4" s="135"/>
+      <c r="AF4" s="135"/>
+      <c r="AG4" s="135"/>
+      <c r="AH4" s="135"/>
+      <c r="AI4" s="135"/>
+      <c r="AJ4" s="135"/>
+      <c r="AK4" s="136"/>
+      <c r="AL4" s="136"/>
+      <c r="AM4" s="136"/>
+      <c r="AN4" s="137"/>
+      <c r="AO4" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="AP4" s="98"/>
-      <c r="AQ4" s="98"/>
-      <c r="AR4" s="98"/>
-      <c r="AS4" s="98"/>
-      <c r="AT4" s="98"/>
-      <c r="AU4" s="98"/>
-      <c r="AV4" s="98"/>
-      <c r="AW4" s="98"/>
-      <c r="AX4" s="98"/>
-      <c r="AY4" s="98"/>
-      <c r="AZ4" s="98"/>
-      <c r="BA4" s="98"/>
-      <c r="BB4" s="98"/>
-      <c r="BC4" s="99"/>
+      <c r="AP4" s="129"/>
+      <c r="AQ4" s="129"/>
+      <c r="AR4" s="129"/>
+      <c r="AS4" s="129"/>
+      <c r="AT4" s="129"/>
+      <c r="AU4" s="129"/>
+      <c r="AV4" s="129"/>
+      <c r="AW4" s="129"/>
+      <c r="AX4" s="129"/>
+      <c r="AY4" s="129"/>
+      <c r="AZ4" s="129"/>
+      <c r="BA4" s="129"/>
+      <c r="BB4" s="129"/>
+      <c r="BC4" s="130"/>
     </row>
     <row r="5" spans="1:55" ht="15" customHeight="1">
       <c r="A5" s="35" t="s">
         <v>589</v>
       </c>
-      <c r="B5" s="129"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="131"/>
-      <c r="I5" s="129" t="s">
+      <c r="B5" s="92"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
-      <c r="L5" s="124"/>
-      <c r="M5" s="124"/>
-      <c r="N5" s="124"/>
-      <c r="O5" s="124"/>
-      <c r="P5" s="124"/>
-      <c r="Q5" s="124"/>
-      <c r="R5" s="124"/>
-      <c r="S5" s="124"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="124"/>
-      <c r="W5" s="124"/>
-      <c r="X5" s="124"/>
-      <c r="Y5" s="124"/>
-      <c r="Z5" s="124"/>
-      <c r="AA5" s="124"/>
-      <c r="AB5" s="124"/>
-      <c r="AC5" s="124"/>
-      <c r="AD5" s="124"/>
-      <c r="AE5" s="124"/>
-      <c r="AF5" s="124"/>
-      <c r="AG5" s="124"/>
-      <c r="AH5" s="124"/>
-      <c r="AI5" s="124"/>
-      <c r="AJ5" s="124"/>
-      <c r="AK5" s="132"/>
-      <c r="AL5" s="132"/>
-      <c r="AM5" s="132"/>
-      <c r="AN5" s="133"/>
-      <c r="AO5" s="123"/>
-      <c r="AP5" s="124"/>
-      <c r="AQ5" s="124"/>
-      <c r="AR5" s="124"/>
-      <c r="AS5" s="124"/>
-      <c r="AT5" s="124"/>
-      <c r="AU5" s="124"/>
-      <c r="AV5" s="124"/>
-      <c r="AW5" s="124"/>
-      <c r="AX5" s="124"/>
-      <c r="AY5" s="124"/>
-      <c r="AZ5" s="124"/>
-      <c r="BA5" s="124"/>
-      <c r="BB5" s="124"/>
-      <c r="BC5" s="125"/>
+      <c r="J5" s="95"/>
+      <c r="K5" s="95"/>
+      <c r="L5" s="95"/>
+      <c r="M5" s="95"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="95"/>
+      <c r="P5" s="95"/>
+      <c r="Q5" s="95"/>
+      <c r="R5" s="95"/>
+      <c r="S5" s="95"/>
+      <c r="T5" s="95"/>
+      <c r="U5" s="95"/>
+      <c r="V5" s="95"/>
+      <c r="W5" s="95"/>
+      <c r="X5" s="95"/>
+      <c r="Y5" s="95"/>
+      <c r="Z5" s="95"/>
+      <c r="AA5" s="95"/>
+      <c r="AB5" s="95"/>
+      <c r="AC5" s="95"/>
+      <c r="AD5" s="95"/>
+      <c r="AE5" s="95"/>
+      <c r="AF5" s="95"/>
+      <c r="AG5" s="95"/>
+      <c r="AH5" s="95"/>
+      <c r="AI5" s="95"/>
+      <c r="AJ5" s="95"/>
+      <c r="AK5" s="96"/>
+      <c r="AL5" s="96"/>
+      <c r="AM5" s="96"/>
+      <c r="AN5" s="97"/>
+      <c r="AO5" s="102"/>
+      <c r="AP5" s="95"/>
+      <c r="AQ5" s="95"/>
+      <c r="AR5" s="95"/>
+      <c r="AS5" s="95"/>
+      <c r="AT5" s="95"/>
+      <c r="AU5" s="95"/>
+      <c r="AV5" s="95"/>
+      <c r="AW5" s="95"/>
+      <c r="AX5" s="95"/>
+      <c r="AY5" s="95"/>
+      <c r="AZ5" s="95"/>
+      <c r="BA5" s="95"/>
+      <c r="BB5" s="95"/>
+      <c r="BC5" s="103"/>
     </row>
     <row r="6" spans="1:55" ht="15" customHeight="1">
       <c r="A6" s="36" t="s">
         <v>957</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="110" t="s">
+      <c r="B6" s="87"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="87" t="s">
         <v>958</v>
       </c>
-      <c r="J6" s="114"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="114"/>
-      <c r="M6" s="114"/>
-      <c r="N6" s="114"/>
-      <c r="O6" s="114"/>
-      <c r="P6" s="114"/>
-      <c r="Q6" s="114"/>
-      <c r="R6" s="114"/>
-      <c r="S6" s="114"/>
-      <c r="T6" s="114"/>
-      <c r="U6" s="114"/>
-      <c r="V6" s="114"/>
-      <c r="W6" s="114"/>
-      <c r="X6" s="114"/>
-      <c r="Y6" s="114"/>
-      <c r="Z6" s="114"/>
-      <c r="AA6" s="114"/>
-      <c r="AB6" s="114"/>
-      <c r="AC6" s="114"/>
-      <c r="AD6" s="114"/>
-      <c r="AE6" s="114"/>
-      <c r="AF6" s="114"/>
-      <c r="AG6" s="114"/>
-      <c r="AH6" s="114"/>
-      <c r="AI6" s="114"/>
-      <c r="AJ6" s="114"/>
-      <c r="AK6" s="116"/>
-      <c r="AL6" s="116"/>
-      <c r="AM6" s="116"/>
-      <c r="AN6" s="117"/>
-      <c r="AO6" s="113" t="s">
+      <c r="J6" s="85"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="85"/>
+      <c r="O6" s="85"/>
+      <c r="P6" s="85"/>
+      <c r="Q6" s="85"/>
+      <c r="R6" s="85"/>
+      <c r="S6" s="85"/>
+      <c r="T6" s="85"/>
+      <c r="U6" s="85"/>
+      <c r="V6" s="85"/>
+      <c r="W6" s="85"/>
+      <c r="X6" s="85"/>
+      <c r="Y6" s="85"/>
+      <c r="Z6" s="85"/>
+      <c r="AA6" s="85"/>
+      <c r="AB6" s="85"/>
+      <c r="AC6" s="85"/>
+      <c r="AD6" s="85"/>
+      <c r="AE6" s="85"/>
+      <c r="AF6" s="85"/>
+      <c r="AG6" s="85"/>
+      <c r="AH6" s="85"/>
+      <c r="AI6" s="85"/>
+      <c r="AJ6" s="85"/>
+      <c r="AK6" s="90"/>
+      <c r="AL6" s="90"/>
+      <c r="AM6" s="90"/>
+      <c r="AN6" s="91"/>
+      <c r="AO6" s="84" t="s">
         <v>956</v>
       </c>
-      <c r="AP6" s="114"/>
-      <c r="AQ6" s="114"/>
-      <c r="AR6" s="114"/>
-      <c r="AS6" s="114"/>
-      <c r="AT6" s="114"/>
-      <c r="AU6" s="114"/>
-      <c r="AV6" s="114"/>
-      <c r="AW6" s="114"/>
-      <c r="AX6" s="114"/>
-      <c r="AY6" s="114"/>
-      <c r="AZ6" s="114"/>
-      <c r="BA6" s="114"/>
-      <c r="BB6" s="114"/>
-      <c r="BC6" s="115"/>
+      <c r="AP6" s="85"/>
+      <c r="AQ6" s="85"/>
+      <c r="AR6" s="85"/>
+      <c r="AS6" s="85"/>
+      <c r="AT6" s="85"/>
+      <c r="AU6" s="85"/>
+      <c r="AV6" s="85"/>
+      <c r="AW6" s="85"/>
+      <c r="AX6" s="85"/>
+      <c r="AY6" s="85"/>
+      <c r="AZ6" s="85"/>
+      <c r="BA6" s="85"/>
+      <c r="BB6" s="85"/>
+      <c r="BC6" s="86"/>
     </row>
     <row r="7" spans="1:55" ht="15" customHeight="1">
       <c r="A7" s="36" t="s">
         <v>1134</v>
       </c>
-      <c r="B7" s="110"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
-      <c r="E7" s="111"/>
-      <c r="F7" s="111"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="112"/>
-      <c r="I7" s="134" t="s">
+      <c r="B7" s="87"/>
+      <c r="C7" s="88"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="88"/>
+      <c r="H7" s="89"/>
+      <c r="I7" s="98" t="s">
         <v>1135</v>
       </c>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
-      <c r="L7" s="135"/>
-      <c r="M7" s="135"/>
-      <c r="N7" s="135"/>
-      <c r="O7" s="135"/>
-      <c r="P7" s="135"/>
-      <c r="Q7" s="135"/>
-      <c r="R7" s="135"/>
-      <c r="S7" s="135"/>
-      <c r="T7" s="135"/>
-      <c r="U7" s="135"/>
-      <c r="V7" s="135"/>
-      <c r="W7" s="135"/>
-      <c r="X7" s="135"/>
-      <c r="Y7" s="135"/>
-      <c r="Z7" s="135"/>
-      <c r="AA7" s="135"/>
-      <c r="AB7" s="135"/>
-      <c r="AC7" s="135"/>
-      <c r="AD7" s="135"/>
-      <c r="AE7" s="135"/>
-      <c r="AF7" s="135"/>
-      <c r="AG7" s="135"/>
-      <c r="AH7" s="135"/>
-      <c r="AI7" s="135"/>
-      <c r="AJ7" s="135"/>
-      <c r="AK7" s="136"/>
-      <c r="AL7" s="136"/>
-      <c r="AM7" s="136"/>
-      <c r="AN7" s="137"/>
-      <c r="AO7" s="126" t="s">
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
+      <c r="M7" s="99"/>
+      <c r="N7" s="99"/>
+      <c r="O7" s="99"/>
+      <c r="P7" s="99"/>
+      <c r="Q7" s="99"/>
+      <c r="R7" s="99"/>
+      <c r="S7" s="99"/>
+      <c r="T7" s="99"/>
+      <c r="U7" s="99"/>
+      <c r="V7" s="99"/>
+      <c r="W7" s="99"/>
+      <c r="X7" s="99"/>
+      <c r="Y7" s="99"/>
+      <c r="Z7" s="99"/>
+      <c r="AA7" s="99"/>
+      <c r="AB7" s="99"/>
+      <c r="AC7" s="99"/>
+      <c r="AD7" s="99"/>
+      <c r="AE7" s="99"/>
+      <c r="AF7" s="99"/>
+      <c r="AG7" s="99"/>
+      <c r="AH7" s="99"/>
+      <c r="AI7" s="99"/>
+      <c r="AJ7" s="99"/>
+      <c r="AK7" s="100"/>
+      <c r="AL7" s="100"/>
+      <c r="AM7" s="100"/>
+      <c r="AN7" s="101"/>
+      <c r="AO7" s="104" t="s">
         <v>1136</v>
       </c>
-      <c r="AP7" s="127"/>
-      <c r="AQ7" s="127"/>
-      <c r="AR7" s="127"/>
-      <c r="AS7" s="127"/>
-      <c r="AT7" s="127"/>
-      <c r="AU7" s="127"/>
-      <c r="AV7" s="127"/>
-      <c r="AW7" s="127"/>
-      <c r="AX7" s="127"/>
-      <c r="AY7" s="127"/>
-      <c r="AZ7" s="127"/>
-      <c r="BA7" s="127"/>
-      <c r="BB7" s="127"/>
-      <c r="BC7" s="128"/>
+      <c r="AP7" s="105"/>
+      <c r="AQ7" s="105"/>
+      <c r="AR7" s="105"/>
+      <c r="AS7" s="105"/>
+      <c r="AT7" s="105"/>
+      <c r="AU7" s="105"/>
+      <c r="AV7" s="105"/>
+      <c r="AW7" s="105"/>
+      <c r="AX7" s="105"/>
+      <c r="AY7" s="105"/>
+      <c r="AZ7" s="105"/>
+      <c r="BA7" s="105"/>
+      <c r="BB7" s="105"/>
+      <c r="BC7" s="106"/>
     </row>
     <row r="8" spans="1:55" ht="15" customHeight="1">
       <c r="A8" s="36"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="111"/>
-      <c r="F8" s="111"/>
-      <c r="G8" s="111"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="114"/>
-      <c r="K8" s="114"/>
-      <c r="L8" s="114"/>
-      <c r="M8" s="114"/>
-      <c r="N8" s="114"/>
-      <c r="O8" s="114"/>
-      <c r="P8" s="114"/>
-      <c r="Q8" s="114"/>
-      <c r="R8" s="114"/>
-      <c r="S8" s="114"/>
-      <c r="T8" s="114"/>
-      <c r="U8" s="114"/>
-      <c r="V8" s="114"/>
-      <c r="W8" s="114"/>
-      <c r="X8" s="114"/>
-      <c r="Y8" s="114"/>
-      <c r="Z8" s="114"/>
-      <c r="AA8" s="114"/>
-      <c r="AB8" s="114"/>
-      <c r="AC8" s="114"/>
-      <c r="AD8" s="114"/>
-      <c r="AE8" s="114"/>
-      <c r="AF8" s="114"/>
-      <c r="AG8" s="114"/>
-      <c r="AH8" s="114"/>
-      <c r="AI8" s="114"/>
-      <c r="AJ8" s="114"/>
-      <c r="AK8" s="116"/>
-      <c r="AL8" s="116"/>
-      <c r="AM8" s="116"/>
-      <c r="AN8" s="117"/>
-      <c r="AO8" s="113"/>
-      <c r="AP8" s="114"/>
-      <c r="AQ8" s="114"/>
-      <c r="AR8" s="114"/>
-      <c r="AS8" s="114"/>
-      <c r="AT8" s="114"/>
-      <c r="AU8" s="114"/>
-      <c r="AV8" s="114"/>
-      <c r="AW8" s="114"/>
-      <c r="AX8" s="114"/>
-      <c r="AY8" s="114"/>
-      <c r="AZ8" s="114"/>
-      <c r="BA8" s="114"/>
-      <c r="BB8" s="114"/>
-      <c r="BC8" s="115"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="89"/>
+      <c r="I8" s="87"/>
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="85"/>
+      <c r="M8" s="85"/>
+      <c r="N8" s="85"/>
+      <c r="O8" s="85"/>
+      <c r="P8" s="85"/>
+      <c r="Q8" s="85"/>
+      <c r="R8" s="85"/>
+      <c r="S8" s="85"/>
+      <c r="T8" s="85"/>
+      <c r="U8" s="85"/>
+      <c r="V8" s="85"/>
+      <c r="W8" s="85"/>
+      <c r="X8" s="85"/>
+      <c r="Y8" s="85"/>
+      <c r="Z8" s="85"/>
+      <c r="AA8" s="85"/>
+      <c r="AB8" s="85"/>
+      <c r="AC8" s="85"/>
+      <c r="AD8" s="85"/>
+      <c r="AE8" s="85"/>
+      <c r="AF8" s="85"/>
+      <c r="AG8" s="85"/>
+      <c r="AH8" s="85"/>
+      <c r="AI8" s="85"/>
+      <c r="AJ8" s="85"/>
+      <c r="AK8" s="90"/>
+      <c r="AL8" s="90"/>
+      <c r="AM8" s="90"/>
+      <c r="AN8" s="91"/>
+      <c r="AO8" s="84"/>
+      <c r="AP8" s="85"/>
+      <c r="AQ8" s="85"/>
+      <c r="AR8" s="85"/>
+      <c r="AS8" s="85"/>
+      <c r="AT8" s="85"/>
+      <c r="AU8" s="85"/>
+      <c r="AV8" s="85"/>
+      <c r="AW8" s="85"/>
+      <c r="AX8" s="85"/>
+      <c r="AY8" s="85"/>
+      <c r="AZ8" s="85"/>
+      <c r="BA8" s="85"/>
+      <c r="BB8" s="85"/>
+      <c r="BC8" s="86"/>
     </row>
     <row r="9" spans="1:55" ht="15" customHeight="1">
       <c r="A9" s="36"/>
-      <c r="B9" s="110"/>
-      <c r="C9" s="111"/>
-      <c r="D9" s="111"/>
-      <c r="E9" s="111"/>
-      <c r="F9" s="111"/>
-      <c r="G9" s="111"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="114"/>
-      <c r="K9" s="114"/>
-      <c r="L9" s="114"/>
-      <c r="M9" s="114"/>
-      <c r="N9" s="114"/>
-      <c r="O9" s="114"/>
-      <c r="P9" s="114"/>
-      <c r="Q9" s="114"/>
-      <c r="R9" s="114"/>
-      <c r="S9" s="114"/>
-      <c r="T9" s="114"/>
-      <c r="U9" s="114"/>
-      <c r="V9" s="114"/>
-      <c r="W9" s="114"/>
-      <c r="X9" s="114"/>
-      <c r="Y9" s="114"/>
-      <c r="Z9" s="114"/>
-      <c r="AA9" s="114"/>
-      <c r="AB9" s="114"/>
-      <c r="AC9" s="114"/>
-      <c r="AD9" s="114"/>
-      <c r="AE9" s="114"/>
-      <c r="AF9" s="114"/>
-      <c r="AG9" s="114"/>
-      <c r="AH9" s="114"/>
-      <c r="AI9" s="114"/>
-      <c r="AJ9" s="114"/>
-      <c r="AK9" s="116"/>
-      <c r="AL9" s="116"/>
-      <c r="AM9" s="116"/>
-      <c r="AN9" s="117"/>
-      <c r="AO9" s="113"/>
-      <c r="AP9" s="114"/>
-      <c r="AQ9" s="114"/>
-      <c r="AR9" s="114"/>
-      <c r="AS9" s="114"/>
-      <c r="AT9" s="114"/>
-      <c r="AU9" s="114"/>
-      <c r="AV9" s="114"/>
-      <c r="AW9" s="114"/>
-      <c r="AX9" s="114"/>
-      <c r="AY9" s="114"/>
-      <c r="AZ9" s="114"/>
-      <c r="BA9" s="114"/>
-      <c r="BB9" s="114"/>
-      <c r="BC9" s="115"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="85"/>
+      <c r="P9" s="85"/>
+      <c r="Q9" s="85"/>
+      <c r="R9" s="85"/>
+      <c r="S9" s="85"/>
+      <c r="T9" s="85"/>
+      <c r="U9" s="85"/>
+      <c r="V9" s="85"/>
+      <c r="W9" s="85"/>
+      <c r="X9" s="85"/>
+      <c r="Y9" s="85"/>
+      <c r="Z9" s="85"/>
+      <c r="AA9" s="85"/>
+      <c r="AB9" s="85"/>
+      <c r="AC9" s="85"/>
+      <c r="AD9" s="85"/>
+      <c r="AE9" s="85"/>
+      <c r="AF9" s="85"/>
+      <c r="AG9" s="85"/>
+      <c r="AH9" s="85"/>
+      <c r="AI9" s="85"/>
+      <c r="AJ9" s="85"/>
+      <c r="AK9" s="90"/>
+      <c r="AL9" s="90"/>
+      <c r="AM9" s="90"/>
+      <c r="AN9" s="91"/>
+      <c r="AO9" s="84"/>
+      <c r="AP9" s="85"/>
+      <c r="AQ9" s="85"/>
+      <c r="AR9" s="85"/>
+      <c r="AS9" s="85"/>
+      <c r="AT9" s="85"/>
+      <c r="AU9" s="85"/>
+      <c r="AV9" s="85"/>
+      <c r="AW9" s="85"/>
+      <c r="AX9" s="85"/>
+      <c r="AY9" s="85"/>
+      <c r="AZ9" s="85"/>
+      <c r="BA9" s="85"/>
+      <c r="BB9" s="85"/>
+      <c r="BC9" s="86"/>
     </row>
     <row r="10" spans="1:55" ht="15" customHeight="1">
       <c r="A10" s="36"/>
-      <c r="B10" s="110"/>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="111"/>
-      <c r="G10" s="111"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="114"/>
-      <c r="K10" s="114"/>
-      <c r="L10" s="114"/>
-      <c r="M10" s="114"/>
-      <c r="N10" s="114"/>
-      <c r="O10" s="114"/>
-      <c r="P10" s="114"/>
-      <c r="Q10" s="114"/>
-      <c r="R10" s="114"/>
-      <c r="S10" s="114"/>
-      <c r="T10" s="114"/>
-      <c r="U10" s="114"/>
-      <c r="V10" s="114"/>
-      <c r="W10" s="114"/>
-      <c r="X10" s="114"/>
-      <c r="Y10" s="114"/>
-      <c r="Z10" s="114"/>
-      <c r="AA10" s="114"/>
-      <c r="AB10" s="114"/>
-      <c r="AC10" s="114"/>
-      <c r="AD10" s="114"/>
-      <c r="AE10" s="114"/>
-      <c r="AF10" s="114"/>
-      <c r="AG10" s="114"/>
-      <c r="AH10" s="114"/>
-      <c r="AI10" s="114"/>
-      <c r="AJ10" s="114"/>
-      <c r="AK10" s="116"/>
-      <c r="AL10" s="116"/>
-      <c r="AM10" s="116"/>
-      <c r="AN10" s="117"/>
-      <c r="AO10" s="113"/>
-      <c r="AP10" s="114"/>
-      <c r="AQ10" s="114"/>
-      <c r="AR10" s="114"/>
-      <c r="AS10" s="114"/>
-      <c r="AT10" s="114"/>
-      <c r="AU10" s="114"/>
-      <c r="AV10" s="114"/>
-      <c r="AW10" s="114"/>
-      <c r="AX10" s="114"/>
-      <c r="AY10" s="114"/>
-      <c r="AZ10" s="114"/>
-      <c r="BA10" s="114"/>
-      <c r="BB10" s="114"/>
-      <c r="BC10" s="115"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="85"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="85"/>
+      <c r="Q10" s="85"/>
+      <c r="R10" s="85"/>
+      <c r="S10" s="85"/>
+      <c r="T10" s="85"/>
+      <c r="U10" s="85"/>
+      <c r="V10" s="85"/>
+      <c r="W10" s="85"/>
+      <c r="X10" s="85"/>
+      <c r="Y10" s="85"/>
+      <c r="Z10" s="85"/>
+      <c r="AA10" s="85"/>
+      <c r="AB10" s="85"/>
+      <c r="AC10" s="85"/>
+      <c r="AD10" s="85"/>
+      <c r="AE10" s="85"/>
+      <c r="AF10" s="85"/>
+      <c r="AG10" s="85"/>
+      <c r="AH10" s="85"/>
+      <c r="AI10" s="85"/>
+      <c r="AJ10" s="85"/>
+      <c r="AK10" s="90"/>
+      <c r="AL10" s="90"/>
+      <c r="AM10" s="90"/>
+      <c r="AN10" s="91"/>
+      <c r="AO10" s="84"/>
+      <c r="AP10" s="85"/>
+      <c r="AQ10" s="85"/>
+      <c r="AR10" s="85"/>
+      <c r="AS10" s="85"/>
+      <c r="AT10" s="85"/>
+      <c r="AU10" s="85"/>
+      <c r="AV10" s="85"/>
+      <c r="AW10" s="85"/>
+      <c r="AX10" s="85"/>
+      <c r="AY10" s="85"/>
+      <c r="AZ10" s="85"/>
+      <c r="BA10" s="85"/>
+      <c r="BB10" s="85"/>
+      <c r="BC10" s="86"/>
     </row>
     <row r="11" spans="1:55" ht="15" customHeight="1">
       <c r="A11" s="36"/>
-      <c r="B11" s="110"/>
-      <c r="C11" s="111"/>
-      <c r="D11" s="111"/>
-      <c r="E11" s="111"/>
-      <c r="F11" s="111"/>
-      <c r="G11" s="111"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="114"/>
-      <c r="K11" s="114"/>
-      <c r="L11" s="114"/>
-      <c r="M11" s="114"/>
-      <c r="N11" s="114"/>
-      <c r="O11" s="114"/>
-      <c r="P11" s="114"/>
-      <c r="Q11" s="114"/>
-      <c r="R11" s="114"/>
-      <c r="S11" s="114"/>
-      <c r="T11" s="114"/>
-      <c r="U11" s="114"/>
-      <c r="V11" s="114"/>
-      <c r="W11" s="114"/>
-      <c r="X11" s="114"/>
-      <c r="Y11" s="114"/>
-      <c r="Z11" s="114"/>
-      <c r="AA11" s="114"/>
-      <c r="AB11" s="114"/>
-      <c r="AC11" s="114"/>
-      <c r="AD11" s="114"/>
-      <c r="AE11" s="114"/>
-      <c r="AF11" s="114"/>
-      <c r="AG11" s="114"/>
-      <c r="AH11" s="114"/>
-      <c r="AI11" s="114"/>
-      <c r="AJ11" s="114"/>
-      <c r="AK11" s="116"/>
-      <c r="AL11" s="116"/>
-      <c r="AM11" s="116"/>
-      <c r="AN11" s="117"/>
-      <c r="AO11" s="113"/>
-      <c r="AP11" s="114"/>
-      <c r="AQ11" s="114"/>
-      <c r="AR11" s="114"/>
-      <c r="AS11" s="114"/>
-      <c r="AT11" s="114"/>
-      <c r="AU11" s="114"/>
-      <c r="AV11" s="114"/>
-      <c r="AW11" s="114"/>
-      <c r="AX11" s="114"/>
-      <c r="AY11" s="114"/>
-      <c r="AZ11" s="114"/>
-      <c r="BA11" s="114"/>
-      <c r="BB11" s="114"/>
-      <c r="BC11" s="115"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="85"/>
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="85"/>
+      <c r="P11" s="85"/>
+      <c r="Q11" s="85"/>
+      <c r="R11" s="85"/>
+      <c r="S11" s="85"/>
+      <c r="T11" s="85"/>
+      <c r="U11" s="85"/>
+      <c r="V11" s="85"/>
+      <c r="W11" s="85"/>
+      <c r="X11" s="85"/>
+      <c r="Y11" s="85"/>
+      <c r="Z11" s="85"/>
+      <c r="AA11" s="85"/>
+      <c r="AB11" s="85"/>
+      <c r="AC11" s="85"/>
+      <c r="AD11" s="85"/>
+      <c r="AE11" s="85"/>
+      <c r="AF11" s="85"/>
+      <c r="AG11" s="85"/>
+      <c r="AH11" s="85"/>
+      <c r="AI11" s="85"/>
+      <c r="AJ11" s="85"/>
+      <c r="AK11" s="90"/>
+      <c r="AL11" s="90"/>
+      <c r="AM11" s="90"/>
+      <c r="AN11" s="91"/>
+      <c r="AO11" s="84"/>
+      <c r="AP11" s="85"/>
+      <c r="AQ11" s="85"/>
+      <c r="AR11" s="85"/>
+      <c r="AS11" s="85"/>
+      <c r="AT11" s="85"/>
+      <c r="AU11" s="85"/>
+      <c r="AV11" s="85"/>
+      <c r="AW11" s="85"/>
+      <c r="AX11" s="85"/>
+      <c r="AY11" s="85"/>
+      <c r="AZ11" s="85"/>
+      <c r="BA11" s="85"/>
+      <c r="BB11" s="85"/>
+      <c r="BC11" s="86"/>
     </row>
     <row r="12" spans="1:55" ht="15" customHeight="1">
       <c r="A12" s="36"/>
-      <c r="B12" s="110"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="114"/>
-      <c r="K12" s="114"/>
-      <c r="L12" s="114"/>
-      <c r="M12" s="114"/>
-      <c r="N12" s="114"/>
-      <c r="O12" s="114"/>
-      <c r="P12" s="114"/>
-      <c r="Q12" s="114"/>
-      <c r="R12" s="114"/>
-      <c r="S12" s="114"/>
-      <c r="T12" s="114"/>
-      <c r="U12" s="114"/>
-      <c r="V12" s="114"/>
-      <c r="W12" s="114"/>
-      <c r="X12" s="114"/>
-      <c r="Y12" s="114"/>
-      <c r="Z12" s="114"/>
-      <c r="AA12" s="114"/>
-      <c r="AB12" s="114"/>
-      <c r="AC12" s="114"/>
-      <c r="AD12" s="114"/>
-      <c r="AE12" s="114"/>
-      <c r="AF12" s="114"/>
-      <c r="AG12" s="114"/>
-      <c r="AH12" s="114"/>
-      <c r="AI12" s="114"/>
-      <c r="AJ12" s="114"/>
-      <c r="AK12" s="116"/>
-      <c r="AL12" s="116"/>
-      <c r="AM12" s="116"/>
-      <c r="AN12" s="117"/>
-      <c r="AO12" s="113"/>
-      <c r="AP12" s="114"/>
-      <c r="AQ12" s="114"/>
-      <c r="AR12" s="114"/>
-      <c r="AS12" s="114"/>
-      <c r="AT12" s="114"/>
-      <c r="AU12" s="114"/>
-      <c r="AV12" s="114"/>
-      <c r="AW12" s="114"/>
-      <c r="AX12" s="114"/>
-      <c r="AY12" s="114"/>
-      <c r="AZ12" s="114"/>
-      <c r="BA12" s="114"/>
-      <c r="BB12" s="114"/>
-      <c r="BC12" s="115"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="89"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="85"/>
+      <c r="K12" s="85"/>
+      <c r="L12" s="85"/>
+      <c r="M12" s="85"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="85"/>
+      <c r="P12" s="85"/>
+      <c r="Q12" s="85"/>
+      <c r="R12" s="85"/>
+      <c r="S12" s="85"/>
+      <c r="T12" s="85"/>
+      <c r="U12" s="85"/>
+      <c r="V12" s="85"/>
+      <c r="W12" s="85"/>
+      <c r="X12" s="85"/>
+      <c r="Y12" s="85"/>
+      <c r="Z12" s="85"/>
+      <c r="AA12" s="85"/>
+      <c r="AB12" s="85"/>
+      <c r="AC12" s="85"/>
+      <c r="AD12" s="85"/>
+      <c r="AE12" s="85"/>
+      <c r="AF12" s="85"/>
+      <c r="AG12" s="85"/>
+      <c r="AH12" s="85"/>
+      <c r="AI12" s="85"/>
+      <c r="AJ12" s="85"/>
+      <c r="AK12" s="90"/>
+      <c r="AL12" s="90"/>
+      <c r="AM12" s="90"/>
+      <c r="AN12" s="91"/>
+      <c r="AO12" s="84"/>
+      <c r="AP12" s="85"/>
+      <c r="AQ12" s="85"/>
+      <c r="AR12" s="85"/>
+      <c r="AS12" s="85"/>
+      <c r="AT12" s="85"/>
+      <c r="AU12" s="85"/>
+      <c r="AV12" s="85"/>
+      <c r="AW12" s="85"/>
+      <c r="AX12" s="85"/>
+      <c r="AY12" s="85"/>
+      <c r="AZ12" s="85"/>
+      <c r="BA12" s="85"/>
+      <c r="BB12" s="85"/>
+      <c r="BC12" s="86"/>
     </row>
     <row r="13" spans="1:55" ht="15" customHeight="1">
       <c r="A13" s="36"/>
-      <c r="B13" s="110"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="112"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="114"/>
-      <c r="K13" s="114"/>
-      <c r="L13" s="114"/>
-      <c r="M13" s="114"/>
-      <c r="N13" s="114"/>
-      <c r="O13" s="114"/>
-      <c r="P13" s="114"/>
-      <c r="Q13" s="114"/>
-      <c r="R13" s="114"/>
-      <c r="S13" s="114"/>
-      <c r="T13" s="114"/>
-      <c r="U13" s="114"/>
-      <c r="V13" s="114"/>
-      <c r="W13" s="114"/>
-      <c r="X13" s="114"/>
-      <c r="Y13" s="114"/>
-      <c r="Z13" s="114"/>
-      <c r="AA13" s="114"/>
-      <c r="AB13" s="114"/>
-      <c r="AC13" s="114"/>
-      <c r="AD13" s="114"/>
-      <c r="AE13" s="114"/>
-      <c r="AF13" s="114"/>
-      <c r="AG13" s="114"/>
-      <c r="AH13" s="114"/>
-      <c r="AI13" s="114"/>
-      <c r="AJ13" s="114"/>
-      <c r="AK13" s="116"/>
-      <c r="AL13" s="116"/>
-      <c r="AM13" s="116"/>
-      <c r="AN13" s="117"/>
-      <c r="AO13" s="113"/>
-      <c r="AP13" s="114"/>
-      <c r="AQ13" s="114"/>
-      <c r="AR13" s="114"/>
-      <c r="AS13" s="114"/>
-      <c r="AT13" s="114"/>
-      <c r="AU13" s="114"/>
-      <c r="AV13" s="114"/>
-      <c r="AW13" s="114"/>
-      <c r="AX13" s="114"/>
-      <c r="AY13" s="114"/>
-      <c r="AZ13" s="114"/>
-      <c r="BA13" s="114"/>
-      <c r="BB13" s="114"/>
-      <c r="BC13" s="115"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="89"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="85"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
+      <c r="M13" s="85"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="85"/>
+      <c r="P13" s="85"/>
+      <c r="Q13" s="85"/>
+      <c r="R13" s="85"/>
+      <c r="S13" s="85"/>
+      <c r="T13" s="85"/>
+      <c r="U13" s="85"/>
+      <c r="V13" s="85"/>
+      <c r="W13" s="85"/>
+      <c r="X13" s="85"/>
+      <c r="Y13" s="85"/>
+      <c r="Z13" s="85"/>
+      <c r="AA13" s="85"/>
+      <c r="AB13" s="85"/>
+      <c r="AC13" s="85"/>
+      <c r="AD13" s="85"/>
+      <c r="AE13" s="85"/>
+      <c r="AF13" s="85"/>
+      <c r="AG13" s="85"/>
+      <c r="AH13" s="85"/>
+      <c r="AI13" s="85"/>
+      <c r="AJ13" s="85"/>
+      <c r="AK13" s="90"/>
+      <c r="AL13" s="90"/>
+      <c r="AM13" s="90"/>
+      <c r="AN13" s="91"/>
+      <c r="AO13" s="84"/>
+      <c r="AP13" s="85"/>
+      <c r="AQ13" s="85"/>
+      <c r="AR13" s="85"/>
+      <c r="AS13" s="85"/>
+      <c r="AT13" s="85"/>
+      <c r="AU13" s="85"/>
+      <c r="AV13" s="85"/>
+      <c r="AW13" s="85"/>
+      <c r="AX13" s="85"/>
+      <c r="AY13" s="85"/>
+      <c r="AZ13" s="85"/>
+      <c r="BA13" s="85"/>
+      <c r="BB13" s="85"/>
+      <c r="BC13" s="86"/>
     </row>
     <row r="14" spans="1:55" ht="15" customHeight="1">
       <c r="A14" s="36"/>
-      <c r="B14" s="110"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="114"/>
-      <c r="K14" s="114"/>
-      <c r="L14" s="114"/>
-      <c r="M14" s="114"/>
-      <c r="N14" s="114"/>
-      <c r="O14" s="114"/>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="114"/>
-      <c r="R14" s="114"/>
-      <c r="S14" s="114"/>
-      <c r="T14" s="114"/>
-      <c r="U14" s="114"/>
-      <c r="V14" s="114"/>
-      <c r="W14" s="114"/>
-      <c r="X14" s="114"/>
-      <c r="Y14" s="114"/>
-      <c r="Z14" s="114"/>
-      <c r="AA14" s="114"/>
-      <c r="AB14" s="114"/>
-      <c r="AC14" s="114"/>
-      <c r="AD14" s="114"/>
-      <c r="AE14" s="114"/>
-      <c r="AF14" s="114"/>
-      <c r="AG14" s="114"/>
-      <c r="AH14" s="114"/>
-      <c r="AI14" s="114"/>
-      <c r="AJ14" s="114"/>
-      <c r="AK14" s="116"/>
-      <c r="AL14" s="116"/>
-      <c r="AM14" s="116"/>
-      <c r="AN14" s="117"/>
-      <c r="AO14" s="113"/>
-      <c r="AP14" s="114"/>
-      <c r="AQ14" s="114"/>
-      <c r="AR14" s="114"/>
-      <c r="AS14" s="114"/>
-      <c r="AT14" s="114"/>
-      <c r="AU14" s="114"/>
-      <c r="AV14" s="114"/>
-      <c r="AW14" s="114"/>
-      <c r="AX14" s="114"/>
-      <c r="AY14" s="114"/>
-      <c r="AZ14" s="114"/>
-      <c r="BA14" s="114"/>
-      <c r="BB14" s="114"/>
-      <c r="BC14" s="115"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="88"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="85"/>
+      <c r="K14" s="85"/>
+      <c r="L14" s="85"/>
+      <c r="M14" s="85"/>
+      <c r="N14" s="85"/>
+      <c r="O14" s="85"/>
+      <c r="P14" s="85"/>
+      <c r="Q14" s="85"/>
+      <c r="R14" s="85"/>
+      <c r="S14" s="85"/>
+      <c r="T14" s="85"/>
+      <c r="U14" s="85"/>
+      <c r="V14" s="85"/>
+      <c r="W14" s="85"/>
+      <c r="X14" s="85"/>
+      <c r="Y14" s="85"/>
+      <c r="Z14" s="85"/>
+      <c r="AA14" s="85"/>
+      <c r="AB14" s="85"/>
+      <c r="AC14" s="85"/>
+      <c r="AD14" s="85"/>
+      <c r="AE14" s="85"/>
+      <c r="AF14" s="85"/>
+      <c r="AG14" s="85"/>
+      <c r="AH14" s="85"/>
+      <c r="AI14" s="85"/>
+      <c r="AJ14" s="85"/>
+      <c r="AK14" s="90"/>
+      <c r="AL14" s="90"/>
+      <c r="AM14" s="90"/>
+      <c r="AN14" s="91"/>
+      <c r="AO14" s="84"/>
+      <c r="AP14" s="85"/>
+      <c r="AQ14" s="85"/>
+      <c r="AR14" s="85"/>
+      <c r="AS14" s="85"/>
+      <c r="AT14" s="85"/>
+      <c r="AU14" s="85"/>
+      <c r="AV14" s="85"/>
+      <c r="AW14" s="85"/>
+      <c r="AX14" s="85"/>
+      <c r="AY14" s="85"/>
+      <c r="AZ14" s="85"/>
+      <c r="BA14" s="85"/>
+      <c r="BB14" s="85"/>
+      <c r="BC14" s="86"/>
     </row>
     <row r="15" spans="1:55" ht="15" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="110"/>
-      <c r="C15" s="111"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="112"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="114"/>
-      <c r="K15" s="114"/>
-      <c r="L15" s="114"/>
-      <c r="M15" s="114"/>
-      <c r="N15" s="114"/>
-      <c r="O15" s="114"/>
-      <c r="P15" s="114"/>
-      <c r="Q15" s="114"/>
-      <c r="R15" s="114"/>
-      <c r="S15" s="114"/>
-      <c r="T15" s="114"/>
-      <c r="U15" s="114"/>
-      <c r="V15" s="114"/>
-      <c r="W15" s="114"/>
-      <c r="X15" s="114"/>
-      <c r="Y15" s="114"/>
-      <c r="Z15" s="114"/>
-      <c r="AA15" s="114"/>
-      <c r="AB15" s="114"/>
-      <c r="AC15" s="114"/>
-      <c r="AD15" s="114"/>
-      <c r="AE15" s="114"/>
-      <c r="AF15" s="114"/>
-      <c r="AG15" s="114"/>
-      <c r="AH15" s="114"/>
-      <c r="AI15" s="114"/>
-      <c r="AJ15" s="114"/>
-      <c r="AK15" s="116"/>
-      <c r="AL15" s="116"/>
-      <c r="AM15" s="116"/>
-      <c r="AN15" s="117"/>
-      <c r="AO15" s="113"/>
-      <c r="AP15" s="114"/>
-      <c r="AQ15" s="114"/>
-      <c r="AR15" s="114"/>
-      <c r="AS15" s="114"/>
-      <c r="AT15" s="114"/>
-      <c r="AU15" s="114"/>
-      <c r="AV15" s="114"/>
-      <c r="AW15" s="114"/>
-      <c r="AX15" s="114"/>
-      <c r="AY15" s="114"/>
-      <c r="AZ15" s="114"/>
-      <c r="BA15" s="114"/>
-      <c r="BB15" s="114"/>
-      <c r="BC15" s="115"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="87"/>
+      <c r="J15" s="85"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="85"/>
+      <c r="M15" s="85"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="85"/>
+      <c r="P15" s="85"/>
+      <c r="Q15" s="85"/>
+      <c r="R15" s="85"/>
+      <c r="S15" s="85"/>
+      <c r="T15" s="85"/>
+      <c r="U15" s="85"/>
+      <c r="V15" s="85"/>
+      <c r="W15" s="85"/>
+      <c r="X15" s="85"/>
+      <c r="Y15" s="85"/>
+      <c r="Z15" s="85"/>
+      <c r="AA15" s="85"/>
+      <c r="AB15" s="85"/>
+      <c r="AC15" s="85"/>
+      <c r="AD15" s="85"/>
+      <c r="AE15" s="85"/>
+      <c r="AF15" s="85"/>
+      <c r="AG15" s="85"/>
+      <c r="AH15" s="85"/>
+      <c r="AI15" s="85"/>
+      <c r="AJ15" s="85"/>
+      <c r="AK15" s="90"/>
+      <c r="AL15" s="90"/>
+      <c r="AM15" s="90"/>
+      <c r="AN15" s="91"/>
+      <c r="AO15" s="84"/>
+      <c r="AP15" s="85"/>
+      <c r="AQ15" s="85"/>
+      <c r="AR15" s="85"/>
+      <c r="AS15" s="85"/>
+      <c r="AT15" s="85"/>
+      <c r="AU15" s="85"/>
+      <c r="AV15" s="85"/>
+      <c r="AW15" s="85"/>
+      <c r="AX15" s="85"/>
+      <c r="AY15" s="85"/>
+      <c r="AZ15" s="85"/>
+      <c r="BA15" s="85"/>
+      <c r="BB15" s="85"/>
+      <c r="BC15" s="86"/>
     </row>
     <row r="16" spans="1:55" ht="15" customHeight="1">
       <c r="A16" s="37"/>
-      <c r="B16" s="110"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="112"/>
-      <c r="I16" s="110"/>
-      <c r="J16" s="114"/>
-      <c r="K16" s="114"/>
-      <c r="L16" s="114"/>
-      <c r="M16" s="114"/>
-      <c r="N16" s="114"/>
-      <c r="O16" s="114"/>
-      <c r="P16" s="114"/>
-      <c r="Q16" s="114"/>
-      <c r="R16" s="114"/>
-      <c r="S16" s="114"/>
-      <c r="T16" s="114"/>
-      <c r="U16" s="114"/>
-      <c r="V16" s="114"/>
-      <c r="W16" s="114"/>
-      <c r="X16" s="114"/>
-      <c r="Y16" s="114"/>
-      <c r="Z16" s="114"/>
-      <c r="AA16" s="114"/>
-      <c r="AB16" s="114"/>
-      <c r="AC16" s="114"/>
-      <c r="AD16" s="114"/>
-      <c r="AE16" s="114"/>
-      <c r="AF16" s="114"/>
-      <c r="AG16" s="114"/>
-      <c r="AH16" s="114"/>
-      <c r="AI16" s="114"/>
-      <c r="AJ16" s="114"/>
-      <c r="AK16" s="116"/>
-      <c r="AL16" s="116"/>
-      <c r="AM16" s="116"/>
-      <c r="AN16" s="117"/>
-      <c r="AO16" s="113"/>
-      <c r="AP16" s="114"/>
-      <c r="AQ16" s="114"/>
-      <c r="AR16" s="114"/>
-      <c r="AS16" s="114"/>
-      <c r="AT16" s="114"/>
-      <c r="AU16" s="114"/>
-      <c r="AV16" s="114"/>
-      <c r="AW16" s="114"/>
-      <c r="AX16" s="114"/>
-      <c r="AY16" s="114"/>
-      <c r="AZ16" s="114"/>
-      <c r="BA16" s="114"/>
-      <c r="BB16" s="114"/>
-      <c r="BC16" s="115"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="88"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="85"/>
+      <c r="K16" s="85"/>
+      <c r="L16" s="85"/>
+      <c r="M16" s="85"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="85"/>
+      <c r="P16" s="85"/>
+      <c r="Q16" s="85"/>
+      <c r="R16" s="85"/>
+      <c r="S16" s="85"/>
+      <c r="T16" s="85"/>
+      <c r="U16" s="85"/>
+      <c r="V16" s="85"/>
+      <c r="W16" s="85"/>
+      <c r="X16" s="85"/>
+      <c r="Y16" s="85"/>
+      <c r="Z16" s="85"/>
+      <c r="AA16" s="85"/>
+      <c r="AB16" s="85"/>
+      <c r="AC16" s="85"/>
+      <c r="AD16" s="85"/>
+      <c r="AE16" s="85"/>
+      <c r="AF16" s="85"/>
+      <c r="AG16" s="85"/>
+      <c r="AH16" s="85"/>
+      <c r="AI16" s="85"/>
+      <c r="AJ16" s="85"/>
+      <c r="AK16" s="90"/>
+      <c r="AL16" s="90"/>
+      <c r="AM16" s="90"/>
+      <c r="AN16" s="91"/>
+      <c r="AO16" s="84"/>
+      <c r="AP16" s="85"/>
+      <c r="AQ16" s="85"/>
+      <c r="AR16" s="85"/>
+      <c r="AS16" s="85"/>
+      <c r="AT16" s="85"/>
+      <c r="AU16" s="85"/>
+      <c r="AV16" s="85"/>
+      <c r="AW16" s="85"/>
+      <c r="AX16" s="85"/>
+      <c r="AY16" s="85"/>
+      <c r="AZ16" s="85"/>
+      <c r="BA16" s="85"/>
+      <c r="BB16" s="85"/>
+      <c r="BC16" s="86"/>
     </row>
     <row r="17" spans="1:55" ht="15" customHeight="1">
       <c r="A17" s="37"/>
-      <c r="B17" s="110"/>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="111"/>
-      <c r="G17" s="111"/>
-      <c r="H17" s="112"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="114"/>
-      <c r="K17" s="114"/>
-      <c r="L17" s="114"/>
-      <c r="M17" s="114"/>
-      <c r="N17" s="114"/>
-      <c r="O17" s="114"/>
-      <c r="P17" s="114"/>
-      <c r="Q17" s="114"/>
-      <c r="R17" s="114"/>
-      <c r="S17" s="114"/>
-      <c r="T17" s="114"/>
-      <c r="U17" s="114"/>
-      <c r="V17" s="114"/>
-      <c r="W17" s="114"/>
-      <c r="X17" s="114"/>
-      <c r="Y17" s="114"/>
-      <c r="Z17" s="114"/>
-      <c r="AA17" s="114"/>
-      <c r="AB17" s="114"/>
-      <c r="AC17" s="114"/>
-      <c r="AD17" s="114"/>
-      <c r="AE17" s="114"/>
-      <c r="AF17" s="114"/>
-      <c r="AG17" s="114"/>
-      <c r="AH17" s="114"/>
-      <c r="AI17" s="114"/>
-      <c r="AJ17" s="114"/>
-      <c r="AK17" s="116"/>
-      <c r="AL17" s="116"/>
-      <c r="AM17" s="116"/>
-      <c r="AN17" s="117"/>
-      <c r="AO17" s="113"/>
-      <c r="AP17" s="114"/>
-      <c r="AQ17" s="114"/>
-      <c r="AR17" s="114"/>
-      <c r="AS17" s="114"/>
-      <c r="AT17" s="114"/>
-      <c r="AU17" s="114"/>
-      <c r="AV17" s="114"/>
-      <c r="AW17" s="114"/>
-      <c r="AX17" s="114"/>
-      <c r="AY17" s="114"/>
-      <c r="AZ17" s="114"/>
-      <c r="BA17" s="114"/>
-      <c r="BB17" s="114"/>
-      <c r="BC17" s="115"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="88"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="87"/>
+      <c r="J17" s="85"/>
+      <c r="K17" s="85"/>
+      <c r="L17" s="85"/>
+      <c r="M17" s="85"/>
+      <c r="N17" s="85"/>
+      <c r="O17" s="85"/>
+      <c r="P17" s="85"/>
+      <c r="Q17" s="85"/>
+      <c r="R17" s="85"/>
+      <c r="S17" s="85"/>
+      <c r="T17" s="85"/>
+      <c r="U17" s="85"/>
+      <c r="V17" s="85"/>
+      <c r="W17" s="85"/>
+      <c r="X17" s="85"/>
+      <c r="Y17" s="85"/>
+      <c r="Z17" s="85"/>
+      <c r="AA17" s="85"/>
+      <c r="AB17" s="85"/>
+      <c r="AC17" s="85"/>
+      <c r="AD17" s="85"/>
+      <c r="AE17" s="85"/>
+      <c r="AF17" s="85"/>
+      <c r="AG17" s="85"/>
+      <c r="AH17" s="85"/>
+      <c r="AI17" s="85"/>
+      <c r="AJ17" s="85"/>
+      <c r="AK17" s="90"/>
+      <c r="AL17" s="90"/>
+      <c r="AM17" s="90"/>
+      <c r="AN17" s="91"/>
+      <c r="AO17" s="84"/>
+      <c r="AP17" s="85"/>
+      <c r="AQ17" s="85"/>
+      <c r="AR17" s="85"/>
+      <c r="AS17" s="85"/>
+      <c r="AT17" s="85"/>
+      <c r="AU17" s="85"/>
+      <c r="AV17" s="85"/>
+      <c r="AW17" s="85"/>
+      <c r="AX17" s="85"/>
+      <c r="AY17" s="85"/>
+      <c r="AZ17" s="85"/>
+      <c r="BA17" s="85"/>
+      <c r="BB17" s="85"/>
+      <c r="BC17" s="86"/>
     </row>
     <row r="18" spans="1:55" ht="15" customHeight="1">
       <c r="A18" s="36"/>
-      <c r="B18" s="110"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="111"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="112"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="114"/>
-      <c r="K18" s="114"/>
-      <c r="L18" s="114"/>
-      <c r="M18" s="114"/>
-      <c r="N18" s="114"/>
-      <c r="O18" s="114"/>
-      <c r="P18" s="114"/>
-      <c r="Q18" s="114"/>
-      <c r="R18" s="114"/>
-      <c r="S18" s="114"/>
-      <c r="T18" s="114"/>
-      <c r="U18" s="114"/>
-      <c r="V18" s="114"/>
-      <c r="W18" s="114"/>
-      <c r="X18" s="114"/>
-      <c r="Y18" s="114"/>
-      <c r="Z18" s="114"/>
-      <c r="AA18" s="114"/>
-      <c r="AB18" s="114"/>
-      <c r="AC18" s="114"/>
-      <c r="AD18" s="114"/>
-      <c r="AE18" s="114"/>
-      <c r="AF18" s="114"/>
-      <c r="AG18" s="114"/>
-      <c r="AH18" s="114"/>
-      <c r="AI18" s="114"/>
-      <c r="AJ18" s="114"/>
-      <c r="AK18" s="116"/>
-      <c r="AL18" s="116"/>
-      <c r="AM18" s="116"/>
-      <c r="AN18" s="117"/>
-      <c r="AO18" s="113"/>
-      <c r="AP18" s="114"/>
-      <c r="AQ18" s="114"/>
-      <c r="AR18" s="114"/>
-      <c r="AS18" s="114"/>
-      <c r="AT18" s="114"/>
-      <c r="AU18" s="114"/>
-      <c r="AV18" s="114"/>
-      <c r="AW18" s="114"/>
-      <c r="AX18" s="114"/>
-      <c r="AY18" s="114"/>
-      <c r="AZ18" s="114"/>
-      <c r="BA18" s="114"/>
-      <c r="BB18" s="114"/>
-      <c r="BC18" s="115"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="88"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="85"/>
+      <c r="M18" s="85"/>
+      <c r="N18" s="85"/>
+      <c r="O18" s="85"/>
+      <c r="P18" s="85"/>
+      <c r="Q18" s="85"/>
+      <c r="R18" s="85"/>
+      <c r="S18" s="85"/>
+      <c r="T18" s="85"/>
+      <c r="U18" s="85"/>
+      <c r="V18" s="85"/>
+      <c r="W18" s="85"/>
+      <c r="X18" s="85"/>
+      <c r="Y18" s="85"/>
+      <c r="Z18" s="85"/>
+      <c r="AA18" s="85"/>
+      <c r="AB18" s="85"/>
+      <c r="AC18" s="85"/>
+      <c r="AD18" s="85"/>
+      <c r="AE18" s="85"/>
+      <c r="AF18" s="85"/>
+      <c r="AG18" s="85"/>
+      <c r="AH18" s="85"/>
+      <c r="AI18" s="85"/>
+      <c r="AJ18" s="85"/>
+      <c r="AK18" s="90"/>
+      <c r="AL18" s="90"/>
+      <c r="AM18" s="90"/>
+      <c r="AN18" s="91"/>
+      <c r="AO18" s="84"/>
+      <c r="AP18" s="85"/>
+      <c r="AQ18" s="85"/>
+      <c r="AR18" s="85"/>
+      <c r="AS18" s="85"/>
+      <c r="AT18" s="85"/>
+      <c r="AU18" s="85"/>
+      <c r="AV18" s="85"/>
+      <c r="AW18" s="85"/>
+      <c r="AX18" s="85"/>
+      <c r="AY18" s="85"/>
+      <c r="AZ18" s="85"/>
+      <c r="BA18" s="85"/>
+      <c r="BB18" s="85"/>
+      <c r="BC18" s="86"/>
     </row>
     <row r="19" spans="1:55" ht="15" customHeight="1">
       <c r="A19" s="36"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="114"/>
-      <c r="K19" s="114"/>
-      <c r="L19" s="114"/>
-      <c r="M19" s="114"/>
-      <c r="N19" s="114"/>
-      <c r="O19" s="114"/>
-      <c r="P19" s="114"/>
-      <c r="Q19" s="114"/>
-      <c r="R19" s="114"/>
-      <c r="S19" s="114"/>
-      <c r="T19" s="114"/>
-      <c r="U19" s="114"/>
-      <c r="V19" s="114"/>
-      <c r="W19" s="114"/>
-      <c r="X19" s="114"/>
-      <c r="Y19" s="114"/>
-      <c r="Z19" s="114"/>
-      <c r="AA19" s="114"/>
-      <c r="AB19" s="114"/>
-      <c r="AC19" s="114"/>
-      <c r="AD19" s="114"/>
-      <c r="AE19" s="114"/>
-      <c r="AF19" s="114"/>
-      <c r="AG19" s="114"/>
-      <c r="AH19" s="114"/>
-      <c r="AI19" s="114"/>
-      <c r="AJ19" s="114"/>
-      <c r="AK19" s="116"/>
-      <c r="AL19" s="116"/>
-      <c r="AM19" s="116"/>
-      <c r="AN19" s="117"/>
-      <c r="AO19" s="113"/>
-      <c r="AP19" s="114"/>
-      <c r="AQ19" s="114"/>
-      <c r="AR19" s="114"/>
-      <c r="AS19" s="114"/>
-      <c r="AT19" s="114"/>
-      <c r="AU19" s="114"/>
-      <c r="AV19" s="114"/>
-      <c r="AW19" s="114"/>
-      <c r="AX19" s="114"/>
-      <c r="AY19" s="114"/>
-      <c r="AZ19" s="114"/>
-      <c r="BA19" s="114"/>
-      <c r="BB19" s="114"/>
-      <c r="BC19" s="115"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="85"/>
+      <c r="K19" s="85"/>
+      <c r="L19" s="85"/>
+      <c r="M19" s="85"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="85"/>
+      <c r="P19" s="85"/>
+      <c r="Q19" s="85"/>
+      <c r="R19" s="85"/>
+      <c r="S19" s="85"/>
+      <c r="T19" s="85"/>
+      <c r="U19" s="85"/>
+      <c r="V19" s="85"/>
+      <c r="W19" s="85"/>
+      <c r="X19" s="85"/>
+      <c r="Y19" s="85"/>
+      <c r="Z19" s="85"/>
+      <c r="AA19" s="85"/>
+      <c r="AB19" s="85"/>
+      <c r="AC19" s="85"/>
+      <c r="AD19" s="85"/>
+      <c r="AE19" s="85"/>
+      <c r="AF19" s="85"/>
+      <c r="AG19" s="85"/>
+      <c r="AH19" s="85"/>
+      <c r="AI19" s="85"/>
+      <c r="AJ19" s="85"/>
+      <c r="AK19" s="90"/>
+      <c r="AL19" s="90"/>
+      <c r="AM19" s="90"/>
+      <c r="AN19" s="91"/>
+      <c r="AO19" s="84"/>
+      <c r="AP19" s="85"/>
+      <c r="AQ19" s="85"/>
+      <c r="AR19" s="85"/>
+      <c r="AS19" s="85"/>
+      <c r="AT19" s="85"/>
+      <c r="AU19" s="85"/>
+      <c r="AV19" s="85"/>
+      <c r="AW19" s="85"/>
+      <c r="AX19" s="85"/>
+      <c r="AY19" s="85"/>
+      <c r="AZ19" s="85"/>
+      <c r="BA19" s="85"/>
+      <c r="BB19" s="85"/>
+      <c r="BC19" s="86"/>
     </row>
     <row r="20" spans="1:55" ht="15" customHeight="1">
       <c r="A20" s="36"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="114"/>
-      <c r="L20" s="114"/>
-      <c r="M20" s="114"/>
-      <c r="N20" s="114"/>
-      <c r="O20" s="114"/>
-      <c r="P20" s="114"/>
-      <c r="Q20" s="114"/>
-      <c r="R20" s="114"/>
-      <c r="S20" s="114"/>
-      <c r="T20" s="114"/>
-      <c r="U20" s="114"/>
-      <c r="V20" s="114"/>
-      <c r="W20" s="114"/>
-      <c r="X20" s="114"/>
-      <c r="Y20" s="114"/>
-      <c r="Z20" s="114"/>
-      <c r="AA20" s="114"/>
-      <c r="AB20" s="114"/>
-      <c r="AC20" s="114"/>
-      <c r="AD20" s="114"/>
-      <c r="AE20" s="114"/>
-      <c r="AF20" s="114"/>
-      <c r="AG20" s="114"/>
-      <c r="AH20" s="114"/>
-      <c r="AI20" s="114"/>
-      <c r="AJ20" s="114"/>
-      <c r="AK20" s="116"/>
-      <c r="AL20" s="116"/>
-      <c r="AM20" s="116"/>
-      <c r="AN20" s="117"/>
-      <c r="AO20" s="113"/>
-      <c r="AP20" s="114"/>
-      <c r="AQ20" s="114"/>
-      <c r="AR20" s="114"/>
-      <c r="AS20" s="114"/>
-      <c r="AT20" s="114"/>
-      <c r="AU20" s="114"/>
-      <c r="AV20" s="114"/>
-      <c r="AW20" s="114"/>
-      <c r="AX20" s="114"/>
-      <c r="AY20" s="114"/>
-      <c r="AZ20" s="114"/>
-      <c r="BA20" s="114"/>
-      <c r="BB20" s="114"/>
-      <c r="BC20" s="115"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="89"/>
+      <c r="I20" s="87"/>
+      <c r="J20" s="85"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="85"/>
+      <c r="M20" s="85"/>
+      <c r="N20" s="85"/>
+      <c r="O20" s="85"/>
+      <c r="P20" s="85"/>
+      <c r="Q20" s="85"/>
+      <c r="R20" s="85"/>
+      <c r="S20" s="85"/>
+      <c r="T20" s="85"/>
+      <c r="U20" s="85"/>
+      <c r="V20" s="85"/>
+      <c r="W20" s="85"/>
+      <c r="X20" s="85"/>
+      <c r="Y20" s="85"/>
+      <c r="Z20" s="85"/>
+      <c r="AA20" s="85"/>
+      <c r="AB20" s="85"/>
+      <c r="AC20" s="85"/>
+      <c r="AD20" s="85"/>
+      <c r="AE20" s="85"/>
+      <c r="AF20" s="85"/>
+      <c r="AG20" s="85"/>
+      <c r="AH20" s="85"/>
+      <c r="AI20" s="85"/>
+      <c r="AJ20" s="85"/>
+      <c r="AK20" s="90"/>
+      <c r="AL20" s="90"/>
+      <c r="AM20" s="90"/>
+      <c r="AN20" s="91"/>
+      <c r="AO20" s="84"/>
+      <c r="AP20" s="85"/>
+      <c r="AQ20" s="85"/>
+      <c r="AR20" s="85"/>
+      <c r="AS20" s="85"/>
+      <c r="AT20" s="85"/>
+      <c r="AU20" s="85"/>
+      <c r="AV20" s="85"/>
+      <c r="AW20" s="85"/>
+      <c r="AX20" s="85"/>
+      <c r="AY20" s="85"/>
+      <c r="AZ20" s="85"/>
+      <c r="BA20" s="85"/>
+      <c r="BB20" s="85"/>
+      <c r="BC20" s="86"/>
     </row>
     <row r="21" spans="1:55" ht="15" customHeight="1">
       <c r="A21" s="36"/>
-      <c r="B21" s="110"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="112"/>
-      <c r="I21" s="110"/>
-      <c r="J21" s="114"/>
-      <c r="K21" s="114"/>
-      <c r="L21" s="114"/>
-      <c r="M21" s="114"/>
-      <c r="N21" s="114"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="114"/>
-      <c r="Q21" s="114"/>
-      <c r="R21" s="114"/>
-      <c r="S21" s="114"/>
-      <c r="T21" s="114"/>
-      <c r="U21" s="114"/>
-      <c r="V21" s="114"/>
-      <c r="W21" s="114"/>
-      <c r="X21" s="114"/>
-      <c r="Y21" s="114"/>
-      <c r="Z21" s="114"/>
-      <c r="AA21" s="114"/>
-      <c r="AB21" s="114"/>
-      <c r="AC21" s="114"/>
-      <c r="AD21" s="114"/>
-      <c r="AE21" s="114"/>
-      <c r="AF21" s="114"/>
-      <c r="AG21" s="114"/>
-      <c r="AH21" s="114"/>
-      <c r="AI21" s="114"/>
-      <c r="AJ21" s="114"/>
-      <c r="AK21" s="116"/>
-      <c r="AL21" s="116"/>
-      <c r="AM21" s="116"/>
-      <c r="AN21" s="117"/>
-      <c r="AO21" s="113"/>
-      <c r="AP21" s="114"/>
-      <c r="AQ21" s="114"/>
-      <c r="AR21" s="114"/>
-      <c r="AS21" s="114"/>
-      <c r="AT21" s="114"/>
-      <c r="AU21" s="114"/>
-      <c r="AV21" s="114"/>
-      <c r="AW21" s="114"/>
-      <c r="AX21" s="114"/>
-      <c r="AY21" s="114"/>
-      <c r="AZ21" s="114"/>
-      <c r="BA21" s="114"/>
-      <c r="BB21" s="114"/>
-      <c r="BC21" s="115"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="87"/>
+      <c r="J21" s="85"/>
+      <c r="K21" s="85"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="85"/>
+      <c r="N21" s="85"/>
+      <c r="O21" s="85"/>
+      <c r="P21" s="85"/>
+      <c r="Q21" s="85"/>
+      <c r="R21" s="85"/>
+      <c r="S21" s="85"/>
+      <c r="T21" s="85"/>
+      <c r="U21" s="85"/>
+      <c r="V21" s="85"/>
+      <c r="W21" s="85"/>
+      <c r="X21" s="85"/>
+      <c r="Y21" s="85"/>
+      <c r="Z21" s="85"/>
+      <c r="AA21" s="85"/>
+      <c r="AB21" s="85"/>
+      <c r="AC21" s="85"/>
+      <c r="AD21" s="85"/>
+      <c r="AE21" s="85"/>
+      <c r="AF21" s="85"/>
+      <c r="AG21" s="85"/>
+      <c r="AH21" s="85"/>
+      <c r="AI21" s="85"/>
+      <c r="AJ21" s="85"/>
+      <c r="AK21" s="90"/>
+      <c r="AL21" s="90"/>
+      <c r="AM21" s="90"/>
+      <c r="AN21" s="91"/>
+      <c r="AO21" s="84"/>
+      <c r="AP21" s="85"/>
+      <c r="AQ21" s="85"/>
+      <c r="AR21" s="85"/>
+      <c r="AS21" s="85"/>
+      <c r="AT21" s="85"/>
+      <c r="AU21" s="85"/>
+      <c r="AV21" s="85"/>
+      <c r="AW21" s="85"/>
+      <c r="AX21" s="85"/>
+      <c r="AY21" s="85"/>
+      <c r="AZ21" s="85"/>
+      <c r="BA21" s="85"/>
+      <c r="BB21" s="85"/>
+      <c r="BC21" s="86"/>
     </row>
     <row r="22" spans="1:55" ht="15" customHeight="1">
       <c r="A22" s="36"/>
-      <c r="B22" s="110"/>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="111"/>
-      <c r="H22" s="112"/>
-      <c r="I22" s="110"/>
-      <c r="J22" s="114"/>
-      <c r="K22" s="114"/>
-      <c r="L22" s="114"/>
-      <c r="M22" s="114"/>
-      <c r="N22" s="114"/>
-      <c r="O22" s="114"/>
-      <c r="P22" s="114"/>
-      <c r="Q22" s="114"/>
-      <c r="R22" s="114"/>
-      <c r="S22" s="114"/>
-      <c r="T22" s="114"/>
-      <c r="U22" s="114"/>
-      <c r="V22" s="114"/>
-      <c r="W22" s="114"/>
-      <c r="X22" s="114"/>
-      <c r="Y22" s="114"/>
-      <c r="Z22" s="114"/>
-      <c r="AA22" s="114"/>
-      <c r="AB22" s="114"/>
-      <c r="AC22" s="114"/>
-      <c r="AD22" s="114"/>
-      <c r="AE22" s="114"/>
-      <c r="AF22" s="114"/>
-      <c r="AG22" s="114"/>
-      <c r="AH22" s="114"/>
-      <c r="AI22" s="114"/>
-      <c r="AJ22" s="114"/>
-      <c r="AK22" s="116"/>
-      <c r="AL22" s="116"/>
-      <c r="AM22" s="116"/>
-      <c r="AN22" s="117"/>
-      <c r="AO22" s="113"/>
-      <c r="AP22" s="114"/>
-      <c r="AQ22" s="114"/>
-      <c r="AR22" s="114"/>
-      <c r="AS22" s="114"/>
-      <c r="AT22" s="114"/>
-      <c r="AU22" s="114"/>
-      <c r="AV22" s="114"/>
-      <c r="AW22" s="114"/>
-      <c r="AX22" s="114"/>
-      <c r="AY22" s="114"/>
-      <c r="AZ22" s="114"/>
-      <c r="BA22" s="114"/>
-      <c r="BB22" s="114"/>
-      <c r="BC22" s="115"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="87"/>
+      <c r="J22" s="85"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="85"/>
+      <c r="M22" s="85"/>
+      <c r="N22" s="85"/>
+      <c r="O22" s="85"/>
+      <c r="P22" s="85"/>
+      <c r="Q22" s="85"/>
+      <c r="R22" s="85"/>
+      <c r="S22" s="85"/>
+      <c r="T22" s="85"/>
+      <c r="U22" s="85"/>
+      <c r="V22" s="85"/>
+      <c r="W22" s="85"/>
+      <c r="X22" s="85"/>
+      <c r="Y22" s="85"/>
+      <c r="Z22" s="85"/>
+      <c r="AA22" s="85"/>
+      <c r="AB22" s="85"/>
+      <c r="AC22" s="85"/>
+      <c r="AD22" s="85"/>
+      <c r="AE22" s="85"/>
+      <c r="AF22" s="85"/>
+      <c r="AG22" s="85"/>
+      <c r="AH22" s="85"/>
+      <c r="AI22" s="85"/>
+      <c r="AJ22" s="85"/>
+      <c r="AK22" s="90"/>
+      <c r="AL22" s="90"/>
+      <c r="AM22" s="90"/>
+      <c r="AN22" s="91"/>
+      <c r="AO22" s="84"/>
+      <c r="AP22" s="85"/>
+      <c r="AQ22" s="85"/>
+      <c r="AR22" s="85"/>
+      <c r="AS22" s="85"/>
+      <c r="AT22" s="85"/>
+      <c r="AU22" s="85"/>
+      <c r="AV22" s="85"/>
+      <c r="AW22" s="85"/>
+      <c r="AX22" s="85"/>
+      <c r="AY22" s="85"/>
+      <c r="AZ22" s="85"/>
+      <c r="BA22" s="85"/>
+      <c r="BB22" s="85"/>
+      <c r="BC22" s="86"/>
     </row>
     <row r="23" spans="1:55" ht="15" customHeight="1">
       <c r="A23" s="36"/>
-      <c r="B23" s="110"/>
-      <c r="C23" s="111"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="112"/>
-      <c r="I23" s="110"/>
-      <c r="J23" s="114"/>
-      <c r="K23" s="114"/>
-      <c r="L23" s="114"/>
-      <c r="M23" s="114"/>
-      <c r="N23" s="114"/>
-      <c r="O23" s="114"/>
-      <c r="P23" s="114"/>
-      <c r="Q23" s="114"/>
-      <c r="R23" s="114"/>
-      <c r="S23" s="114"/>
-      <c r="T23" s="114"/>
-      <c r="U23" s="114"/>
-      <c r="V23" s="114"/>
-      <c r="W23" s="114"/>
-      <c r="X23" s="114"/>
-      <c r="Y23" s="114"/>
-      <c r="Z23" s="114"/>
-      <c r="AA23" s="114"/>
-      <c r="AB23" s="114"/>
-      <c r="AC23" s="114"/>
-      <c r="AD23" s="114"/>
-      <c r="AE23" s="114"/>
-      <c r="AF23" s="114"/>
-      <c r="AG23" s="114"/>
-      <c r="AH23" s="114"/>
-      <c r="AI23" s="114"/>
-      <c r="AJ23" s="114"/>
-      <c r="AK23" s="116"/>
-      <c r="AL23" s="116"/>
-      <c r="AM23" s="116"/>
-      <c r="AN23" s="117"/>
-      <c r="AO23" s="113"/>
-      <c r="AP23" s="114"/>
-      <c r="AQ23" s="114"/>
-      <c r="AR23" s="114"/>
-      <c r="AS23" s="114"/>
-      <c r="AT23" s="114"/>
-      <c r="AU23" s="114"/>
-      <c r="AV23" s="114"/>
-      <c r="AW23" s="114"/>
-      <c r="AX23" s="114"/>
-      <c r="AY23" s="114"/>
-      <c r="AZ23" s="114"/>
-      <c r="BA23" s="114"/>
-      <c r="BB23" s="114"/>
-      <c r="BC23" s="115"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="87"/>
+      <c r="J23" s="85"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
+      <c r="M23" s="85"/>
+      <c r="N23" s="85"/>
+      <c r="O23" s="85"/>
+      <c r="P23" s="85"/>
+      <c r="Q23" s="85"/>
+      <c r="R23" s="85"/>
+      <c r="S23" s="85"/>
+      <c r="T23" s="85"/>
+      <c r="U23" s="85"/>
+      <c r="V23" s="85"/>
+      <c r="W23" s="85"/>
+      <c r="X23" s="85"/>
+      <c r="Y23" s="85"/>
+      <c r="Z23" s="85"/>
+      <c r="AA23" s="85"/>
+      <c r="AB23" s="85"/>
+      <c r="AC23" s="85"/>
+      <c r="AD23" s="85"/>
+      <c r="AE23" s="85"/>
+      <c r="AF23" s="85"/>
+      <c r="AG23" s="85"/>
+      <c r="AH23" s="85"/>
+      <c r="AI23" s="85"/>
+      <c r="AJ23" s="85"/>
+      <c r="AK23" s="90"/>
+      <c r="AL23" s="90"/>
+      <c r="AM23" s="90"/>
+      <c r="AN23" s="91"/>
+      <c r="AO23" s="84"/>
+      <c r="AP23" s="85"/>
+      <c r="AQ23" s="85"/>
+      <c r="AR23" s="85"/>
+      <c r="AS23" s="85"/>
+      <c r="AT23" s="85"/>
+      <c r="AU23" s="85"/>
+      <c r="AV23" s="85"/>
+      <c r="AW23" s="85"/>
+      <c r="AX23" s="85"/>
+      <c r="AY23" s="85"/>
+      <c r="AZ23" s="85"/>
+      <c r="BA23" s="85"/>
+      <c r="BB23" s="85"/>
+      <c r="BC23" s="86"/>
     </row>
     <row r="24" spans="1:55" ht="15" customHeight="1">
       <c r="A24" s="36"/>
-      <c r="B24" s="110"/>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="112"/>
-      <c r="I24" s="110"/>
-      <c r="J24" s="114"/>
-      <c r="K24" s="114"/>
-      <c r="L24" s="114"/>
-      <c r="M24" s="114"/>
-      <c r="N24" s="114"/>
-      <c r="O24" s="114"/>
-      <c r="P24" s="114"/>
-      <c r="Q24" s="114"/>
-      <c r="R24" s="114"/>
-      <c r="S24" s="114"/>
-      <c r="T24" s="114"/>
-      <c r="U24" s="114"/>
-      <c r="V24" s="114"/>
-      <c r="W24" s="114"/>
-      <c r="X24" s="114"/>
-      <c r="Y24" s="114"/>
-      <c r="Z24" s="114"/>
-      <c r="AA24" s="114"/>
-      <c r="AB24" s="114"/>
-      <c r="AC24" s="114"/>
-      <c r="AD24" s="114"/>
-      <c r="AE24" s="114"/>
-      <c r="AF24" s="114"/>
-      <c r="AG24" s="114"/>
-      <c r="AH24" s="114"/>
-      <c r="AI24" s="114"/>
-      <c r="AJ24" s="114"/>
-      <c r="AK24" s="116"/>
-      <c r="AL24" s="116"/>
-      <c r="AM24" s="116"/>
-      <c r="AN24" s="117"/>
-      <c r="AO24" s="113"/>
-      <c r="AP24" s="114"/>
-      <c r="AQ24" s="114"/>
-      <c r="AR24" s="114"/>
-      <c r="AS24" s="114"/>
-      <c r="AT24" s="114"/>
-      <c r="AU24" s="114"/>
-      <c r="AV24" s="114"/>
-      <c r="AW24" s="114"/>
-      <c r="AX24" s="114"/>
-      <c r="AY24" s="114"/>
-      <c r="AZ24" s="114"/>
-      <c r="BA24" s="114"/>
-      <c r="BB24" s="114"/>
-      <c r="BC24" s="115"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="87"/>
+      <c r="J24" s="85"/>
+      <c r="K24" s="85"/>
+      <c r="L24" s="85"/>
+      <c r="M24" s="85"/>
+      <c r="N24" s="85"/>
+      <c r="O24" s="85"/>
+      <c r="P24" s="85"/>
+      <c r="Q24" s="85"/>
+      <c r="R24" s="85"/>
+      <c r="S24" s="85"/>
+      <c r="T24" s="85"/>
+      <c r="U24" s="85"/>
+      <c r="V24" s="85"/>
+      <c r="W24" s="85"/>
+      <c r="X24" s="85"/>
+      <c r="Y24" s="85"/>
+      <c r="Z24" s="85"/>
+      <c r="AA24" s="85"/>
+      <c r="AB24" s="85"/>
+      <c r="AC24" s="85"/>
+      <c r="AD24" s="85"/>
+      <c r="AE24" s="85"/>
+      <c r="AF24" s="85"/>
+      <c r="AG24" s="85"/>
+      <c r="AH24" s="85"/>
+      <c r="AI24" s="85"/>
+      <c r="AJ24" s="85"/>
+      <c r="AK24" s="90"/>
+      <c r="AL24" s="90"/>
+      <c r="AM24" s="90"/>
+      <c r="AN24" s="91"/>
+      <c r="AO24" s="84"/>
+      <c r="AP24" s="85"/>
+      <c r="AQ24" s="85"/>
+      <c r="AR24" s="85"/>
+      <c r="AS24" s="85"/>
+      <c r="AT24" s="85"/>
+      <c r="AU24" s="85"/>
+      <c r="AV24" s="85"/>
+      <c r="AW24" s="85"/>
+      <c r="AX24" s="85"/>
+      <c r="AY24" s="85"/>
+      <c r="AZ24" s="85"/>
+      <c r="BA24" s="85"/>
+      <c r="BB24" s="85"/>
+      <c r="BC24" s="86"/>
     </row>
     <row r="25" spans="1:55" ht="15" customHeight="1">
       <c r="A25" s="36"/>
-      <c r="B25" s="110"/>
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="112"/>
-      <c r="I25" s="110"/>
-      <c r="J25" s="114"/>
-      <c r="K25" s="114"/>
-      <c r="L25" s="114"/>
-      <c r="M25" s="114"/>
-      <c r="N25" s="114"/>
-      <c r="O25" s="114"/>
-      <c r="P25" s="114"/>
-      <c r="Q25" s="114"/>
-      <c r="R25" s="114"/>
-      <c r="S25" s="114"/>
-      <c r="T25" s="114"/>
-      <c r="U25" s="114"/>
-      <c r="V25" s="114"/>
-      <c r="W25" s="114"/>
-      <c r="X25" s="114"/>
-      <c r="Y25" s="114"/>
-      <c r="Z25" s="114"/>
-      <c r="AA25" s="114"/>
-      <c r="AB25" s="114"/>
-      <c r="AC25" s="114"/>
-      <c r="AD25" s="114"/>
-      <c r="AE25" s="114"/>
-      <c r="AF25" s="114"/>
-      <c r="AG25" s="114"/>
-      <c r="AH25" s="114"/>
-      <c r="AI25" s="114"/>
-      <c r="AJ25" s="114"/>
-      <c r="AK25" s="116"/>
-      <c r="AL25" s="116"/>
-      <c r="AM25" s="116"/>
-      <c r="AN25" s="117"/>
-      <c r="AO25" s="113"/>
-      <c r="AP25" s="114"/>
-      <c r="AQ25" s="114"/>
-      <c r="AR25" s="114"/>
-      <c r="AS25" s="114"/>
-      <c r="AT25" s="114"/>
-      <c r="AU25" s="114"/>
-      <c r="AV25" s="114"/>
-      <c r="AW25" s="114"/>
-      <c r="AX25" s="114"/>
-      <c r="AY25" s="114"/>
-      <c r="AZ25" s="114"/>
-      <c r="BA25" s="114"/>
-      <c r="BB25" s="114"/>
-      <c r="BC25" s="115"/>
+      <c r="B25" s="87"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="87"/>
+      <c r="J25" s="85"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="85"/>
+      <c r="M25" s="85"/>
+      <c r="N25" s="85"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="85"/>
+      <c r="Q25" s="85"/>
+      <c r="R25" s="85"/>
+      <c r="S25" s="85"/>
+      <c r="T25" s="85"/>
+      <c r="U25" s="85"/>
+      <c r="V25" s="85"/>
+      <c r="W25" s="85"/>
+      <c r="X25" s="85"/>
+      <c r="Y25" s="85"/>
+      <c r="Z25" s="85"/>
+      <c r="AA25" s="85"/>
+      <c r="AB25" s="85"/>
+      <c r="AC25" s="85"/>
+      <c r="AD25" s="85"/>
+      <c r="AE25" s="85"/>
+      <c r="AF25" s="85"/>
+      <c r="AG25" s="85"/>
+      <c r="AH25" s="85"/>
+      <c r="AI25" s="85"/>
+      <c r="AJ25" s="85"/>
+      <c r="AK25" s="90"/>
+      <c r="AL25" s="90"/>
+      <c r="AM25" s="90"/>
+      <c r="AN25" s="91"/>
+      <c r="AO25" s="84"/>
+      <c r="AP25" s="85"/>
+      <c r="AQ25" s="85"/>
+      <c r="AR25" s="85"/>
+      <c r="AS25" s="85"/>
+      <c r="AT25" s="85"/>
+      <c r="AU25" s="85"/>
+      <c r="AV25" s="85"/>
+      <c r="AW25" s="85"/>
+      <c r="AX25" s="85"/>
+      <c r="AY25" s="85"/>
+      <c r="AZ25" s="85"/>
+      <c r="BA25" s="85"/>
+      <c r="BB25" s="85"/>
+      <c r="BC25" s="86"/>
     </row>
     <row r="26" spans="1:55" ht="15" customHeight="1">
       <c r="A26" s="36"/>
-      <c r="B26" s="110"/>
-      <c r="C26" s="111"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="112"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="114"/>
-      <c r="K26" s="114"/>
-      <c r="L26" s="114"/>
-      <c r="M26" s="114"/>
-      <c r="N26" s="114"/>
-      <c r="O26" s="114"/>
-      <c r="P26" s="114"/>
-      <c r="Q26" s="114"/>
-      <c r="R26" s="114"/>
-      <c r="S26" s="114"/>
-      <c r="T26" s="114"/>
-      <c r="U26" s="114"/>
-      <c r="V26" s="114"/>
-      <c r="W26" s="114"/>
-      <c r="X26" s="114"/>
-      <c r="Y26" s="114"/>
-      <c r="Z26" s="114"/>
-      <c r="AA26" s="114"/>
-      <c r="AB26" s="114"/>
-      <c r="AC26" s="114"/>
-      <c r="AD26" s="114"/>
-      <c r="AE26" s="114"/>
-      <c r="AF26" s="114"/>
-      <c r="AG26" s="114"/>
-      <c r="AH26" s="114"/>
-      <c r="AI26" s="114"/>
-      <c r="AJ26" s="114"/>
-      <c r="AK26" s="116"/>
-      <c r="AL26" s="116"/>
-      <c r="AM26" s="116"/>
-      <c r="AN26" s="117"/>
-      <c r="AO26" s="113"/>
-      <c r="AP26" s="114"/>
-      <c r="AQ26" s="114"/>
-      <c r="AR26" s="114"/>
-      <c r="AS26" s="114"/>
-      <c r="AT26" s="114"/>
-      <c r="AU26" s="114"/>
-      <c r="AV26" s="114"/>
-      <c r="AW26" s="114"/>
-      <c r="AX26" s="114"/>
-      <c r="AY26" s="114"/>
-      <c r="AZ26" s="114"/>
-      <c r="BA26" s="114"/>
-      <c r="BB26" s="114"/>
-      <c r="BC26" s="115"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="88"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="87"/>
+      <c r="J26" s="85"/>
+      <c r="K26" s="85"/>
+      <c r="L26" s="85"/>
+      <c r="M26" s="85"/>
+      <c r="N26" s="85"/>
+      <c r="O26" s="85"/>
+      <c r="P26" s="85"/>
+      <c r="Q26" s="85"/>
+      <c r="R26" s="85"/>
+      <c r="S26" s="85"/>
+      <c r="T26" s="85"/>
+      <c r="U26" s="85"/>
+      <c r="V26" s="85"/>
+      <c r="W26" s="85"/>
+      <c r="X26" s="85"/>
+      <c r="Y26" s="85"/>
+      <c r="Z26" s="85"/>
+      <c r="AA26" s="85"/>
+      <c r="AB26" s="85"/>
+      <c r="AC26" s="85"/>
+      <c r="AD26" s="85"/>
+      <c r="AE26" s="85"/>
+      <c r="AF26" s="85"/>
+      <c r="AG26" s="85"/>
+      <c r="AH26" s="85"/>
+      <c r="AI26" s="85"/>
+      <c r="AJ26" s="85"/>
+      <c r="AK26" s="90"/>
+      <c r="AL26" s="90"/>
+      <c r="AM26" s="90"/>
+      <c r="AN26" s="91"/>
+      <c r="AO26" s="84"/>
+      <c r="AP26" s="85"/>
+      <c r="AQ26" s="85"/>
+      <c r="AR26" s="85"/>
+      <c r="AS26" s="85"/>
+      <c r="AT26" s="85"/>
+      <c r="AU26" s="85"/>
+      <c r="AV26" s="85"/>
+      <c r="AW26" s="85"/>
+      <c r="AX26" s="85"/>
+      <c r="AY26" s="85"/>
+      <c r="AZ26" s="85"/>
+      <c r="BA26" s="85"/>
+      <c r="BB26" s="85"/>
+      <c r="BC26" s="86"/>
     </row>
     <row r="27" spans="1:55" ht="15" customHeight="1">
       <c r="A27" s="36"/>
-      <c r="B27" s="110"/>
-      <c r="C27" s="111"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="112"/>
-      <c r="I27" s="110"/>
-      <c r="J27" s="114"/>
-      <c r="K27" s="114"/>
-      <c r="L27" s="114"/>
-      <c r="M27" s="114"/>
-      <c r="N27" s="114"/>
-      <c r="O27" s="114"/>
-      <c r="P27" s="114"/>
-      <c r="Q27" s="114"/>
-      <c r="R27" s="114"/>
-      <c r="S27" s="114"/>
-      <c r="T27" s="114"/>
-      <c r="U27" s="114"/>
-      <c r="V27" s="114"/>
-      <c r="W27" s="114"/>
-      <c r="X27" s="114"/>
-      <c r="Y27" s="114"/>
-      <c r="Z27" s="114"/>
-      <c r="AA27" s="114"/>
-      <c r="AB27" s="114"/>
-      <c r="AC27" s="114"/>
-      <c r="AD27" s="114"/>
-      <c r="AE27" s="114"/>
-      <c r="AF27" s="114"/>
-      <c r="AG27" s="114"/>
-      <c r="AH27" s="114"/>
-      <c r="AI27" s="114"/>
-      <c r="AJ27" s="114"/>
-      <c r="AK27" s="116"/>
-      <c r="AL27" s="116"/>
-      <c r="AM27" s="116"/>
-      <c r="AN27" s="117"/>
-      <c r="AO27" s="113"/>
-      <c r="AP27" s="114"/>
-      <c r="AQ27" s="114"/>
-      <c r="AR27" s="114"/>
-      <c r="AS27" s="114"/>
-      <c r="AT27" s="114"/>
-      <c r="AU27" s="114"/>
-      <c r="AV27" s="114"/>
-      <c r="AW27" s="114"/>
-      <c r="AX27" s="114"/>
-      <c r="AY27" s="114"/>
-      <c r="AZ27" s="114"/>
-      <c r="BA27" s="114"/>
-      <c r="BB27" s="114"/>
-      <c r="BC27" s="115"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="87"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="85"/>
+      <c r="M27" s="85"/>
+      <c r="N27" s="85"/>
+      <c r="O27" s="85"/>
+      <c r="P27" s="85"/>
+      <c r="Q27" s="85"/>
+      <c r="R27" s="85"/>
+      <c r="S27" s="85"/>
+      <c r="T27" s="85"/>
+      <c r="U27" s="85"/>
+      <c r="V27" s="85"/>
+      <c r="W27" s="85"/>
+      <c r="X27" s="85"/>
+      <c r="Y27" s="85"/>
+      <c r="Z27" s="85"/>
+      <c r="AA27" s="85"/>
+      <c r="AB27" s="85"/>
+      <c r="AC27" s="85"/>
+      <c r="AD27" s="85"/>
+      <c r="AE27" s="85"/>
+      <c r="AF27" s="85"/>
+      <c r="AG27" s="85"/>
+      <c r="AH27" s="85"/>
+      <c r="AI27" s="85"/>
+      <c r="AJ27" s="85"/>
+      <c r="AK27" s="90"/>
+      <c r="AL27" s="90"/>
+      <c r="AM27" s="90"/>
+      <c r="AN27" s="91"/>
+      <c r="AO27" s="84"/>
+      <c r="AP27" s="85"/>
+      <c r="AQ27" s="85"/>
+      <c r="AR27" s="85"/>
+      <c r="AS27" s="85"/>
+      <c r="AT27" s="85"/>
+      <c r="AU27" s="85"/>
+      <c r="AV27" s="85"/>
+      <c r="AW27" s="85"/>
+      <c r="AX27" s="85"/>
+      <c r="AY27" s="85"/>
+      <c r="AZ27" s="85"/>
+      <c r="BA27" s="85"/>
+      <c r="BB27" s="85"/>
+      <c r="BC27" s="86"/>
     </row>
     <row r="28" spans="1:55" ht="15" customHeight="1">
       <c r="A28" s="36"/>
-      <c r="B28" s="110"/>
-      <c r="C28" s="111"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="111"/>
-      <c r="G28" s="111"/>
-      <c r="H28" s="112"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="114"/>
-      <c r="K28" s="114"/>
-      <c r="L28" s="114"/>
-      <c r="M28" s="114"/>
-      <c r="N28" s="114"/>
-      <c r="O28" s="114"/>
-      <c r="P28" s="114"/>
-      <c r="Q28" s="114"/>
-      <c r="R28" s="114"/>
-      <c r="S28" s="114"/>
-      <c r="T28" s="114"/>
-      <c r="U28" s="114"/>
-      <c r="V28" s="114"/>
-      <c r="W28" s="114"/>
-      <c r="X28" s="114"/>
-      <c r="Y28" s="114"/>
-      <c r="Z28" s="114"/>
-      <c r="AA28" s="114"/>
-      <c r="AB28" s="114"/>
-      <c r="AC28" s="114"/>
-      <c r="AD28" s="114"/>
-      <c r="AE28" s="114"/>
-      <c r="AF28" s="114"/>
-      <c r="AG28" s="114"/>
-      <c r="AH28" s="114"/>
-      <c r="AI28" s="114"/>
-      <c r="AJ28" s="114"/>
-      <c r="AK28" s="116"/>
-      <c r="AL28" s="116"/>
-      <c r="AM28" s="116"/>
-      <c r="AN28" s="117"/>
-      <c r="AO28" s="113"/>
-      <c r="AP28" s="114"/>
-      <c r="AQ28" s="114"/>
-      <c r="AR28" s="114"/>
-      <c r="AS28" s="114"/>
-      <c r="AT28" s="114"/>
-      <c r="AU28" s="114"/>
-      <c r="AV28" s="114"/>
-      <c r="AW28" s="114"/>
-      <c r="AX28" s="114"/>
-      <c r="AY28" s="114"/>
-      <c r="AZ28" s="114"/>
-      <c r="BA28" s="114"/>
-      <c r="BB28" s="114"/>
-      <c r="BC28" s="115"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="88"/>
+      <c r="D28" s="88"/>
+      <c r="E28" s="88"/>
+      <c r="F28" s="88"/>
+      <c r="G28" s="88"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="87"/>
+      <c r="J28" s="85"/>
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
+      <c r="M28" s="85"/>
+      <c r="N28" s="85"/>
+      <c r="O28" s="85"/>
+      <c r="P28" s="85"/>
+      <c r="Q28" s="85"/>
+      <c r="R28" s="85"/>
+      <c r="S28" s="85"/>
+      <c r="T28" s="85"/>
+      <c r="U28" s="85"/>
+      <c r="V28" s="85"/>
+      <c r="W28" s="85"/>
+      <c r="X28" s="85"/>
+      <c r="Y28" s="85"/>
+      <c r="Z28" s="85"/>
+      <c r="AA28" s="85"/>
+      <c r="AB28" s="85"/>
+      <c r="AC28" s="85"/>
+      <c r="AD28" s="85"/>
+      <c r="AE28" s="85"/>
+      <c r="AF28" s="85"/>
+      <c r="AG28" s="85"/>
+      <c r="AH28" s="85"/>
+      <c r="AI28" s="85"/>
+      <c r="AJ28" s="85"/>
+      <c r="AK28" s="90"/>
+      <c r="AL28" s="90"/>
+      <c r="AM28" s="90"/>
+      <c r="AN28" s="91"/>
+      <c r="AO28" s="84"/>
+      <c r="AP28" s="85"/>
+      <c r="AQ28" s="85"/>
+      <c r="AR28" s="85"/>
+      <c r="AS28" s="85"/>
+      <c r="AT28" s="85"/>
+      <c r="AU28" s="85"/>
+      <c r="AV28" s="85"/>
+      <c r="AW28" s="85"/>
+      <c r="AX28" s="85"/>
+      <c r="AY28" s="85"/>
+      <c r="AZ28" s="85"/>
+      <c r="BA28" s="85"/>
+      <c r="BB28" s="85"/>
+      <c r="BC28" s="86"/>
     </row>
     <row r="29" spans="1:55" ht="15" customHeight="1">
       <c r="A29" s="36"/>
-      <c r="B29" s="110"/>
-      <c r="C29" s="111"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="111"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="112"/>
-      <c r="I29" s="110"/>
-      <c r="J29" s="114"/>
-      <c r="K29" s="114"/>
-      <c r="L29" s="114"/>
-      <c r="M29" s="114"/>
-      <c r="N29" s="114"/>
-      <c r="O29" s="114"/>
-      <c r="P29" s="114"/>
-      <c r="Q29" s="114"/>
-      <c r="R29" s="114"/>
-      <c r="S29" s="114"/>
-      <c r="T29" s="114"/>
-      <c r="U29" s="114"/>
-      <c r="V29" s="114"/>
-      <c r="W29" s="114"/>
-      <c r="X29" s="114"/>
-      <c r="Y29" s="114"/>
-      <c r="Z29" s="114"/>
-      <c r="AA29" s="114"/>
-      <c r="AB29" s="114"/>
-      <c r="AC29" s="114"/>
-      <c r="AD29" s="114"/>
-      <c r="AE29" s="114"/>
-      <c r="AF29" s="114"/>
-      <c r="AG29" s="114"/>
-      <c r="AH29" s="114"/>
-      <c r="AI29" s="114"/>
-      <c r="AJ29" s="114"/>
-      <c r="AK29" s="116"/>
-      <c r="AL29" s="116"/>
-      <c r="AM29" s="116"/>
-      <c r="AN29" s="117"/>
-      <c r="AO29" s="113"/>
-      <c r="AP29" s="114"/>
-      <c r="AQ29" s="114"/>
-      <c r="AR29" s="114"/>
-      <c r="AS29" s="114"/>
-      <c r="AT29" s="114"/>
-      <c r="AU29" s="114"/>
-      <c r="AV29" s="114"/>
-      <c r="AW29" s="114"/>
-      <c r="AX29" s="114"/>
-      <c r="AY29" s="114"/>
-      <c r="AZ29" s="114"/>
-      <c r="BA29" s="114"/>
-      <c r="BB29" s="114"/>
-      <c r="BC29" s="115"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="87"/>
+      <c r="J29" s="85"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="85"/>
+      <c r="M29" s="85"/>
+      <c r="N29" s="85"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="85"/>
+      <c r="Q29" s="85"/>
+      <c r="R29" s="85"/>
+      <c r="S29" s="85"/>
+      <c r="T29" s="85"/>
+      <c r="U29" s="85"/>
+      <c r="V29" s="85"/>
+      <c r="W29" s="85"/>
+      <c r="X29" s="85"/>
+      <c r="Y29" s="85"/>
+      <c r="Z29" s="85"/>
+      <c r="AA29" s="85"/>
+      <c r="AB29" s="85"/>
+      <c r="AC29" s="85"/>
+      <c r="AD29" s="85"/>
+      <c r="AE29" s="85"/>
+      <c r="AF29" s="85"/>
+      <c r="AG29" s="85"/>
+      <c r="AH29" s="85"/>
+      <c r="AI29" s="85"/>
+      <c r="AJ29" s="85"/>
+      <c r="AK29" s="90"/>
+      <c r="AL29" s="90"/>
+      <c r="AM29" s="90"/>
+      <c r="AN29" s="91"/>
+      <c r="AO29" s="84"/>
+      <c r="AP29" s="85"/>
+      <c r="AQ29" s="85"/>
+      <c r="AR29" s="85"/>
+      <c r="AS29" s="85"/>
+      <c r="AT29" s="85"/>
+      <c r="AU29" s="85"/>
+      <c r="AV29" s="85"/>
+      <c r="AW29" s="85"/>
+      <c r="AX29" s="85"/>
+      <c r="AY29" s="85"/>
+      <c r="AZ29" s="85"/>
+      <c r="BA29" s="85"/>
+      <c r="BB29" s="85"/>
+      <c r="BC29" s="86"/>
     </row>
     <row r="30" spans="1:55" ht="15" customHeight="1">
       <c r="A30" s="36"/>
-      <c r="B30" s="110"/>
-      <c r="C30" s="111"/>
-      <c r="D30" s="111"/>
-      <c r="E30" s="111"/>
-      <c r="F30" s="111"/>
-      <c r="G30" s="111"/>
-      <c r="H30" s="112"/>
-      <c r="I30" s="110"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="114"/>
-      <c r="L30" s="114"/>
-      <c r="M30" s="114"/>
-      <c r="N30" s="114"/>
-      <c r="O30" s="114"/>
-      <c r="P30" s="114"/>
-      <c r="Q30" s="114"/>
-      <c r="R30" s="114"/>
-      <c r="S30" s="114"/>
-      <c r="T30" s="114"/>
-      <c r="U30" s="114"/>
-      <c r="V30" s="114"/>
-      <c r="W30" s="114"/>
-      <c r="X30" s="114"/>
-      <c r="Y30" s="114"/>
-      <c r="Z30" s="114"/>
-      <c r="AA30" s="114"/>
-      <c r="AB30" s="114"/>
-      <c r="AC30" s="114"/>
-      <c r="AD30" s="114"/>
-      <c r="AE30" s="114"/>
-      <c r="AF30" s="114"/>
-      <c r="AG30" s="114"/>
-      <c r="AH30" s="114"/>
-      <c r="AI30" s="114"/>
-      <c r="AJ30" s="114"/>
-      <c r="AK30" s="116"/>
-      <c r="AL30" s="116"/>
-      <c r="AM30" s="116"/>
-      <c r="AN30" s="117"/>
-      <c r="AO30" s="113"/>
-      <c r="AP30" s="114"/>
-      <c r="AQ30" s="114"/>
-      <c r="AR30" s="114"/>
-      <c r="AS30" s="114"/>
-      <c r="AT30" s="114"/>
-      <c r="AU30" s="114"/>
-      <c r="AV30" s="114"/>
-      <c r="AW30" s="114"/>
-      <c r="AX30" s="114"/>
-      <c r="AY30" s="114"/>
-      <c r="AZ30" s="114"/>
-      <c r="BA30" s="114"/>
-      <c r="BB30" s="114"/>
-      <c r="BC30" s="115"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="88"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="87"/>
+      <c r="J30" s="85"/>
+      <c r="K30" s="85"/>
+      <c r="L30" s="85"/>
+      <c r="M30" s="85"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="85"/>
+      <c r="P30" s="85"/>
+      <c r="Q30" s="85"/>
+      <c r="R30" s="85"/>
+      <c r="S30" s="85"/>
+      <c r="T30" s="85"/>
+      <c r="U30" s="85"/>
+      <c r="V30" s="85"/>
+      <c r="W30" s="85"/>
+      <c r="X30" s="85"/>
+      <c r="Y30" s="85"/>
+      <c r="Z30" s="85"/>
+      <c r="AA30" s="85"/>
+      <c r="AB30" s="85"/>
+      <c r="AC30" s="85"/>
+      <c r="AD30" s="85"/>
+      <c r="AE30" s="85"/>
+      <c r="AF30" s="85"/>
+      <c r="AG30" s="85"/>
+      <c r="AH30" s="85"/>
+      <c r="AI30" s="85"/>
+      <c r="AJ30" s="85"/>
+      <c r="AK30" s="90"/>
+      <c r="AL30" s="90"/>
+      <c r="AM30" s="90"/>
+      <c r="AN30" s="91"/>
+      <c r="AO30" s="84"/>
+      <c r="AP30" s="85"/>
+      <c r="AQ30" s="85"/>
+      <c r="AR30" s="85"/>
+      <c r="AS30" s="85"/>
+      <c r="AT30" s="85"/>
+      <c r="AU30" s="85"/>
+      <c r="AV30" s="85"/>
+      <c r="AW30" s="85"/>
+      <c r="AX30" s="85"/>
+      <c r="AY30" s="85"/>
+      <c r="AZ30" s="85"/>
+      <c r="BA30" s="85"/>
+      <c r="BB30" s="85"/>
+      <c r="BC30" s="86"/>
     </row>
     <row r="31" spans="1:55" ht="15" customHeight="1">
       <c r="A31" s="36"/>
-      <c r="B31" s="110"/>
-      <c r="C31" s="111"/>
-      <c r="D31" s="111"/>
-      <c r="E31" s="111"/>
-      <c r="F31" s="111"/>
-      <c r="G31" s="111"/>
-      <c r="H31" s="112"/>
-      <c r="I31" s="110"/>
-      <c r="J31" s="114"/>
-      <c r="K31" s="114"/>
-      <c r="L31" s="114"/>
-      <c r="M31" s="114"/>
-      <c r="N31" s="114"/>
-      <c r="O31" s="114"/>
-      <c r="P31" s="114"/>
-      <c r="Q31" s="114"/>
-      <c r="R31" s="114"/>
-      <c r="S31" s="114"/>
-      <c r="T31" s="114"/>
-      <c r="U31" s="114"/>
-      <c r="V31" s="114"/>
-      <c r="W31" s="114"/>
-      <c r="X31" s="114"/>
-      <c r="Y31" s="114"/>
-      <c r="Z31" s="114"/>
-      <c r="AA31" s="114"/>
-      <c r="AB31" s="114"/>
-      <c r="AC31" s="114"/>
-      <c r="AD31" s="114"/>
-      <c r="AE31" s="114"/>
-      <c r="AF31" s="114"/>
-      <c r="AG31" s="114"/>
-      <c r="AH31" s="114"/>
-      <c r="AI31" s="114"/>
-      <c r="AJ31" s="114"/>
-      <c r="AK31" s="116"/>
-      <c r="AL31" s="116"/>
-      <c r="AM31" s="116"/>
-      <c r="AN31" s="117"/>
-      <c r="AO31" s="113"/>
-      <c r="AP31" s="114"/>
-      <c r="AQ31" s="114"/>
-      <c r="AR31" s="114"/>
-      <c r="AS31" s="114"/>
-      <c r="AT31" s="114"/>
-      <c r="AU31" s="114"/>
-      <c r="AV31" s="114"/>
-      <c r="AW31" s="114"/>
-      <c r="AX31" s="114"/>
-      <c r="AY31" s="114"/>
-      <c r="AZ31" s="114"/>
-      <c r="BA31" s="114"/>
-      <c r="BB31" s="114"/>
-      <c r="BC31" s="115"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="87"/>
+      <c r="J31" s="85"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="85"/>
+      <c r="P31" s="85"/>
+      <c r="Q31" s="85"/>
+      <c r="R31" s="85"/>
+      <c r="S31" s="85"/>
+      <c r="T31" s="85"/>
+      <c r="U31" s="85"/>
+      <c r="V31" s="85"/>
+      <c r="W31" s="85"/>
+      <c r="X31" s="85"/>
+      <c r="Y31" s="85"/>
+      <c r="Z31" s="85"/>
+      <c r="AA31" s="85"/>
+      <c r="AB31" s="85"/>
+      <c r="AC31" s="85"/>
+      <c r="AD31" s="85"/>
+      <c r="AE31" s="85"/>
+      <c r="AF31" s="85"/>
+      <c r="AG31" s="85"/>
+      <c r="AH31" s="85"/>
+      <c r="AI31" s="85"/>
+      <c r="AJ31" s="85"/>
+      <c r="AK31" s="90"/>
+      <c r="AL31" s="90"/>
+      <c r="AM31" s="90"/>
+      <c r="AN31" s="91"/>
+      <c r="AO31" s="84"/>
+      <c r="AP31" s="85"/>
+      <c r="AQ31" s="85"/>
+      <c r="AR31" s="85"/>
+      <c r="AS31" s="85"/>
+      <c r="AT31" s="85"/>
+      <c r="AU31" s="85"/>
+      <c r="AV31" s="85"/>
+      <c r="AW31" s="85"/>
+      <c r="AX31" s="85"/>
+      <c r="AY31" s="85"/>
+      <c r="AZ31" s="85"/>
+      <c r="BA31" s="85"/>
+      <c r="BB31" s="85"/>
+      <c r="BC31" s="86"/>
     </row>
     <row r="32" spans="1:55" ht="15" customHeight="1">
       <c r="A32" s="36"/>
-      <c r="B32" s="110"/>
-      <c r="C32" s="111"/>
-      <c r="D32" s="111"/>
-      <c r="E32" s="111"/>
-      <c r="F32" s="111"/>
-      <c r="G32" s="111"/>
-      <c r="H32" s="112"/>
-      <c r="I32" s="110"/>
-      <c r="J32" s="114"/>
-      <c r="K32" s="114"/>
-      <c r="L32" s="114"/>
-      <c r="M32" s="114"/>
-      <c r="N32" s="114"/>
-      <c r="O32" s="114"/>
-      <c r="P32" s="114"/>
-      <c r="Q32" s="114"/>
-      <c r="R32" s="114"/>
-      <c r="S32" s="114"/>
-      <c r="T32" s="114"/>
-      <c r="U32" s="114"/>
-      <c r="V32" s="114"/>
-      <c r="W32" s="114"/>
-      <c r="X32" s="114"/>
-      <c r="Y32" s="114"/>
-      <c r="Z32" s="114"/>
-      <c r="AA32" s="114"/>
-      <c r="AB32" s="114"/>
-      <c r="AC32" s="114"/>
-      <c r="AD32" s="114"/>
-      <c r="AE32" s="114"/>
-      <c r="AF32" s="114"/>
-      <c r="AG32" s="114"/>
-      <c r="AH32" s="114"/>
-      <c r="AI32" s="114"/>
-      <c r="AJ32" s="114"/>
-      <c r="AK32" s="116"/>
-      <c r="AL32" s="116"/>
-      <c r="AM32" s="116"/>
-      <c r="AN32" s="117"/>
-      <c r="AO32" s="113"/>
-      <c r="AP32" s="114"/>
-      <c r="AQ32" s="114"/>
-      <c r="AR32" s="114"/>
-      <c r="AS32" s="114"/>
-      <c r="AT32" s="114"/>
-      <c r="AU32" s="114"/>
-      <c r="AV32" s="114"/>
-      <c r="AW32" s="114"/>
-      <c r="AX32" s="114"/>
-      <c r="AY32" s="114"/>
-      <c r="AZ32" s="114"/>
-      <c r="BA32" s="114"/>
-      <c r="BB32" s="114"/>
-      <c r="BC32" s="115"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="88"/>
+      <c r="D32" s="88"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="88"/>
+      <c r="G32" s="88"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="87"/>
+      <c r="J32" s="85"/>
+      <c r="K32" s="85"/>
+      <c r="L32" s="85"/>
+      <c r="M32" s="85"/>
+      <c r="N32" s="85"/>
+      <c r="O32" s="85"/>
+      <c r="P32" s="85"/>
+      <c r="Q32" s="85"/>
+      <c r="R32" s="85"/>
+      <c r="S32" s="85"/>
+      <c r="T32" s="85"/>
+      <c r="U32" s="85"/>
+      <c r="V32" s="85"/>
+      <c r="W32" s="85"/>
+      <c r="X32" s="85"/>
+      <c r="Y32" s="85"/>
+      <c r="Z32" s="85"/>
+      <c r="AA32" s="85"/>
+      <c r="AB32" s="85"/>
+      <c r="AC32" s="85"/>
+      <c r="AD32" s="85"/>
+      <c r="AE32" s="85"/>
+      <c r="AF32" s="85"/>
+      <c r="AG32" s="85"/>
+      <c r="AH32" s="85"/>
+      <c r="AI32" s="85"/>
+      <c r="AJ32" s="85"/>
+      <c r="AK32" s="90"/>
+      <c r="AL32" s="90"/>
+      <c r="AM32" s="90"/>
+      <c r="AN32" s="91"/>
+      <c r="AO32" s="84"/>
+      <c r="AP32" s="85"/>
+      <c r="AQ32" s="85"/>
+      <c r="AR32" s="85"/>
+      <c r="AS32" s="85"/>
+      <c r="AT32" s="85"/>
+      <c r="AU32" s="85"/>
+      <c r="AV32" s="85"/>
+      <c r="AW32" s="85"/>
+      <c r="AX32" s="85"/>
+      <c r="AY32" s="85"/>
+      <c r="AZ32" s="85"/>
+      <c r="BA32" s="85"/>
+      <c r="BB32" s="85"/>
+      <c r="BC32" s="86"/>
     </row>
     <row r="33" spans="1:55" ht="15" customHeight="1">
       <c r="A33" s="36"/>
-      <c r="B33" s="110"/>
-      <c r="C33" s="111"/>
-      <c r="D33" s="111"/>
-      <c r="E33" s="111"/>
-      <c r="F33" s="111"/>
-      <c r="G33" s="111"/>
-      <c r="H33" s="112"/>
-      <c r="I33" s="110"/>
-      <c r="J33" s="114"/>
-      <c r="K33" s="114"/>
-      <c r="L33" s="114"/>
-      <c r="M33" s="114"/>
-      <c r="N33" s="114"/>
-      <c r="O33" s="114"/>
-      <c r="P33" s="114"/>
-      <c r="Q33" s="114"/>
-      <c r="R33" s="114"/>
-      <c r="S33" s="114"/>
-      <c r="T33" s="114"/>
-      <c r="U33" s="114"/>
-      <c r="V33" s="114"/>
-      <c r="W33" s="114"/>
-      <c r="X33" s="114"/>
-      <c r="Y33" s="114"/>
-      <c r="Z33" s="114"/>
-      <c r="AA33" s="114"/>
-      <c r="AB33" s="114"/>
-      <c r="AC33" s="114"/>
-      <c r="AD33" s="114"/>
-      <c r="AE33" s="114"/>
-      <c r="AF33" s="114"/>
-      <c r="AG33" s="114"/>
-      <c r="AH33" s="114"/>
-      <c r="AI33" s="114"/>
-      <c r="AJ33" s="114"/>
-      <c r="AK33" s="116"/>
-      <c r="AL33" s="116"/>
-      <c r="AM33" s="116"/>
-      <c r="AN33" s="117"/>
-      <c r="AO33" s="113"/>
-      <c r="AP33" s="114"/>
-      <c r="AQ33" s="114"/>
-      <c r="AR33" s="114"/>
-      <c r="AS33" s="114"/>
-      <c r="AT33" s="114"/>
-      <c r="AU33" s="114"/>
-      <c r="AV33" s="114"/>
-      <c r="AW33" s="114"/>
-      <c r="AX33" s="114"/>
-      <c r="AY33" s="114"/>
-      <c r="AZ33" s="114"/>
-      <c r="BA33" s="114"/>
-      <c r="BB33" s="114"/>
-      <c r="BC33" s="115"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="88"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="88"/>
+      <c r="G33" s="88"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="87"/>
+      <c r="J33" s="85"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="85"/>
+      <c r="M33" s="85"/>
+      <c r="N33" s="85"/>
+      <c r="O33" s="85"/>
+      <c r="P33" s="85"/>
+      <c r="Q33" s="85"/>
+      <c r="R33" s="85"/>
+      <c r="S33" s="85"/>
+      <c r="T33" s="85"/>
+      <c r="U33" s="85"/>
+      <c r="V33" s="85"/>
+      <c r="W33" s="85"/>
+      <c r="X33" s="85"/>
+      <c r="Y33" s="85"/>
+      <c r="Z33" s="85"/>
+      <c r="AA33" s="85"/>
+      <c r="AB33" s="85"/>
+      <c r="AC33" s="85"/>
+      <c r="AD33" s="85"/>
+      <c r="AE33" s="85"/>
+      <c r="AF33" s="85"/>
+      <c r="AG33" s="85"/>
+      <c r="AH33" s="85"/>
+      <c r="AI33" s="85"/>
+      <c r="AJ33" s="85"/>
+      <c r="AK33" s="90"/>
+      <c r="AL33" s="90"/>
+      <c r="AM33" s="90"/>
+      <c r="AN33" s="91"/>
+      <c r="AO33" s="84"/>
+      <c r="AP33" s="85"/>
+      <c r="AQ33" s="85"/>
+      <c r="AR33" s="85"/>
+      <c r="AS33" s="85"/>
+      <c r="AT33" s="85"/>
+      <c r="AU33" s="85"/>
+      <c r="AV33" s="85"/>
+      <c r="AW33" s="85"/>
+      <c r="AX33" s="85"/>
+      <c r="AY33" s="85"/>
+      <c r="AZ33" s="85"/>
+      <c r="BA33" s="85"/>
+      <c r="BB33" s="85"/>
+      <c r="BC33" s="86"/>
     </row>
     <row r="34" spans="1:55" ht="15" customHeight="1">
       <c r="A34" s="36"/>
-      <c r="B34" s="110"/>
-      <c r="C34" s="111"/>
-      <c r="D34" s="111"/>
-      <c r="E34" s="111"/>
-      <c r="F34" s="111"/>
-      <c r="G34" s="111"/>
-      <c r="H34" s="112"/>
-      <c r="I34" s="110"/>
-      <c r="J34" s="114"/>
-      <c r="K34" s="114"/>
-      <c r="L34" s="114"/>
-      <c r="M34" s="114"/>
-      <c r="N34" s="114"/>
-      <c r="O34" s="114"/>
-      <c r="P34" s="114"/>
-      <c r="Q34" s="114"/>
-      <c r="R34" s="114"/>
-      <c r="S34" s="114"/>
-      <c r="T34" s="114"/>
-      <c r="U34" s="114"/>
-      <c r="V34" s="114"/>
-      <c r="W34" s="114"/>
-      <c r="X34" s="114"/>
-      <c r="Y34" s="114"/>
-      <c r="Z34" s="114"/>
-      <c r="AA34" s="114"/>
-      <c r="AB34" s="114"/>
-      <c r="AC34" s="114"/>
-      <c r="AD34" s="114"/>
-      <c r="AE34" s="114"/>
-      <c r="AF34" s="114"/>
-      <c r="AG34" s="114"/>
-      <c r="AH34" s="114"/>
-      <c r="AI34" s="114"/>
-      <c r="AJ34" s="114"/>
-      <c r="AK34" s="116"/>
-      <c r="AL34" s="116"/>
-      <c r="AM34" s="116"/>
-      <c r="AN34" s="117"/>
-      <c r="AO34" s="113"/>
-      <c r="AP34" s="114"/>
-      <c r="AQ34" s="114"/>
-      <c r="AR34" s="114"/>
-      <c r="AS34" s="114"/>
-      <c r="AT34" s="114"/>
-      <c r="AU34" s="114"/>
-      <c r="AV34" s="114"/>
-      <c r="AW34" s="114"/>
-      <c r="AX34" s="114"/>
-      <c r="AY34" s="114"/>
-      <c r="AZ34" s="114"/>
-      <c r="BA34" s="114"/>
-      <c r="BB34" s="114"/>
-      <c r="BC34" s="115"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="88"/>
+      <c r="D34" s="88"/>
+      <c r="E34" s="88"/>
+      <c r="F34" s="88"/>
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="87"/>
+      <c r="J34" s="85"/>
+      <c r="K34" s="85"/>
+      <c r="L34" s="85"/>
+      <c r="M34" s="85"/>
+      <c r="N34" s="85"/>
+      <c r="O34" s="85"/>
+      <c r="P34" s="85"/>
+      <c r="Q34" s="85"/>
+      <c r="R34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="85"/>
+      <c r="V34" s="85"/>
+      <c r="W34" s="85"/>
+      <c r="X34" s="85"/>
+      <c r="Y34" s="85"/>
+      <c r="Z34" s="85"/>
+      <c r="AA34" s="85"/>
+      <c r="AB34" s="85"/>
+      <c r="AC34" s="85"/>
+      <c r="AD34" s="85"/>
+      <c r="AE34" s="85"/>
+      <c r="AF34" s="85"/>
+      <c r="AG34" s="85"/>
+      <c r="AH34" s="85"/>
+      <c r="AI34" s="85"/>
+      <c r="AJ34" s="85"/>
+      <c r="AK34" s="90"/>
+      <c r="AL34" s="90"/>
+      <c r="AM34" s="90"/>
+      <c r="AN34" s="91"/>
+      <c r="AO34" s="84"/>
+      <c r="AP34" s="85"/>
+      <c r="AQ34" s="85"/>
+      <c r="AR34" s="85"/>
+      <c r="AS34" s="85"/>
+      <c r="AT34" s="85"/>
+      <c r="AU34" s="85"/>
+      <c r="AV34" s="85"/>
+      <c r="AW34" s="85"/>
+      <c r="AX34" s="85"/>
+      <c r="AY34" s="85"/>
+      <c r="AZ34" s="85"/>
+      <c r="BA34" s="85"/>
+      <c r="BB34" s="85"/>
+      <c r="BC34" s="86"/>
     </row>
     <row r="35" spans="1:55" ht="15" customHeight="1" thickBot="1">
       <c r="A35" s="38"/>
-      <c r="B35" s="118"/>
-      <c r="C35" s="121"/>
-      <c r="D35" s="121"/>
-      <c r="E35" s="121"/>
-      <c r="F35" s="121"/>
-      <c r="G35" s="121"/>
-      <c r="H35" s="122"/>
-      <c r="I35" s="118"/>
+      <c r="B35" s="110"/>
+      <c r="C35" s="113"/>
+      <c r="D35" s="113"/>
+      <c r="E35" s="113"/>
+      <c r="F35" s="113"/>
+      <c r="G35" s="113"/>
+      <c r="H35" s="114"/>
+      <c r="I35" s="110"/>
       <c r="J35" s="108"/>
       <c r="K35" s="108"/>
       <c r="L35" s="108"/>
@@ -11745,10 +11767,10 @@
       <c r="AH35" s="108"/>
       <c r="AI35" s="108"/>
       <c r="AJ35" s="108"/>
-      <c r="AK35" s="119"/>
-      <c r="AL35" s="119"/>
-      <c r="AM35" s="119"/>
-      <c r="AN35" s="120"/>
+      <c r="AK35" s="111"/>
+      <c r="AL35" s="111"/>
+      <c r="AM35" s="111"/>
+      <c r="AN35" s="112"/>
       <c r="AO35" s="107"/>
       <c r="AP35" s="108"/>
       <c r="AQ35" s="108"/>
@@ -11767,6 +11789,90 @@
     </row>
   </sheetData>
   <mergeCells count="100">
+    <mergeCell ref="AY1:BC1"/>
+    <mergeCell ref="AY2:BC2"/>
+    <mergeCell ref="I1:AX2"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="AO4:BC4"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I4:AN4"/>
+    <mergeCell ref="AO35:BC35"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="AO34:BC34"/>
+    <mergeCell ref="I34:AN34"/>
+    <mergeCell ref="I35:AN35"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="AO6:BC6"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="AO29:BC29"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="AO14:BC14"/>
+    <mergeCell ref="AO9:BC9"/>
+    <mergeCell ref="AO8:BC8"/>
+    <mergeCell ref="I10:AN10"/>
+    <mergeCell ref="AO15:BC15"/>
+    <mergeCell ref="AO18:BC18"/>
+    <mergeCell ref="AO11:BC11"/>
+    <mergeCell ref="AO27:BC27"/>
+    <mergeCell ref="AO19:BC19"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:AN14"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="I32:AN32"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="I27:AN27"/>
+    <mergeCell ref="I19:AN19"/>
+    <mergeCell ref="AO31:BC31"/>
+    <mergeCell ref="I33:AN33"/>
+    <mergeCell ref="I17:AN17"/>
+    <mergeCell ref="I18:AN18"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="I20:AN20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="I29:AN29"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="I22:AN22"/>
+    <mergeCell ref="AO22:BC22"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="AO5:BC5"/>
+    <mergeCell ref="AO33:BC33"/>
+    <mergeCell ref="I21:AN21"/>
+    <mergeCell ref="AO7:BC7"/>
+    <mergeCell ref="AO32:BC32"/>
+    <mergeCell ref="AO20:BC20"/>
+    <mergeCell ref="I16:AN16"/>
+    <mergeCell ref="AO28:BC28"/>
+    <mergeCell ref="AO17:BC17"/>
+    <mergeCell ref="I15:AN15"/>
+    <mergeCell ref="I30:AN30"/>
+    <mergeCell ref="I31:AN31"/>
+    <mergeCell ref="I28:AN28"/>
+    <mergeCell ref="AO21:BC21"/>
+    <mergeCell ref="AO30:BC30"/>
+    <mergeCell ref="AO16:BC16"/>
+    <mergeCell ref="I11:AN11"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="I13:AN13"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="I9:AN9"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="I5:AN5"/>
+    <mergeCell ref="I7:AN7"/>
+    <mergeCell ref="I8:AN8"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="I6:AN6"/>
     <mergeCell ref="AO10:BC10"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="I25:AN25"/>
@@ -11783,90 +11889,6 @@
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="AO12:BC12"/>
     <mergeCell ref="I12:AN12"/>
-    <mergeCell ref="I11:AN11"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="I13:AN13"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="I9:AN9"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="I5:AN5"/>
-    <mergeCell ref="I7:AN7"/>
-    <mergeCell ref="I8:AN8"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="I6:AN6"/>
-    <mergeCell ref="AO5:BC5"/>
-    <mergeCell ref="AO33:BC33"/>
-    <mergeCell ref="I21:AN21"/>
-    <mergeCell ref="AO7:BC7"/>
-    <mergeCell ref="AO32:BC32"/>
-    <mergeCell ref="AO20:BC20"/>
-    <mergeCell ref="I16:AN16"/>
-    <mergeCell ref="AO28:BC28"/>
-    <mergeCell ref="AO17:BC17"/>
-    <mergeCell ref="I15:AN15"/>
-    <mergeCell ref="I30:AN30"/>
-    <mergeCell ref="I31:AN31"/>
-    <mergeCell ref="I28:AN28"/>
-    <mergeCell ref="AO21:BC21"/>
-    <mergeCell ref="AO30:BC30"/>
-    <mergeCell ref="AO16:BC16"/>
-    <mergeCell ref="AO31:BC31"/>
-    <mergeCell ref="I33:AN33"/>
-    <mergeCell ref="I17:AN17"/>
-    <mergeCell ref="I18:AN18"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="I20:AN20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="I29:AN29"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="I22:AN22"/>
-    <mergeCell ref="AO22:BC22"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I14:AN14"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="I32:AN32"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="I27:AN27"/>
-    <mergeCell ref="I19:AN19"/>
-    <mergeCell ref="AO6:BC6"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="AO29:BC29"/>
-    <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="AO14:BC14"/>
-    <mergeCell ref="AO9:BC9"/>
-    <mergeCell ref="AO8:BC8"/>
-    <mergeCell ref="I10:AN10"/>
-    <mergeCell ref="AO15:BC15"/>
-    <mergeCell ref="AO18:BC18"/>
-    <mergeCell ref="AO11:BC11"/>
-    <mergeCell ref="AO27:BC27"/>
-    <mergeCell ref="AO19:BC19"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="AO35:BC35"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="AO34:BC34"/>
-    <mergeCell ref="I34:AN34"/>
-    <mergeCell ref="I35:AN35"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="AY1:BC1"/>
-    <mergeCell ref="AY2:BC2"/>
-    <mergeCell ref="I1:AX2"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="AO4:BC4"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="I4:AN4"/>
   </mergeCells>
   <phoneticPr fontId="37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -11924,17 +11946,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9"/>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
       <c r="K3" s="42"/>
     </row>
     <row r="4" spans="1:11">
@@ -12000,17 +12022,17 @@
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="59" t="s">
         <v>609</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="64"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="61"/>
       <c r="K7" s="44"/>
     </row>
     <row r="8" spans="1:11" ht="36">
@@ -12195,7 +12217,7 @@
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K665"/>
+  <dimension ref="A1:K670"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="2" width="4.6640625" style="10" customWidth="1"/>
@@ -12239,17 +12261,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9"/>
-      <c r="B3" s="65" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
       <c r="K3" s="42"/>
     </row>
     <row r="4" spans="1:11">
@@ -12315,17 +12337,17 @@
     </row>
     <row r="7" spans="1:11" ht="24" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="59" t="s">
         <v>610</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="64"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="61"/>
       <c r="K7" s="44"/>
     </row>
     <row r="8" spans="1:11">
@@ -12410,17 +12432,17 @@
     </row>
     <row r="12" spans="1:11" ht="24" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="59" t="s">
         <v>611</v>
       </c>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="64"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
       <c r="K12" s="44"/>
     </row>
     <row r="13" spans="1:11">
@@ -12502,17 +12524,17 @@
     </row>
     <row r="17" spans="1:11" ht="24" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="62" t="s">
+      <c r="B17" s="59" t="s">
         <v>612</v>
       </c>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="64"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="61"/>
       <c r="K17" s="44"/>
     </row>
     <row r="18" spans="1:11">
@@ -12594,17 +12616,17 @@
     </row>
     <row r="22" spans="1:11" ht="24" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="62" t="s">
+      <c r="B22" s="59" t="s">
         <v>613</v>
       </c>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="64"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="61"/>
       <c r="K22" s="44"/>
     </row>
     <row r="23" spans="1:11">
@@ -12686,17 +12708,17 @@
     </row>
     <row r="27" spans="1:11" ht="24" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="62" t="s">
+      <c r="B27" s="59" t="s">
         <v>615</v>
       </c>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="63"/>
-      <c r="J27" s="64"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="61"/>
       <c r="K27" s="44"/>
     </row>
     <row r="28" spans="1:11">
@@ -12778,17 +12800,17 @@
     </row>
     <row r="32" spans="1:11" ht="24" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="62" t="s">
+      <c r="B32" s="59" t="s">
         <v>617</v>
       </c>
-      <c r="C32" s="63"/>
-      <c r="D32" s="63"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="63"/>
-      <c r="I32" s="63"/>
-      <c r="J32" s="64"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="61"/>
       <c r="K32" s="44"/>
     </row>
     <row r="33" spans="1:11">
@@ -12870,17 +12892,17 @@
     </row>
     <row r="37" spans="1:11" ht="24" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="62" t="s">
+      <c r="B37" s="59" t="s">
         <v>619</v>
       </c>
-      <c r="C37" s="63"/>
-      <c r="D37" s="63"/>
-      <c r="E37" s="63"/>
-      <c r="F37" s="63"/>
-      <c r="G37" s="63"/>
-      <c r="H37" s="63"/>
-      <c r="I37" s="63"/>
-      <c r="J37" s="64"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
       <c r="K37" s="44"/>
     </row>
     <row r="38" spans="1:11">
@@ -12962,17 +12984,17 @@
     </row>
     <row r="42" spans="1:11" ht="24" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="62" t="s">
+      <c r="B42" s="59" t="s">
         <v>621</v>
       </c>
-      <c r="C42" s="63"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="63"/>
-      <c r="G42" s="63"/>
-      <c r="H42" s="63"/>
-      <c r="I42" s="63"/>
-      <c r="J42" s="64"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="60"/>
+      <c r="H42" s="60"/>
+      <c r="I42" s="60"/>
+      <c r="J42" s="61"/>
       <c r="K42" s="44"/>
     </row>
     <row r="43" spans="1:11">
@@ -13054,17 +13076,17 @@
     </row>
     <row r="47" spans="1:11" ht="24" customHeight="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="62" t="s">
+      <c r="B47" s="59" t="s">
         <v>623</v>
       </c>
-      <c r="C47" s="63"/>
-      <c r="D47" s="63"/>
-      <c r="E47" s="63"/>
-      <c r="F47" s="63"/>
-      <c r="G47" s="63"/>
-      <c r="H47" s="63"/>
-      <c r="I47" s="63"/>
-      <c r="J47" s="64"/>
+      <c r="C47" s="60"/>
+      <c r="D47" s="60"/>
+      <c r="E47" s="60"/>
+      <c r="F47" s="60"/>
+      <c r="G47" s="60"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="60"/>
+      <c r="J47" s="61"/>
       <c r="K47" s="44"/>
     </row>
     <row r="48" spans="1:11">
@@ -13146,17 +13168,17 @@
     </row>
     <row r="52" spans="1:11" ht="36" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="62" t="s">
+      <c r="B52" s="59" t="s">
         <v>849</v>
       </c>
-      <c r="C52" s="63"/>
-      <c r="D52" s="63"/>
-      <c r="E52" s="63"/>
-      <c r="F52" s="63"/>
-      <c r="G52" s="63"/>
-      <c r="H52" s="63"/>
-      <c r="I52" s="63"/>
-      <c r="J52" s="64"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="60"/>
+      <c r="E52" s="60"/>
+      <c r="F52" s="60"/>
+      <c r="G52" s="60"/>
+      <c r="H52" s="60"/>
+      <c r="I52" s="60"/>
+      <c r="J52" s="61"/>
       <c r="K52" s="44"/>
     </row>
     <row r="53" spans="1:11">
@@ -13238,17 +13260,17 @@
     </row>
     <row r="57" spans="1:11" ht="24" customHeight="1">
       <c r="A57" s="1"/>
-      <c r="B57" s="62" t="s">
+      <c r="B57" s="59" t="s">
         <v>626</v>
       </c>
-      <c r="C57" s="63"/>
-      <c r="D57" s="63"/>
-      <c r="E57" s="63"/>
-      <c r="F57" s="63"/>
-      <c r="G57" s="63"/>
-      <c r="H57" s="63"/>
-      <c r="I57" s="63"/>
-      <c r="J57" s="64"/>
+      <c r="C57" s="60"/>
+      <c r="D57" s="60"/>
+      <c r="E57" s="60"/>
+      <c r="F57" s="60"/>
+      <c r="G57" s="60"/>
+      <c r="H57" s="60"/>
+      <c r="I57" s="60"/>
+      <c r="J57" s="61"/>
       <c r="K57" s="44"/>
     </row>
     <row r="58" spans="1:11">
@@ -13330,17 +13352,17 @@
     </row>
     <row r="62" spans="1:11" ht="24" customHeight="1">
       <c r="A62" s="1"/>
-      <c r="B62" s="62" t="s">
+      <c r="B62" s="59" t="s">
         <v>628</v>
       </c>
-      <c r="C62" s="63"/>
-      <c r="D62" s="63"/>
-      <c r="E62" s="63"/>
-      <c r="F62" s="63"/>
-      <c r="G62" s="63"/>
-      <c r="H62" s="63"/>
-      <c r="I62" s="63"/>
-      <c r="J62" s="64"/>
+      <c r="C62" s="60"/>
+      <c r="D62" s="60"/>
+      <c r="E62" s="60"/>
+      <c r="F62" s="60"/>
+      <c r="G62" s="60"/>
+      <c r="H62" s="60"/>
+      <c r="I62" s="60"/>
+      <c r="J62" s="61"/>
       <c r="K62" s="44"/>
     </row>
     <row r="63" spans="1:11">
@@ -13422,17 +13444,17 @@
     </row>
     <row r="67" spans="1:11" ht="24" customHeight="1">
       <c r="A67" s="1"/>
-      <c r="B67" s="62" t="s">
+      <c r="B67" s="59" t="s">
         <v>630</v>
       </c>
-      <c r="C67" s="63"/>
-      <c r="D67" s="63"/>
-      <c r="E67" s="63"/>
-      <c r="F67" s="63"/>
-      <c r="G67" s="63"/>
-      <c r="H67" s="63"/>
-      <c r="I67" s="63"/>
-      <c r="J67" s="64"/>
+      <c r="C67" s="60"/>
+      <c r="D67" s="60"/>
+      <c r="E67" s="60"/>
+      <c r="F67" s="60"/>
+      <c r="G67" s="60"/>
+      <c r="H67" s="60"/>
+      <c r="I67" s="60"/>
+      <c r="J67" s="61"/>
       <c r="K67" s="44"/>
     </row>
     <row r="68" spans="1:11">
@@ -13514,17 +13536,17 @@
     </row>
     <row r="72" spans="1:11" ht="24" customHeight="1">
       <c r="A72" s="1"/>
-      <c r="B72" s="62" t="s">
+      <c r="B72" s="59" t="s">
         <v>632</v>
       </c>
-      <c r="C72" s="63"/>
-      <c r="D72" s="63"/>
-      <c r="E72" s="63"/>
-      <c r="F72" s="63"/>
-      <c r="G72" s="63"/>
-      <c r="H72" s="63"/>
-      <c r="I72" s="63"/>
-      <c r="J72" s="64"/>
+      <c r="C72" s="60"/>
+      <c r="D72" s="60"/>
+      <c r="E72" s="60"/>
+      <c r="F72" s="60"/>
+      <c r="G72" s="60"/>
+      <c r="H72" s="60"/>
+      <c r="I72" s="60"/>
+      <c r="J72" s="61"/>
       <c r="K72" s="44"/>
     </row>
     <row r="73" spans="1:11">
@@ -13606,17 +13628,17 @@
     </row>
     <row r="77" spans="1:11" ht="24" customHeight="1">
       <c r="A77" s="1"/>
-      <c r="B77" s="62" t="s">
+      <c r="B77" s="59" t="s">
         <v>633</v>
       </c>
-      <c r="C77" s="63"/>
-      <c r="D77" s="63"/>
-      <c r="E77" s="63"/>
-      <c r="F77" s="63"/>
-      <c r="G77" s="63"/>
-      <c r="H77" s="63"/>
-      <c r="I77" s="63"/>
-      <c r="J77" s="64"/>
+      <c r="C77" s="60"/>
+      <c r="D77" s="60"/>
+      <c r="E77" s="60"/>
+      <c r="F77" s="60"/>
+      <c r="G77" s="60"/>
+      <c r="H77" s="60"/>
+      <c r="I77" s="60"/>
+      <c r="J77" s="61"/>
       <c r="K77" s="44"/>
     </row>
     <row r="78" spans="1:11">
@@ -13698,17 +13720,17 @@
     </row>
     <row r="82" spans="1:11" ht="24" customHeight="1">
       <c r="A82" s="1"/>
-      <c r="B82" s="62" t="s">
+      <c r="B82" s="59" t="s">
         <v>635</v>
       </c>
-      <c r="C82" s="63"/>
-      <c r="D82" s="63"/>
-      <c r="E82" s="63"/>
-      <c r="F82" s="63"/>
-      <c r="G82" s="63"/>
-      <c r="H82" s="63"/>
-      <c r="I82" s="63"/>
-      <c r="J82" s="64"/>
+      <c r="C82" s="60"/>
+      <c r="D82" s="60"/>
+      <c r="E82" s="60"/>
+      <c r="F82" s="60"/>
+      <c r="G82" s="60"/>
+      <c r="H82" s="60"/>
+      <c r="I82" s="60"/>
+      <c r="J82" s="61"/>
       <c r="K82" s="44"/>
     </row>
     <row r="83" spans="1:11">
@@ -13790,17 +13812,17 @@
     </row>
     <row r="87" spans="1:11" ht="24" customHeight="1">
       <c r="A87" s="1"/>
-      <c r="B87" s="62" t="s">
+      <c r="B87" s="59" t="s">
         <v>637</v>
       </c>
-      <c r="C87" s="63"/>
-      <c r="D87" s="63"/>
-      <c r="E87" s="63"/>
-      <c r="F87" s="63"/>
-      <c r="G87" s="63"/>
-      <c r="H87" s="63"/>
-      <c r="I87" s="63"/>
-      <c r="J87" s="64"/>
+      <c r="C87" s="60"/>
+      <c r="D87" s="60"/>
+      <c r="E87" s="60"/>
+      <c r="F87" s="60"/>
+      <c r="G87" s="60"/>
+      <c r="H87" s="60"/>
+      <c r="I87" s="60"/>
+      <c r="J87" s="61"/>
       <c r="K87" s="44"/>
     </row>
     <row r="88" spans="1:11">
@@ -13882,17 +13904,17 @@
     </row>
     <row r="92" spans="1:11" ht="24" customHeight="1">
       <c r="A92" s="1"/>
-      <c r="B92" s="62" t="s">
+      <c r="B92" s="59" t="s">
         <v>639</v>
       </c>
-      <c r="C92" s="63"/>
-      <c r="D92" s="63"/>
-      <c r="E92" s="63"/>
-      <c r="F92" s="63"/>
-      <c r="G92" s="63"/>
-      <c r="H92" s="63"/>
-      <c r="I92" s="63"/>
-      <c r="J92" s="64"/>
+      <c r="C92" s="60"/>
+      <c r="D92" s="60"/>
+      <c r="E92" s="60"/>
+      <c r="F92" s="60"/>
+      <c r="G92" s="60"/>
+      <c r="H92" s="60"/>
+      <c r="I92" s="60"/>
+      <c r="J92" s="61"/>
       <c r="K92" s="44"/>
     </row>
     <row r="93" spans="1:11">
@@ -13974,17 +13996,17 @@
     </row>
     <row r="97" spans="1:11" ht="24" customHeight="1">
       <c r="A97" s="1"/>
-      <c r="B97" s="62" t="s">
+      <c r="B97" s="59" t="s">
         <v>641</v>
       </c>
-      <c r="C97" s="63"/>
-      <c r="D97" s="63"/>
-      <c r="E97" s="63"/>
-      <c r="F97" s="63"/>
-      <c r="G97" s="63"/>
-      <c r="H97" s="63"/>
-      <c r="I97" s="63"/>
-      <c r="J97" s="64"/>
+      <c r="C97" s="60"/>
+      <c r="D97" s="60"/>
+      <c r="E97" s="60"/>
+      <c r="F97" s="60"/>
+      <c r="G97" s="60"/>
+      <c r="H97" s="60"/>
+      <c r="I97" s="60"/>
+      <c r="J97" s="61"/>
       <c r="K97" s="44"/>
     </row>
     <row r="98" spans="1:11">
@@ -14066,17 +14088,17 @@
     </row>
     <row r="102" spans="1:11" ht="24" customHeight="1">
       <c r="A102" s="1"/>
-      <c r="B102" s="62" t="s">
+      <c r="B102" s="59" t="s">
         <v>643</v>
       </c>
-      <c r="C102" s="63"/>
-      <c r="D102" s="63"/>
-      <c r="E102" s="63"/>
-      <c r="F102" s="63"/>
-      <c r="G102" s="63"/>
-      <c r="H102" s="63"/>
-      <c r="I102" s="63"/>
-      <c r="J102" s="64"/>
+      <c r="C102" s="60"/>
+      <c r="D102" s="60"/>
+      <c r="E102" s="60"/>
+      <c r="F102" s="60"/>
+      <c r="G102" s="60"/>
+      <c r="H102" s="60"/>
+      <c r="I102" s="60"/>
+      <c r="J102" s="61"/>
       <c r="K102" s="44"/>
     </row>
     <row r="103" spans="1:11">
@@ -14158,17 +14180,17 @@
     </row>
     <row r="107" spans="1:11" ht="24" customHeight="1">
       <c r="A107" s="1"/>
-      <c r="B107" s="62" t="s">
+      <c r="B107" s="59" t="s">
         <v>645</v>
       </c>
-      <c r="C107" s="63"/>
-      <c r="D107" s="63"/>
-      <c r="E107" s="63"/>
-      <c r="F107" s="63"/>
-      <c r="G107" s="63"/>
-      <c r="H107" s="63"/>
-      <c r="I107" s="63"/>
-      <c r="J107" s="64"/>
+      <c r="C107" s="60"/>
+      <c r="D107" s="60"/>
+      <c r="E107" s="60"/>
+      <c r="F107" s="60"/>
+      <c r="G107" s="60"/>
+      <c r="H107" s="60"/>
+      <c r="I107" s="60"/>
+      <c r="J107" s="61"/>
       <c r="K107" s="44"/>
     </row>
     <row r="108" spans="1:11">
@@ -14250,17 +14272,17 @@
     </row>
     <row r="112" spans="1:11" ht="24" customHeight="1">
       <c r="A112" s="1"/>
-      <c r="B112" s="62" t="s">
+      <c r="B112" s="59" t="s">
         <v>647</v>
       </c>
-      <c r="C112" s="63"/>
-      <c r="D112" s="63"/>
-      <c r="E112" s="63"/>
-      <c r="F112" s="63"/>
-      <c r="G112" s="63"/>
-      <c r="H112" s="63"/>
-      <c r="I112" s="63"/>
-      <c r="J112" s="64"/>
+      <c r="C112" s="60"/>
+      <c r="D112" s="60"/>
+      <c r="E112" s="60"/>
+      <c r="F112" s="60"/>
+      <c r="G112" s="60"/>
+      <c r="H112" s="60"/>
+      <c r="I112" s="60"/>
+      <c r="J112" s="61"/>
       <c r="K112" s="44"/>
     </row>
     <row r="113" spans="1:11">
@@ -14342,17 +14364,17 @@
     </row>
     <row r="117" spans="1:11" ht="24" customHeight="1">
       <c r="A117" s="1"/>
-      <c r="B117" s="62" t="s">
+      <c r="B117" s="59" t="s">
         <v>649</v>
       </c>
-      <c r="C117" s="63"/>
-      <c r="D117" s="63"/>
-      <c r="E117" s="63"/>
-      <c r="F117" s="63"/>
-      <c r="G117" s="63"/>
-      <c r="H117" s="63"/>
-      <c r="I117" s="63"/>
-      <c r="J117" s="64"/>
+      <c r="C117" s="60"/>
+      <c r="D117" s="60"/>
+      <c r="E117" s="60"/>
+      <c r="F117" s="60"/>
+      <c r="G117" s="60"/>
+      <c r="H117" s="60"/>
+      <c r="I117" s="60"/>
+      <c r="J117" s="61"/>
       <c r="K117" s="44"/>
     </row>
     <row r="118" spans="1:11">
@@ -14434,17 +14456,17 @@
     </row>
     <row r="122" spans="1:11" ht="24" customHeight="1">
       <c r="A122" s="1"/>
-      <c r="B122" s="62" t="s">
+      <c r="B122" s="59" t="s">
         <v>651</v>
       </c>
-      <c r="C122" s="63"/>
-      <c r="D122" s="63"/>
-      <c r="E122" s="63"/>
-      <c r="F122" s="63"/>
-      <c r="G122" s="63"/>
-      <c r="H122" s="63"/>
-      <c r="I122" s="63"/>
-      <c r="J122" s="64"/>
+      <c r="C122" s="60"/>
+      <c r="D122" s="60"/>
+      <c r="E122" s="60"/>
+      <c r="F122" s="60"/>
+      <c r="G122" s="60"/>
+      <c r="H122" s="60"/>
+      <c r="I122" s="60"/>
+      <c r="J122" s="61"/>
       <c r="K122" s="44"/>
     </row>
     <row r="123" spans="1:11">
@@ -14526,17 +14548,17 @@
     </row>
     <row r="127" spans="1:11" ht="24" customHeight="1">
       <c r="A127" s="1"/>
-      <c r="B127" s="62" t="s">
+      <c r="B127" s="59" t="s">
         <v>653</v>
       </c>
-      <c r="C127" s="63"/>
-      <c r="D127" s="63"/>
-      <c r="E127" s="63"/>
-      <c r="F127" s="63"/>
-      <c r="G127" s="63"/>
-      <c r="H127" s="63"/>
-      <c r="I127" s="63"/>
-      <c r="J127" s="64"/>
+      <c r="C127" s="60"/>
+      <c r="D127" s="60"/>
+      <c r="E127" s="60"/>
+      <c r="F127" s="60"/>
+      <c r="G127" s="60"/>
+      <c r="H127" s="60"/>
+      <c r="I127" s="60"/>
+      <c r="J127" s="61"/>
       <c r="K127" s="44"/>
     </row>
     <row r="128" spans="1:11">
@@ -14616,17 +14638,17 @@
     </row>
     <row r="132" spans="1:11" ht="24" customHeight="1">
       <c r="A132" s="1"/>
-      <c r="B132" s="62" t="s">
+      <c r="B132" s="59" t="s">
         <v>655</v>
       </c>
-      <c r="C132" s="63"/>
-      <c r="D132" s="63"/>
-      <c r="E132" s="63"/>
-      <c r="F132" s="63"/>
-      <c r="G132" s="63"/>
-      <c r="H132" s="63"/>
-      <c r="I132" s="63"/>
-      <c r="J132" s="64"/>
+      <c r="C132" s="60"/>
+      <c r="D132" s="60"/>
+      <c r="E132" s="60"/>
+      <c r="F132" s="60"/>
+      <c r="G132" s="60"/>
+      <c r="H132" s="60"/>
+      <c r="I132" s="60"/>
+      <c r="J132" s="61"/>
       <c r="K132" s="44"/>
     </row>
     <row r="133" spans="1:11">
@@ -14706,17 +14728,17 @@
     </row>
     <row r="137" spans="1:11" ht="24" customHeight="1">
       <c r="A137" s="1"/>
-      <c r="B137" s="62" t="s">
+      <c r="B137" s="59" t="s">
         <v>657</v>
       </c>
-      <c r="C137" s="63"/>
-      <c r="D137" s="63"/>
-      <c r="E137" s="63"/>
-      <c r="F137" s="63"/>
-      <c r="G137" s="63"/>
-      <c r="H137" s="63"/>
-      <c r="I137" s="63"/>
-      <c r="J137" s="64"/>
+      <c r="C137" s="60"/>
+      <c r="D137" s="60"/>
+      <c r="E137" s="60"/>
+      <c r="F137" s="60"/>
+      <c r="G137" s="60"/>
+      <c r="H137" s="60"/>
+      <c r="I137" s="60"/>
+      <c r="J137" s="61"/>
       <c r="K137" s="44"/>
     </row>
     <row r="138" spans="1:11">
@@ -14796,17 +14818,17 @@
     </row>
     <row r="142" spans="1:11" ht="24" customHeight="1">
       <c r="A142" s="1"/>
-      <c r="B142" s="62" t="s">
+      <c r="B142" s="59" t="s">
         <v>659</v>
       </c>
-      <c r="C142" s="63"/>
-      <c r="D142" s="63"/>
-      <c r="E142" s="63"/>
-      <c r="F142" s="63"/>
-      <c r="G142" s="63"/>
-      <c r="H142" s="63"/>
-      <c r="I142" s="63"/>
-      <c r="J142" s="64"/>
+      <c r="C142" s="60"/>
+      <c r="D142" s="60"/>
+      <c r="E142" s="60"/>
+      <c r="F142" s="60"/>
+      <c r="G142" s="60"/>
+      <c r="H142" s="60"/>
+      <c r="I142" s="60"/>
+      <c r="J142" s="61"/>
       <c r="K142" s="44"/>
     </row>
     <row r="143" spans="1:11">
@@ -14886,17 +14908,17 @@
     </row>
     <row r="147" spans="1:11" ht="24" customHeight="1">
       <c r="A147" s="1"/>
-      <c r="B147" s="62" t="s">
+      <c r="B147" s="59" t="s">
         <v>661</v>
       </c>
-      <c r="C147" s="63"/>
-      <c r="D147" s="63"/>
-      <c r="E147" s="63"/>
-      <c r="F147" s="63"/>
-      <c r="G147" s="63"/>
-      <c r="H147" s="63"/>
-      <c r="I147" s="63"/>
-      <c r="J147" s="64"/>
+      <c r="C147" s="60"/>
+      <c r="D147" s="60"/>
+      <c r="E147" s="60"/>
+      <c r="F147" s="60"/>
+      <c r="G147" s="60"/>
+      <c r="H147" s="60"/>
+      <c r="I147" s="60"/>
+      <c r="J147" s="61"/>
       <c r="K147" s="44"/>
     </row>
     <row r="148" spans="1:11">
@@ -14978,17 +15000,17 @@
     </row>
     <row r="152" spans="1:11" ht="24" customHeight="1">
       <c r="A152" s="1"/>
-      <c r="B152" s="62" t="s">
+      <c r="B152" s="59" t="s">
         <v>663</v>
       </c>
-      <c r="C152" s="63"/>
-      <c r="D152" s="63"/>
-      <c r="E152" s="63"/>
-      <c r="F152" s="63"/>
-      <c r="G152" s="63"/>
-      <c r="H152" s="63"/>
-      <c r="I152" s="63"/>
-      <c r="J152" s="64"/>
+      <c r="C152" s="60"/>
+      <c r="D152" s="60"/>
+      <c r="E152" s="60"/>
+      <c r="F152" s="60"/>
+      <c r="G152" s="60"/>
+      <c r="H152" s="60"/>
+      <c r="I152" s="60"/>
+      <c r="J152" s="61"/>
       <c r="K152" s="44"/>
     </row>
     <row r="153" spans="1:11">
@@ -15070,17 +15092,17 @@
     </row>
     <row r="157" spans="1:11" ht="24" customHeight="1">
       <c r="A157" s="1"/>
-      <c r="B157" s="62" t="s">
+      <c r="B157" s="59" t="s">
         <v>665</v>
       </c>
-      <c r="C157" s="63"/>
-      <c r="D157" s="63"/>
-      <c r="E157" s="63"/>
-      <c r="F157" s="63"/>
-      <c r="G157" s="63"/>
-      <c r="H157" s="63"/>
-      <c r="I157" s="63"/>
-      <c r="J157" s="64"/>
+      <c r="C157" s="60"/>
+      <c r="D157" s="60"/>
+      <c r="E157" s="60"/>
+      <c r="F157" s="60"/>
+      <c r="G157" s="60"/>
+      <c r="H157" s="60"/>
+      <c r="I157" s="60"/>
+      <c r="J157" s="61"/>
       <c r="K157" s="44"/>
     </row>
     <row r="158" spans="1:11">
@@ -15162,17 +15184,17 @@
     </row>
     <row r="162" spans="1:11" ht="24" customHeight="1">
       <c r="A162" s="1"/>
-      <c r="B162" s="62" t="s">
+      <c r="B162" s="59" t="s">
         <v>667</v>
       </c>
-      <c r="C162" s="63"/>
-      <c r="D162" s="63"/>
-      <c r="E162" s="63"/>
-      <c r="F162" s="63"/>
-      <c r="G162" s="63"/>
-      <c r="H162" s="63"/>
-      <c r="I162" s="63"/>
-      <c r="J162" s="64"/>
+      <c r="C162" s="60"/>
+      <c r="D162" s="60"/>
+      <c r="E162" s="60"/>
+      <c r="F162" s="60"/>
+      <c r="G162" s="60"/>
+      <c r="H162" s="60"/>
+      <c r="I162" s="60"/>
+      <c r="J162" s="61"/>
       <c r="K162" s="44"/>
     </row>
     <row r="163" spans="1:11">
@@ -15254,17 +15276,17 @@
     </row>
     <row r="167" spans="1:11" ht="24" customHeight="1">
       <c r="A167" s="1"/>
-      <c r="B167" s="62" t="s">
+      <c r="B167" s="59" t="s">
         <v>669</v>
       </c>
-      <c r="C167" s="63"/>
-      <c r="D167" s="63"/>
-      <c r="E167" s="63"/>
-      <c r="F167" s="63"/>
-      <c r="G167" s="63"/>
-      <c r="H167" s="63"/>
-      <c r="I167" s="63"/>
-      <c r="J167" s="64"/>
+      <c r="C167" s="60"/>
+      <c r="D167" s="60"/>
+      <c r="E167" s="60"/>
+      <c r="F167" s="60"/>
+      <c r="G167" s="60"/>
+      <c r="H167" s="60"/>
+      <c r="I167" s="60"/>
+      <c r="J167" s="61"/>
       <c r="K167" s="44"/>
     </row>
     <row r="168" spans="1:11">
@@ -15342,17 +15364,17 @@
     </row>
     <row r="172" spans="1:11" ht="24" customHeight="1">
       <c r="A172" s="1"/>
-      <c r="B172" s="62" t="s">
+      <c r="B172" s="59" t="s">
         <v>670</v>
       </c>
-      <c r="C172" s="63"/>
-      <c r="D172" s="63"/>
-      <c r="E172" s="63"/>
-      <c r="F172" s="63"/>
-      <c r="G172" s="63"/>
-      <c r="H172" s="63"/>
-      <c r="I172" s="63"/>
-      <c r="J172" s="64"/>
+      <c r="C172" s="60"/>
+      <c r="D172" s="60"/>
+      <c r="E172" s="60"/>
+      <c r="F172" s="60"/>
+      <c r="G172" s="60"/>
+      <c r="H172" s="60"/>
+      <c r="I172" s="60"/>
+      <c r="J172" s="61"/>
       <c r="K172" s="44"/>
     </row>
     <row r="173" spans="1:11">
@@ -15434,17 +15456,17 @@
     </row>
     <row r="177" spans="1:11" ht="24" customHeight="1">
       <c r="A177" s="1"/>
-      <c r="B177" s="62" t="s">
+      <c r="B177" s="59" t="s">
         <v>672</v>
       </c>
-      <c r="C177" s="63"/>
-      <c r="D177" s="63"/>
-      <c r="E177" s="63"/>
-      <c r="F177" s="63"/>
-      <c r="G177" s="63"/>
-      <c r="H177" s="63"/>
-      <c r="I177" s="63"/>
-      <c r="J177" s="64"/>
+      <c r="C177" s="60"/>
+      <c r="D177" s="60"/>
+      <c r="E177" s="60"/>
+      <c r="F177" s="60"/>
+      <c r="G177" s="60"/>
+      <c r="H177" s="60"/>
+      <c r="I177" s="60"/>
+      <c r="J177" s="61"/>
       <c r="K177" s="44"/>
     </row>
     <row r="178" spans="1:11">
@@ -15526,17 +15548,17 @@
     </row>
     <row r="182" spans="1:11" ht="24" customHeight="1">
       <c r="A182" s="1"/>
-      <c r="B182" s="62" t="s">
+      <c r="B182" s="59" t="s">
         <v>674</v>
       </c>
-      <c r="C182" s="63"/>
-      <c r="D182" s="63"/>
-      <c r="E182" s="63"/>
-      <c r="F182" s="63"/>
-      <c r="G182" s="63"/>
-      <c r="H182" s="63"/>
-      <c r="I182" s="63"/>
-      <c r="J182" s="64"/>
+      <c r="C182" s="60"/>
+      <c r="D182" s="60"/>
+      <c r="E182" s="60"/>
+      <c r="F182" s="60"/>
+      <c r="G182" s="60"/>
+      <c r="H182" s="60"/>
+      <c r="I182" s="60"/>
+      <c r="J182" s="61"/>
       <c r="K182" s="44"/>
     </row>
     <row r="183" spans="1:11">
@@ -15618,17 +15640,17 @@
     </row>
     <row r="187" spans="1:11" ht="24" customHeight="1">
       <c r="A187" s="1"/>
-      <c r="B187" s="62" t="s">
+      <c r="B187" s="59" t="s">
         <v>676</v>
       </c>
-      <c r="C187" s="63"/>
-      <c r="D187" s="63"/>
-      <c r="E187" s="63"/>
-      <c r="F187" s="63"/>
-      <c r="G187" s="63"/>
-      <c r="H187" s="63"/>
-      <c r="I187" s="63"/>
-      <c r="J187" s="64"/>
+      <c r="C187" s="60"/>
+      <c r="D187" s="60"/>
+      <c r="E187" s="60"/>
+      <c r="F187" s="60"/>
+      <c r="G187" s="60"/>
+      <c r="H187" s="60"/>
+      <c r="I187" s="60"/>
+      <c r="J187" s="61"/>
       <c r="K187" s="44"/>
     </row>
     <row r="188" spans="1:11">
@@ -15710,17 +15732,17 @@
     </row>
     <row r="192" spans="1:11" ht="24" customHeight="1">
       <c r="A192" s="1"/>
-      <c r="B192" s="62" t="s">
+      <c r="B192" s="59" t="s">
         <v>678</v>
       </c>
-      <c r="C192" s="63"/>
-      <c r="D192" s="63"/>
-      <c r="E192" s="63"/>
-      <c r="F192" s="63"/>
-      <c r="G192" s="63"/>
-      <c r="H192" s="63"/>
-      <c r="I192" s="63"/>
-      <c r="J192" s="64"/>
+      <c r="C192" s="60"/>
+      <c r="D192" s="60"/>
+      <c r="E192" s="60"/>
+      <c r="F192" s="60"/>
+      <c r="G192" s="60"/>
+      <c r="H192" s="60"/>
+      <c r="I192" s="60"/>
+      <c r="J192" s="61"/>
       <c r="K192" s="44"/>
     </row>
     <row r="193" spans="1:11">
@@ -15802,17 +15824,17 @@
     </row>
     <row r="197" spans="1:11" ht="24" customHeight="1">
       <c r="A197" s="1"/>
-      <c r="B197" s="62" t="s">
+      <c r="B197" s="59" t="s">
         <v>680</v>
       </c>
-      <c r="C197" s="63"/>
-      <c r="D197" s="63"/>
-      <c r="E197" s="63"/>
-      <c r="F197" s="63"/>
-      <c r="G197" s="63"/>
-      <c r="H197" s="63"/>
-      <c r="I197" s="63"/>
-      <c r="J197" s="64"/>
+      <c r="C197" s="60"/>
+      <c r="D197" s="60"/>
+      <c r="E197" s="60"/>
+      <c r="F197" s="60"/>
+      <c r="G197" s="60"/>
+      <c r="H197" s="60"/>
+      <c r="I197" s="60"/>
+      <c r="J197" s="61"/>
       <c r="K197" s="44"/>
     </row>
     <row r="198" spans="1:11">
@@ -15894,17 +15916,17 @@
     </row>
     <row r="202" spans="1:11" ht="24" customHeight="1">
       <c r="A202" s="1"/>
-      <c r="B202" s="62" t="s">
+      <c r="B202" s="59" t="s">
         <v>682</v>
       </c>
-      <c r="C202" s="63"/>
-      <c r="D202" s="63"/>
-      <c r="E202" s="63"/>
-      <c r="F202" s="63"/>
-      <c r="G202" s="63"/>
-      <c r="H202" s="63"/>
-      <c r="I202" s="63"/>
-      <c r="J202" s="64"/>
+      <c r="C202" s="60"/>
+      <c r="D202" s="60"/>
+      <c r="E202" s="60"/>
+      <c r="F202" s="60"/>
+      <c r="G202" s="60"/>
+      <c r="H202" s="60"/>
+      <c r="I202" s="60"/>
+      <c r="J202" s="61"/>
       <c r="K202" s="44"/>
     </row>
     <row r="203" spans="1:11">
@@ -15986,17 +16008,17 @@
     </row>
     <row r="207" spans="1:11" ht="24" customHeight="1">
       <c r="A207" s="1"/>
-      <c r="B207" s="62" t="s">
+      <c r="B207" s="59" t="s">
         <v>684</v>
       </c>
-      <c r="C207" s="63"/>
-      <c r="D207" s="63"/>
-      <c r="E207" s="63"/>
-      <c r="F207" s="63"/>
-      <c r="G207" s="63"/>
-      <c r="H207" s="63"/>
-      <c r="I207" s="63"/>
-      <c r="J207" s="64"/>
+      <c r="C207" s="60"/>
+      <c r="D207" s="60"/>
+      <c r="E207" s="60"/>
+      <c r="F207" s="60"/>
+      <c r="G207" s="60"/>
+      <c r="H207" s="60"/>
+      <c r="I207" s="60"/>
+      <c r="J207" s="61"/>
       <c r="K207" s="44"/>
     </row>
     <row r="208" spans="1:11">
@@ -16078,17 +16100,17 @@
     </row>
     <row r="212" spans="1:11" ht="24" customHeight="1">
       <c r="A212" s="1"/>
-      <c r="B212" s="62" t="s">
+      <c r="B212" s="59" t="s">
         <v>686</v>
       </c>
-      <c r="C212" s="63"/>
-      <c r="D212" s="63"/>
-      <c r="E212" s="63"/>
-      <c r="F212" s="63"/>
-      <c r="G212" s="63"/>
-      <c r="H212" s="63"/>
-      <c r="I212" s="63"/>
-      <c r="J212" s="64"/>
+      <c r="C212" s="60"/>
+      <c r="D212" s="60"/>
+      <c r="E212" s="60"/>
+      <c r="F212" s="60"/>
+      <c r="G212" s="60"/>
+      <c r="H212" s="60"/>
+      <c r="I212" s="60"/>
+      <c r="J212" s="61"/>
       <c r="K212" s="44"/>
     </row>
     <row r="213" spans="1:11">
@@ -16170,17 +16192,17 @@
     </row>
     <row r="217" spans="1:11" ht="24" customHeight="1">
       <c r="A217" s="1"/>
-      <c r="B217" s="62" t="s">
+      <c r="B217" s="59" t="s">
         <v>688</v>
       </c>
-      <c r="C217" s="63"/>
-      <c r="D217" s="63"/>
-      <c r="E217" s="63"/>
-      <c r="F217" s="63"/>
-      <c r="G217" s="63"/>
-      <c r="H217" s="63"/>
-      <c r="I217" s="63"/>
-      <c r="J217" s="64"/>
+      <c r="C217" s="60"/>
+      <c r="D217" s="60"/>
+      <c r="E217" s="60"/>
+      <c r="F217" s="60"/>
+      <c r="G217" s="60"/>
+      <c r="H217" s="60"/>
+      <c r="I217" s="60"/>
+      <c r="J217" s="61"/>
       <c r="K217" s="44"/>
     </row>
     <row r="218" spans="1:11">
@@ -16262,17 +16284,17 @@
     </row>
     <row r="222" spans="1:11" ht="24" customHeight="1">
       <c r="A222" s="1"/>
-      <c r="B222" s="62" t="s">
+      <c r="B222" s="59" t="s">
         <v>689</v>
       </c>
-      <c r="C222" s="63"/>
-      <c r="D222" s="63"/>
-      <c r="E222" s="63"/>
-      <c r="F222" s="63"/>
-      <c r="G222" s="63"/>
-      <c r="H222" s="63"/>
-      <c r="I222" s="63"/>
-      <c r="J222" s="64"/>
+      <c r="C222" s="60"/>
+      <c r="D222" s="60"/>
+      <c r="E222" s="60"/>
+      <c r="F222" s="60"/>
+      <c r="G222" s="60"/>
+      <c r="H222" s="60"/>
+      <c r="I222" s="60"/>
+      <c r="J222" s="61"/>
       <c r="K222" s="44"/>
     </row>
     <row r="223" spans="1:11">
@@ -16354,17 +16376,17 @@
     </row>
     <row r="227" spans="1:11" ht="24" customHeight="1">
       <c r="A227" s="1"/>
-      <c r="B227" s="62" t="s">
+      <c r="B227" s="59" t="s">
         <v>691</v>
       </c>
-      <c r="C227" s="63"/>
-      <c r="D227" s="63"/>
-      <c r="E227" s="63"/>
-      <c r="F227" s="63"/>
-      <c r="G227" s="63"/>
-      <c r="H227" s="63"/>
-      <c r="I227" s="63"/>
-      <c r="J227" s="64"/>
+      <c r="C227" s="60"/>
+      <c r="D227" s="60"/>
+      <c r="E227" s="60"/>
+      <c r="F227" s="60"/>
+      <c r="G227" s="60"/>
+      <c r="H227" s="60"/>
+      <c r="I227" s="60"/>
+      <c r="J227" s="61"/>
       <c r="K227" s="44"/>
     </row>
     <row r="228" spans="1:11">
@@ -16446,17 +16468,17 @@
     </row>
     <row r="232" spans="1:11" ht="24" customHeight="1">
       <c r="A232" s="1"/>
-      <c r="B232" s="62" t="s">
+      <c r="B232" s="59" t="s">
         <v>693</v>
       </c>
-      <c r="C232" s="63"/>
-      <c r="D232" s="63"/>
-      <c r="E232" s="63"/>
-      <c r="F232" s="63"/>
-      <c r="G232" s="63"/>
-      <c r="H232" s="63"/>
-      <c r="I232" s="63"/>
-      <c r="J232" s="64"/>
+      <c r="C232" s="60"/>
+      <c r="D232" s="60"/>
+      <c r="E232" s="60"/>
+      <c r="F232" s="60"/>
+      <c r="G232" s="60"/>
+      <c r="H232" s="60"/>
+      <c r="I232" s="60"/>
+      <c r="J232" s="61"/>
       <c r="K232" s="44"/>
     </row>
     <row r="233" spans="1:11">
@@ -16538,17 +16560,17 @@
     </row>
     <row r="237" spans="1:11" ht="24" customHeight="1">
       <c r="A237" s="1"/>
-      <c r="B237" s="62" t="s">
+      <c r="B237" s="59" t="s">
         <v>695</v>
       </c>
-      <c r="C237" s="63"/>
-      <c r="D237" s="63"/>
-      <c r="E237" s="63"/>
-      <c r="F237" s="63"/>
-      <c r="G237" s="63"/>
-      <c r="H237" s="63"/>
-      <c r="I237" s="63"/>
-      <c r="J237" s="64"/>
+      <c r="C237" s="60"/>
+      <c r="D237" s="60"/>
+      <c r="E237" s="60"/>
+      <c r="F237" s="60"/>
+      <c r="G237" s="60"/>
+      <c r="H237" s="60"/>
+      <c r="I237" s="60"/>
+      <c r="J237" s="61"/>
       <c r="K237" s="44"/>
     </row>
     <row r="238" spans="1:11">
@@ -16630,17 +16652,17 @@
     </row>
     <row r="242" spans="1:11" ht="24" customHeight="1">
       <c r="A242" s="1"/>
-      <c r="B242" s="62" t="s">
+      <c r="B242" s="59" t="s">
         <v>697</v>
       </c>
-      <c r="C242" s="63"/>
-      <c r="D242" s="63"/>
-      <c r="E242" s="63"/>
-      <c r="F242" s="63"/>
-      <c r="G242" s="63"/>
-      <c r="H242" s="63"/>
-      <c r="I242" s="63"/>
-      <c r="J242" s="64"/>
+      <c r="C242" s="60"/>
+      <c r="D242" s="60"/>
+      <c r="E242" s="60"/>
+      <c r="F242" s="60"/>
+      <c r="G242" s="60"/>
+      <c r="H242" s="60"/>
+      <c r="I242" s="60"/>
+      <c r="J242" s="61"/>
       <c r="K242" s="44"/>
     </row>
     <row r="243" spans="1:11">
@@ -16722,17 +16744,17 @@
     </row>
     <row r="247" spans="1:11" ht="24" customHeight="1">
       <c r="A247" s="1"/>
-      <c r="B247" s="62" t="s">
+      <c r="B247" s="59" t="s">
         <v>699</v>
       </c>
-      <c r="C247" s="63"/>
-      <c r="D247" s="63"/>
-      <c r="E247" s="63"/>
-      <c r="F247" s="63"/>
-      <c r="G247" s="63"/>
-      <c r="H247" s="63"/>
-      <c r="I247" s="63"/>
-      <c r="J247" s="64"/>
+      <c r="C247" s="60"/>
+      <c r="D247" s="60"/>
+      <c r="E247" s="60"/>
+      <c r="F247" s="60"/>
+      <c r="G247" s="60"/>
+      <c r="H247" s="60"/>
+      <c r="I247" s="60"/>
+      <c r="J247" s="61"/>
       <c r="K247" s="44"/>
     </row>
     <row r="248" spans="1:11">
@@ -16814,17 +16836,17 @@
     </row>
     <row r="252" spans="1:11" ht="24" customHeight="1">
       <c r="A252" s="1"/>
-      <c r="B252" s="62" t="s">
+      <c r="B252" s="59" t="s">
         <v>701</v>
       </c>
-      <c r="C252" s="63"/>
-      <c r="D252" s="63"/>
-      <c r="E252" s="63"/>
-      <c r="F252" s="63"/>
-      <c r="G252" s="63"/>
-      <c r="H252" s="63"/>
-      <c r="I252" s="63"/>
-      <c r="J252" s="64"/>
+      <c r="C252" s="60"/>
+      <c r="D252" s="60"/>
+      <c r="E252" s="60"/>
+      <c r="F252" s="60"/>
+      <c r="G252" s="60"/>
+      <c r="H252" s="60"/>
+      <c r="I252" s="60"/>
+      <c r="J252" s="61"/>
       <c r="K252" s="44"/>
     </row>
     <row r="253" spans="1:11">
@@ -16906,17 +16928,17 @@
     </row>
     <row r="257" spans="1:11" ht="24" customHeight="1">
       <c r="A257" s="1"/>
-      <c r="B257" s="62" t="s">
+      <c r="B257" s="59" t="s">
         <v>703</v>
       </c>
-      <c r="C257" s="63"/>
-      <c r="D257" s="63"/>
-      <c r="E257" s="63"/>
-      <c r="F257" s="63"/>
-      <c r="G257" s="63"/>
-      <c r="H257" s="63"/>
-      <c r="I257" s="63"/>
-      <c r="J257" s="64"/>
+      <c r="C257" s="60"/>
+      <c r="D257" s="60"/>
+      <c r="E257" s="60"/>
+      <c r="F257" s="60"/>
+      <c r="G257" s="60"/>
+      <c r="H257" s="60"/>
+      <c r="I257" s="60"/>
+      <c r="J257" s="61"/>
       <c r="K257" s="44"/>
     </row>
     <row r="258" spans="1:11">
@@ -16998,17 +17020,17 @@
     </row>
     <row r="262" spans="1:11" ht="24" customHeight="1">
       <c r="A262" s="1"/>
-      <c r="B262" s="62" t="s">
+      <c r="B262" s="59" t="s">
         <v>705</v>
       </c>
-      <c r="C262" s="63"/>
-      <c r="D262" s="63"/>
-      <c r="E262" s="63"/>
-      <c r="F262" s="63"/>
-      <c r="G262" s="63"/>
-      <c r="H262" s="63"/>
-      <c r="I262" s="63"/>
-      <c r="J262" s="64"/>
+      <c r="C262" s="60"/>
+      <c r="D262" s="60"/>
+      <c r="E262" s="60"/>
+      <c r="F262" s="60"/>
+      <c r="G262" s="60"/>
+      <c r="H262" s="60"/>
+      <c r="I262" s="60"/>
+      <c r="J262" s="61"/>
       <c r="K262" s="44"/>
     </row>
     <row r="263" spans="1:11">
@@ -17090,17 +17112,17 @@
     </row>
     <row r="267" spans="1:11" ht="24" customHeight="1">
       <c r="A267" s="1"/>
-      <c r="B267" s="62" t="s">
+      <c r="B267" s="59" t="s">
         <v>707</v>
       </c>
-      <c r="C267" s="63"/>
-      <c r="D267" s="63"/>
-      <c r="E267" s="63"/>
-      <c r="F267" s="63"/>
-      <c r="G267" s="63"/>
-      <c r="H267" s="63"/>
-      <c r="I267" s="63"/>
-      <c r="J267" s="64"/>
+      <c r="C267" s="60"/>
+      <c r="D267" s="60"/>
+      <c r="E267" s="60"/>
+      <c r="F267" s="60"/>
+      <c r="G267" s="60"/>
+      <c r="H267" s="60"/>
+      <c r="I267" s="60"/>
+      <c r="J267" s="61"/>
       <c r="K267" s="44"/>
     </row>
     <row r="268" spans="1:11">
@@ -17182,17 +17204,17 @@
     </row>
     <row r="272" spans="1:11" ht="24" customHeight="1">
       <c r="A272" s="1"/>
-      <c r="B272" s="62" t="s">
+      <c r="B272" s="59" t="s">
         <v>709</v>
       </c>
-      <c r="C272" s="63"/>
-      <c r="D272" s="63"/>
-      <c r="E272" s="63"/>
-      <c r="F272" s="63"/>
-      <c r="G272" s="63"/>
-      <c r="H272" s="63"/>
-      <c r="I272" s="63"/>
-      <c r="J272" s="64"/>
+      <c r="C272" s="60"/>
+      <c r="D272" s="60"/>
+      <c r="E272" s="60"/>
+      <c r="F272" s="60"/>
+      <c r="G272" s="60"/>
+      <c r="H272" s="60"/>
+      <c r="I272" s="60"/>
+      <c r="J272" s="61"/>
       <c r="K272" s="44"/>
     </row>
     <row r="273" spans="1:11">
@@ -17274,17 +17296,17 @@
     </row>
     <row r="277" spans="1:11" ht="24" customHeight="1">
       <c r="A277" s="1"/>
-      <c r="B277" s="62" t="s">
+      <c r="B277" s="59" t="s">
         <v>711</v>
       </c>
-      <c r="C277" s="63"/>
-      <c r="D277" s="63"/>
-      <c r="E277" s="63"/>
-      <c r="F277" s="63"/>
-      <c r="G277" s="63"/>
-      <c r="H277" s="63"/>
-      <c r="I277" s="63"/>
-      <c r="J277" s="64"/>
+      <c r="C277" s="60"/>
+      <c r="D277" s="60"/>
+      <c r="E277" s="60"/>
+      <c r="F277" s="60"/>
+      <c r="G277" s="60"/>
+      <c r="H277" s="60"/>
+      <c r="I277" s="60"/>
+      <c r="J277" s="61"/>
       <c r="K277" s="44"/>
     </row>
     <row r="278" spans="1:11">
@@ -17366,17 +17388,17 @@
     </row>
     <row r="282" spans="1:11" ht="24" customHeight="1">
       <c r="A282" s="1"/>
-      <c r="B282" s="62" t="s">
+      <c r="B282" s="59" t="s">
         <v>713</v>
       </c>
-      <c r="C282" s="63"/>
-      <c r="D282" s="63"/>
-      <c r="E282" s="63"/>
-      <c r="F282" s="63"/>
-      <c r="G282" s="63"/>
-      <c r="H282" s="63"/>
-      <c r="I282" s="63"/>
-      <c r="J282" s="64"/>
+      <c r="C282" s="60"/>
+      <c r="D282" s="60"/>
+      <c r="E282" s="60"/>
+      <c r="F282" s="60"/>
+      <c r="G282" s="60"/>
+      <c r="H282" s="60"/>
+      <c r="I282" s="60"/>
+      <c r="J282" s="61"/>
       <c r="K282" s="44"/>
     </row>
     <row r="283" spans="1:11">
@@ -17458,17 +17480,17 @@
     </row>
     <row r="287" spans="1:11" ht="24" customHeight="1">
       <c r="A287" s="1"/>
-      <c r="B287" s="62" t="s">
+      <c r="B287" s="59" t="s">
         <v>715</v>
       </c>
-      <c r="C287" s="63"/>
-      <c r="D287" s="63"/>
-      <c r="E287" s="63"/>
-      <c r="F287" s="63"/>
-      <c r="G287" s="63"/>
-      <c r="H287" s="63"/>
-      <c r="I287" s="63"/>
-      <c r="J287" s="64"/>
+      <c r="C287" s="60"/>
+      <c r="D287" s="60"/>
+      <c r="E287" s="60"/>
+      <c r="F287" s="60"/>
+      <c r="G287" s="60"/>
+      <c r="H287" s="60"/>
+      <c r="I287" s="60"/>
+      <c r="J287" s="61"/>
       <c r="K287" s="44"/>
     </row>
     <row r="288" spans="1:11">
@@ -17550,17 +17572,17 @@
     </row>
     <row r="292" spans="1:11" ht="24" customHeight="1">
       <c r="A292" s="1"/>
-      <c r="B292" s="62" t="s">
+      <c r="B292" s="59" t="s">
         <v>717</v>
       </c>
-      <c r="C292" s="63"/>
-      <c r="D292" s="63"/>
-      <c r="E292" s="63"/>
-      <c r="F292" s="63"/>
-      <c r="G292" s="63"/>
-      <c r="H292" s="63"/>
-      <c r="I292" s="63"/>
-      <c r="J292" s="64"/>
+      <c r="C292" s="60"/>
+      <c r="D292" s="60"/>
+      <c r="E292" s="60"/>
+      <c r="F292" s="60"/>
+      <c r="G292" s="60"/>
+      <c r="H292" s="60"/>
+      <c r="I292" s="60"/>
+      <c r="J292" s="61"/>
       <c r="K292" s="44"/>
     </row>
     <row r="293" spans="1:11">
@@ -17642,17 +17664,17 @@
     </row>
     <row r="297" spans="1:11" ht="24" customHeight="1">
       <c r="A297" s="1"/>
-      <c r="B297" s="62" t="s">
+      <c r="B297" s="59" t="s">
         <v>719</v>
       </c>
-      <c r="C297" s="63"/>
-      <c r="D297" s="63"/>
-      <c r="E297" s="63"/>
-      <c r="F297" s="63"/>
-      <c r="G297" s="63"/>
-      <c r="H297" s="63"/>
-      <c r="I297" s="63"/>
-      <c r="J297" s="64"/>
+      <c r="C297" s="60"/>
+      <c r="D297" s="60"/>
+      <c r="E297" s="60"/>
+      <c r="F297" s="60"/>
+      <c r="G297" s="60"/>
+      <c r="H297" s="60"/>
+      <c r="I297" s="60"/>
+      <c r="J297" s="61"/>
       <c r="K297" s="44"/>
     </row>
     <row r="298" spans="1:11">
@@ -17734,17 +17756,17 @@
     </row>
     <row r="302" spans="1:11" ht="24" customHeight="1">
       <c r="A302" s="1"/>
-      <c r="B302" s="62" t="s">
+      <c r="B302" s="59" t="s">
         <v>721</v>
       </c>
-      <c r="C302" s="63"/>
-      <c r="D302" s="63"/>
-      <c r="E302" s="63"/>
-      <c r="F302" s="63"/>
-      <c r="G302" s="63"/>
-      <c r="H302" s="63"/>
-      <c r="I302" s="63"/>
-      <c r="J302" s="64"/>
+      <c r="C302" s="60"/>
+      <c r="D302" s="60"/>
+      <c r="E302" s="60"/>
+      <c r="F302" s="60"/>
+      <c r="G302" s="60"/>
+      <c r="H302" s="60"/>
+      <c r="I302" s="60"/>
+      <c r="J302" s="61"/>
       <c r="K302" s="44"/>
     </row>
     <row r="303" spans="1:11">
@@ -17826,17 +17848,17 @@
     </row>
     <row r="307" spans="1:11" ht="24" customHeight="1">
       <c r="A307" s="1"/>
-      <c r="B307" s="62" t="s">
+      <c r="B307" s="59" t="s">
         <v>723</v>
       </c>
-      <c r="C307" s="63"/>
-      <c r="D307" s="63"/>
-      <c r="E307" s="63"/>
-      <c r="F307" s="63"/>
-      <c r="G307" s="63"/>
-      <c r="H307" s="63"/>
-      <c r="I307" s="63"/>
-      <c r="J307" s="64"/>
+      <c r="C307" s="60"/>
+      <c r="D307" s="60"/>
+      <c r="E307" s="60"/>
+      <c r="F307" s="60"/>
+      <c r="G307" s="60"/>
+      <c r="H307" s="60"/>
+      <c r="I307" s="60"/>
+      <c r="J307" s="61"/>
       <c r="K307" s="44"/>
     </row>
     <row r="308" spans="1:11">
@@ -17918,17 +17940,17 @@
     </row>
     <row r="312" spans="1:11" ht="24" customHeight="1">
       <c r="A312" s="1"/>
-      <c r="B312" s="62" t="s">
+      <c r="B312" s="59" t="s">
         <v>725</v>
       </c>
-      <c r="C312" s="63"/>
-      <c r="D312" s="63"/>
-      <c r="E312" s="63"/>
-      <c r="F312" s="63"/>
-      <c r="G312" s="63"/>
-      <c r="H312" s="63"/>
-      <c r="I312" s="63"/>
-      <c r="J312" s="64"/>
+      <c r="C312" s="60"/>
+      <c r="D312" s="60"/>
+      <c r="E312" s="60"/>
+      <c r="F312" s="60"/>
+      <c r="G312" s="60"/>
+      <c r="H312" s="60"/>
+      <c r="I312" s="60"/>
+      <c r="J312" s="61"/>
       <c r="K312" s="44"/>
     </row>
     <row r="313" spans="1:11">
@@ -18010,17 +18032,17 @@
     </row>
     <row r="317" spans="1:11" ht="24" customHeight="1">
       <c r="A317" s="1"/>
-      <c r="B317" s="62" t="s">
+      <c r="B317" s="59" t="s">
         <v>727</v>
       </c>
-      <c r="C317" s="63"/>
-      <c r="D317" s="63"/>
-      <c r="E317" s="63"/>
-      <c r="F317" s="63"/>
-      <c r="G317" s="63"/>
-      <c r="H317" s="63"/>
-      <c r="I317" s="63"/>
-      <c r="J317" s="64"/>
+      <c r="C317" s="60"/>
+      <c r="D317" s="60"/>
+      <c r="E317" s="60"/>
+      <c r="F317" s="60"/>
+      <c r="G317" s="60"/>
+      <c r="H317" s="60"/>
+      <c r="I317" s="60"/>
+      <c r="J317" s="61"/>
       <c r="K317" s="44"/>
     </row>
     <row r="318" spans="1:11">
@@ -18102,17 +18124,17 @@
     </row>
     <row r="322" spans="1:11" ht="24" customHeight="1">
       <c r="A322" s="1"/>
-      <c r="B322" s="62" t="s">
+      <c r="B322" s="59" t="s">
         <v>729</v>
       </c>
-      <c r="C322" s="63"/>
-      <c r="D322" s="63"/>
-      <c r="E322" s="63"/>
-      <c r="F322" s="63"/>
-      <c r="G322" s="63"/>
-      <c r="H322" s="63"/>
-      <c r="I322" s="63"/>
-      <c r="J322" s="64"/>
+      <c r="C322" s="60"/>
+      <c r="D322" s="60"/>
+      <c r="E322" s="60"/>
+      <c r="F322" s="60"/>
+      <c r="G322" s="60"/>
+      <c r="H322" s="60"/>
+      <c r="I322" s="60"/>
+      <c r="J322" s="61"/>
       <c r="K322" s="44"/>
     </row>
     <row r="323" spans="1:11">
@@ -18194,17 +18216,17 @@
     </row>
     <row r="327" spans="1:11" ht="24" customHeight="1">
       <c r="A327" s="1"/>
-      <c r="B327" s="62" t="s">
+      <c r="B327" s="59" t="s">
         <v>731</v>
       </c>
-      <c r="C327" s="63"/>
-      <c r="D327" s="63"/>
-      <c r="E327" s="63"/>
-      <c r="F327" s="63"/>
-      <c r="G327" s="63"/>
-      <c r="H327" s="63"/>
-      <c r="I327" s="63"/>
-      <c r="J327" s="64"/>
+      <c r="C327" s="60"/>
+      <c r="D327" s="60"/>
+      <c r="E327" s="60"/>
+      <c r="F327" s="60"/>
+      <c r="G327" s="60"/>
+      <c r="H327" s="60"/>
+      <c r="I327" s="60"/>
+      <c r="J327" s="61"/>
       <c r="K327" s="44"/>
     </row>
     <row r="328" spans="1:11">
@@ -18286,17 +18308,17 @@
     </row>
     <row r="332" spans="1:11" ht="24" customHeight="1">
       <c r="A332" s="1"/>
-      <c r="B332" s="62" t="s">
+      <c r="B332" s="59" t="s">
         <v>733</v>
       </c>
-      <c r="C332" s="63"/>
-      <c r="D332" s="63"/>
-      <c r="E332" s="63"/>
-      <c r="F332" s="63"/>
-      <c r="G332" s="63"/>
-      <c r="H332" s="63"/>
-      <c r="I332" s="63"/>
-      <c r="J332" s="64"/>
+      <c r="C332" s="60"/>
+      <c r="D332" s="60"/>
+      <c r="E332" s="60"/>
+      <c r="F332" s="60"/>
+      <c r="G332" s="60"/>
+      <c r="H332" s="60"/>
+      <c r="I332" s="60"/>
+      <c r="J332" s="61"/>
       <c r="K332" s="44"/>
     </row>
     <row r="333" spans="1:11">
@@ -18378,17 +18400,17 @@
     </row>
     <row r="337" spans="1:11" ht="24" customHeight="1">
       <c r="A337" s="1"/>
-      <c r="B337" s="62" t="s">
+      <c r="B337" s="59" t="s">
         <v>734</v>
       </c>
-      <c r="C337" s="63"/>
-      <c r="D337" s="63"/>
-      <c r="E337" s="63"/>
-      <c r="F337" s="63"/>
-      <c r="G337" s="63"/>
-      <c r="H337" s="63"/>
-      <c r="I337" s="63"/>
-      <c r="J337" s="64"/>
+      <c r="C337" s="60"/>
+      <c r="D337" s="60"/>
+      <c r="E337" s="60"/>
+      <c r="F337" s="60"/>
+      <c r="G337" s="60"/>
+      <c r="H337" s="60"/>
+      <c r="I337" s="60"/>
+      <c r="J337" s="61"/>
       <c r="K337" s="44"/>
     </row>
     <row r="338" spans="1:11">
@@ -18470,17 +18492,17 @@
     </row>
     <row r="342" spans="1:11" ht="24" customHeight="1">
       <c r="A342" s="1"/>
-      <c r="B342" s="62" t="s">
+      <c r="B342" s="59" t="s">
         <v>736</v>
       </c>
-      <c r="C342" s="63"/>
-      <c r="D342" s="63"/>
-      <c r="E342" s="63"/>
-      <c r="F342" s="63"/>
-      <c r="G342" s="63"/>
-      <c r="H342" s="63"/>
-      <c r="I342" s="63"/>
-      <c r="J342" s="64"/>
+      <c r="C342" s="60"/>
+      <c r="D342" s="60"/>
+      <c r="E342" s="60"/>
+      <c r="F342" s="60"/>
+      <c r="G342" s="60"/>
+      <c r="H342" s="60"/>
+      <c r="I342" s="60"/>
+      <c r="J342" s="61"/>
       <c r="K342" s="44"/>
     </row>
     <row r="343" spans="1:11">
@@ -18562,17 +18584,17 @@
     </row>
     <row r="347" spans="1:11" ht="24" customHeight="1">
       <c r="A347" s="1"/>
-      <c r="B347" s="62" t="s">
+      <c r="B347" s="59" t="s">
         <v>738</v>
       </c>
-      <c r="C347" s="63"/>
-      <c r="D347" s="63"/>
-      <c r="E347" s="63"/>
-      <c r="F347" s="63"/>
-      <c r="G347" s="63"/>
-      <c r="H347" s="63"/>
-      <c r="I347" s="63"/>
-      <c r="J347" s="64"/>
+      <c r="C347" s="60"/>
+      <c r="D347" s="60"/>
+      <c r="E347" s="60"/>
+      <c r="F347" s="60"/>
+      <c r="G347" s="60"/>
+      <c r="H347" s="60"/>
+      <c r="I347" s="60"/>
+      <c r="J347" s="61"/>
       <c r="K347" s="44"/>
     </row>
     <row r="348" spans="1:11">
@@ -18654,17 +18676,17 @@
     </row>
     <row r="352" spans="1:11" ht="24" customHeight="1">
       <c r="A352" s="1"/>
-      <c r="B352" s="62" t="s">
+      <c r="B352" s="59" t="s">
         <v>740</v>
       </c>
-      <c r="C352" s="63"/>
-      <c r="D352" s="63"/>
-      <c r="E352" s="63"/>
-      <c r="F352" s="63"/>
-      <c r="G352" s="63"/>
-      <c r="H352" s="63"/>
-      <c r="I352" s="63"/>
-      <c r="J352" s="64"/>
+      <c r="C352" s="60"/>
+      <c r="D352" s="60"/>
+      <c r="E352" s="60"/>
+      <c r="F352" s="60"/>
+      <c r="G352" s="60"/>
+      <c r="H352" s="60"/>
+      <c r="I352" s="60"/>
+      <c r="J352" s="61"/>
       <c r="K352" s="44"/>
     </row>
     <row r="353" spans="1:11">
@@ -18746,17 +18768,17 @@
     </row>
     <row r="357" spans="1:11" ht="24" customHeight="1">
       <c r="A357" s="1"/>
-      <c r="B357" s="62" t="s">
+      <c r="B357" s="59" t="s">
         <v>742</v>
       </c>
-      <c r="C357" s="63"/>
-      <c r="D357" s="63"/>
-      <c r="E357" s="63"/>
-      <c r="F357" s="63"/>
-      <c r="G357" s="63"/>
-      <c r="H357" s="63"/>
-      <c r="I357" s="63"/>
-      <c r="J357" s="64"/>
+      <c r="C357" s="60"/>
+      <c r="D357" s="60"/>
+      <c r="E357" s="60"/>
+      <c r="F357" s="60"/>
+      <c r="G357" s="60"/>
+      <c r="H357" s="60"/>
+      <c r="I357" s="60"/>
+      <c r="J357" s="61"/>
       <c r="K357" s="44"/>
     </row>
     <row r="358" spans="1:11">
@@ -18838,17 +18860,17 @@
     </row>
     <row r="362" spans="1:11" ht="24" customHeight="1">
       <c r="A362" s="1"/>
-      <c r="B362" s="62" t="s">
+      <c r="B362" s="59" t="s">
         <v>744</v>
       </c>
-      <c r="C362" s="63"/>
-      <c r="D362" s="63"/>
-      <c r="E362" s="63"/>
-      <c r="F362" s="63"/>
-      <c r="G362" s="63"/>
-      <c r="H362" s="63"/>
-      <c r="I362" s="63"/>
-      <c r="J362" s="64"/>
+      <c r="C362" s="60"/>
+      <c r="D362" s="60"/>
+      <c r="E362" s="60"/>
+      <c r="F362" s="60"/>
+      <c r="G362" s="60"/>
+      <c r="H362" s="60"/>
+      <c r="I362" s="60"/>
+      <c r="J362" s="61"/>
       <c r="K362" s="44"/>
     </row>
     <row r="363" spans="1:11">
@@ -18930,17 +18952,17 @@
     </row>
     <row r="367" spans="1:11" ht="24" customHeight="1">
       <c r="A367" s="1"/>
-      <c r="B367" s="62" t="s">
+      <c r="B367" s="59" t="s">
         <v>745</v>
       </c>
-      <c r="C367" s="63"/>
-      <c r="D367" s="63"/>
-      <c r="E367" s="63"/>
-      <c r="F367" s="63"/>
-      <c r="G367" s="63"/>
-      <c r="H367" s="63"/>
-      <c r="I367" s="63"/>
-      <c r="J367" s="64"/>
+      <c r="C367" s="60"/>
+      <c r="D367" s="60"/>
+      <c r="E367" s="60"/>
+      <c r="F367" s="60"/>
+      <c r="G367" s="60"/>
+      <c r="H367" s="60"/>
+      <c r="I367" s="60"/>
+      <c r="J367" s="61"/>
       <c r="K367" s="44"/>
     </row>
     <row r="368" spans="1:11">
@@ -19022,17 +19044,17 @@
     </row>
     <row r="372" spans="1:11" ht="24" customHeight="1">
       <c r="A372" s="1"/>
-      <c r="B372" s="62" t="s">
+      <c r="B372" s="59" t="s">
         <v>747</v>
       </c>
-      <c r="C372" s="63"/>
-      <c r="D372" s="63"/>
-      <c r="E372" s="63"/>
-      <c r="F372" s="63"/>
-      <c r="G372" s="63"/>
-      <c r="H372" s="63"/>
-      <c r="I372" s="63"/>
-      <c r="J372" s="64"/>
+      <c r="C372" s="60"/>
+      <c r="D372" s="60"/>
+      <c r="E372" s="60"/>
+      <c r="F372" s="60"/>
+      <c r="G372" s="60"/>
+      <c r="H372" s="60"/>
+      <c r="I372" s="60"/>
+      <c r="J372" s="61"/>
       <c r="K372" s="44"/>
     </row>
     <row r="373" spans="1:11">
@@ -19114,17 +19136,17 @@
     </row>
     <row r="377" spans="1:11" ht="24" customHeight="1">
       <c r="A377" s="1"/>
-      <c r="B377" s="62" t="s">
+      <c r="B377" s="59" t="s">
         <v>749</v>
       </c>
-      <c r="C377" s="63"/>
-      <c r="D377" s="63"/>
-      <c r="E377" s="63"/>
-      <c r="F377" s="63"/>
-      <c r="G377" s="63"/>
-      <c r="H377" s="63"/>
-      <c r="I377" s="63"/>
-      <c r="J377" s="64"/>
+      <c r="C377" s="60"/>
+      <c r="D377" s="60"/>
+      <c r="E377" s="60"/>
+      <c r="F377" s="60"/>
+      <c r="G377" s="60"/>
+      <c r="H377" s="60"/>
+      <c r="I377" s="60"/>
+      <c r="J377" s="61"/>
       <c r="K377" s="44"/>
     </row>
     <row r="378" spans="1:11">
@@ -19206,17 +19228,17 @@
     </row>
     <row r="382" spans="1:11" ht="24" customHeight="1">
       <c r="A382" s="1"/>
-      <c r="B382" s="62" t="s">
+      <c r="B382" s="59" t="s">
         <v>751</v>
       </c>
-      <c r="C382" s="63"/>
-      <c r="D382" s="63"/>
-      <c r="E382" s="63"/>
-      <c r="F382" s="63"/>
-      <c r="G382" s="63"/>
-      <c r="H382" s="63"/>
-      <c r="I382" s="63"/>
-      <c r="J382" s="64"/>
+      <c r="C382" s="60"/>
+      <c r="D382" s="60"/>
+      <c r="E382" s="60"/>
+      <c r="F382" s="60"/>
+      <c r="G382" s="60"/>
+      <c r="H382" s="60"/>
+      <c r="I382" s="60"/>
+      <c r="J382" s="61"/>
       <c r="K382" s="44"/>
     </row>
     <row r="383" spans="1:11">
@@ -19298,17 +19320,17 @@
     </row>
     <row r="387" spans="1:11" ht="24" customHeight="1">
       <c r="A387" s="1"/>
-      <c r="B387" s="62" t="s">
+      <c r="B387" s="59" t="s">
         <v>753</v>
       </c>
-      <c r="C387" s="63"/>
-      <c r="D387" s="63"/>
-      <c r="E387" s="63"/>
-      <c r="F387" s="63"/>
-      <c r="G387" s="63"/>
-      <c r="H387" s="63"/>
-      <c r="I387" s="63"/>
-      <c r="J387" s="64"/>
+      <c r="C387" s="60"/>
+      <c r="D387" s="60"/>
+      <c r="E387" s="60"/>
+      <c r="F387" s="60"/>
+      <c r="G387" s="60"/>
+      <c r="H387" s="60"/>
+      <c r="I387" s="60"/>
+      <c r="J387" s="61"/>
       <c r="K387" s="44"/>
     </row>
     <row r="388" spans="1:11">
@@ -19390,17 +19412,17 @@
     </row>
     <row r="392" spans="1:11" ht="24" customHeight="1">
       <c r="A392" s="1"/>
-      <c r="B392" s="62" t="s">
+      <c r="B392" s="59" t="s">
         <v>755</v>
       </c>
-      <c r="C392" s="63"/>
-      <c r="D392" s="63"/>
-      <c r="E392" s="63"/>
-      <c r="F392" s="63"/>
-      <c r="G392" s="63"/>
-      <c r="H392" s="63"/>
-      <c r="I392" s="63"/>
-      <c r="J392" s="64"/>
+      <c r="C392" s="60"/>
+      <c r="D392" s="60"/>
+      <c r="E392" s="60"/>
+      <c r="F392" s="60"/>
+      <c r="G392" s="60"/>
+      <c r="H392" s="60"/>
+      <c r="I392" s="60"/>
+      <c r="J392" s="61"/>
       <c r="K392" s="44"/>
     </row>
     <row r="393" spans="1:11">
@@ -19482,17 +19504,17 @@
     </row>
     <row r="397" spans="1:11" ht="24" customHeight="1">
       <c r="A397" s="1"/>
-      <c r="B397" s="62" t="s">
+      <c r="B397" s="59" t="s">
         <v>757</v>
       </c>
-      <c r="C397" s="63"/>
-      <c r="D397" s="63"/>
-      <c r="E397" s="63"/>
-      <c r="F397" s="63"/>
-      <c r="G397" s="63"/>
-      <c r="H397" s="63"/>
-      <c r="I397" s="63"/>
-      <c r="J397" s="64"/>
+      <c r="C397" s="60"/>
+      <c r="D397" s="60"/>
+      <c r="E397" s="60"/>
+      <c r="F397" s="60"/>
+      <c r="G397" s="60"/>
+      <c r="H397" s="60"/>
+      <c r="I397" s="60"/>
+      <c r="J397" s="61"/>
       <c r="K397" s="44"/>
     </row>
     <row r="398" spans="1:11">
@@ -19574,17 +19596,17 @@
     </row>
     <row r="402" spans="1:11" ht="24" customHeight="1">
       <c r="A402" s="1"/>
-      <c r="B402" s="62" t="s">
+      <c r="B402" s="59" t="s">
         <v>759</v>
       </c>
-      <c r="C402" s="63"/>
-      <c r="D402" s="63"/>
-      <c r="E402" s="63"/>
-      <c r="F402" s="63"/>
-      <c r="G402" s="63"/>
-      <c r="H402" s="63"/>
-      <c r="I402" s="63"/>
-      <c r="J402" s="64"/>
+      <c r="C402" s="60"/>
+      <c r="D402" s="60"/>
+      <c r="E402" s="60"/>
+      <c r="F402" s="60"/>
+      <c r="G402" s="60"/>
+      <c r="H402" s="60"/>
+      <c r="I402" s="60"/>
+      <c r="J402" s="61"/>
       <c r="K402" s="44"/>
     </row>
     <row r="403" spans="1:11">
@@ -19666,17 +19688,17 @@
     </row>
     <row r="407" spans="1:11" ht="24" customHeight="1">
       <c r="A407" s="1"/>
-      <c r="B407" s="62" t="s">
+      <c r="B407" s="59" t="s">
         <v>848</v>
       </c>
-      <c r="C407" s="63"/>
-      <c r="D407" s="63"/>
-      <c r="E407" s="63"/>
-      <c r="F407" s="63"/>
-      <c r="G407" s="63"/>
-      <c r="H407" s="63"/>
-      <c r="I407" s="63"/>
-      <c r="J407" s="64"/>
+      <c r="C407" s="60"/>
+      <c r="D407" s="60"/>
+      <c r="E407" s="60"/>
+      <c r="F407" s="60"/>
+      <c r="G407" s="60"/>
+      <c r="H407" s="60"/>
+      <c r="I407" s="60"/>
+      <c r="J407" s="61"/>
       <c r="K407" s="44"/>
     </row>
     <row r="408" spans="1:11">
@@ -19758,17 +19780,17 @@
     </row>
     <row r="412" spans="1:11" ht="24" customHeight="1">
       <c r="A412" s="1"/>
-      <c r="B412" s="62" t="s">
+      <c r="B412" s="59" t="s">
         <v>761</v>
       </c>
-      <c r="C412" s="63"/>
-      <c r="D412" s="63"/>
-      <c r="E412" s="63"/>
-      <c r="F412" s="63"/>
-      <c r="G412" s="63"/>
-      <c r="H412" s="63"/>
-      <c r="I412" s="63"/>
-      <c r="J412" s="64"/>
+      <c r="C412" s="60"/>
+      <c r="D412" s="60"/>
+      <c r="E412" s="60"/>
+      <c r="F412" s="60"/>
+      <c r="G412" s="60"/>
+      <c r="H412" s="60"/>
+      <c r="I412" s="60"/>
+      <c r="J412" s="61"/>
       <c r="K412" s="44"/>
     </row>
     <row r="413" spans="1:11">
@@ -19850,17 +19872,17 @@
     </row>
     <row r="417" spans="1:11" ht="24" customHeight="1">
       <c r="A417" s="1"/>
-      <c r="B417" s="62" t="s">
+      <c r="B417" s="59" t="s">
         <v>763</v>
       </c>
-      <c r="C417" s="63"/>
-      <c r="D417" s="63"/>
-      <c r="E417" s="63"/>
-      <c r="F417" s="63"/>
-      <c r="G417" s="63"/>
-      <c r="H417" s="63"/>
-      <c r="I417" s="63"/>
-      <c r="J417" s="64"/>
+      <c r="C417" s="60"/>
+      <c r="D417" s="60"/>
+      <c r="E417" s="60"/>
+      <c r="F417" s="60"/>
+      <c r="G417" s="60"/>
+      <c r="H417" s="60"/>
+      <c r="I417" s="60"/>
+      <c r="J417" s="61"/>
       <c r="K417" s="44"/>
     </row>
     <row r="418" spans="1:11">
@@ -19942,17 +19964,17 @@
     </row>
     <row r="422" spans="1:11" ht="24" customHeight="1">
       <c r="A422" s="1"/>
-      <c r="B422" s="62" t="s">
+      <c r="B422" s="59" t="s">
         <v>765</v>
       </c>
-      <c r="C422" s="63"/>
-      <c r="D422" s="63"/>
-      <c r="E422" s="63"/>
-      <c r="F422" s="63"/>
-      <c r="G422" s="63"/>
-      <c r="H422" s="63"/>
-      <c r="I422" s="63"/>
-      <c r="J422" s="64"/>
+      <c r="C422" s="60"/>
+      <c r="D422" s="60"/>
+      <c r="E422" s="60"/>
+      <c r="F422" s="60"/>
+      <c r="G422" s="60"/>
+      <c r="H422" s="60"/>
+      <c r="I422" s="60"/>
+      <c r="J422" s="61"/>
       <c r="K422" s="44"/>
     </row>
     <row r="423" spans="1:11">
@@ -20034,17 +20056,17 @@
     </row>
     <row r="427" spans="1:11" ht="24" customHeight="1">
       <c r="A427" s="1"/>
-      <c r="B427" s="62" t="s">
+      <c r="B427" s="59" t="s">
         <v>767</v>
       </c>
-      <c r="C427" s="63"/>
-      <c r="D427" s="63"/>
-      <c r="E427" s="63"/>
-      <c r="F427" s="63"/>
-      <c r="G427" s="63"/>
-      <c r="H427" s="63"/>
-      <c r="I427" s="63"/>
-      <c r="J427" s="64"/>
+      <c r="C427" s="60"/>
+      <c r="D427" s="60"/>
+      <c r="E427" s="60"/>
+      <c r="F427" s="60"/>
+      <c r="G427" s="60"/>
+      <c r="H427" s="60"/>
+      <c r="I427" s="60"/>
+      <c r="J427" s="61"/>
       <c r="K427" s="44"/>
     </row>
     <row r="428" spans="1:11">
@@ -20126,17 +20148,17 @@
     </row>
     <row r="432" spans="1:11" ht="24" customHeight="1">
       <c r="A432" s="1"/>
-      <c r="B432" s="62" t="s">
+      <c r="B432" s="59" t="s">
         <v>769</v>
       </c>
-      <c r="C432" s="63"/>
-      <c r="D432" s="63"/>
-      <c r="E432" s="63"/>
-      <c r="F432" s="63"/>
-      <c r="G432" s="63"/>
-      <c r="H432" s="63"/>
-      <c r="I432" s="63"/>
-      <c r="J432" s="64"/>
+      <c r="C432" s="60"/>
+      <c r="D432" s="60"/>
+      <c r="E432" s="60"/>
+      <c r="F432" s="60"/>
+      <c r="G432" s="60"/>
+      <c r="H432" s="60"/>
+      <c r="I432" s="60"/>
+      <c r="J432" s="61"/>
       <c r="K432" s="44"/>
     </row>
     <row r="433" spans="1:11">
@@ -20218,17 +20240,17 @@
     </row>
     <row r="437" spans="1:11" ht="24" customHeight="1">
       <c r="A437" s="1"/>
-      <c r="B437" s="62" t="s">
+      <c r="B437" s="59" t="s">
         <v>771</v>
       </c>
-      <c r="C437" s="63"/>
-      <c r="D437" s="63"/>
-      <c r="E437" s="63"/>
-      <c r="F437" s="63"/>
-      <c r="G437" s="63"/>
-      <c r="H437" s="63"/>
-      <c r="I437" s="63"/>
-      <c r="J437" s="64"/>
+      <c r="C437" s="60"/>
+      <c r="D437" s="60"/>
+      <c r="E437" s="60"/>
+      <c r="F437" s="60"/>
+      <c r="G437" s="60"/>
+      <c r="H437" s="60"/>
+      <c r="I437" s="60"/>
+      <c r="J437" s="61"/>
       <c r="K437" s="44"/>
     </row>
     <row r="438" spans="1:11">
@@ -20310,17 +20332,17 @@
     </row>
     <row r="442" spans="1:11" ht="24" customHeight="1">
       <c r="A442" s="1"/>
-      <c r="B442" s="62" t="s">
+      <c r="B442" s="59" t="s">
         <v>773</v>
       </c>
-      <c r="C442" s="63"/>
-      <c r="D442" s="63"/>
-      <c r="E442" s="63"/>
-      <c r="F442" s="63"/>
-      <c r="G442" s="63"/>
-      <c r="H442" s="63"/>
-      <c r="I442" s="63"/>
-      <c r="J442" s="64"/>
+      <c r="C442" s="60"/>
+      <c r="D442" s="60"/>
+      <c r="E442" s="60"/>
+      <c r="F442" s="60"/>
+      <c r="G442" s="60"/>
+      <c r="H442" s="60"/>
+      <c r="I442" s="60"/>
+      <c r="J442" s="61"/>
       <c r="K442" s="44"/>
     </row>
     <row r="443" spans="1:11">
@@ -20402,17 +20424,17 @@
     </row>
     <row r="447" spans="1:11" ht="24" customHeight="1">
       <c r="A447" s="1"/>
-      <c r="B447" s="62" t="s">
+      <c r="B447" s="59" t="s">
         <v>775</v>
       </c>
-      <c r="C447" s="63"/>
-      <c r="D447" s="63"/>
-      <c r="E447" s="63"/>
-      <c r="F447" s="63"/>
-      <c r="G447" s="63"/>
-      <c r="H447" s="63"/>
-      <c r="I447" s="63"/>
-      <c r="J447" s="64"/>
+      <c r="C447" s="60"/>
+      <c r="D447" s="60"/>
+      <c r="E447" s="60"/>
+      <c r="F447" s="60"/>
+      <c r="G447" s="60"/>
+      <c r="H447" s="60"/>
+      <c r="I447" s="60"/>
+      <c r="J447" s="61"/>
       <c r="K447" s="44"/>
     </row>
     <row r="448" spans="1:11">
@@ -20494,17 +20516,17 @@
     </row>
     <row r="452" spans="1:11" ht="24" customHeight="1">
       <c r="A452" s="1"/>
-      <c r="B452" s="62" t="s">
+      <c r="B452" s="59" t="s">
         <v>777</v>
       </c>
-      <c r="C452" s="63"/>
-      <c r="D452" s="63"/>
-      <c r="E452" s="63"/>
-      <c r="F452" s="63"/>
-      <c r="G452" s="63"/>
-      <c r="H452" s="63"/>
-      <c r="I452" s="63"/>
-      <c r="J452" s="64"/>
+      <c r="C452" s="60"/>
+      <c r="D452" s="60"/>
+      <c r="E452" s="60"/>
+      <c r="F452" s="60"/>
+      <c r="G452" s="60"/>
+      <c r="H452" s="60"/>
+      <c r="I452" s="60"/>
+      <c r="J452" s="61"/>
       <c r="K452" s="44"/>
     </row>
     <row r="453" spans="1:11">
@@ -20586,17 +20608,17 @@
     </row>
     <row r="457" spans="1:11" ht="24" customHeight="1">
       <c r="A457" s="1"/>
-      <c r="B457" s="62" t="s">
+      <c r="B457" s="59" t="s">
         <v>779</v>
       </c>
-      <c r="C457" s="63"/>
-      <c r="D457" s="63"/>
-      <c r="E457" s="63"/>
-      <c r="F457" s="63"/>
-      <c r="G457" s="63"/>
-      <c r="H457" s="63"/>
-      <c r="I457" s="63"/>
-      <c r="J457" s="64"/>
+      <c r="C457" s="60"/>
+      <c r="D457" s="60"/>
+      <c r="E457" s="60"/>
+      <c r="F457" s="60"/>
+      <c r="G457" s="60"/>
+      <c r="H457" s="60"/>
+      <c r="I457" s="60"/>
+      <c r="J457" s="61"/>
       <c r="K457" s="44"/>
     </row>
     <row r="458" spans="1:11">
@@ -20678,17 +20700,17 @@
     </row>
     <row r="462" spans="1:11" ht="24" customHeight="1">
       <c r="A462" s="1"/>
-      <c r="B462" s="62" t="s">
+      <c r="B462" s="59" t="s">
         <v>781</v>
       </c>
-      <c r="C462" s="63"/>
-      <c r="D462" s="63"/>
-      <c r="E462" s="63"/>
-      <c r="F462" s="63"/>
-      <c r="G462" s="63"/>
-      <c r="H462" s="63"/>
-      <c r="I462" s="63"/>
-      <c r="J462" s="64"/>
+      <c r="C462" s="60"/>
+      <c r="D462" s="60"/>
+      <c r="E462" s="60"/>
+      <c r="F462" s="60"/>
+      <c r="G462" s="60"/>
+      <c r="H462" s="60"/>
+      <c r="I462" s="60"/>
+      <c r="J462" s="61"/>
       <c r="K462" s="44"/>
     </row>
     <row r="463" spans="1:11">
@@ -20770,17 +20792,17 @@
     </row>
     <row r="467" spans="1:11" ht="24" customHeight="1">
       <c r="A467" s="1"/>
-      <c r="B467" s="62" t="s">
+      <c r="B467" s="59" t="s">
         <v>783</v>
       </c>
-      <c r="C467" s="63"/>
-      <c r="D467" s="63"/>
-      <c r="E467" s="63"/>
-      <c r="F467" s="63"/>
-      <c r="G467" s="63"/>
-      <c r="H467" s="63"/>
-      <c r="I467" s="63"/>
-      <c r="J467" s="64"/>
+      <c r="C467" s="60"/>
+      <c r="D467" s="60"/>
+      <c r="E467" s="60"/>
+      <c r="F467" s="60"/>
+      <c r="G467" s="60"/>
+      <c r="H467" s="60"/>
+      <c r="I467" s="60"/>
+      <c r="J467" s="61"/>
       <c r="K467" s="44"/>
     </row>
     <row r="468" spans="1:11">
@@ -20862,17 +20884,17 @@
     </row>
     <row r="472" spans="1:11" ht="24" customHeight="1">
       <c r="A472" s="1"/>
-      <c r="B472" s="62" t="s">
+      <c r="B472" s="59" t="s">
         <v>785</v>
       </c>
-      <c r="C472" s="63"/>
-      <c r="D472" s="63"/>
-      <c r="E472" s="63"/>
-      <c r="F472" s="63"/>
-      <c r="G472" s="63"/>
-      <c r="H472" s="63"/>
-      <c r="I472" s="63"/>
-      <c r="J472" s="64"/>
+      <c r="C472" s="60"/>
+      <c r="D472" s="60"/>
+      <c r="E472" s="60"/>
+      <c r="F472" s="60"/>
+      <c r="G472" s="60"/>
+      <c r="H472" s="60"/>
+      <c r="I472" s="60"/>
+      <c r="J472" s="61"/>
       <c r="K472" s="44"/>
     </row>
     <row r="473" spans="1:11">
@@ -20954,17 +20976,17 @@
     </row>
     <row r="477" spans="1:11" ht="24" customHeight="1">
       <c r="A477" s="1"/>
-      <c r="B477" s="62" t="s">
+      <c r="B477" s="59" t="s">
         <v>786</v>
       </c>
-      <c r="C477" s="63"/>
-      <c r="D477" s="63"/>
-      <c r="E477" s="63"/>
-      <c r="F477" s="63"/>
-      <c r="G477" s="63"/>
-      <c r="H477" s="63"/>
-      <c r="I477" s="63"/>
-      <c r="J477" s="64"/>
+      <c r="C477" s="60"/>
+      <c r="D477" s="60"/>
+      <c r="E477" s="60"/>
+      <c r="F477" s="60"/>
+      <c r="G477" s="60"/>
+      <c r="H477" s="60"/>
+      <c r="I477" s="60"/>
+      <c r="J477" s="61"/>
       <c r="K477" s="44"/>
     </row>
     <row r="478" spans="1:11">
@@ -21046,17 +21068,17 @@
     </row>
     <row r="482" spans="1:11" ht="24" customHeight="1">
       <c r="A482" s="1"/>
-      <c r="B482" s="62" t="s">
+      <c r="B482" s="59" t="s">
         <v>788</v>
       </c>
-      <c r="C482" s="63"/>
-      <c r="D482" s="63"/>
-      <c r="E482" s="63"/>
-      <c r="F482" s="63"/>
-      <c r="G482" s="63"/>
-      <c r="H482" s="63"/>
-      <c r="I482" s="63"/>
-      <c r="J482" s="64"/>
+      <c r="C482" s="60"/>
+      <c r="D482" s="60"/>
+      <c r="E482" s="60"/>
+      <c r="F482" s="60"/>
+      <c r="G482" s="60"/>
+      <c r="H482" s="60"/>
+      <c r="I482" s="60"/>
+      <c r="J482" s="61"/>
       <c r="K482" s="44"/>
     </row>
     <row r="483" spans="1:11">
@@ -21138,17 +21160,17 @@
     </row>
     <row r="487" spans="1:11" ht="24" customHeight="1">
       <c r="A487" s="1"/>
-      <c r="B487" s="62" t="s">
+      <c r="B487" s="59" t="s">
         <v>790</v>
       </c>
-      <c r="C487" s="63"/>
-      <c r="D487" s="63"/>
-      <c r="E487" s="63"/>
-      <c r="F487" s="63"/>
-      <c r="G487" s="63"/>
-      <c r="H487" s="63"/>
-      <c r="I487" s="63"/>
-      <c r="J487" s="64"/>
+      <c r="C487" s="60"/>
+      <c r="D487" s="60"/>
+      <c r="E487" s="60"/>
+      <c r="F487" s="60"/>
+      <c r="G487" s="60"/>
+      <c r="H487" s="60"/>
+      <c r="I487" s="60"/>
+      <c r="J487" s="61"/>
       <c r="K487" s="44"/>
     </row>
     <row r="488" spans="1:11">
@@ -21230,17 +21252,17 @@
     </row>
     <row r="492" spans="1:11" ht="24" customHeight="1">
       <c r="A492" s="1"/>
-      <c r="B492" s="62" t="s">
+      <c r="B492" s="59" t="s">
         <v>792</v>
       </c>
-      <c r="C492" s="63"/>
-      <c r="D492" s="63"/>
-      <c r="E492" s="63"/>
-      <c r="F492" s="63"/>
-      <c r="G492" s="63"/>
-      <c r="H492" s="63"/>
-      <c r="I492" s="63"/>
-      <c r="J492" s="64"/>
+      <c r="C492" s="60"/>
+      <c r="D492" s="60"/>
+      <c r="E492" s="60"/>
+      <c r="F492" s="60"/>
+      <c r="G492" s="60"/>
+      <c r="H492" s="60"/>
+      <c r="I492" s="60"/>
+      <c r="J492" s="61"/>
       <c r="K492" s="44"/>
     </row>
     <row r="493" spans="1:11">
@@ -21322,17 +21344,17 @@
     </row>
     <row r="497" spans="1:11" ht="24" customHeight="1">
       <c r="A497" s="1"/>
-      <c r="B497" s="62" t="s">
+      <c r="B497" s="59" t="s">
         <v>794</v>
       </c>
-      <c r="C497" s="63"/>
-      <c r="D497" s="63"/>
-      <c r="E497" s="63"/>
-      <c r="F497" s="63"/>
-      <c r="G497" s="63"/>
-      <c r="H497" s="63"/>
-      <c r="I497" s="63"/>
-      <c r="J497" s="64"/>
+      <c r="C497" s="60"/>
+      <c r="D497" s="60"/>
+      <c r="E497" s="60"/>
+      <c r="F497" s="60"/>
+      <c r="G497" s="60"/>
+      <c r="H497" s="60"/>
+      <c r="I497" s="60"/>
+      <c r="J497" s="61"/>
       <c r="K497" s="44"/>
     </row>
     <row r="498" spans="1:11">
@@ -21414,17 +21436,17 @@
     </row>
     <row r="502" spans="1:11" ht="24" customHeight="1">
       <c r="A502" s="1"/>
-      <c r="B502" s="62" t="s">
+      <c r="B502" s="59" t="s">
         <v>796</v>
       </c>
-      <c r="C502" s="63"/>
-      <c r="D502" s="63"/>
-      <c r="E502" s="63"/>
-      <c r="F502" s="63"/>
-      <c r="G502" s="63"/>
-      <c r="H502" s="63"/>
-      <c r="I502" s="63"/>
-      <c r="J502" s="64"/>
+      <c r="C502" s="60"/>
+      <c r="D502" s="60"/>
+      <c r="E502" s="60"/>
+      <c r="F502" s="60"/>
+      <c r="G502" s="60"/>
+      <c r="H502" s="60"/>
+      <c r="I502" s="60"/>
+      <c r="J502" s="61"/>
       <c r="K502" s="44"/>
     </row>
     <row r="503" spans="1:11">
@@ -21506,17 +21528,17 @@
     </row>
     <row r="507" spans="1:11" ht="24" customHeight="1">
       <c r="A507" s="1"/>
-      <c r="B507" s="62" t="s">
+      <c r="B507" s="59" t="s">
         <v>798</v>
       </c>
-      <c r="C507" s="63"/>
-      <c r="D507" s="63"/>
-      <c r="E507" s="63"/>
-      <c r="F507" s="63"/>
-      <c r="G507" s="63"/>
-      <c r="H507" s="63"/>
-      <c r="I507" s="63"/>
-      <c r="J507" s="64"/>
+      <c r="C507" s="60"/>
+      <c r="D507" s="60"/>
+      <c r="E507" s="60"/>
+      <c r="F507" s="60"/>
+      <c r="G507" s="60"/>
+      <c r="H507" s="60"/>
+      <c r="I507" s="60"/>
+      <c r="J507" s="61"/>
       <c r="K507" s="44"/>
     </row>
     <row r="508" spans="1:11">
@@ -21598,17 +21620,17 @@
     </row>
     <row r="512" spans="1:11" ht="24" customHeight="1">
       <c r="A512" s="1"/>
-      <c r="B512" s="62" t="s">
+      <c r="B512" s="59" t="s">
         <v>800</v>
       </c>
-      <c r="C512" s="63"/>
-      <c r="D512" s="63"/>
-      <c r="E512" s="63"/>
-      <c r="F512" s="63"/>
-      <c r="G512" s="63"/>
-      <c r="H512" s="63"/>
-      <c r="I512" s="63"/>
-      <c r="J512" s="64"/>
+      <c r="C512" s="60"/>
+      <c r="D512" s="60"/>
+      <c r="E512" s="60"/>
+      <c r="F512" s="60"/>
+      <c r="G512" s="60"/>
+      <c r="H512" s="60"/>
+      <c r="I512" s="60"/>
+      <c r="J512" s="61"/>
       <c r="K512" s="44"/>
     </row>
     <row r="513" spans="1:11">
@@ -21690,17 +21712,17 @@
     </row>
     <row r="517" spans="1:11" ht="24" customHeight="1">
       <c r="A517" s="1"/>
-      <c r="B517" s="62" t="s">
+      <c r="B517" s="59" t="s">
         <v>802</v>
       </c>
-      <c r="C517" s="63"/>
-      <c r="D517" s="63"/>
-      <c r="E517" s="63"/>
-      <c r="F517" s="63"/>
-      <c r="G517" s="63"/>
-      <c r="H517" s="63"/>
-      <c r="I517" s="63"/>
-      <c r="J517" s="64"/>
+      <c r="C517" s="60"/>
+      <c r="D517" s="60"/>
+      <c r="E517" s="60"/>
+      <c r="F517" s="60"/>
+      <c r="G517" s="60"/>
+      <c r="H517" s="60"/>
+      <c r="I517" s="60"/>
+      <c r="J517" s="61"/>
       <c r="K517" s="44"/>
     </row>
     <row r="518" spans="1:11" ht="24">
@@ -21782,17 +21804,17 @@
     </row>
     <row r="522" spans="1:11" ht="24" customHeight="1">
       <c r="A522" s="1"/>
-      <c r="B522" s="62" t="s">
+      <c r="B522" s="59" t="s">
         <v>804</v>
       </c>
-      <c r="C522" s="63"/>
-      <c r="D522" s="63"/>
-      <c r="E522" s="63"/>
-      <c r="F522" s="63"/>
-      <c r="G522" s="63"/>
-      <c r="H522" s="63"/>
-      <c r="I522" s="63"/>
-      <c r="J522" s="64"/>
+      <c r="C522" s="60"/>
+      <c r="D522" s="60"/>
+      <c r="E522" s="60"/>
+      <c r="F522" s="60"/>
+      <c r="G522" s="60"/>
+      <c r="H522" s="60"/>
+      <c r="I522" s="60"/>
+      <c r="J522" s="61"/>
       <c r="K522" s="44"/>
     </row>
     <row r="523" spans="1:11">
@@ -21874,17 +21896,17 @@
     </row>
     <row r="527" spans="1:11" ht="24" customHeight="1">
       <c r="A527" s="1"/>
-      <c r="B527" s="62" t="s">
+      <c r="B527" s="59" t="s">
         <v>806</v>
       </c>
-      <c r="C527" s="63"/>
-      <c r="D527" s="63"/>
-      <c r="E527" s="63"/>
-      <c r="F527" s="63"/>
-      <c r="G527" s="63"/>
-      <c r="H527" s="63"/>
-      <c r="I527" s="63"/>
-      <c r="J527" s="64"/>
+      <c r="C527" s="60"/>
+      <c r="D527" s="60"/>
+      <c r="E527" s="60"/>
+      <c r="F527" s="60"/>
+      <c r="G527" s="60"/>
+      <c r="H527" s="60"/>
+      <c r="I527" s="60"/>
+      <c r="J527" s="61"/>
       <c r="K527" s="44"/>
     </row>
     <row r="528" spans="1:11">
@@ -21966,17 +21988,17 @@
     </row>
     <row r="532" spans="1:11" ht="24" customHeight="1">
       <c r="A532" s="1"/>
-      <c r="B532" s="62" t="s">
+      <c r="B532" s="59" t="s">
         <v>807</v>
       </c>
-      <c r="C532" s="63"/>
-      <c r="D532" s="63"/>
-      <c r="E532" s="63"/>
-      <c r="F532" s="63"/>
-      <c r="G532" s="63"/>
-      <c r="H532" s="63"/>
-      <c r="I532" s="63"/>
-      <c r="J532" s="64"/>
+      <c r="C532" s="60"/>
+      <c r="D532" s="60"/>
+      <c r="E532" s="60"/>
+      <c r="F532" s="60"/>
+      <c r="G532" s="60"/>
+      <c r="H532" s="60"/>
+      <c r="I532" s="60"/>
+      <c r="J532" s="61"/>
       <c r="K532" s="44"/>
     </row>
     <row r="533" spans="1:11">
@@ -22058,17 +22080,17 @@
     </row>
     <row r="537" spans="1:11" ht="24" customHeight="1">
       <c r="A537" s="1"/>
-      <c r="B537" s="62" t="s">
+      <c r="B537" s="59" t="s">
         <v>809</v>
       </c>
-      <c r="C537" s="63"/>
-      <c r="D537" s="63"/>
-      <c r="E537" s="63"/>
-      <c r="F537" s="63"/>
-      <c r="G537" s="63"/>
-      <c r="H537" s="63"/>
-      <c r="I537" s="63"/>
-      <c r="J537" s="64"/>
+      <c r="C537" s="60"/>
+      <c r="D537" s="60"/>
+      <c r="E537" s="60"/>
+      <c r="F537" s="60"/>
+      <c r="G537" s="60"/>
+      <c r="H537" s="60"/>
+      <c r="I537" s="60"/>
+      <c r="J537" s="61"/>
       <c r="K537" s="44"/>
     </row>
     <row r="538" spans="1:11">
@@ -22150,17 +22172,17 @@
     </row>
     <row r="542" spans="1:11" ht="24" customHeight="1">
       <c r="A542" s="1"/>
-      <c r="B542" s="62" t="s">
+      <c r="B542" s="59" t="s">
         <v>811</v>
       </c>
-      <c r="C542" s="63"/>
-      <c r="D542" s="63"/>
-      <c r="E542" s="63"/>
-      <c r="F542" s="63"/>
-      <c r="G542" s="63"/>
-      <c r="H542" s="63"/>
-      <c r="I542" s="63"/>
-      <c r="J542" s="64"/>
+      <c r="C542" s="60"/>
+      <c r="D542" s="60"/>
+      <c r="E542" s="60"/>
+      <c r="F542" s="60"/>
+      <c r="G542" s="60"/>
+      <c r="H542" s="60"/>
+      <c r="I542" s="60"/>
+      <c r="J542" s="61"/>
       <c r="K542" s="44"/>
     </row>
     <row r="543" spans="1:11">
@@ -22242,17 +22264,17 @@
     </row>
     <row r="547" spans="1:11" ht="24" customHeight="1">
       <c r="A547" s="1"/>
-      <c r="B547" s="62" t="s">
+      <c r="B547" s="59" t="s">
         <v>813</v>
       </c>
-      <c r="C547" s="63"/>
-      <c r="D547" s="63"/>
-      <c r="E547" s="63"/>
-      <c r="F547" s="63"/>
-      <c r="G547" s="63"/>
-      <c r="H547" s="63"/>
-      <c r="I547" s="63"/>
-      <c r="J547" s="64"/>
+      <c r="C547" s="60"/>
+      <c r="D547" s="60"/>
+      <c r="E547" s="60"/>
+      <c r="F547" s="60"/>
+      <c r="G547" s="60"/>
+      <c r="H547" s="60"/>
+      <c r="I547" s="60"/>
+      <c r="J547" s="61"/>
       <c r="K547" s="44"/>
     </row>
     <row r="548" spans="1:11">
@@ -22334,17 +22356,17 @@
     </row>
     <row r="552" spans="1:11" ht="24" customHeight="1">
       <c r="A552" s="1"/>
-      <c r="B552" s="62" t="s">
+      <c r="B552" s="59" t="s">
         <v>814</v>
       </c>
-      <c r="C552" s="63"/>
-      <c r="D552" s="63"/>
-      <c r="E552" s="63"/>
-      <c r="F552" s="63"/>
-      <c r="G552" s="63"/>
-      <c r="H552" s="63"/>
-      <c r="I552" s="63"/>
-      <c r="J552" s="64"/>
+      <c r="C552" s="60"/>
+      <c r="D552" s="60"/>
+      <c r="E552" s="60"/>
+      <c r="F552" s="60"/>
+      <c r="G552" s="60"/>
+      <c r="H552" s="60"/>
+      <c r="I552" s="60"/>
+      <c r="J552" s="61"/>
       <c r="K552" s="44"/>
     </row>
     <row r="553" spans="1:11">
@@ -22426,17 +22448,17 @@
     </row>
     <row r="557" spans="1:11" ht="24" customHeight="1">
       <c r="A557" s="1"/>
-      <c r="B557" s="62" t="s">
+      <c r="B557" s="59" t="s">
         <v>816</v>
       </c>
-      <c r="C557" s="63"/>
-      <c r="D557" s="63"/>
-      <c r="E557" s="63"/>
-      <c r="F557" s="63"/>
-      <c r="G557" s="63"/>
-      <c r="H557" s="63"/>
-      <c r="I557" s="63"/>
-      <c r="J557" s="64"/>
+      <c r="C557" s="60"/>
+      <c r="D557" s="60"/>
+      <c r="E557" s="60"/>
+      <c r="F557" s="60"/>
+      <c r="G557" s="60"/>
+      <c r="H557" s="60"/>
+      <c r="I557" s="60"/>
+      <c r="J557" s="61"/>
       <c r="K557" s="44"/>
     </row>
     <row r="558" spans="1:11">
@@ -22518,17 +22540,17 @@
     </row>
     <row r="562" spans="1:11" ht="24" customHeight="1">
       <c r="A562" s="1"/>
-      <c r="B562" s="62" t="s">
+      <c r="B562" s="59" t="s">
         <v>818</v>
       </c>
-      <c r="C562" s="63"/>
-      <c r="D562" s="63"/>
-      <c r="E562" s="63"/>
-      <c r="F562" s="63"/>
-      <c r="G562" s="63"/>
-      <c r="H562" s="63"/>
-      <c r="I562" s="63"/>
-      <c r="J562" s="64"/>
+      <c r="C562" s="60"/>
+      <c r="D562" s="60"/>
+      <c r="E562" s="60"/>
+      <c r="F562" s="60"/>
+      <c r="G562" s="60"/>
+      <c r="H562" s="60"/>
+      <c r="I562" s="60"/>
+      <c r="J562" s="61"/>
       <c r="K562" s="44"/>
     </row>
     <row r="563" spans="1:11">
@@ -22610,17 +22632,17 @@
     </row>
     <row r="567" spans="1:11" ht="24" customHeight="1">
       <c r="A567" s="1"/>
-      <c r="B567" s="62" t="s">
+      <c r="B567" s="59" t="s">
         <v>820</v>
       </c>
-      <c r="C567" s="63"/>
-      <c r="D567" s="63"/>
-      <c r="E567" s="63"/>
-      <c r="F567" s="63"/>
-      <c r="G567" s="63"/>
-      <c r="H567" s="63"/>
-      <c r="I567" s="63"/>
-      <c r="J567" s="64"/>
+      <c r="C567" s="60"/>
+      <c r="D567" s="60"/>
+      <c r="E567" s="60"/>
+      <c r="F567" s="60"/>
+      <c r="G567" s="60"/>
+      <c r="H567" s="60"/>
+      <c r="I567" s="60"/>
+      <c r="J567" s="61"/>
       <c r="K567" s="44"/>
     </row>
     <row r="568" spans="1:11">
@@ -22702,17 +22724,17 @@
     </row>
     <row r="572" spans="1:11" ht="24" customHeight="1">
       <c r="A572" s="1"/>
-      <c r="B572" s="62" t="s">
+      <c r="B572" s="59" t="s">
         <v>822</v>
       </c>
-      <c r="C572" s="63"/>
-      <c r="D572" s="63"/>
-      <c r="E572" s="63"/>
-      <c r="F572" s="63"/>
-      <c r="G572" s="63"/>
-      <c r="H572" s="63"/>
-      <c r="I572" s="63"/>
-      <c r="J572" s="64"/>
+      <c r="C572" s="60"/>
+      <c r="D572" s="60"/>
+      <c r="E572" s="60"/>
+      <c r="F572" s="60"/>
+      <c r="G572" s="60"/>
+      <c r="H572" s="60"/>
+      <c r="I572" s="60"/>
+      <c r="J572" s="61"/>
       <c r="K572" s="44"/>
     </row>
     <row r="573" spans="1:11">
@@ -22794,17 +22816,17 @@
     </row>
     <row r="577" spans="1:11" ht="24" customHeight="1">
       <c r="A577" s="1"/>
-      <c r="B577" s="62" t="s">
+      <c r="B577" s="59" t="s">
         <v>823</v>
       </c>
-      <c r="C577" s="63"/>
-      <c r="D577" s="63"/>
-      <c r="E577" s="63"/>
-      <c r="F577" s="63"/>
-      <c r="G577" s="63"/>
-      <c r="H577" s="63"/>
-      <c r="I577" s="63"/>
-      <c r="J577" s="64"/>
+      <c r="C577" s="60"/>
+      <c r="D577" s="60"/>
+      <c r="E577" s="60"/>
+      <c r="F577" s="60"/>
+      <c r="G577" s="60"/>
+      <c r="H577" s="60"/>
+      <c r="I577" s="60"/>
+      <c r="J577" s="61"/>
       <c r="K577" s="44"/>
     </row>
     <row r="578" spans="1:11">
@@ -22886,17 +22908,17 @@
     </row>
     <row r="582" spans="1:11" ht="24" customHeight="1">
       <c r="A582" s="1"/>
-      <c r="B582" s="62" t="s">
+      <c r="B582" s="59" t="s">
         <v>824</v>
       </c>
-      <c r="C582" s="63"/>
-      <c r="D582" s="63"/>
-      <c r="E582" s="63"/>
-      <c r="F582" s="63"/>
-      <c r="G582" s="63"/>
-      <c r="H582" s="63"/>
-      <c r="I582" s="63"/>
-      <c r="J582" s="64"/>
+      <c r="C582" s="60"/>
+      <c r="D582" s="60"/>
+      <c r="E582" s="60"/>
+      <c r="F582" s="60"/>
+      <c r="G582" s="60"/>
+      <c r="H582" s="60"/>
+      <c r="I582" s="60"/>
+      <c r="J582" s="61"/>
       <c r="K582" s="44"/>
     </row>
     <row r="583" spans="1:11">
@@ -22978,17 +23000,17 @@
     </row>
     <row r="587" spans="1:11" ht="24" customHeight="1">
       <c r="A587" s="1"/>
-      <c r="B587" s="62" t="s">
+      <c r="B587" s="59" t="s">
         <v>825</v>
       </c>
-      <c r="C587" s="63"/>
-      <c r="D587" s="63"/>
-      <c r="E587" s="63"/>
-      <c r="F587" s="63"/>
-      <c r="G587" s="63"/>
-      <c r="H587" s="63"/>
-      <c r="I587" s="63"/>
-      <c r="J587" s="64"/>
+      <c r="C587" s="60"/>
+      <c r="D587" s="60"/>
+      <c r="E587" s="60"/>
+      <c r="F587" s="60"/>
+      <c r="G587" s="60"/>
+      <c r="H587" s="60"/>
+      <c r="I587" s="60"/>
+      <c r="J587" s="61"/>
       <c r="K587" s="44"/>
     </row>
     <row r="588" spans="1:11">
@@ -23070,17 +23092,17 @@
     </row>
     <row r="592" spans="1:11" ht="24" customHeight="1">
       <c r="A592" s="1"/>
-      <c r="B592" s="62" t="s">
+      <c r="B592" s="59" t="s">
         <v>826</v>
       </c>
-      <c r="C592" s="63"/>
-      <c r="D592" s="63"/>
-      <c r="E592" s="63"/>
-      <c r="F592" s="63"/>
-      <c r="G592" s="63"/>
-      <c r="H592" s="63"/>
-      <c r="I592" s="63"/>
-      <c r="J592" s="64"/>
+      <c r="C592" s="60"/>
+      <c r="D592" s="60"/>
+      <c r="E592" s="60"/>
+      <c r="F592" s="60"/>
+      <c r="G592" s="60"/>
+      <c r="H592" s="60"/>
+      <c r="I592" s="60"/>
+      <c r="J592" s="61"/>
       <c r="K592" s="44"/>
     </row>
     <row r="593" spans="1:11">
@@ -23162,17 +23184,17 @@
     </row>
     <row r="597" spans="1:11" ht="24" customHeight="1">
       <c r="A597" s="1"/>
-      <c r="B597" s="62" t="s">
+      <c r="B597" s="59" t="s">
         <v>828</v>
       </c>
-      <c r="C597" s="63"/>
-      <c r="D597" s="63"/>
-      <c r="E597" s="63"/>
-      <c r="F597" s="63"/>
-      <c r="G597" s="63"/>
-      <c r="H597" s="63"/>
-      <c r="I597" s="63"/>
-      <c r="J597" s="64"/>
+      <c r="C597" s="60"/>
+      <c r="D597" s="60"/>
+      <c r="E597" s="60"/>
+      <c r="F597" s="60"/>
+      <c r="G597" s="60"/>
+      <c r="H597" s="60"/>
+      <c r="I597" s="60"/>
+      <c r="J597" s="61"/>
       <c r="K597" s="44"/>
     </row>
     <row r="598" spans="1:11">
@@ -23254,17 +23276,17 @@
     </row>
     <row r="602" spans="1:11" ht="24" customHeight="1">
       <c r="A602" s="1"/>
-      <c r="B602" s="62" t="s">
+      <c r="B602" s="59" t="s">
         <v>830</v>
       </c>
-      <c r="C602" s="63"/>
-      <c r="D602" s="63"/>
-      <c r="E602" s="63"/>
-      <c r="F602" s="63"/>
-      <c r="G602" s="63"/>
-      <c r="H602" s="63"/>
-      <c r="I602" s="63"/>
-      <c r="J602" s="64"/>
+      <c r="C602" s="60"/>
+      <c r="D602" s="60"/>
+      <c r="E602" s="60"/>
+      <c r="F602" s="60"/>
+      <c r="G602" s="60"/>
+      <c r="H602" s="60"/>
+      <c r="I602" s="60"/>
+      <c r="J602" s="61"/>
       <c r="K602" s="44"/>
     </row>
     <row r="603" spans="1:11">
@@ -23346,17 +23368,17 @@
     </row>
     <row r="607" spans="1:11" ht="24" customHeight="1">
       <c r="A607" s="1"/>
-      <c r="B607" s="62" t="s">
+      <c r="B607" s="59" t="s">
         <v>832</v>
       </c>
-      <c r="C607" s="63"/>
-      <c r="D607" s="63"/>
-      <c r="E607" s="63"/>
-      <c r="F607" s="63"/>
-      <c r="G607" s="63"/>
-      <c r="H607" s="63"/>
-      <c r="I607" s="63"/>
-      <c r="J607" s="64"/>
+      <c r="C607" s="60"/>
+      <c r="D607" s="60"/>
+      <c r="E607" s="60"/>
+      <c r="F607" s="60"/>
+      <c r="G607" s="60"/>
+      <c r="H607" s="60"/>
+      <c r="I607" s="60"/>
+      <c r="J607" s="61"/>
       <c r="K607" s="44"/>
     </row>
     <row r="608" spans="1:11">
@@ -23438,17 +23460,17 @@
     </row>
     <row r="612" spans="1:11" ht="24" customHeight="1">
       <c r="A612" s="1"/>
-      <c r="B612" s="62" t="s">
+      <c r="B612" s="59" t="s">
         <v>834</v>
       </c>
-      <c r="C612" s="63"/>
-      <c r="D612" s="63"/>
-      <c r="E612" s="63"/>
-      <c r="F612" s="63"/>
-      <c r="G612" s="63"/>
-      <c r="H612" s="63"/>
-      <c r="I612" s="63"/>
-      <c r="J612" s="64"/>
+      <c r="C612" s="60"/>
+      <c r="D612" s="60"/>
+      <c r="E612" s="60"/>
+      <c r="F612" s="60"/>
+      <c r="G612" s="60"/>
+      <c r="H612" s="60"/>
+      <c r="I612" s="60"/>
+      <c r="J612" s="61"/>
       <c r="K612" s="44"/>
     </row>
     <row r="613" spans="1:11">
@@ -23530,17 +23552,17 @@
     </row>
     <row r="617" spans="1:11" ht="24" customHeight="1">
       <c r="A617" s="1"/>
-      <c r="B617" s="62" t="s">
+      <c r="B617" s="59" t="s">
         <v>836</v>
       </c>
-      <c r="C617" s="63"/>
-      <c r="D617" s="63"/>
-      <c r="E617" s="63"/>
-      <c r="F617" s="63"/>
-      <c r="G617" s="63"/>
-      <c r="H617" s="63"/>
-      <c r="I617" s="63"/>
-      <c r="J617" s="64"/>
+      <c r="C617" s="60"/>
+      <c r="D617" s="60"/>
+      <c r="E617" s="60"/>
+      <c r="F617" s="60"/>
+      <c r="G617" s="60"/>
+      <c r="H617" s="60"/>
+      <c r="I617" s="60"/>
+      <c r="J617" s="61"/>
       <c r="K617" s="44"/>
     </row>
     <row r="618" spans="1:11">
@@ -23622,17 +23644,17 @@
     </row>
     <row r="622" spans="1:11" ht="24" customHeight="1">
       <c r="A622" s="1"/>
-      <c r="B622" s="62" t="s">
+      <c r="B622" s="59" t="s">
         <v>838</v>
       </c>
-      <c r="C622" s="63"/>
-      <c r="D622" s="63"/>
-      <c r="E622" s="63"/>
-      <c r="F622" s="63"/>
-      <c r="G622" s="63"/>
-      <c r="H622" s="63"/>
-      <c r="I622" s="63"/>
-      <c r="J622" s="64"/>
+      <c r="C622" s="60"/>
+      <c r="D622" s="60"/>
+      <c r="E622" s="60"/>
+      <c r="F622" s="60"/>
+      <c r="G622" s="60"/>
+      <c r="H622" s="60"/>
+      <c r="I622" s="60"/>
+      <c r="J622" s="61"/>
       <c r="K622" s="44"/>
     </row>
     <row r="623" spans="1:11">
@@ -23714,17 +23736,17 @@
     </row>
     <row r="627" spans="1:11" ht="24" customHeight="1">
       <c r="A627" s="1"/>
-      <c r="B627" s="62" t="s">
+      <c r="B627" s="59" t="s">
         <v>840</v>
       </c>
-      <c r="C627" s="63"/>
-      <c r="D627" s="63"/>
-      <c r="E627" s="63"/>
-      <c r="F627" s="63"/>
-      <c r="G627" s="63"/>
-      <c r="H627" s="63"/>
-      <c r="I627" s="63"/>
-      <c r="J627" s="64"/>
+      <c r="C627" s="60"/>
+      <c r="D627" s="60"/>
+      <c r="E627" s="60"/>
+      <c r="F627" s="60"/>
+      <c r="G627" s="60"/>
+      <c r="H627" s="60"/>
+      <c r="I627" s="60"/>
+      <c r="J627" s="61"/>
       <c r="K627" s="44"/>
     </row>
     <row r="628" spans="1:11">
@@ -23806,17 +23828,17 @@
     </row>
     <row r="632" spans="1:11" ht="24" customHeight="1">
       <c r="A632" s="1"/>
-      <c r="B632" s="62" t="s">
+      <c r="B632" s="59" t="s">
         <v>841</v>
       </c>
-      <c r="C632" s="63"/>
-      <c r="D632" s="63"/>
-      <c r="E632" s="63"/>
-      <c r="F632" s="63"/>
-      <c r="G632" s="63"/>
-      <c r="H632" s="63"/>
-      <c r="I632" s="63"/>
-      <c r="J632" s="64"/>
+      <c r="C632" s="60"/>
+      <c r="D632" s="60"/>
+      <c r="E632" s="60"/>
+      <c r="F632" s="60"/>
+      <c r="G632" s="60"/>
+      <c r="H632" s="60"/>
+      <c r="I632" s="60"/>
+      <c r="J632" s="61"/>
       <c r="K632" s="44"/>
     </row>
     <row r="633" spans="1:11">
@@ -23898,17 +23920,17 @@
     </row>
     <row r="637" spans="1:11" ht="24" customHeight="1">
       <c r="A637" s="1"/>
-      <c r="B637" s="62" t="s">
+      <c r="B637" s="59" t="s">
         <v>842</v>
       </c>
-      <c r="C637" s="63"/>
-      <c r="D637" s="63"/>
-      <c r="E637" s="63"/>
-      <c r="F637" s="63"/>
-      <c r="G637" s="63"/>
-      <c r="H637" s="63"/>
-      <c r="I637" s="63"/>
-      <c r="J637" s="64"/>
+      <c r="C637" s="60"/>
+      <c r="D637" s="60"/>
+      <c r="E637" s="60"/>
+      <c r="F637" s="60"/>
+      <c r="G637" s="60"/>
+      <c r="H637" s="60"/>
+      <c r="I637" s="60"/>
+      <c r="J637" s="61"/>
       <c r="K637" s="44"/>
     </row>
     <row r="638" spans="1:11">
@@ -23990,17 +24012,17 @@
     </row>
     <row r="642" spans="1:11" ht="24" customHeight="1">
       <c r="A642" s="1"/>
-      <c r="B642" s="62" t="s">
+      <c r="B642" s="59" t="s">
         <v>844</v>
       </c>
-      <c r="C642" s="63"/>
-      <c r="D642" s="63"/>
-      <c r="E642" s="63"/>
-      <c r="F642" s="63"/>
-      <c r="G642" s="63"/>
-      <c r="H642" s="63"/>
-      <c r="I642" s="63"/>
-      <c r="J642" s="64"/>
+      <c r="C642" s="60"/>
+      <c r="D642" s="60"/>
+      <c r="E642" s="60"/>
+      <c r="F642" s="60"/>
+      <c r="G642" s="60"/>
+      <c r="H642" s="60"/>
+      <c r="I642" s="60"/>
+      <c r="J642" s="61"/>
       <c r="K642" s="44"/>
     </row>
     <row r="643" spans="1:11">
@@ -24082,17 +24104,17 @@
     </row>
     <row r="647" spans="1:11" ht="24" customHeight="1">
       <c r="A647" s="1"/>
-      <c r="B647" s="62" t="s">
+      <c r="B647" s="59" t="s">
         <v>846</v>
       </c>
-      <c r="C647" s="63"/>
-      <c r="D647" s="63"/>
-      <c r="E647" s="63"/>
-      <c r="F647" s="63"/>
-      <c r="G647" s="63"/>
-      <c r="H647" s="63"/>
-      <c r="I647" s="63"/>
-      <c r="J647" s="64"/>
+      <c r="C647" s="60"/>
+      <c r="D647" s="60"/>
+      <c r="E647" s="60"/>
+      <c r="F647" s="60"/>
+      <c r="G647" s="60"/>
+      <c r="H647" s="60"/>
+      <c r="I647" s="60"/>
+      <c r="J647" s="61"/>
       <c r="K647" s="44"/>
     </row>
     <row r="648" spans="1:11">
@@ -24174,17 +24196,17 @@
     </row>
     <row r="652" spans="1:11" ht="24" customHeight="1">
       <c r="A652" s="1"/>
-      <c r="B652" s="62" t="s">
+      <c r="B652" s="59" t="s">
         <v>919</v>
       </c>
-      <c r="C652" s="63"/>
-      <c r="D652" s="63"/>
-      <c r="E652" s="63"/>
-      <c r="F652" s="63"/>
-      <c r="G652" s="63"/>
-      <c r="H652" s="63"/>
-      <c r="I652" s="63"/>
-      <c r="J652" s="64"/>
+      <c r="C652" s="60"/>
+      <c r="D652" s="60"/>
+      <c r="E652" s="60"/>
+      <c r="F652" s="60"/>
+      <c r="G652" s="60"/>
+      <c r="H652" s="60"/>
+      <c r="I652" s="60"/>
+      <c r="J652" s="61"/>
       <c r="K652" s="44"/>
     </row>
     <row r="653" spans="1:11">
@@ -24266,17 +24288,17 @@
     </row>
     <row r="657" spans="1:11" ht="24" customHeight="1">
       <c r="A657" s="1"/>
-      <c r="B657" s="62" t="s">
+      <c r="B657" s="59" t="s">
         <v>923</v>
       </c>
-      <c r="C657" s="63"/>
-      <c r="D657" s="63"/>
-      <c r="E657" s="63"/>
-      <c r="F657" s="63"/>
-      <c r="G657" s="63"/>
-      <c r="H657" s="63"/>
-      <c r="I657" s="63"/>
-      <c r="J657" s="64"/>
+      <c r="C657" s="60"/>
+      <c r="D657" s="60"/>
+      <c r="E657" s="60"/>
+      <c r="F657" s="60"/>
+      <c r="G657" s="60"/>
+      <c r="H657" s="60"/>
+      <c r="I657" s="60"/>
+      <c r="J657" s="61"/>
       <c r="K657" s="44"/>
     </row>
     <row r="658" spans="1:11">
@@ -24358,17 +24380,17 @@
     </row>
     <row r="662" spans="1:11" s="54" customFormat="1" ht="24" customHeight="1">
       <c r="A662" s="47"/>
-      <c r="B662" s="59" t="s">
+      <c r="B662" s="63" t="s">
         <v>1142</v>
       </c>
-      <c r="C662" s="60"/>
-      <c r="D662" s="60"/>
-      <c r="E662" s="60"/>
-      <c r="F662" s="60"/>
-      <c r="G662" s="60"/>
-      <c r="H662" s="60"/>
-      <c r="I662" s="60"/>
-      <c r="J662" s="61"/>
+      <c r="C662" s="64"/>
+      <c r="D662" s="64"/>
+      <c r="E662" s="64"/>
+      <c r="F662" s="64"/>
+      <c r="G662" s="64"/>
+      <c r="H662" s="64"/>
+      <c r="I662" s="64"/>
+      <c r="J662" s="65"/>
       <c r="K662" s="53"/>
     </row>
     <row r="663" spans="1:11" s="54" customFormat="1">
@@ -24426,8 +24448,213 @@
     <row r="665" spans="1:11" s="54" customFormat="1">
       <c r="K665" s="58"/>
     </row>
+    <row r="666" spans="1:11" s="54" customFormat="1">
+      <c r="A666" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B666" s="48" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C666" s="49"/>
+      <c r="D666" s="50" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E666" s="51"/>
+      <c r="F666" s="52">
+        <v>2</v>
+      </c>
+      <c r="G666" s="48" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H666" s="49"/>
+      <c r="I666" s="48"/>
+      <c r="J666" s="49"/>
+      <c r="K666" s="53" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="667" spans="1:11" s="54" customFormat="1" ht="24" customHeight="1">
+      <c r="A667" s="47"/>
+      <c r="B667" s="63" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C667" s="64"/>
+      <c r="D667" s="64"/>
+      <c r="E667" s="64"/>
+      <c r="F667" s="64"/>
+      <c r="G667" s="64"/>
+      <c r="H667" s="64"/>
+      <c r="I667" s="64"/>
+      <c r="J667" s="65"/>
+      <c r="K667" s="53"/>
+    </row>
+    <row r="668" spans="1:11" s="54" customFormat="1">
+      <c r="A668" s="47"/>
+      <c r="B668" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C668" s="55" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D668" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="E668" s="52">
+        <v>10</v>
+      </c>
+      <c r="F668" s="52">
+        <v>10</v>
+      </c>
+      <c r="G668" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="H668" s="57"/>
+      <c r="I668" s="57"/>
+      <c r="J668" s="51"/>
+      <c r="K668" s="53" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="669" spans="1:11" s="54" customFormat="1">
+      <c r="A669" s="47"/>
+      <c r="B669" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C669" s="55" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D669" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="E669" s="52">
+        <v>20</v>
+      </c>
+      <c r="F669" s="52"/>
+      <c r="G669" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="H669" s="57"/>
+      <c r="I669" s="57"/>
+      <c r="J669" s="51"/>
+      <c r="K669" s="53" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="670" spans="1:11" s="54" customFormat="1">
+      <c r="K670" s="58"/>
+    </row>
   </sheetData>
-  <mergeCells count="133">
+  <mergeCells count="134">
+    <mergeCell ref="B667:J667"/>
+    <mergeCell ref="B77:J77"/>
+    <mergeCell ref="B82:J82"/>
+    <mergeCell ref="B147:J147"/>
+    <mergeCell ref="B167:J167"/>
+    <mergeCell ref="B172:J172"/>
+    <mergeCell ref="B117:J117"/>
+    <mergeCell ref="B122:J122"/>
+    <mergeCell ref="B127:J127"/>
+    <mergeCell ref="B622:J622"/>
+    <mergeCell ref="B137:J137"/>
+    <mergeCell ref="B142:J142"/>
+    <mergeCell ref="B132:J132"/>
+    <mergeCell ref="B177:J177"/>
+    <mergeCell ref="B187:J187"/>
+    <mergeCell ref="B152:J152"/>
+    <mergeCell ref="B157:J157"/>
+    <mergeCell ref="B162:J162"/>
+    <mergeCell ref="B217:J217"/>
+    <mergeCell ref="B182:J182"/>
+    <mergeCell ref="B322:J322"/>
+    <mergeCell ref="B327:J327"/>
+    <mergeCell ref="B332:J332"/>
+    <mergeCell ref="B362:J362"/>
+    <mergeCell ref="B662:J662"/>
+    <mergeCell ref="B657:J657"/>
+    <mergeCell ref="B652:J652"/>
+    <mergeCell ref="B637:J637"/>
+    <mergeCell ref="B627:J627"/>
+    <mergeCell ref="B347:J347"/>
+    <mergeCell ref="B352:J352"/>
+    <mergeCell ref="B357:J357"/>
+    <mergeCell ref="B367:J367"/>
+    <mergeCell ref="B237:J237"/>
+    <mergeCell ref="B632:J632"/>
+    <mergeCell ref="B277:J277"/>
+    <mergeCell ref="B282:J282"/>
+    <mergeCell ref="B287:J287"/>
+    <mergeCell ref="B292:J292"/>
+    <mergeCell ref="B247:J247"/>
+    <mergeCell ref="B252:J252"/>
+    <mergeCell ref="B257:J257"/>
+    <mergeCell ref="B262:J262"/>
+    <mergeCell ref="B267:J267"/>
+    <mergeCell ref="B337:J337"/>
+    <mergeCell ref="B342:J342"/>
+    <mergeCell ref="B297:J297"/>
+    <mergeCell ref="B302:J302"/>
+    <mergeCell ref="B307:J307"/>
+    <mergeCell ref="B312:J312"/>
+    <mergeCell ref="B317:J317"/>
+    <mergeCell ref="B372:J372"/>
+    <mergeCell ref="B377:J377"/>
+    <mergeCell ref="B192:J192"/>
+    <mergeCell ref="B197:J197"/>
+    <mergeCell ref="B202:J202"/>
+    <mergeCell ref="B207:J207"/>
+    <mergeCell ref="B212:J212"/>
+    <mergeCell ref="B272:J272"/>
+    <mergeCell ref="B227:J227"/>
+    <mergeCell ref="B232:J232"/>
+    <mergeCell ref="B242:J242"/>
+    <mergeCell ref="B542:J542"/>
+    <mergeCell ref="B572:J572"/>
+    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="B92:J92"/>
+    <mergeCell ref="B97:J97"/>
+    <mergeCell ref="B102:J102"/>
+    <mergeCell ref="B107:J107"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B72:J72"/>
+    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="B47:J47"/>
+    <mergeCell ref="B52:J52"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="B62:J62"/>
+    <mergeCell ref="B67:J67"/>
+    <mergeCell ref="B387:J387"/>
+    <mergeCell ref="B222:J222"/>
+    <mergeCell ref="B532:J532"/>
+    <mergeCell ref="B527:J527"/>
+    <mergeCell ref="B422:J422"/>
+    <mergeCell ref="B427:J427"/>
+    <mergeCell ref="B432:J432"/>
+    <mergeCell ref="B437:J437"/>
+    <mergeCell ref="B382:J382"/>
+    <mergeCell ref="B582:J582"/>
+    <mergeCell ref="B562:J562"/>
+    <mergeCell ref="B567:J567"/>
+    <mergeCell ref="B442:J442"/>
+    <mergeCell ref="B392:J392"/>
+    <mergeCell ref="B397:J397"/>
+    <mergeCell ref="B402:J402"/>
+    <mergeCell ref="B407:J407"/>
+    <mergeCell ref="B412:J412"/>
+    <mergeCell ref="B417:J417"/>
+    <mergeCell ref="B447:J447"/>
+    <mergeCell ref="B452:J452"/>
+    <mergeCell ref="B502:J502"/>
+    <mergeCell ref="B507:J507"/>
+    <mergeCell ref="B512:J512"/>
+    <mergeCell ref="B517:J517"/>
+    <mergeCell ref="B547:J547"/>
     <mergeCell ref="B522:J522"/>
     <mergeCell ref="B497:J497"/>
     <mergeCell ref="B462:J462"/>
@@ -24452,115 +24679,6 @@
     <mergeCell ref="B552:J552"/>
     <mergeCell ref="B557:J557"/>
     <mergeCell ref="B537:J537"/>
-    <mergeCell ref="B532:J532"/>
-    <mergeCell ref="B527:J527"/>
-    <mergeCell ref="B422:J422"/>
-    <mergeCell ref="B427:J427"/>
-    <mergeCell ref="B432:J432"/>
-    <mergeCell ref="B437:J437"/>
-    <mergeCell ref="B382:J382"/>
-    <mergeCell ref="B582:J582"/>
-    <mergeCell ref="B562:J562"/>
-    <mergeCell ref="B567:J567"/>
-    <mergeCell ref="B442:J442"/>
-    <mergeCell ref="B392:J392"/>
-    <mergeCell ref="B397:J397"/>
-    <mergeCell ref="B402:J402"/>
-    <mergeCell ref="B407:J407"/>
-    <mergeCell ref="B412:J412"/>
-    <mergeCell ref="B417:J417"/>
-    <mergeCell ref="B447:J447"/>
-    <mergeCell ref="B452:J452"/>
-    <mergeCell ref="B502:J502"/>
-    <mergeCell ref="B507:J507"/>
-    <mergeCell ref="B512:J512"/>
-    <mergeCell ref="B517:J517"/>
-    <mergeCell ref="B547:J547"/>
-    <mergeCell ref="B542:J542"/>
-    <mergeCell ref="B572:J572"/>
-    <mergeCell ref="B87:J87"/>
-    <mergeCell ref="B92:J92"/>
-    <mergeCell ref="B97:J97"/>
-    <mergeCell ref="B102:J102"/>
-    <mergeCell ref="B107:J107"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B72:J72"/>
-    <mergeCell ref="B42:J42"/>
-    <mergeCell ref="B47:J47"/>
-    <mergeCell ref="B52:J52"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B37:J37"/>
-    <mergeCell ref="B57:J57"/>
-    <mergeCell ref="B62:J62"/>
-    <mergeCell ref="B67:J67"/>
-    <mergeCell ref="B387:J387"/>
-    <mergeCell ref="B222:J222"/>
-    <mergeCell ref="B192:J192"/>
-    <mergeCell ref="B197:J197"/>
-    <mergeCell ref="B202:J202"/>
-    <mergeCell ref="B207:J207"/>
-    <mergeCell ref="B212:J212"/>
-    <mergeCell ref="B272:J272"/>
-    <mergeCell ref="B227:J227"/>
-    <mergeCell ref="B232:J232"/>
-    <mergeCell ref="B242:J242"/>
-    <mergeCell ref="B347:J347"/>
-    <mergeCell ref="B352:J352"/>
-    <mergeCell ref="B357:J357"/>
-    <mergeCell ref="B367:J367"/>
-    <mergeCell ref="B237:J237"/>
-    <mergeCell ref="B632:J632"/>
-    <mergeCell ref="B277:J277"/>
-    <mergeCell ref="B282:J282"/>
-    <mergeCell ref="B287:J287"/>
-    <mergeCell ref="B292:J292"/>
-    <mergeCell ref="B247:J247"/>
-    <mergeCell ref="B252:J252"/>
-    <mergeCell ref="B257:J257"/>
-    <mergeCell ref="B262:J262"/>
-    <mergeCell ref="B267:J267"/>
-    <mergeCell ref="B337:J337"/>
-    <mergeCell ref="B342:J342"/>
-    <mergeCell ref="B297:J297"/>
-    <mergeCell ref="B302:J302"/>
-    <mergeCell ref="B307:J307"/>
-    <mergeCell ref="B312:J312"/>
-    <mergeCell ref="B317:J317"/>
-    <mergeCell ref="B372:J372"/>
-    <mergeCell ref="B377:J377"/>
-    <mergeCell ref="B322:J322"/>
-    <mergeCell ref="B327:J327"/>
-    <mergeCell ref="B332:J332"/>
-    <mergeCell ref="B362:J362"/>
-    <mergeCell ref="B662:J662"/>
-    <mergeCell ref="B657:J657"/>
-    <mergeCell ref="B652:J652"/>
-    <mergeCell ref="B637:J637"/>
-    <mergeCell ref="B627:J627"/>
-    <mergeCell ref="B77:J77"/>
-    <mergeCell ref="B82:J82"/>
-    <mergeCell ref="B147:J147"/>
-    <mergeCell ref="B167:J167"/>
-    <mergeCell ref="B172:J172"/>
-    <mergeCell ref="B117:J117"/>
-    <mergeCell ref="B122:J122"/>
-    <mergeCell ref="B127:J127"/>
-    <mergeCell ref="B622:J622"/>
-    <mergeCell ref="B137:J137"/>
-    <mergeCell ref="B142:J142"/>
-    <mergeCell ref="B132:J132"/>
-    <mergeCell ref="B177:J177"/>
-    <mergeCell ref="B187:J187"/>
-    <mergeCell ref="B152:J152"/>
-    <mergeCell ref="B157:J157"/>
-    <mergeCell ref="B162:J162"/>
-    <mergeCell ref="B217:J217"/>
-    <mergeCell ref="B182:J182"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -24618,17 +24736,17 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9"/>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
       <c r="K3" s="42"/>
     </row>
     <row r="4" spans="1:11">
@@ -24684,7 +24802,7 @@
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="59" t="s">
         <v>853</v>
       </c>
       <c r="C7" s="138"/>
